--- a/Översikt HÄRJEDALEN.xlsx
+++ b/Översikt HÄRJEDALEN.xlsx
@@ -567,7 +567,7 @@
         <v>45513</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         <v>44785</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>45763</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>44790</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>44553</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>44844</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>44837</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>44749</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>44406</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>44182</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>45691</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>45761.58262731481</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>44831</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>45531</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>44496.94013888889</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>44865.57574074074</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2394,7 +2394,7 @@
         <v>45667</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>44650</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>45250</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>45351</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>45180</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>44200</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>44182</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>45544.35653935185</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>45631</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         <v>45554</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>44690</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>44501</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3681,7 +3681,7 @@
         <v>44193</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>44487</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
         <v>45631</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>45544</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4095,7 +4095,7 @@
         <v>44440</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         <v>44406</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4289,7 +4289,7 @@
         <v>45571</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4389,7 +4389,7 @@
         <v>45106</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4489,7 +4489,7 @@
         <v>45837</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
         <v>45217</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         <v>44774</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4792,7 +4792,7 @@
         <v>44357</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
         <v>45544</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         <v>45457.38396990741</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5094,7 +5094,7 @@
         <v>45198</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5202,7 +5202,7 @@
         <v>45411</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5300,7 +5300,7 @@
         <v>45531</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5398,7 +5398,7 @@
         <v>45694</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5496,7 +5496,7 @@
         <v>45477.46537037037</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5599,7 +5599,7 @@
         <v>45833.43898148148</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
         <v>44553</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         <v>45471.59034722222</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5902,7 +5902,7 @@
         <v>44406</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         <v>45614.45413194445</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6105,7 +6105,7 @@
         <v>44517</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6198,7 +6198,7 @@
         <v>44553</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6295,7 +6295,7 @@
         <v>44377</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         <v>45741.82913194445</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6483,7 +6483,7 @@
         <v>45175</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6584,7 +6584,7 @@
         <v>45426</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         <v>45677.45212962963</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6772,7 +6772,7 @@
         <v>44430</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6868,7 +6868,7 @@
         <v>44553</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>45531.45444444445</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         <v>45007</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7159,7 +7159,7 @@
         <v>45715</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7259,7 +7259,7 @@
         <v>44242</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7349,7 +7349,7 @@
         <v>45772.51116898148</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>45616.6450462963</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7542,7 +7542,7 @@
         <v>45568</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7637,7 +7637,7 @@
         <v>45719</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7731,7 +7731,7 @@
         <v>45869.60545138889</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7825,7 +7825,7 @@
         <v>45559</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7924,7 +7924,7 @@
         <v>45574</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8018,7 +8018,7 @@
         <v>44053</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8120,7 +8120,7 @@
         <v>45625.45384259259</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8218,7 +8218,7 @@
         <v>45432.94736111111</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8316,7 +8316,7 @@
         <v>45243</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8409,7 +8409,7 @@
         <v>44517</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8498,7 +8498,7 @@
         <v>44882</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8591,7 +8591,7 @@
         <v>44979</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         <v>44430</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         <v>44294</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         <v>44294</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         <v>45085</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9049,7 +9049,7 @@
         <v>45506.35658564815</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9141,7 +9141,7 @@
         <v>44377</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9233,7 +9233,7 @@
         <v>44476</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         <v>45694</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9413,7 +9413,7 @@
         <v>45467.47204861111</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9506,7 +9506,7 @@
         <v>45559.38894675926</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9603,7 +9603,7 @@
         <v>45537.45818287037</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9700,7 +9700,7 @@
         <v>45838.73927083334</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9793,7 +9793,7 @@
         <v>44977</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9890,7 +9890,7 @@
         <v>45552</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
         <v>44957</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10070,7 +10070,7 @@
         <v>45007</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10163,7 +10163,7 @@
         <v>45531.45752314815</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10251,7 +10251,7 @@
         <v>44475</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10338,7 +10338,7 @@
         <v>44441</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10425,7 +10425,7 @@
         <v>44475</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10512,7 +10512,7 @@
         <v>44475</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10599,7 +10599,7 @@
         <v>44713</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         <v>45468</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10786,7 +10786,7 @@
         <v>44074</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10882,7 +10882,7 @@
         <v>44107</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         <v>45791</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11065,7 +11065,7 @@
         <v>45841.41003472222</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11152,7 +11152,7 @@
         <v>45800.3484375</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11244,7 +11244,7 @@
         <v>45617</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11340,7 +11340,7 @@
         <v>45849.35011574074</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11427,7 +11427,7 @@
         <v>45821.56523148148</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11519,7 +11519,7 @@
         <v>44180</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11611,7 +11611,7 @@
         <v>44186</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11702,7 +11702,7 @@
         <v>44677</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11793,7 +11793,7 @@
         <v>44286</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11879,7 +11879,7 @@
         <v>45153</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11969,7 +11969,7 @@
         <v>44475</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12055,7 +12055,7 @@
         <v>44866.46503472222</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12150,7 +12150,7 @@
         <v>45035</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12245,7 +12245,7 @@
         <v>44449</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12331,7 +12331,7 @@
         <v>44955</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12421,7 +12421,7 @@
         <v>45595.58056712963</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12512,7 +12512,7 @@
         <v>45772.51070601852</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12603,7 +12603,7 @@
         <v>45538</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12694,7 +12694,7 @@
         <v>45786.6590625</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12785,7 +12785,7 @@
         <v>45786.66594907407</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12876,7 +12876,7 @@
         <v>45786.65452546296</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -12967,7 +12967,7 @@
         <v>45786.6768287037</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13058,7 +13058,7 @@
         <v>45786.67261574074</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13149,7 +13149,7 @@
         <v>44987</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13244,7 +13244,7 @@
         <v>45786.67016203704</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13335,7 +13335,7 @@
         <v>44475</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13421,7 +13421,7 @@
         <v>44221</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13507,7 +13507,7 @@
         <v>45644.56555555556</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13602,7 +13602,7 @@
         <v>45621</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13697,7 +13697,7 @@
         <v>45805.73822916667</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13788,7 +13788,7 @@
         <v>45191</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -13879,7 +13879,7 @@
         <v>45833</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -13965,7 +13965,7 @@
         <v>45772.36488425926</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14060,7 +14060,7 @@
         <v>45552</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14150,7 +14150,7 @@
         <v>44853</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14240,7 +14240,7 @@
         <v>45694</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14326,7 +14326,7 @@
         <v>44096</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14416,7 +14416,7 @@
         <v>44475</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14501,7 +14501,7 @@
         <v>44475</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14586,7 +14586,7 @@
         <v>44475</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14671,7 +14671,7 @@
         <v>44321</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -14761,7 +14761,7 @@
         <v>44113</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -14846,7 +14846,7 @@
         <v>44105</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -14931,7 +14931,7 @@
         <v>44769.48783564815</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15021,7 +15021,7 @@
         <v>45672.50416666667</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15106,7 +15106,7 @@
         <v>45758.70164351852</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15191,7 +15191,7 @@
         <v>45308</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15280,7 +15280,7 @@
         <v>45457.38677083333</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15370,7 +15370,7 @@
         <v>45540.69512731482</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -15460,7 +15460,7 @@
         <v>45320</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -15545,7 +15545,7 @@
         <v>45345</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -15635,7 +15635,7 @@
         <v>45729.64623842593</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -15725,7 +15725,7 @@
         <v>45538.57630787037</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -15814,7 +15814,7 @@
         <v>45621.47555555555</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -15904,7 +15904,7 @@
         <v>44475</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -15989,7 +15989,7 @@
         <v>45714.55248842593</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16083,7 +16083,7 @@
         <v>45835.7499537037</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -16173,7 +16173,7 @@
         <v>45838.773125</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -16263,7 +16263,7 @@
         <v>45603</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -16353,7 +16353,7 @@
         <v>45111</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -16443,7 +16443,7 @@
         <v>45638.33607638889</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -16533,7 +16533,7 @@
         <v>45800.63043981481</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -16627,7 +16627,7 @@
         <v>45805.66601851852</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -16721,7 +16721,7 @@
         <v>45805.73546296296</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -16811,7 +16811,7 @@
         <v>45791</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -16896,7 +16896,7 @@
         <v>45617</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -16990,7 +16990,7 @@
         <v>45454.62443287037</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17075,7 +17075,7 @@
         <v>45812.82244212963</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -17165,7 +17165,7 @@
         <v>45869.61471064815</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -17250,7 +17250,7 @@
         <v>45875.46476851852</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -17339,7 +17339,7 @@
         <v>44320</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -17396,7 +17396,7 @@
         <v>44320</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -17458,7 +17458,7 @@
         <v>44316</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -17515,7 +17515,7 @@
         <v>44105</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -17572,7 +17572,7 @@
         <v>44810</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -17634,7 +17634,7 @@
         <v>44543</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -17691,7 +17691,7 @@
         <v>44430</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -17753,7 +17753,7 @@
         <v>44614</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -17815,7 +17815,7 @@
         <v>44727.70908564814</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -17877,7 +17877,7 @@
         <v>44404</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -17934,7 +17934,7 @@
         <v>44417.38271990741</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -17991,7 +17991,7 @@
         <v>44417.38614583333</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -18048,7 +18048,7 @@
         <v>44497</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -18105,7 +18105,7 @@
         <v>44475</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -18162,7 +18162,7 @@
         <v>44154.40430555555</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -18239,7 +18239,7 @@
         <v>44531</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -18296,7 +18296,7 @@
         <v>44600</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -18353,7 +18353,7 @@
         <v>44361</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -18410,7 +18410,7 @@
         <v>44540</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -18472,7 +18472,7 @@
         <v>44475</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -18529,7 +18529,7 @@
         <v>44385.93652777778</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -18591,7 +18591,7 @@
         <v>44406</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -18648,7 +18648,7 @@
         <v>44538</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -18710,7 +18710,7 @@
         <v>44475</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -18767,7 +18767,7 @@
         <v>44854</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -18824,7 +18824,7 @@
         <v>44102</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -18881,7 +18881,7 @@
         <v>44823</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -18943,7 +18943,7 @@
         <v>44424</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -19000,7 +19000,7 @@
         <v>44316</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -19057,7 +19057,7 @@
         <v>44483</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -19114,7 +19114,7 @@
         <v>44421</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -19171,7 +19171,7 @@
         <v>44418</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -19233,7 +19233,7 @@
         <v>44488</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -19295,7 +19295,7 @@
         <v>44603</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -19357,7 +19357,7 @@
         <v>44132</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -19414,7 +19414,7 @@
         <v>44179</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -19471,7 +19471,7 @@
         <v>44418</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -19533,7 +19533,7 @@
         <v>44564.6747337963</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -19595,7 +19595,7 @@
         <v>44361</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -19657,7 +19657,7 @@
         <v>44466.81701388889</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -19714,7 +19714,7 @@
         <v>44615</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -19776,7 +19776,7 @@
         <v>44218</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -19833,7 +19833,7 @@
         <v>44475</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -19890,7 +19890,7 @@
         <v>44475</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -19947,7 +19947,7 @@
         <v>44286</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -20004,7 +20004,7 @@
         <v>44410.74284722222</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -20061,7 +20061,7 @@
         <v>44631</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -20123,7 +20123,7 @@
         <v>44631.41535879629</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -20185,7 +20185,7 @@
         <v>44810</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -20247,7 +20247,7 @@
         <v>44728</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -20304,7 +20304,7 @@
         <v>44417.37519675926</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -20361,7 +20361,7 @@
         <v>44344</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -20418,7 +20418,7 @@
         <v>44174</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -20475,7 +20475,7 @@
         <v>44057</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -20537,7 +20537,7 @@
         <v>44084</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -20599,7 +20599,7 @@
         <v>44475</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -20656,7 +20656,7 @@
         <v>44078</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -20713,7 +20713,7 @@
         <v>44424</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -20770,7 +20770,7 @@
         <v>44424</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -20827,7 +20827,7 @@
         <v>44258</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -20884,7 +20884,7 @@
         <v>44818</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -20941,7 +20941,7 @@
         <v>44770.53315972222</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -20998,7 +20998,7 @@
         <v>44690</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -21055,7 +21055,7 @@
         <v>44285</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -21112,7 +21112,7 @@
         <v>44286</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -21169,7 +21169,7 @@
         <v>44385.93658564815</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -21231,7 +21231,7 @@
         <v>44243.63096064814</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -21288,7 +21288,7 @@
         <v>44792.68023148148</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -21345,7 +21345,7 @@
         <v>44298</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -21402,7 +21402,7 @@
         <v>44183</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -21459,7 +21459,7 @@
         <v>44319</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -21516,7 +21516,7 @@
         <v>44316</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -21573,7 +21573,7 @@
         <v>44316</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -21630,7 +21630,7 @@
         <v>44126</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -21687,7 +21687,7 @@
         <v>44825</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -21744,7 +21744,7 @@
         <v>44154</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -21806,7 +21806,7 @@
         <v>44174</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -21863,7 +21863,7 @@
         <v>44396</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -21920,7 +21920,7 @@
         <v>44475</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -21977,7 +21977,7 @@
         <v>44127</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -22039,7 +22039,7 @@
         <v>44475</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -22096,7 +22096,7 @@
         <v>44475</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -22153,7 +22153,7 @@
         <v>44475</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -22210,7 +22210,7 @@
         <v>44475</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -22267,7 +22267,7 @@
         <v>44544</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -22329,7 +22329,7 @@
         <v>44420.33096064815</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -22386,7 +22386,7 @@
         <v>44188</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -22448,7 +22448,7 @@
         <v>44483.36435185185</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -22505,7 +22505,7 @@
         <v>44417</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -22562,7 +22562,7 @@
         <v>44181</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -22624,7 +22624,7 @@
         <v>44426.45706018519</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -22681,7 +22681,7 @@
         <v>44859</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -22743,7 +22743,7 @@
         <v>44473</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -22800,7 +22800,7 @@
         <v>44314</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -22857,7 +22857,7 @@
         <v>44727.71858796296</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -22919,7 +22919,7 @@
         <v>44335.4837962963</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -22976,7 +22976,7 @@
         <v>44475</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -23033,7 +23033,7 @@
         <v>44543</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -23095,7 +23095,7 @@
         <v>44475</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -23152,7 +23152,7 @@
         <v>44475</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -23209,7 +23209,7 @@
         <v>44481.67951388889</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -23266,7 +23266,7 @@
         <v>44725</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -23328,7 +23328,7 @@
         <v>44631.37421296296</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -23390,7 +23390,7 @@
         <v>44230</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -23447,7 +23447,7 @@
         <v>44631.45398148148</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -23509,7 +23509,7 @@
         <v>44538</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -23571,7 +23571,7 @@
         <v>44855.60383101852</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -23628,7 +23628,7 @@
         <v>44417.37207175926</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -23685,7 +23685,7 @@
         <v>44133</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -23747,7 +23747,7 @@
         <v>44768.44859953703</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -23804,7 +23804,7 @@
         <v>44475</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -23861,7 +23861,7 @@
         <v>44475</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -23918,7 +23918,7 @@
         <v>44475</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -23975,7 +23975,7 @@
         <v>44475</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -24032,7 +24032,7 @@
         <v>44368</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -24089,7 +24089,7 @@
         <v>44403</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -24146,7 +24146,7 @@
         <v>44886.62578703704</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -24203,7 +24203,7 @@
         <v>44886.629375</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -24260,7 +24260,7 @@
         <v>44838</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -24322,7 +24322,7 @@
         <v>44126</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -24384,7 +24384,7 @@
         <v>44540.56034722222</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -24441,7 +24441,7 @@
         <v>44872</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -24503,7 +24503,7 @@
         <v>44708.46081018518</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -24565,7 +24565,7 @@
         <v>44684</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -24627,7 +24627,7 @@
         <v>44742</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -24689,7 +24689,7 @@
         <v>44166</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -24751,7 +24751,7 @@
         <v>44169</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -24808,7 +24808,7 @@
         <v>44531</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -24865,7 +24865,7 @@
         <v>44180</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -24922,7 +24922,7 @@
         <v>44207</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -24984,7 +24984,7 @@
         <v>44531</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -25041,7 +25041,7 @@
         <v>44531</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -25098,7 +25098,7 @@
         <v>44188</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -25155,7 +25155,7 @@
         <v>44060</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -25232,7 +25232,7 @@
         <v>44413</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -25289,7 +25289,7 @@
         <v>44530.40607638889</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -25346,7 +25346,7 @@
         <v>44316</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -25403,7 +25403,7 @@
         <v>44270</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -25460,7 +25460,7 @@
         <v>44316</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -25517,7 +25517,7 @@
         <v>44788.67976851852</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -25579,7 +25579,7 @@
         <v>44706.66417824074</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -25641,7 +25641,7 @@
         <v>44389</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -25703,7 +25703,7 @@
         <v>44475</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -25760,7 +25760,7 @@
         <v>44803</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -25817,7 +25817,7 @@
         <v>44627.36047453704</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -25879,7 +25879,7 @@
         <v>44285</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -25936,7 +25936,7 @@
         <v>45154</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -25993,7 +25993,7 @@
         <v>45688.46570601852</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -26055,7 +26055,7 @@
         <v>44377</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -26112,7 +26112,7 @@
         <v>44825</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -26169,7 +26169,7 @@
         <v>44155</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -26226,7 +26226,7 @@
         <v>45768.29469907407</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -26288,7 +26288,7 @@
         <v>45768.30260416667</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -26350,7 +26350,7 @@
         <v>45768.30388888889</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -26412,7 +26412,7 @@
         <v>45471.66556712963</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -26474,7 +26474,7 @@
         <v>45705.32643518518</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -26531,7 +26531,7 @@
         <v>45642</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -26588,7 +26588,7 @@
         <v>45685.50063657408</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -26650,7 +26650,7 @@
         <v>45687.54329861111</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -26707,7 +26707,7 @@
         <v>45063</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -26764,7 +26764,7 @@
         <v>45484.58422453704</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -26826,7 +26826,7 @@
         <v>45371.66217592593</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -26888,7 +26888,7 @@
         <v>44474.59423611111</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -26945,7 +26945,7 @@
         <v>45280</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -27002,7 +27002,7 @@
         <v>45743.61899305556</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -27059,7 +27059,7 @@
         <v>45743.62116898148</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -27116,7 +27116,7 @@
         <v>45772.46965277778</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -27178,7 +27178,7 @@
         <v>45772.46988425926</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -27240,7 +27240,7 @@
         <v>45764</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -27297,7 +27297,7 @@
         <v>44886</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -27359,7 +27359,7 @@
         <v>44300</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -27416,7 +27416,7 @@
         <v>45754.35055555555</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -27473,7 +27473,7 @@
         <v>45539.43545138889</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -27530,7 +27530,7 @@
         <v>45204</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -27587,7 +27587,7 @@
         <v>45688.6749537037</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -27649,7 +27649,7 @@
         <v>45071.92488425926</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -27706,7 +27706,7 @@
         <v>44827</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -27763,7 +27763,7 @@
         <v>44827</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -27820,7 +27820,7 @@
         <v>45238.46430555556</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -27877,7 +27877,7 @@
         <v>45303.5047337963</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -27934,7 +27934,7 @@
         <v>45772.36106481482</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -27996,7 +27996,7 @@
         <v>45735.57390046296</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -28053,7 +28053,7 @@
         <v>45119.38151620371</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -28115,7 +28115,7 @@
         <v>45345.66555555556</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -28177,7 +28177,7 @@
         <v>45665.59925925926</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -28234,7 +28234,7 @@
         <v>45362.64613425926</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -28291,7 +28291,7 @@
         <v>45362.65407407407</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -28348,7 +28348,7 @@
         <v>45362.67789351852</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -28405,7 +28405,7 @@
         <v>45593.6821412037</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -28462,7 +28462,7 @@
         <v>45593.68434027778</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -28519,7 +28519,7 @@
         <v>45532</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -28576,7 +28576,7 @@
         <v>45625.56934027778</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -28638,7 +28638,7 @@
         <v>45274</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -28695,7 +28695,7 @@
         <v>44886</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -28757,7 +28757,7 @@
         <v>45406</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -28819,7 +28819,7 @@
         <v>45406</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -28881,7 +28881,7 @@
         <v>44823.84673611111</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -28938,7 +28938,7 @@
         <v>44361</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -28995,7 +28995,7 @@
         <v>45342</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -29052,7 +29052,7 @@
         <v>45688.67935185185</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -29114,7 +29114,7 @@
         <v>45411.44549768518</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -29176,7 +29176,7 @@
         <v>45758.66108796297</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -29233,7 +29233,7 @@
         <v>45758.69123842593</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -29290,7 +29290,7 @@
         <v>45303.5187037037</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -29347,7 +29347,7 @@
         <v>45688.67145833333</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -29409,7 +29409,7 @@
         <v>44312</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -29466,7 +29466,7 @@
         <v>44853</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -29523,7 +29523,7 @@
         <v>44925.33584490741</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -29585,7 +29585,7 @@
         <v>45741.45597222223</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>45119.39105324074</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -29704,7 +29704,7 @@
         <v>45706</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -29761,7 +29761,7 @@
         <v>45085</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -29818,7 +29818,7 @@
         <v>45635.42027777778</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -29880,7 +29880,7 @@
         <v>45741.39084490741</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -29937,7 +29937,7 @@
         <v>45728.61006944445</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -29994,7 +29994,7 @@
         <v>45670</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -30056,7 +30056,7 @@
         <v>44985.6125</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -30118,7 +30118,7 @@
         <v>45763.4266087963</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -30175,7 +30175,7 @@
         <v>45345.65929398148</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -30237,7 +30237,7 @@
         <v>45611.38759259259</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -30294,7 +30294,7 @@
         <v>44642</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -30356,7 +30356,7 @@
         <v>45688.6769212963</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -30418,7 +30418,7 @@
         <v>45740.44842592593</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -30480,7 +30480,7 @@
         <v>45439.43106481482</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -30542,7 +30542,7 @@
         <v>44972.57449074074</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -30599,7 +30599,7 @@
         <v>45244</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -30656,7 +30656,7 @@
         <v>44484.55535879629</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -30713,7 +30713,7 @@
         <v>45229.92739583334</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -30770,7 +30770,7 @@
         <v>44862</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -30832,7 +30832,7 @@
         <v>45243.63798611111</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -30889,7 +30889,7 @@
         <v>45429</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -30946,7 +30946,7 @@
         <v>44889.56582175926</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -31003,7 +31003,7 @@
         <v>45460.47969907407</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -31060,7 +31060,7 @@
         <v>45531.66196759259</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -31122,7 +31122,7 @@
         <v>45407.36894675926</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -31184,7 +31184,7 @@
         <v>44928</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -31246,7 +31246,7 @@
         <v>44928</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -31308,7 +31308,7 @@
         <v>45252.48409722222</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -31365,7 +31365,7 @@
         <v>45252</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -31422,7 +31422,7 @@
         <v>45731.69629629629</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -31479,7 +31479,7 @@
         <v>45667</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -31536,7 +31536,7 @@
         <v>44819.56722222222</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -31593,7 +31593,7 @@
         <v>45509</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -31655,7 +31655,7 @@
         <v>44414.58354166667</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -31712,7 +31712,7 @@
         <v>45631.63091435185</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -31769,7 +31769,7 @@
         <v>44167</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -31826,7 +31826,7 @@
         <v>45303.52626157407</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -31883,7 +31883,7 @@
         <v>45719.48778935185</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -31940,7 +31940,7 @@
         <v>45574.66106481481</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -31997,7 +31997,7 @@
         <v>44854</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -32059,7 +32059,7 @@
         <v>45264.92637731481</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -32116,7 +32116,7 @@
         <v>45751.65657407408</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -32178,7 +32178,7 @@
         <v>45763.41402777778</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -32235,7 +32235,7 @@
         <v>45338</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -32297,7 +32297,7 @@
         <v>45496.59202546296</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -32359,7 +32359,7 @@
         <v>45260.59042824074</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -32416,7 +32416,7 @@
         <v>45756</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -32473,7 +32473,7 @@
         <v>45075.59148148148</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -32535,7 +32535,7 @@
         <v>44082</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -32597,7 +32597,7 @@
         <v>45063.92605324074</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -32654,7 +32654,7 @@
         <v>45575.60996527778</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -32716,7 +32716,7 @@
         <v>45260.35777777778</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -32773,7 +32773,7 @@
         <v>45290.39024305555</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -32830,7 +32830,7 @@
         <v>45460.48582175926</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -32887,7 +32887,7 @@
         <v>45447.35144675926</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -32944,7 +32944,7 @@
         <v>44925.64049768518</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -33006,7 +33006,7 @@
         <v>45680.42497685185</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -33063,7 +33063,7 @@
         <v>45153.42725694444</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -33125,7 +33125,7 @@
         <v>45054</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -33187,7 +33187,7 @@
         <v>45588.56039351852</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -33244,7 +33244,7 @@
         <v>44348</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -33301,7 +33301,7 @@
         <v>45257</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -33363,7 +33363,7 @@
         <v>45568</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -33425,7 +33425,7 @@
         <v>45685</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -33487,7 +33487,7 @@
         <v>45279.57732638889</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -33544,7 +33544,7 @@
         <v>45477.66773148148</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -33606,7 +33606,7 @@
         <v>44883</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -33663,7 +33663,7 @@
         <v>45509</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -33725,7 +33725,7 @@
         <v>44091</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -33782,7 +33782,7 @@
         <v>44853.41693287037</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -33839,7 +33839,7 @@
         <v>45761.61501157407</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -33901,7 +33901,7 @@
         <v>45637.39587962963</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -33963,7 +33963,7 @@
         <v>45559.43645833333</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -34025,7 +34025,7 @@
         <v>45257</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -34082,7 +34082,7 @@
         <v>45517.69590277778</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -34144,7 +34144,7 @@
         <v>45590.31899305555</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -34201,7 +34201,7 @@
         <v>45642.41907407407</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -34258,7 +34258,7 @@
         <v>45049.59826388889</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -34315,7 +34315,7 @@
         <v>45684.51006944444</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -34372,7 +34372,7 @@
         <v>44957</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -34434,7 +34434,7 @@
         <v>45579.57390046296</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -34496,7 +34496,7 @@
         <v>44643.81518518519</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -34553,7 +34553,7 @@
         <v>44999.60127314815</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -34610,7 +34610,7 @@
         <v>45601.58355324074</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -34667,7 +34667,7 @@
         <v>44475</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -34724,7 +34724,7 @@
         <v>45096.62344907408</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -34786,7 +34786,7 @@
         <v>45429.39</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -34843,7 +34843,7 @@
         <v>44216</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -34905,7 +34905,7 @@
         <v>45635.4916087963</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -34962,7 +34962,7 @@
         <v>45012</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -35024,7 +35024,7 @@
         <v>45607</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -35081,7 +35081,7 @@
         <v>44571</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -35138,7 +35138,7 @@
         <v>45579.59980324074</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -35195,7 +35195,7 @@
         <v>45632</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -35252,7 +35252,7 @@
         <v>45632</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -35309,7 +35309,7 @@
         <v>45672.44825231482</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -35366,7 +35366,7 @@
         <v>45467</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -35423,7 +35423,7 @@
         <v>45484</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -35485,7 +35485,7 @@
         <v>45106</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -35547,7 +35547,7 @@
         <v>45604.32543981481</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -35609,7 +35609,7 @@
         <v>45506.36534722222</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -35666,7 +35666,7 @@
         <v>45478.48700231482</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -35728,7 +35728,7 @@
         <v>45491.5859375</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -35785,7 +35785,7 @@
         <v>45603</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -35847,7 +35847,7 @@
         <v>45733.38637731481</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -35904,7 +35904,7 @@
         <v>45604.33195601852</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -35966,7 +35966,7 @@
         <v>45575</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -36023,7 +36023,7 @@
         <v>44472</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -36080,7 +36080,7 @@
         <v>45509</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -36142,7 +36142,7 @@
         <v>45254</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -36199,7 +36199,7 @@
         <v>45345.35003472222</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -36261,7 +36261,7 @@
         <v>45729.65261574074</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -36323,7 +36323,7 @@
         <v>45687.65449074074</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -36385,7 +36385,7 @@
         <v>45635.33439814814</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -36447,7 +36447,7 @@
         <v>44987.34981481481</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -36509,7 +36509,7 @@
         <v>45537.60471064815</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -36571,7 +36571,7 @@
         <v>45484.66521990741</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -36633,7 +36633,7 @@
         <v>45485</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -36695,7 +36695,7 @@
         <v>45485</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -36757,7 +36757,7 @@
         <v>45485</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -36819,7 +36819,7 @@
         <v>45776.69569444445</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -36876,7 +36876,7 @@
         <v>45253.55737268519</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -36933,7 +36933,7 @@
         <v>45768.29630787037</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -36995,7 +36995,7 @@
         <v>45768.30954861111</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -37057,7 +37057,7 @@
         <v>44565.31975694445</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -37119,7 +37119,7 @@
         <v>44565</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -37181,7 +37181,7 @@
         <v>45776.43898148148</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -37238,7 +37238,7 @@
         <v>44316</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -37295,7 +37295,7 @@
         <v>45642.35256944445</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -37352,7 +37352,7 @@
         <v>44924.61315972222</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -37414,7 +37414,7 @@
         <v>45779.48611111111</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -37476,7 +37476,7 @@
         <v>45779.38211805555</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -37538,7 +37538,7 @@
         <v>45779.47704861111</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -37600,7 +37600,7 @@
         <v>45779.50052083333</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -37662,7 +37662,7 @@
         <v>45779.41844907407</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -37724,7 +37724,7 @@
         <v>45737</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -37781,7 +37781,7 @@
         <v>45782.41581018519</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -37838,7 +37838,7 @@
         <v>45779.50886574074</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -37900,7 +37900,7 @@
         <v>45779.51943287037</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -37962,7 +37962,7 @@
         <v>45275</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -38019,7 +38019,7 @@
         <v>45779.52488425926</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -38081,7 +38081,7 @@
         <v>45568</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -38143,7 +38143,7 @@
         <v>45782.42744212963</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -38200,7 +38200,7 @@
         <v>45779.51357638889</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -38262,7 +38262,7 @@
         <v>44925</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -38319,7 +38319,7 @@
         <v>44732</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -38376,7 +38376,7 @@
         <v>45784.59012731481</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -38438,7 +38438,7 @@
         <v>45618.35961805555</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -38495,7 +38495,7 @@
         <v>45560.33311342593</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -38557,7 +38557,7 @@
         <v>45540.4264699074</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -38619,7 +38619,7 @@
         <v>45783.68547453704</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -38681,7 +38681,7 @@
         <v>45632.64078703704</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -38738,7 +38738,7 @@
         <v>45624.57098379629</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -38795,7 +38795,7 @@
         <v>45483.47572916667</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -38852,7 +38852,7 @@
         <v>44312</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -38909,7 +38909,7 @@
         <v>44914</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -38991,7 +38991,7 @@
         <v>44928.48072916667</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -39053,7 +39053,7 @@
         <v>45531.78386574074</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -39110,7 +39110,7 @@
         <v>45097</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -39172,7 +39172,7 @@
         <v>45202</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -39234,7 +39234,7 @@
         <v>45362.65903935185</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -39291,7 +39291,7 @@
         <v>45610.56706018518</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -39353,7 +39353,7 @@
         <v>45642</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -39410,7 +39410,7 @@
         <v>44924.59140046296</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -39472,7 +39472,7 @@
         <v>45569.6909837963</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -39529,7 +39529,7 @@
         <v>44985</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -39591,7 +39591,7 @@
         <v>45786.66032407407</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -39653,7 +39653,7 @@
         <v>45786.66853009259</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -39715,7 +39715,7 @@
         <v>44631.37701388889</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -39777,7 +39777,7 @@
         <v>45252.45481481482</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -39834,7 +39834,7 @@
         <v>44631.42353009259</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -39896,7 +39896,7 @@
         <v>44914</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -39953,7 +39953,7 @@
         <v>45453.6619212963</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -40010,7 +40010,7 @@
         <v>45607.44832175926</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -40072,7 +40072,7 @@
         <v>44698</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -40134,7 +40134,7 @@
         <v>45617</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -40196,7 +40196,7 @@
         <v>45212</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -40253,7 +40253,7 @@
         <v>45582.59753472222</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -40315,7 +40315,7 @@
         <v>45786.66209490741</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -40377,7 +40377,7 @@
         <v>44925</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -40439,7 +40439,7 @@
         <v>45670.34313657408</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -40496,7 +40496,7 @@
         <v>45691</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -40558,7 +40558,7 @@
         <v>45691</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -40620,7 +40620,7 @@
         <v>45786.66425925926</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -40682,7 +40682,7 @@
         <v>45177.9224537037</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -40739,7 +40739,7 @@
         <v>45632</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -40796,7 +40796,7 @@
         <v>45387</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -40853,7 +40853,7 @@
         <v>45457.92854166667</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -40910,7 +40910,7 @@
         <v>45624.36858796296</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -40967,7 +40967,7 @@
         <v>45785.34165509259</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -41024,7 +41024,7 @@
         <v>45785.33164351852</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -41081,7 +41081,7 @@
         <v>45546.54530092593</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -41138,7 +41138,7 @@
         <v>44162.65819444445</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -41200,7 +41200,7 @@
         <v>45484.57285879629</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -41262,7 +41262,7 @@
         <v>45510</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -41319,7 +41319,7 @@
         <v>45638.416875</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -41381,7 +41381,7 @@
         <v>45758.49096064815</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -41443,7 +41443,7 @@
         <v>45568</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -41505,7 +41505,7 @@
         <v>45790.43</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -41567,7 +41567,7 @@
         <v>45607</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -41629,7 +41629,7 @@
         <v>45754.67329861111</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -41686,7 +41686,7 @@
         <v>44987.35282407407</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -41748,7 +41748,7 @@
         <v>45622.64627314815</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -41805,7 +41805,7 @@
         <v>45772.69290509259</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -41867,7 +41867,7 @@
         <v>45485</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -41924,7 +41924,7 @@
         <v>45041</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -41981,7 +41981,7 @@
         <v>45687.53689814815</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -42038,7 +42038,7 @@
         <v>45432</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -42100,7 +42100,7 @@
         <v>44242</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -42157,7 +42157,7 @@
         <v>44939.45376157408</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -42214,7 +42214,7 @@
         <v>44994</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -42271,7 +42271,7 @@
         <v>45173</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -42328,7 +42328,7 @@
         <v>45170.4643287037</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -42390,7 +42390,7 @@
         <v>45576.48657407407</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -42452,7 +42452,7 @@
         <v>45637</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -42509,7 +42509,7 @@
         <v>45481.3330787037</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -42571,7 +42571,7 @@
         <v>45560</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -42628,7 +42628,7 @@
         <v>44916</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -42685,7 +42685,7 @@
         <v>44440</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -42742,7 +42742,7 @@
         <v>44977.44643518519</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -42804,7 +42804,7 @@
         <v>45559</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -42861,7 +42861,7 @@
         <v>44957</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -42923,7 +42923,7 @@
         <v>44082</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -42985,7 +42985,7 @@
         <v>45506.36702546296</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -43042,7 +43042,7 @@
         <v>45834.80229166667</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -43099,7 +43099,7 @@
         <v>45792.64795138889</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -43156,7 +43156,7 @@
         <v>44258</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -43213,7 +43213,7 @@
         <v>45496.66903935185</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -43275,7 +43275,7 @@
         <v>45509</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -43337,7 +43337,7 @@
         <v>45509.6427662037</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -43399,7 +43399,7 @@
         <v>45790.87653935186</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -43456,7 +43456,7 @@
         <v>45562.65759259259</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -43518,7 +43518,7 @@
         <v>44153</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -43575,7 +43575,7 @@
         <v>45792.65047453704</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -43632,7 +43632,7 @@
         <v>45634.65831018519</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -43689,7 +43689,7 @@
         <v>45061.36835648148</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -43746,7 +43746,7 @@
         <v>45728</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -43803,7 +43803,7 @@
         <v>45517.39274305556</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -43865,7 +43865,7 @@
         <v>45632.64769675926</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -43922,7 +43922,7 @@
         <v>45792.50942129629</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -43984,7 +43984,7 @@
         <v>45483.47207175926</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -44041,7 +44041,7 @@
         <v>45593.67809027778</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -44098,7 +44098,7 @@
         <v>45733.43663194445</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -44160,7 +44160,7 @@
         <v>44424</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -44217,7 +44217,7 @@
         <v>44628.36402777778</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -44274,7 +44274,7 @@
         <v>44985</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -44336,7 +44336,7 @@
         <v>44475</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -44393,7 +44393,7 @@
         <v>45575.6125925926</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -44455,7 +44455,7 @@
         <v>45644.50141203704</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -44517,7 +44517,7 @@
         <v>45345.47642361111</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -44579,7 +44579,7 @@
         <v>45345.48181712963</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -44641,7 +44641,7 @@
         <v>45345.4940625</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -44703,7 +44703,7 @@
         <v>45618.35097222222</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -44760,7 +44760,7 @@
         <v>45665.563125</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -44822,7 +44822,7 @@
         <v>45595.5666550926</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -44879,7 +44879,7 @@
         <v>45362.67293981482</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -44936,7 +44936,7 @@
         <v>45835.55998842593</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -44998,7 +44998,7 @@
         <v>44953</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -45055,7 +45055,7 @@
         <v>45835.5583912037</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -45117,7 +45117,7 @@
         <v>45614.47960648148</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -45174,7 +45174,7 @@
         <v>44305</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -45231,7 +45231,7 @@
         <v>44531.43927083333</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -45293,7 +45293,7 @@
         <v>45517.38320601852</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -45350,7 +45350,7 @@
         <v>45345</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -45412,7 +45412,7 @@
         <v>45835.57069444445</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -45469,7 +45469,7 @@
         <v>45203</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -45526,7 +45526,7 @@
         <v>45208</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -45583,7 +45583,7 @@
         <v>45796.39770833333</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -45640,7 +45640,7 @@
         <v>45772.46951388889</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -45702,7 +45702,7 @@
         <v>45793.41994212963</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -45764,7 +45764,7 @@
         <v>45644.56674768519</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -45826,7 +45826,7 @@
         <v>45635.35274305556</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -45888,7 +45888,7 @@
         <v>45485.42287037037</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -45945,7 +45945,7 @@
         <v>45485</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -46002,7 +46002,7 @@
         <v>45485.44258101852</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -46064,7 +46064,7 @@
         <v>45796.57802083333</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -46121,7 +46121,7 @@
         <v>45533.75398148148</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -46178,7 +46178,7 @@
         <v>45159.60288194445</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -46235,7 +46235,7 @@
         <v>45603</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -46297,7 +46297,7 @@
         <v>45622</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -46359,7 +46359,7 @@
         <v>45705.32456018519</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -46416,7 +46416,7 @@
         <v>45209.45420138889</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -46473,7 +46473,7 @@
         <v>44225</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -46530,7 +46530,7 @@
         <v>45453.6672800926</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -46587,7 +46587,7 @@
         <v>45225.58005787037</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -46644,7 +46644,7 @@
         <v>45839.5658912037</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -46701,7 +46701,7 @@
         <v>45408</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -46758,7 +46758,7 @@
         <v>45646</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -46815,7 +46815,7 @@
         <v>45840.64394675926</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -46877,7 +46877,7 @@
         <v>45631</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -46939,7 +46939,7 @@
         <v>45621</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -47001,7 +47001,7 @@
         <v>44153</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -47063,7 +47063,7 @@
         <v>45350</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -47120,7 +47120,7 @@
         <v>45351</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -47177,7 +47177,7 @@
         <v>45674.57393518519</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -47234,7 +47234,7 @@
         <v>45569</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -47296,7 +47296,7 @@
         <v>45625.49736111111</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -47353,7 +47353,7 @@
         <v>45345.34219907408</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -47415,7 +47415,7 @@
         <v>45730</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -47472,7 +47472,7 @@
         <v>45170.46134259259</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -47534,7 +47534,7 @@
         <v>45737.37006944444</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -47591,7 +47591,7 @@
         <v>45604.31657407407</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -47653,7 +47653,7 @@
         <v>44075</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -47710,7 +47710,7 @@
         <v>45111</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -47767,7 +47767,7 @@
         <v>45631</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -47829,7 +47829,7 @@
         <v>45791</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -47886,7 +47886,7 @@
         <v>45768.29289351852</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -47948,7 +47948,7 @@
         <v>45768.30086805556</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -48010,7 +48010,7 @@
         <v>45119.38675925926</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -48072,7 +48072,7 @@
         <v>45345</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -48134,7 +48134,7 @@
         <v>45797.37096064815</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -48191,7 +48191,7 @@
         <v>45800.58859953703</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -48248,7 +48248,7 @@
         <v>45800.59567129629</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -48310,7 +48310,7 @@
         <v>45800.64719907408</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -48372,7 +48372,7 @@
         <v>45751.34636574074</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -48434,7 +48434,7 @@
         <v>45740.57487268518</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -48496,7 +48496,7 @@
         <v>45800.56313657408</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -48553,7 +48553,7 @@
         <v>45800.57837962963</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -48615,7 +48615,7 @@
         <v>45830</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -48672,7 +48672,7 @@
         <v>44638.44958333333</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -48729,7 +48729,7 @@
         <v>44784.60677083334</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -48791,7 +48791,7 @@
         <v>45800.48060185185</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -48853,7 +48853,7 @@
         <v>45799.64804398148</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -48915,7 +48915,7 @@
         <v>45837</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -48972,7 +48972,7 @@
         <v>45800.3787037037</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -49034,7 +49034,7 @@
         <v>45841.4312037037</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -49091,7 +49091,7 @@
         <v>45642.33616898148</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -49148,7 +49148,7 @@
         <v>44827</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -49205,7 +49205,7 @@
         <v>45061.61002314815</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -49267,7 +49267,7 @@
         <v>45834</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -49324,7 +49324,7 @@
         <v>45800.44868055556</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -49386,7 +49386,7 @@
         <v>45800.4687962963</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -49448,7 +49448,7 @@
         <v>45841.45137731481</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -49505,7 +49505,7 @@
         <v>45800.50431712963</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -49567,7 +49567,7 @@
         <v>45841.69273148148</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -49624,7 +49624,7 @@
         <v>45800.56222222222</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -49686,7 +49686,7 @@
         <v>45799.57883101852</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -49743,7 +49743,7 @@
         <v>45799.45770833334</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -49805,7 +49805,7 @@
         <v>45830</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -49862,7 +49862,7 @@
         <v>45830</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -49919,7 +49919,7 @@
         <v>45800.65341435185</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -49981,7 +49981,7 @@
         <v>45799.47225694444</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -50043,7 +50043,7 @@
         <v>45580.92037037037</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -50100,7 +50100,7 @@
         <v>45762.55899305556</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -50157,7 +50157,7 @@
         <v>45800.33436342593</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -50219,7 +50219,7 @@
         <v>45800.3425</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -50281,7 +50281,7 @@
         <v>45799.43550925926</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -50343,7 +50343,7 @@
         <v>45800.46069444445</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -50405,7 +50405,7 @@
         <v>45800.48515046296</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -50467,7 +50467,7 @@
         <v>45842.48990740741</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -50524,7 +50524,7 @@
         <v>45800.56995370371</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -50586,7 +50586,7 @@
         <v>44280</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -50643,7 +50643,7 @@
         <v>45800.37524305555</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -50705,7 +50705,7 @@
         <v>45800.42797453704</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -50762,7 +50762,7 @@
         <v>45800.44090277778</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -50819,7 +50819,7 @@
         <v>45800.64065972222</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -50881,7 +50881,7 @@
         <v>45237.5815162037</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -50938,7 +50938,7 @@
         <v>45841.46512731481</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -51000,7 +51000,7 @@
         <v>45800.63738425926</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -51062,7 +51062,7 @@
         <v>45830</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -51119,7 +51119,7 @@
         <v>45231</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -51176,7 +51176,7 @@
         <v>45685.38901620371</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -51238,7 +51238,7 @@
         <v>45800.60508101852</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -51300,7 +51300,7 @@
         <v>45677.44273148148</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -51357,7 +51357,7 @@
         <v>45800.66043981481</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -51419,7 +51419,7 @@
         <v>45799.4658912037</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -51481,7 +51481,7 @@
         <v>45799.46642361111</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -51538,7 +51538,7 @@
         <v>45800.3503587963</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -51600,7 +51600,7 @@
         <v>45800.35670138889</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -51662,7 +51662,7 @@
         <v>45622.64012731481</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -51724,7 +51724,7 @@
         <v>45800.41883101852</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -51786,7 +51786,7 @@
         <v>45667</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -51848,7 +51848,7 @@
         <v>45439.62893518519</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -51905,7 +51905,7 @@
         <v>45478.44497685185</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -51967,7 +51967,7 @@
         <v>45799.43086805556</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -52029,7 +52029,7 @@
         <v>45195.61476851852</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -52086,7 +52086,7 @@
         <v>45240</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -52143,7 +52143,7 @@
         <v>45804.5813425926</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -52205,7 +52205,7 @@
         <v>45215</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -52262,7 +52262,7 @@
         <v>45803.37258101852</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -52319,7 +52319,7 @@
         <v>45845.60496527778</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -52376,7 +52376,7 @@
         <v>45196</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -52438,7 +52438,7 @@
         <v>45622.45239583333</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -52500,7 +52500,7 @@
         <v>45638</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -52562,7 +52562,7 @@
         <v>45603</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -52624,7 +52624,7 @@
         <v>45107</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -52681,7 +52681,7 @@
         <v>45845.6920949074</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -52743,7 +52743,7 @@
         <v>45611.4021875</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -52800,7 +52800,7 @@
         <v>45622</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -52862,7 +52862,7 @@
         <v>44708.45504629629</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -52924,7 +52924,7 @@
         <v>45618</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -52981,7 +52981,7 @@
         <v>44708</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -53043,7 +53043,7 @@
         <v>45845.55266203704</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -53100,7 +53100,7 @@
         <v>45118.47491898148</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -53162,7 +53162,7 @@
         <v>45804.589375</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -53219,7 +53219,7 @@
         <v>45216</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -53276,7 +53276,7 @@
         <v>45845.55259259259</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -53333,7 +53333,7 @@
         <v>45845.55270833334</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -53390,7 +53390,7 @@
         <v>45803.37480324074</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -53447,7 +53447,7 @@
         <v>45685</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -53509,7 +53509,7 @@
         <v>45728.44329861111</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -53571,7 +53571,7 @@
         <v>45848.45113425926</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -53633,7 +53633,7 @@
         <v>45728.49267361111</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -53695,7 +53695,7 @@
         <v>45848.57644675926</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -53757,7 +53757,7 @@
         <v>45569</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -53819,7 +53819,7 @@
         <v>45505</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -53876,7 +53876,7 @@
         <v>45505</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -53938,7 +53938,7 @@
         <v>45645.47609953704</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -54000,7 +54000,7 @@
         <v>45645.48079861111</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -54062,7 +54062,7 @@
         <v>45848.65003472222</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -54119,7 +54119,7 @@
         <v>45568</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -54181,7 +54181,7 @@
         <v>44214</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -54243,7 +54243,7 @@
         <v>45205</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -54300,7 +54300,7 @@
         <v>45614.62445601852</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -54362,7 +54362,7 @@
         <v>45805.53280092592</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -54424,7 +54424,7 @@
         <v>45730</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -54481,7 +54481,7 @@
         <v>45848.68640046296</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -54543,7 +54543,7 @@
         <v>45569.48626157407</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -54600,7 +54600,7 @@
         <v>44728</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -54662,7 +54662,7 @@
         <v>45670.66085648148</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -54719,7 +54719,7 @@
         <v>45848.6568287037</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -54776,7 +54776,7 @@
         <v>45569</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -54838,7 +54838,7 @@
         <v>45848.62873842593</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -54895,7 +54895,7 @@
         <v>45197.46966435185</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -54952,7 +54952,7 @@
         <v>45568</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -55014,7 +55014,7 @@
         <v>45848.639375</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -55071,7 +55071,7 @@
         <v>45730</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -55128,7 +55128,7 @@
         <v>45632</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -55185,7 +55185,7 @@
         <v>45848.35400462963</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -55242,7 +55242,7 @@
         <v>45847.58865740741</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -55304,7 +55304,7 @@
         <v>45569</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -55366,7 +55366,7 @@
         <v>45666</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -55428,7 +55428,7 @@
         <v>45174</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -55485,7 +55485,7 @@
         <v>45741.38347222222</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -55542,7 +55542,7 @@
         <v>45610.55846064815</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -55604,7 +55604,7 @@
         <v>45159.46996527778</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -55666,7 +55666,7 @@
         <v>44925.60457175926</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -55728,7 +55728,7 @@
         <v>44925.64309027778</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -55790,7 +55790,7 @@
         <v>45807.60333333333</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -55852,7 +55852,7 @@
         <v>45807.58868055556</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -55914,7 +55914,7 @@
         <v>45617</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -55976,7 +55976,7 @@
         <v>45807.59407407408</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -56038,7 +56038,7 @@
         <v>45807.41287037037</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -56100,7 +56100,7 @@
         <v>45807.42212962963</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -56162,7 +56162,7 @@
         <v>45807.45288194445</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -56224,7 +56224,7 @@
         <v>45807.49436342593</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -56286,7 +56286,7 @@
         <v>45807.49832175926</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -56348,7 +56348,7 @@
         <v>45807.58393518518</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -56410,7 +56410,7 @@
         <v>45751.63266203704</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -56472,7 +56472,7 @@
         <v>45848</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -56534,7 +56534,7 @@
         <v>45807.36304398148</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -56596,7 +56596,7 @@
         <v>45807.41717592593</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -56658,7 +56658,7 @@
         <v>45807.43461805556</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -56720,7 +56720,7 @@
         <v>45807.44070601852</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -56782,7 +56782,7 @@
         <v>45807.44608796296</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -56844,7 +56844,7 @@
         <v>45238.64153935185</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -56901,7 +56901,7 @@
         <v>45807.63334490741</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -56963,7 +56963,7 @@
         <v>45265</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -57020,7 +57020,7 @@
         <v>45807.47479166667</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -57082,7 +57082,7 @@
         <v>45807.49045138889</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -57144,7 +57144,7 @@
         <v>45533.67138888889</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -57201,7 +57201,7 @@
         <v>45758.69638888889</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -57258,7 +57258,7 @@
         <v>45195.35877314815</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -57315,7 +57315,7 @@
         <v>45195.3878125</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -57372,7 +57372,7 @@
         <v>45159</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -57434,7 +57434,7 @@
         <v>45159</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -57496,7 +57496,7 @@
         <v>45644</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -57553,7 +57553,7 @@
         <v>44314</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -57610,7 +57610,7 @@
         <v>45852.48290509259</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -57667,7 +57667,7 @@
         <v>45807.65438657408</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -57729,7 +57729,7 @@
         <v>45807.3409837963</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -57791,7 +57791,7 @@
         <v>45807.35476851852</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -57853,7 +57853,7 @@
         <v>45807.55893518519</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -57915,7 +57915,7 @@
         <v>44998</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -57972,7 +57972,7 @@
         <v>45459</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -58029,7 +58029,7 @@
         <v>45807.5684375</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -58091,7 +58091,7 @@
         <v>45218.58609953704</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -58148,7 +58148,7 @@
         <v>45751.69827546296</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -58210,7 +58210,7 @@
         <v>45721.33868055556</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -58267,7 +58267,7 @@
         <v>45617</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -58329,7 +58329,7 @@
         <v>45852</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -58386,7 +58386,7 @@
         <v>45807.56403935186</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -58448,7 +58448,7 @@
         <v>45334</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -58510,7 +58510,7 @@
         <v>45582.49792824074</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -58572,7 +58572,7 @@
         <v>45685</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -58629,7 +58629,7 @@
         <v>45854.44850694444</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -58691,7 +58691,7 @@
         <v>45854.44864583333</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -58753,7 +58753,7 @@
         <v>45170.46923611111</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -58815,7 +58815,7 @@
         <v>45474.54432870371</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -58872,7 +58872,7 @@
         <v>45853.61865740741</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -58929,7 +58929,7 @@
         <v>45280</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -58986,7 +58986,7 @@
         <v>45811.34540509259</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -59048,7 +59048,7 @@
         <v>45811.34564814815</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -59110,7 +59110,7 @@
         <v>44091</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -59167,7 +59167,7 @@
         <v>44726</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -59224,7 +59224,7 @@
         <v>45853.28325231482</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -59281,7 +59281,7 @@
         <v>44423</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -59338,7 +59338,7 @@
         <v>45853.62415509259</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -59400,7 +59400,7 @@
         <v>45854.40662037037</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -59462,7 +59462,7 @@
         <v>45733</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -59519,7 +59519,7 @@
         <v>45719.40480324074</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -59576,7 +59576,7 @@
         <v>45811.34578703704</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -59638,7 +59638,7 @@
         <v>45617.89371527778</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -59695,7 +59695,7 @@
         <v>45621</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -59757,7 +59757,7 @@
         <v>45154</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -59814,7 +59814,7 @@
         <v>44182</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -59871,7 +59871,7 @@
         <v>45719.45215277778</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -59928,7 +59928,7 @@
         <v>45111</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -59990,7 +59990,7 @@
         <v>44665</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -60047,7 +60047,7 @@
         <v>45604.66936342593</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -60104,7 +60104,7 @@
         <v>45173</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -60166,7 +60166,7 @@
         <v>45118.91633101852</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -60223,7 +60223,7 @@
         <v>45119</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -60280,7 +60280,7 @@
         <v>44708.48859953704</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -60342,7 +60342,7 @@
         <v>45632.65197916667</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -60399,7 +60399,7 @@
         <v>45723.58140046296</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -60456,7 +60456,7 @@
         <v>44209</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -60518,7 +60518,7 @@
         <v>45245</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -60575,7 +60575,7 @@
         <v>44229</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -60637,7 +60637,7 @@
         <v>45813.64590277777</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -60694,7 +60694,7 @@
         <v>44225</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -60751,7 +60751,7 @@
         <v>45813.47074074074</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -60808,7 +60808,7 @@
         <v>45740.36546296296</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -60870,7 +60870,7 @@
         <v>45147</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -60927,7 +60927,7 @@
         <v>45813.48734953703</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -60984,7 +60984,7 @@
         <v>45406.64024305555</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -61046,7 +61046,7 @@
         <v>45303</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -61103,7 +61103,7 @@
         <v>45622</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -61160,7 +61160,7 @@
         <v>45859</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -61217,7 +61217,7 @@
         <v>45506.3637962963</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -61274,7 +61274,7 @@
         <v>45659.57361111111</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -61336,7 +61336,7 @@
         <v>44883</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -61393,7 +61393,7 @@
         <v>45063</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -61450,7 +61450,7 @@
         <v>45817.33819444444</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -61512,7 +61512,7 @@
         <v>45849</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -61569,7 +61569,7 @@
         <v>45397.64855324074</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -61626,7 +61626,7 @@
         <v>44818</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -61683,7 +61683,7 @@
         <v>45817.62439814815</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -61740,7 +61740,7 @@
         <v>45630.62513888889</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -61797,7 +61797,7 @@
         <v>45817.594375</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -61859,7 +61859,7 @@
         <v>45755</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -61916,7 +61916,7 @@
         <v>45631.39950231482</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -61978,7 +61978,7 @@
         <v>45630.5731712963</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -62040,7 +62040,7 @@
         <v>45678.37956018518</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -62097,7 +62097,7 @@
         <v>45707</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -62154,7 +62154,7 @@
         <v>45442</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -62216,7 +62216,7 @@
         <v>45764.44861111111</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -62278,7 +62278,7 @@
         <v>45727.35621527778</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -62340,7 +62340,7 @@
         <v>45510</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -62402,7 +62402,7 @@
         <v>45820.64821759259</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -62459,7 +62459,7 @@
         <v>45484.65768518519</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -62521,7 +62521,7 @@
         <v>45691</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -62583,7 +62583,7 @@
         <v>45691</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -62645,7 +62645,7 @@
         <v>45866.40701388889</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -62702,7 +62702,7 @@
         <v>45866.62908564815</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -62759,7 +62759,7 @@
         <v>45621</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -62816,7 +62816,7 @@
         <v>45621</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -62873,7 +62873,7 @@
         <v>45821.77903935185</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -62930,7 +62930,7 @@
         <v>45485</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -62987,7 +62987,7 @@
         <v>45821.57201388889</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -63049,7 +63049,7 @@
         <v>45118.3959375</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -63111,7 +63111,7 @@
         <v>45643.56899305555</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -63173,7 +63173,7 @@
         <v>45791</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -63230,7 +63230,7 @@
         <v>45867.55305555555</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -63287,7 +63287,7 @@
         <v>45867.55642361111</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -63349,7 +63349,7 @@
         <v>45733.59667824074</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -63411,7 +63411,7 @@
         <v>45098.48666666666</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -63473,7 +63473,7 @@
         <v>45868.639375</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -63530,7 +63530,7 @@
         <v>44928.36418981481</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -63592,7 +63592,7 @@
         <v>44231</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -63654,7 +63654,7 @@
         <v>45707</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -63711,7 +63711,7 @@
         <v>44795</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -63768,7 +63768,7 @@
         <v>45826.43267361111</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -63830,7 +63830,7 @@
         <v>44088</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -63887,7 +63887,7 @@
         <v>45742.42793981481</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -63949,7 +63949,7 @@
         <v>45705.72106481482</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -64006,7 +64006,7 @@
         <v>44385</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -64063,7 +64063,7 @@
         <v>45827.42467592593</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -64125,7 +64125,7 @@
         <v>45827</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -64182,7 +64182,7 @@
         <v>45869.61858796296</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -64239,7 +64239,7 @@
         <v>45869.62335648148</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -64296,7 +64296,7 @@
         <v>45827.41753472222</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -64358,7 +64358,7 @@
         <v>44757.37524305555</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -64415,7 +64415,7 @@
         <v>45764.44825231482</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -64477,7 +64477,7 @@
         <v>45485</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -64539,7 +64539,7 @@
         <v>45485</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -64601,7 +64601,7 @@
         <v>44180</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -64658,7 +64658,7 @@
         <v>45869.61069444445</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -64715,7 +64715,7 @@
         <v>44435</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -64777,7 +64777,7 @@
         <v>44925</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -64834,7 +64834,7 @@
         <v>45873.59511574074</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -64896,7 +64896,7 @@
         <v>45832.64047453704</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -64953,7 +64953,7 @@
         <v>45496.67342592592</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -65015,7 +65015,7 @@
         <v>45831</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -65077,7 +65077,7 @@
         <v>45572.60001157408</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -65134,7 +65134,7 @@
         <v>45509</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -65196,7 +65196,7 @@
         <v>44958</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -65258,7 +65258,7 @@
         <v>45737.3787962963</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -65315,7 +65315,7 @@
         <v>45743.38449074074</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -65372,7 +65372,7 @@
         <v>45688.67932870371</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -65434,7 +65434,7 @@
         <v>45832</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -65496,7 +65496,7 @@
         <v>45874.64513888889</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -65553,7 +65553,7 @@
         <v>45832</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -65615,7 +65615,7 @@
         <v>45832.3859837963</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -65677,7 +65677,7 @@
         <v>45775.36587962963</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -65734,7 +65734,7 @@
         <v>45775.36589120371</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -65791,7 +65791,7 @@
         <v>45832</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -65853,7 +65853,7 @@
         <v>45874.64199074074</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -65910,7 +65910,7 @@
         <v>44483</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -65967,7 +65967,7 @@
         <v>45664.56502314815</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -66024,7 +66024,7 @@
         <v>45834.51079861111</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -66086,7 +66086,7 @@
         <v>45876.39362268519</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -66148,7 +66148,7 @@
         <v>45484.48854166667</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -66210,7 +66210,7 @@
         <v>45834.38173611111</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -66267,7 +66267,7 @@
         <v>45488</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -66324,7 +66324,7 @@
         <v>45875.5196875</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -66381,7 +66381,7 @@
         <v>45834.69577546296</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -66438,7 +66438,7 @@
         <v>45834.71440972222</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -66495,7 +66495,7 @@
         <v>44858</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -66552,7 +66552,7 @@
         <v>45288.58685185185</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -66609,7 +66609,7 @@
         <v>45834</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -66671,7 +66671,7 @@
         <v>45833</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -66733,7 +66733,7 @@
         <v>45876.50833333333</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -66795,7 +66795,7 @@
         <v>45833.36467592593</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -66857,7 +66857,7 @@
         <v>45833.6081712963</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -66919,7 +66919,7 @@
         <v>45833</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -66981,7 +66981,7 @@
         <v>45547.59543981482</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -67038,7 +67038,7 @@
         <v>45875.47854166666</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -67100,7 +67100,7 @@
         <v>45833</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -67162,7 +67162,7 @@
         <v>45509.5980787037</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -67224,7 +67224,7 @@
         <v>45834.6568287037</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -67281,7 +67281,7 @@
         <v>45834</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -67338,7 +67338,7 @@
         <v>45834</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -67400,7 +67400,7 @@
         <v>45834.7087962963</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -67457,7 +67457,7 @@
         <v>45876.51233796297</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -67519,7 +67519,7 @@
         <v>45876.49113425926</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -67576,7 +67576,7 @@
         <v>44381</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -67633,7 +67633,7 @@
         <v>45768.30814814815</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -67695,7 +67695,7 @@
         <v>45656.51157407407</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -67757,7 +67757,7 @@
         <v>44964</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -67814,7 +67814,7 @@
         <v>44925.59333333333</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -67876,7 +67876,7 @@
         <v>45385</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -67933,7 +67933,7 @@
         <v>44216</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -67995,7 +67995,7 @@
         <v>44151</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -68052,7 +68052,7 @@
         <v>44169</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -68109,7 +68109,7 @@
         <v>44126</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -68166,7 +68166,7 @@
         <v>44985.61403935185</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -68228,7 +68228,7 @@
         <v>45433</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -68285,7 +68285,7 @@
         <v>45166.34795138889</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -68342,7 +68342,7 @@
         <v>44928</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -68404,7 +68404,7 @@
         <v>45432</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -68466,7 +68466,7 @@
         <v>44987.35637731481</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -68528,7 +68528,7 @@
         <v>44987</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -68590,7 +68590,7 @@
         <v>45670.4570949074</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -68652,7 +68652,7 @@
         <v>45477.62255787037</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -68714,7 +68714,7 @@
         <v>45624.63614583333</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -68776,7 +68776,7 @@
         <v>45041</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -68833,7 +68833,7 @@
         <v>45041</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -68890,7 +68890,7 @@
         <v>44550.39550925926</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -68947,7 +68947,7 @@
         <v>45791</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -69004,7 +69004,7 @@
         <v>44722</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -69061,7 +69061,7 @@
         <v>45154</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -69118,7 +69118,7 @@
         <v>45496.67178240741</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -69180,7 +69180,7 @@
         <v>45282.64012731481</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -69242,7 +69242,7 @@
         <v>45673.65925925926</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -69304,7 +69304,7 @@
         <v>45420.44414351852</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -69366,7 +69366,7 @@
         <v>45677.43028935185</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -69423,7 +69423,7 @@
         <v>44460.44315972222</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -69485,7 +69485,7 @@
         <v>45239.43173611111</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -69547,7 +69547,7 @@
         <v>45624.36090277778</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -69604,7 +69604,7 @@
         <v>45020</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -69661,7 +69661,7 @@
         <v>44872</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -69718,7 +69718,7 @@
         <v>45075.59358796296</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -69780,7 +69780,7 @@
         <v>45685.52405092592</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -69842,7 +69842,7 @@
         <v>45685.5349074074</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -69904,7 +69904,7 @@
         <v>45672.61748842592</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -69961,7 +69961,7 @@
         <v>45390</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -70018,7 +70018,7 @@
         <v>45735.60342592592</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -70075,7 +70075,7 @@
         <v>45719.45277777778</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -70132,7 +70132,7 @@
         <v>45763.4178587963</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -70189,7 +70189,7 @@
         <v>45351</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -70246,7 +70246,7 @@
         <v>45575</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -70303,7 +70303,7 @@
         <v>45616.49530092593</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>

--- a/Översikt HÄRJEDALEN.xlsx
+++ b/Översikt HÄRJEDALEN.xlsx
@@ -567,7 +567,7 @@
         <v>45513</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         <v>45763</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>44785</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>44790</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>44553</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>44837</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>44844</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>44749</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>45691</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>44406</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>44182</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>44154.40430555555</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>45531</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>44831</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>45761.58262731481</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>44496.94013888889</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>44865.57574074074</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
         <v>45667</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>44650</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2727,7 +2727,7 @@
         <v>45250</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>45351</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>45180</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3043,7 +3043,7 @@
         <v>44200</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>45631</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>45554</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>44690</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
         <v>44501</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
         <v>44193</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         <v>44182</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>45544.35653935185</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>44487</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
         <v>45631</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>45625.49736111111</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4211,7 +4211,7 @@
         <v>44440</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         <v>44406</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         <v>45544</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4506,7 +4506,7 @@
         <v>45106</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         <v>45837</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>45217</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>45571</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         <v>44774</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>44357</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         <v>45198</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
         <v>45544</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5315,7 +5315,7 @@
         <v>45457.38396990741</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         <v>45175</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5527,7 +5527,7 @@
         <v>45411</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         <v>45531</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         <v>45694</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5821,7 +5821,7 @@
         <v>45477.46537037037</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>45833.43898148148</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>44553</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>45471.59034722222</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
         <v>44406</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
         <v>45614.45413194445</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6430,7 +6430,7 @@
         <v>44517</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6523,7 +6523,7 @@
         <v>44553</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6620,7 +6620,7 @@
         <v>44377</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
         <v>45426</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6808,7 +6808,7 @@
         <v>45677.45212962963</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         <v>45741.82913194445</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         <v>44430</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7092,7 +7092,7 @@
         <v>44553</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         <v>45007</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7288,7 +7288,7 @@
         <v>45715</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         <v>45531.45444444445</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7483,7 +7483,7 @@
         <v>44242</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7573,7 +7573,7 @@
         <v>45772.51116898148</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7668,7 +7668,7 @@
         <v>45616.6450462963</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7766,7 +7766,7 @@
         <v>45568</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7861,7 +7861,7 @@
         <v>45719</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         <v>45869.60545138889</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         <v>45559</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8148,7 +8148,7 @@
         <v>45574</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8242,7 +8242,7 @@
         <v>45625.45384259259</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8340,7 +8340,7 @@
         <v>45432.94736111111</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8438,7 +8438,7 @@
         <v>45243</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8531,7 +8531,7 @@
         <v>44517</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8620,7 +8620,7 @@
         <v>44882</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8713,7 +8713,7 @@
         <v>44979</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8802,7 +8802,7 @@
         <v>44430</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8903,7 +8903,7 @@
         <v>44294</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8991,7 +8991,7 @@
         <v>44294</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         <v>45694</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9167,7 +9167,7 @@
         <v>44476</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9259,7 +9259,7 @@
         <v>45467.47204861111</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9352,7 +9352,7 @@
         <v>45559.38894675926</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         <v>45537.45818287037</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9546,7 +9546,7 @@
         <v>44957</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9638,7 +9638,7 @@
         <v>45838.73927083334</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9731,7 +9731,7 @@
         <v>44977</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9828,7 +9828,7 @@
         <v>45552</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9916,7 +9916,7 @@
         <v>45007</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10009,7 +10009,7 @@
         <v>45531.45752314815</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10097,7 +10097,7 @@
         <v>45085</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10189,7 +10189,7 @@
         <v>45506.35658564815</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10281,7 +10281,7 @@
         <v>44377</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10373,7 +10373,7 @@
         <v>44475</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10460,7 +10460,7 @@
         <v>44441</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10547,7 +10547,7 @@
         <v>44475</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>44475</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10721,7 +10721,7 @@
         <v>44713</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10821,7 +10821,7 @@
         <v>45791</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10908,7 +10908,7 @@
         <v>45800.3484375</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11000,7 +11000,7 @@
         <v>45468</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11087,7 +11087,7 @@
         <v>44074</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11183,7 +11183,7 @@
         <v>45617</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11279,7 +11279,7 @@
         <v>45849.35011574074</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11366,7 +11366,7 @@
         <v>44107</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11462,7 +11462,7 @@
         <v>45821.56523148148</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
         <v>45841.41003472222</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11641,7 +11641,7 @@
         <v>44180</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11733,7 +11733,7 @@
         <v>44186</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11824,7 +11824,7 @@
         <v>44677</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11915,7 +11915,7 @@
         <v>44286</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12001,7 +12001,7 @@
         <v>45772.51070601852</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12092,7 +12092,7 @@
         <v>45538</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12183,7 +12183,7 @@
         <v>45035</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12278,7 +12278,7 @@
         <v>44475</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12364,7 +12364,7 @@
         <v>45786.6590625</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12455,7 +12455,7 @@
         <v>45786.66594907407</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12546,7 +12546,7 @@
         <v>45786.65452546296</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12637,7 +12637,7 @@
         <v>45786.6768287037</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12728,7 +12728,7 @@
         <v>45786.67261574074</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12819,7 +12819,7 @@
         <v>44987</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12914,7 +12914,7 @@
         <v>45786.67016203704</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13005,7 +13005,7 @@
         <v>45644.56555555556</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13100,7 +13100,7 @@
         <v>45805.73822916667</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13191,7 +13191,7 @@
         <v>45833</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13277,7 +13277,7 @@
         <v>45191</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13368,7 +13368,7 @@
         <v>45772.36488425926</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13463,7 +13463,7 @@
         <v>45552</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13553,7 +13553,7 @@
         <v>45880.37559027778</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13639,7 +13639,7 @@
         <v>44853</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13729,7 +13729,7 @@
         <v>44475</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13815,7 +13815,7 @@
         <v>44221</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -13901,7 +13901,7 @@
         <v>45621</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -13996,7 +13996,7 @@
         <v>45694</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14082,7 +14082,7 @@
         <v>45153</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14172,7 +14172,7 @@
         <v>44449</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14258,7 +14258,7 @@
         <v>44866.46503472222</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14353,7 +14353,7 @@
         <v>44955</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14443,7 +14443,7 @@
         <v>45595.58056712963</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14534,7 +14534,7 @@
         <v>44096</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14624,7 +14624,7 @@
         <v>44475</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14709,7 +14709,7 @@
         <v>44475</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -14794,7 +14794,7 @@
         <v>44321</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -14884,7 +14884,7 @@
         <v>44475</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -14969,7 +14969,7 @@
         <v>44105</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15054,7 +15054,7 @@
         <v>44113</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15139,7 +15139,7 @@
         <v>44769.48783564815</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15229,7 +15229,7 @@
         <v>45729.64623842593</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15319,7 +15319,7 @@
         <v>45345</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15409,7 +15409,7 @@
         <v>45457.38677083333</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -15499,7 +15499,7 @@
         <v>45621.47555555555</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -15589,7 +15589,7 @@
         <v>45714.55248842593</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -15683,7 +15683,7 @@
         <v>45800.63043981481</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -15777,7 +15777,7 @@
         <v>45603</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -15867,7 +15867,7 @@
         <v>45805.66601851852</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -15961,7 +15961,7 @@
         <v>45111</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16051,7 +16051,7 @@
         <v>45805.73546296296</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16141,7 +16141,7 @@
         <v>45320</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -16226,7 +16226,7 @@
         <v>45638.33607638889</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -16316,7 +16316,7 @@
         <v>45617</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -16410,7 +16410,7 @@
         <v>45454.62443287037</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -16495,7 +16495,7 @@
         <v>45812.82244212963</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         <v>45791</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -16670,7 +16670,7 @@
         <v>45538.57630787037</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -16759,7 +16759,7 @@
         <v>45869.61471064815</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -16844,7 +16844,7 @@
         <v>45875.46476851852</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -16933,7 +16933,7 @@
         <v>45835.7499537037</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17023,7 +17023,7 @@
         <v>44475</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17108,7 +17108,7 @@
         <v>45838.773125</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -17198,7 +17198,7 @@
         <v>45672.50416666667</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -17283,7 +17283,7 @@
         <v>45758.70164351852</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -17368,7 +17368,7 @@
         <v>45308</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -17457,7 +17457,7 @@
         <v>45540.69512731482</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -17547,7 +17547,7 @@
         <v>44320</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -17604,7 +17604,7 @@
         <v>44316</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -17661,7 +17661,7 @@
         <v>44320</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -17723,7 +17723,7 @@
         <v>44105</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -17780,7 +17780,7 @@
         <v>44810</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -17842,7 +17842,7 @@
         <v>44727.70908564814</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -17904,7 +17904,7 @@
         <v>44430</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -17966,7 +17966,7 @@
         <v>44543</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -18023,7 +18023,7 @@
         <v>44614</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -18085,7 +18085,7 @@
         <v>44404</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -18142,7 +18142,7 @@
         <v>44417.38271990741</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -18199,7 +18199,7 @@
         <v>44417.38614583333</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -18256,7 +18256,7 @@
         <v>44497</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -18313,7 +18313,7 @@
         <v>44475</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -18370,7 +18370,7 @@
         <v>44531</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -18427,7 +18427,7 @@
         <v>44361</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -18484,7 +18484,7 @@
         <v>44600</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -18541,7 +18541,7 @@
         <v>44540</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -18603,7 +18603,7 @@
         <v>44475</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -18660,7 +18660,7 @@
         <v>44385.93652777778</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -18722,7 +18722,7 @@
         <v>44475</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -18779,7 +18779,7 @@
         <v>44538</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -18841,7 +18841,7 @@
         <v>44406</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -18898,7 +18898,7 @@
         <v>44854</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -18955,7 +18955,7 @@
         <v>44102</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -19012,7 +19012,7 @@
         <v>44823</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -19074,7 +19074,7 @@
         <v>44424</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -19131,7 +19131,7 @@
         <v>44316</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -19188,7 +19188,7 @@
         <v>44483</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -19245,7 +19245,7 @@
         <v>44421</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -19302,7 +19302,7 @@
         <v>44418</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -19364,7 +19364,7 @@
         <v>44488</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -19426,7 +19426,7 @@
         <v>44603</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -19488,7 +19488,7 @@
         <v>44132</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -19545,7 +19545,7 @@
         <v>44179</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -19602,7 +19602,7 @@
         <v>44418</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -19664,7 +19664,7 @@
         <v>44564.6747337963</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -19726,7 +19726,7 @@
         <v>44361</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -19788,7 +19788,7 @@
         <v>44615</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -19850,7 +19850,7 @@
         <v>44466.81701388889</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -19907,7 +19907,7 @@
         <v>44218</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -19964,7 +19964,7 @@
         <v>44475</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -20021,7 +20021,7 @@
         <v>44475</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -20078,7 +20078,7 @@
         <v>44410.74284722222</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -20135,7 +20135,7 @@
         <v>44631</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -20197,7 +20197,7 @@
         <v>44286</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -20254,7 +20254,7 @@
         <v>44631.41535879629</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -20316,7 +20316,7 @@
         <v>44810</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -20378,7 +20378,7 @@
         <v>44728</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -20435,7 +20435,7 @@
         <v>44417.37519675926</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -20492,7 +20492,7 @@
         <v>44344</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -20549,7 +20549,7 @@
         <v>44174</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -20606,7 +20606,7 @@
         <v>44084</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -20668,7 +20668,7 @@
         <v>44475</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -20725,7 +20725,7 @@
         <v>44078</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -20782,7 +20782,7 @@
         <v>44424</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -20839,7 +20839,7 @@
         <v>44424</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -20896,7 +20896,7 @@
         <v>44258</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -20953,7 +20953,7 @@
         <v>44818</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -21010,7 +21010,7 @@
         <v>44690</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -21067,7 +21067,7 @@
         <v>44770.53315972222</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -21124,7 +21124,7 @@
         <v>44285</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -21181,7 +21181,7 @@
         <v>44286</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -21238,7 +21238,7 @@
         <v>44792.68023148148</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -21295,7 +21295,7 @@
         <v>44385.93658564815</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -21357,7 +21357,7 @@
         <v>44243.63096064814</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -21414,7 +21414,7 @@
         <v>44298</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -21471,7 +21471,7 @@
         <v>44183</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -21528,7 +21528,7 @@
         <v>44319</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -21585,7 +21585,7 @@
         <v>44316</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -21642,7 +21642,7 @@
         <v>44316</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -21699,7 +21699,7 @@
         <v>44126</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -21756,7 +21756,7 @@
         <v>44825</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -21813,7 +21813,7 @@
         <v>44174</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -21870,7 +21870,7 @@
         <v>44154</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -21932,7 +21932,7 @@
         <v>44396</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -21989,7 +21989,7 @@
         <v>44475</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -22046,7 +22046,7 @@
         <v>44127</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -22108,7 +22108,7 @@
         <v>44475</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -22165,7 +22165,7 @@
         <v>44475</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -22222,7 +22222,7 @@
         <v>44475</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -22279,7 +22279,7 @@
         <v>44475</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -22336,7 +22336,7 @@
         <v>44544</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -22398,7 +22398,7 @@
         <v>44420.33096064815</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -22455,7 +22455,7 @@
         <v>44188</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -22517,7 +22517,7 @@
         <v>44483.36435185185</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -22574,7 +22574,7 @@
         <v>44417</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -22631,7 +22631,7 @@
         <v>44181</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -22693,7 +22693,7 @@
         <v>44426.45706018519</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -22750,7 +22750,7 @@
         <v>44859</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -22812,7 +22812,7 @@
         <v>44473</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -22869,7 +22869,7 @@
         <v>44335.4837962963</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -22926,7 +22926,7 @@
         <v>44314</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -22983,7 +22983,7 @@
         <v>44475</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -23040,7 +23040,7 @@
         <v>44543</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -23102,7 +23102,7 @@
         <v>44475</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -23159,7 +23159,7 @@
         <v>44475</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -23216,7 +23216,7 @@
         <v>44725</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -23278,7 +23278,7 @@
         <v>44481.67951388889</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -23335,7 +23335,7 @@
         <v>44631.45398148148</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -23397,7 +23397,7 @@
         <v>44631.37421296296</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -23459,7 +23459,7 @@
         <v>44855.60383101852</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -23516,7 +23516,7 @@
         <v>44133</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -23578,7 +23578,7 @@
         <v>44417.37207175926</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -23635,7 +23635,7 @@
         <v>44538</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -23697,7 +23697,7 @@
         <v>44230</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -23754,7 +23754,7 @@
         <v>44768.44859953703</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -23811,7 +23811,7 @@
         <v>44475</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -23868,7 +23868,7 @@
         <v>44475</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -23925,7 +23925,7 @@
         <v>44475</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -23982,7 +23982,7 @@
         <v>44475</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -24039,7 +24039,7 @@
         <v>44368</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -24096,7 +24096,7 @@
         <v>44403</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -24153,7 +24153,7 @@
         <v>44886.62578703704</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -24210,7 +24210,7 @@
         <v>44886.629375</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -24267,7 +24267,7 @@
         <v>44838</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -24329,7 +24329,7 @@
         <v>44126</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -24391,7 +24391,7 @@
         <v>44540.56034722222</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -24448,7 +24448,7 @@
         <v>44872</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -24510,7 +24510,7 @@
         <v>44742</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -24572,7 +24572,7 @@
         <v>44708.46081018518</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -24634,7 +24634,7 @@
         <v>44166</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -24696,7 +24696,7 @@
         <v>44684</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -24758,7 +24758,7 @@
         <v>44531</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -24815,7 +24815,7 @@
         <v>44169</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -24872,7 +24872,7 @@
         <v>44188</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -24929,7 +24929,7 @@
         <v>44060</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -25006,7 +25006,7 @@
         <v>44180</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -25063,7 +25063,7 @@
         <v>44531</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -25120,7 +25120,7 @@
         <v>44531</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -25177,7 +25177,7 @@
         <v>44207</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -25239,7 +25239,7 @@
         <v>44530.40607638889</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -25296,7 +25296,7 @@
         <v>44413</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -25353,7 +25353,7 @@
         <v>44270</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -25410,7 +25410,7 @@
         <v>44706.66417824074</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -25472,7 +25472,7 @@
         <v>44788.67976851852</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -25534,7 +25534,7 @@
         <v>44475</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -25591,7 +25591,7 @@
         <v>44316</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -25648,7 +25648,7 @@
         <v>44803</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -25705,7 +25705,7 @@
         <v>44316</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -25762,7 +25762,7 @@
         <v>44389</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -25824,7 +25824,7 @@
         <v>44285</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -25881,7 +25881,7 @@
         <v>44377</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -25938,7 +25938,7 @@
         <v>44627.36047453704</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -26000,7 +26000,7 @@
         <v>44825</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -26057,7 +26057,7 @@
         <v>44727.71858796296</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -26119,7 +26119,7 @@
         <v>45471.66556712963</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -26181,7 +26181,7 @@
         <v>45705.32643518518</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -26238,7 +26238,7 @@
         <v>45684.51006944444</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -26295,7 +26295,7 @@
         <v>45280</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -26352,7 +26352,7 @@
         <v>45406</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -26414,7 +26414,7 @@
         <v>45406</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -26476,7 +26476,7 @@
         <v>44823.84673611111</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -26533,7 +26533,7 @@
         <v>45579.57390046296</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -26595,7 +26595,7 @@
         <v>44643.81518518519</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -26652,7 +26652,7 @@
         <v>44361</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -26709,7 +26709,7 @@
         <v>45342</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -26766,7 +26766,7 @@
         <v>44999.60127314815</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -26823,7 +26823,7 @@
         <v>45688.67935185185</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -26885,7 +26885,7 @@
         <v>45772.46965277778</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -26947,7 +26947,7 @@
         <v>45772.46988425926</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -27009,7 +27009,7 @@
         <v>45688.67145833333</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -27071,7 +27071,7 @@
         <v>44312</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -27128,7 +27128,7 @@
         <v>44216</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -27190,7 +27190,7 @@
         <v>45741.45597222223</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -27247,7 +27247,7 @@
         <v>45119.39105324074</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -27309,7 +27309,7 @@
         <v>44300</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -27366,7 +27366,7 @@
         <v>45085</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -27423,7 +27423,7 @@
         <v>45604.32543981481</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -27485,7 +27485,7 @@
         <v>45672.44825231482</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -27542,7 +27542,7 @@
         <v>45603</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -27604,7 +27604,7 @@
         <v>45106</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -27666,7 +27666,7 @@
         <v>45740.44842592593</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -27728,7 +27728,7 @@
         <v>45071.92488425926</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -27785,7 +27785,7 @@
         <v>45733.38637731481</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -27842,7 +27842,7 @@
         <v>45509</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -27904,7 +27904,7 @@
         <v>45729.65261574074</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -27966,7 +27966,7 @@
         <v>44862</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -28028,7 +28028,7 @@
         <v>45687.65449074074</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -28090,7 +28090,7 @@
         <v>45243.63798611111</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -28147,7 +28147,7 @@
         <v>45772.36106481482</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -28209,7 +28209,7 @@
         <v>45575</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -28266,7 +28266,7 @@
         <v>45429</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -28323,7 +28323,7 @@
         <v>45484.66521990741</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -28385,7 +28385,7 @@
         <v>45460.47969907407</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -28442,7 +28442,7 @@
         <v>45407.36894675926</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -28504,7 +28504,7 @@
         <v>45345.66555555556</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -28566,7 +28566,7 @@
         <v>44472</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -28623,7 +28623,7 @@
         <v>45254</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -28680,7 +28680,7 @@
         <v>45345.35003472222</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -28742,7 +28742,7 @@
         <v>45776.69569444445</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -28799,7 +28799,7 @@
         <v>45362.64613425926</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -28856,7 +28856,7 @@
         <v>45362.65407407407</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -28913,7 +28913,7 @@
         <v>45362.67789351852</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -28970,7 +28970,7 @@
         <v>44414.58354166667</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -29027,7 +29027,7 @@
         <v>44167</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -29084,7 +29084,7 @@
         <v>45776.43898148148</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -29141,7 +29141,7 @@
         <v>45537.60471064815</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -29203,7 +29203,7 @@
         <v>45779.48611111111</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -29265,7 +29265,7 @@
         <v>45768.29630787037</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -29327,7 +29327,7 @@
         <v>45768.30954861111</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -29389,7 +29389,7 @@
         <v>45779.38211805555</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -29451,7 +29451,7 @@
         <v>45779.47704861111</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -29513,7 +29513,7 @@
         <v>45779.50052083333</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -29575,7 +29575,7 @@
         <v>45779.41844907407</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -29637,7 +29637,7 @@
         <v>45737</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -29694,7 +29694,7 @@
         <v>45782.41581018519</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -29751,7 +29751,7 @@
         <v>45779.50886574074</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -29813,7 +29813,7 @@
         <v>45779.51943287037</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -29875,7 +29875,7 @@
         <v>45779.52488425926</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -29937,7 +29937,7 @@
         <v>45782.42744212963</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -29994,7 +29994,7 @@
         <v>45779.51357638889</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -30056,7 +30056,7 @@
         <v>45275</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -30113,7 +30113,7 @@
         <v>45568</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -30175,7 +30175,7 @@
         <v>44925</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -30232,7 +30232,7 @@
         <v>45784.59012731481</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -30294,7 +30294,7 @@
         <v>45618.35961805555</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -30351,7 +30351,7 @@
         <v>44732</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -30408,7 +30408,7 @@
         <v>45783.68547453704</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -30470,7 +30470,7 @@
         <v>45560.33311342593</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -30532,7 +30532,7 @@
         <v>45632.64078703704</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -30589,7 +30589,7 @@
         <v>45540.4264699074</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -30651,7 +30651,7 @@
         <v>45483.47572916667</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -30708,7 +30708,7 @@
         <v>44312</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -30765,7 +30765,7 @@
         <v>45642</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -30822,7 +30822,7 @@
         <v>45569.6909837963</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -30879,7 +30879,7 @@
         <v>45610.56706018518</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -30941,7 +30941,7 @@
         <v>44985</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -31003,7 +31003,7 @@
         <v>45786.66032407407</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -31065,7 +31065,7 @@
         <v>45786.66853009259</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -31127,7 +31127,7 @@
         <v>45453.6619212963</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -31184,7 +31184,7 @@
         <v>45786.66209490741</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -31246,7 +31246,7 @@
         <v>45670.34313657408</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -31303,7 +31303,7 @@
         <v>45252.45481481482</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -31360,7 +31360,7 @@
         <v>45786.66425925926</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -31422,7 +31422,7 @@
         <v>45387</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -31479,7 +31479,7 @@
         <v>45457.92854166667</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -31536,7 +31536,7 @@
         <v>45582.59753472222</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -31598,7 +31598,7 @@
         <v>45785.34165509259</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -31655,7 +31655,7 @@
         <v>45785.33164351852</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -31712,7 +31712,7 @@
         <v>45790.43</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -31774,7 +31774,7 @@
         <v>45177.9224537037</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -31831,7 +31831,7 @@
         <v>45632</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -31888,7 +31888,7 @@
         <v>45624.36858796296</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -31945,7 +31945,7 @@
         <v>45484.57285879629</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -32007,7 +32007,7 @@
         <v>45638.416875</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -32069,7 +32069,7 @@
         <v>45607</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -32131,7 +32131,7 @@
         <v>44987.35282407407</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -32193,7 +32193,7 @@
         <v>45772.69290509259</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -32255,7 +32255,7 @@
         <v>45485</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -32312,7 +32312,7 @@
         <v>45041</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -32369,7 +32369,7 @@
         <v>45792.64795138889</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -32426,7 +32426,7 @@
         <v>45173</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -32483,7 +32483,7 @@
         <v>45790.87653935186</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -32540,7 +32540,7 @@
         <v>44153</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -32597,7 +32597,7 @@
         <v>45170.4643287037</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -32659,7 +32659,7 @@
         <v>45792.65047453704</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -32716,7 +32716,7 @@
         <v>45517.39274305556</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -32778,7 +32778,7 @@
         <v>45792.50942129629</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -32840,7 +32840,7 @@
         <v>45637</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -32897,7 +32897,7 @@
         <v>44424</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -32954,7 +32954,7 @@
         <v>45481.3330787037</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -33016,7 +33016,7 @@
         <v>45618.35097222222</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -33073,7 +33073,7 @@
         <v>45559</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -33130,7 +33130,7 @@
         <v>44082</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -33192,7 +33192,7 @@
         <v>45506.36702546296</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -33249,7 +33249,7 @@
         <v>45509</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -33311,7 +33311,7 @@
         <v>45509.6427662037</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -33373,7 +33373,7 @@
         <v>45796.39770833333</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -33430,7 +33430,7 @@
         <v>45763.41402777778</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -33487,7 +33487,7 @@
         <v>45793.41994212963</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -33549,7 +33549,7 @@
         <v>45632.64769675926</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -33606,7 +33606,7 @@
         <v>45483.47207175926</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -33663,7 +33663,7 @@
         <v>45593.67809027778</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -33720,7 +33720,7 @@
         <v>44628.36402777778</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -33777,7 +33777,7 @@
         <v>45796.57802083333</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -33834,7 +33834,7 @@
         <v>45453.6672800926</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -33891,7 +33891,7 @@
         <v>45644.50141203704</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -33953,7 +33953,7 @@
         <v>45345.47642361111</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -34015,7 +34015,7 @@
         <v>45345.48181712963</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -34077,7 +34077,7 @@
         <v>45345.4940625</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -34139,7 +34139,7 @@
         <v>45631</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -34201,7 +34201,7 @@
         <v>45665.563125</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -34263,7 +34263,7 @@
         <v>45621</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -34325,7 +34325,7 @@
         <v>45674.57393518519</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -34382,7 +34382,7 @@
         <v>45362.67293981482</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -34439,7 +34439,7 @@
         <v>45569</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -34501,7 +34501,7 @@
         <v>45614.47960648148</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -34558,7 +34558,7 @@
         <v>44075</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -34615,7 +34615,7 @@
         <v>44305</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -34672,7 +34672,7 @@
         <v>45631</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -34734,7 +34734,7 @@
         <v>45791</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -34791,7 +34791,7 @@
         <v>45797.37096064815</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -34848,7 +34848,7 @@
         <v>45800.58859953703</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -34905,7 +34905,7 @@
         <v>45800.59567129629</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -34967,7 +34967,7 @@
         <v>45800.64719907408</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -35029,7 +35029,7 @@
         <v>45800.56313657408</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -35086,7 +35086,7 @@
         <v>45800.57837962963</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -35148,7 +35148,7 @@
         <v>45830</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -35205,7 +35205,7 @@
         <v>45800.48060185185</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -35267,7 +35267,7 @@
         <v>45517.38320601852</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -35324,7 +35324,7 @@
         <v>45799.64804398148</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -35386,7 +35386,7 @@
         <v>45345</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -35448,7 +35448,7 @@
         <v>45837</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -35505,7 +35505,7 @@
         <v>45800.3787037037</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -35567,7 +35567,7 @@
         <v>45834</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -35624,7 +35624,7 @@
         <v>45800.44868055556</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -35686,7 +35686,7 @@
         <v>45800.4687962963</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -35748,7 +35748,7 @@
         <v>45800.50431712963</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -35810,7 +35810,7 @@
         <v>45800.56222222222</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -35872,7 +35872,7 @@
         <v>45799.57883101852</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -35929,7 +35929,7 @@
         <v>45799.45770833334</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -35991,7 +35991,7 @@
         <v>45830</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -36048,7 +36048,7 @@
         <v>45830</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -36105,7 +36105,7 @@
         <v>45800.65341435185</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -36167,7 +36167,7 @@
         <v>45799.47225694444</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -36229,7 +36229,7 @@
         <v>45800.33436342593</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -36291,7 +36291,7 @@
         <v>45800.3425</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -36353,7 +36353,7 @@
         <v>45799.43550925926</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -36415,7 +36415,7 @@
         <v>45800.46069444445</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -36477,7 +36477,7 @@
         <v>45800.48515046296</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -36539,7 +36539,7 @@
         <v>45800.56995370371</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -36601,7 +36601,7 @@
         <v>45800.37524305555</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -36663,7 +36663,7 @@
         <v>45800.42797453704</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -36720,7 +36720,7 @@
         <v>45800.44090277778</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -36777,7 +36777,7 @@
         <v>45800.64065972222</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -36839,7 +36839,7 @@
         <v>45237.5815162037</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -36896,7 +36896,7 @@
         <v>45800.63738425926</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -36958,7 +36958,7 @@
         <v>45830</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -37015,7 +37015,7 @@
         <v>45800.60508101852</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -37077,7 +37077,7 @@
         <v>45644.56674768519</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -37139,7 +37139,7 @@
         <v>45800.66043981481</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -37201,7 +37201,7 @@
         <v>45799.4658912037</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -37263,7 +37263,7 @@
         <v>45799.46642361111</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -37320,7 +37320,7 @@
         <v>45800.3503587963</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -37382,7 +37382,7 @@
         <v>45800.35670138889</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -37444,7 +37444,7 @@
         <v>45800.41883101852</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -37506,7 +37506,7 @@
         <v>45635.35274305556</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -37568,7 +37568,7 @@
         <v>45799.43086805556</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -37630,7 +37630,7 @@
         <v>45485.42287037037</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -37687,7 +37687,7 @@
         <v>45485</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -37744,7 +37744,7 @@
         <v>45485.44258101852</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -37806,7 +37806,7 @@
         <v>45804.5813425926</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -37868,7 +37868,7 @@
         <v>45159.60288194445</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -37925,7 +37925,7 @@
         <v>45603</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -37987,7 +37987,7 @@
         <v>45803.37258101852</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -38044,7 +38044,7 @@
         <v>45845.60496527778</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -38101,7 +38101,7 @@
         <v>45622</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -38163,7 +38163,7 @@
         <v>45845.6920949074</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -38225,7 +38225,7 @@
         <v>45225.58005787037</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -38282,7 +38282,7 @@
         <v>45845.55266203704</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -38339,7 +38339,7 @@
         <v>45408</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -38396,7 +38396,7 @@
         <v>45646</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -38453,7 +38453,7 @@
         <v>45804.589375</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -38510,7 +38510,7 @@
         <v>45845.55259259259</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -38567,7 +38567,7 @@
         <v>45845.55270833334</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -38624,7 +38624,7 @@
         <v>45803.37480324074</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -38681,7 +38681,7 @@
         <v>45685</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -38743,7 +38743,7 @@
         <v>45848.45113425926</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -38805,7 +38805,7 @@
         <v>44153</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -38867,7 +38867,7 @@
         <v>45848.57644675926</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -38929,7 +38929,7 @@
         <v>45569</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -38991,7 +38991,7 @@
         <v>45350</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -39048,7 +39048,7 @@
         <v>45351</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -39105,7 +39105,7 @@
         <v>45848.65003472222</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -39162,7 +39162,7 @@
         <v>45345.34219907408</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -39224,7 +39224,7 @@
         <v>45568</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -39286,7 +39286,7 @@
         <v>44082</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -39348,7 +39348,7 @@
         <v>45730</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -39405,7 +39405,7 @@
         <v>45170.46134259259</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -39467,7 +39467,7 @@
         <v>45737.37006944444</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -39524,7 +39524,7 @@
         <v>45805.53280092592</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -39586,7 +39586,7 @@
         <v>45730</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -39643,7 +39643,7 @@
         <v>45848.68640046296</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -39705,7 +39705,7 @@
         <v>45260.35777777778</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -39762,7 +39762,7 @@
         <v>45848.6568287037</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -39819,7 +39819,7 @@
         <v>45569</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -39881,7 +39881,7 @@
         <v>45111</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -39938,7 +39938,7 @@
         <v>45848.62873842593</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -39995,7 +39995,7 @@
         <v>45568</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -40057,7 +40057,7 @@
         <v>45848.639375</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -40114,7 +40114,7 @@
         <v>45730</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -40171,7 +40171,7 @@
         <v>45768.29289351852</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -40233,7 +40233,7 @@
         <v>45768.30086805556</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -40295,7 +40295,7 @@
         <v>45119.38675925926</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -40357,7 +40357,7 @@
         <v>45848.35400462963</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -40414,7 +40414,7 @@
         <v>45847.58865740741</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -40476,7 +40476,7 @@
         <v>44925.64049768518</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -40538,7 +40538,7 @@
         <v>44638.44958333333</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -40595,7 +40595,7 @@
         <v>45569</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -40657,7 +40657,7 @@
         <v>45588.56039351852</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -40714,7 +40714,7 @@
         <v>45642.33616898148</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -40771,7 +40771,7 @@
         <v>45061.61002314815</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -40833,7 +40833,7 @@
         <v>44348</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -40890,7 +40890,7 @@
         <v>45257</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -40952,7 +40952,7 @@
         <v>45807.60333333333</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -41014,7 +41014,7 @@
         <v>45807.58868055556</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -41076,7 +41076,7 @@
         <v>45617</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -41138,7 +41138,7 @@
         <v>45807.59407407408</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -41200,7 +41200,7 @@
         <v>45807.41287037037</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -41262,7 +41262,7 @@
         <v>45807.42212962963</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -41324,7 +41324,7 @@
         <v>45807.45288194445</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -41386,7 +41386,7 @@
         <v>45807.49436342593</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -41448,7 +41448,7 @@
         <v>45279.57732638889</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -41505,7 +41505,7 @@
         <v>45807.49832175926</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -41567,7 +41567,7 @@
         <v>45807.58393518518</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -41629,7 +41629,7 @@
         <v>44883</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -41686,7 +41686,7 @@
         <v>45762.55899305556</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -41743,7 +41743,7 @@
         <v>45509</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -41805,7 +41805,7 @@
         <v>44091</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -41862,7 +41862,7 @@
         <v>44853.41693287037</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -41919,7 +41919,7 @@
         <v>45848</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -41981,7 +41981,7 @@
         <v>45807.36304398148</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -42043,7 +42043,7 @@
         <v>45807.41717592593</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -42105,7 +42105,7 @@
         <v>45807.43461805556</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -42167,7 +42167,7 @@
         <v>45807.44070601852</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -42229,7 +42229,7 @@
         <v>45807.44608796296</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -42291,7 +42291,7 @@
         <v>45807.63334490741</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -42353,7 +42353,7 @@
         <v>45807.47479166667</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -42415,7 +42415,7 @@
         <v>45807.49045138889</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -42477,7 +42477,7 @@
         <v>45231</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -42534,7 +42534,7 @@
         <v>45685.38901620371</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -42596,7 +42596,7 @@
         <v>45677.44273148148</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -42653,7 +42653,7 @@
         <v>45667</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -42715,7 +42715,7 @@
         <v>45439.62893518519</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -42772,7 +42772,7 @@
         <v>45195.61476851852</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -42829,7 +42829,7 @@
         <v>44957</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -42891,7 +42891,7 @@
         <v>45240</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -42948,7 +42948,7 @@
         <v>45215</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -43005,7 +43005,7 @@
         <v>44475</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -43062,7 +43062,7 @@
         <v>45196</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -43124,7 +43124,7 @@
         <v>45096.62344907408</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -43186,7 +43186,7 @@
         <v>44708.45504629629</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -43248,7 +43248,7 @@
         <v>44708</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -43310,7 +43310,7 @@
         <v>45118.47491898148</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -43372,7 +43372,7 @@
         <v>45852.48290509259</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -43429,7 +43429,7 @@
         <v>45807.65438657408</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -43491,7 +43491,7 @@
         <v>45807.3409837963</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -43553,7 +43553,7 @@
         <v>45807.35476851852</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -43615,7 +43615,7 @@
         <v>45807.55893518519</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -43677,7 +43677,7 @@
         <v>45467</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -43734,7 +43734,7 @@
         <v>45216</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -43791,7 +43791,7 @@
         <v>45807.5684375</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -43853,7 +43853,7 @@
         <v>45728.44329861111</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -43915,7 +43915,7 @@
         <v>45728.49267361111</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -43977,7 +43977,7 @@
         <v>45484</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -44039,7 +44039,7 @@
         <v>45505</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -44096,7 +44096,7 @@
         <v>45505</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -44158,7 +44158,7 @@
         <v>45645.47609953704</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -44220,7 +44220,7 @@
         <v>45645.48079861111</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -44282,7 +44282,7 @@
         <v>45617</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -44344,7 +44344,7 @@
         <v>44214</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -44406,7 +44406,7 @@
         <v>45205</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -44463,7 +44463,7 @@
         <v>45614.62445601852</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -44525,7 +44525,7 @@
         <v>45852</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -44582,7 +44582,7 @@
         <v>45506.36534722222</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -44639,7 +44639,7 @@
         <v>45478.48700231482</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -44701,7 +44701,7 @@
         <v>45491.5859375</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -44758,7 +44758,7 @@
         <v>44728</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -44820,7 +44820,7 @@
         <v>45807.56403935186</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -44882,7 +44882,7 @@
         <v>45334</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -44944,7 +44944,7 @@
         <v>45604.33195601852</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -45006,7 +45006,7 @@
         <v>45670.66085648148</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -45063,7 +45063,7 @@
         <v>45685</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -45120,7 +45120,7 @@
         <v>45854.44850694444</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -45182,7 +45182,7 @@
         <v>45854.44864583333</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -45244,7 +45244,7 @@
         <v>45853.61865740741</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -45301,7 +45301,7 @@
         <v>45280</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -45358,7 +45358,7 @@
         <v>45811.34540509259</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -45420,7 +45420,7 @@
         <v>45811.34564814815</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -45482,7 +45482,7 @@
         <v>45197.46966435185</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -45539,7 +45539,7 @@
         <v>45853.28325231482</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -45596,7 +45596,7 @@
         <v>45853.62415509259</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -45658,7 +45658,7 @@
         <v>45854.40662037037</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -45720,7 +45720,7 @@
         <v>45733</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -45777,7 +45777,7 @@
         <v>45635.33439814814</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -45839,7 +45839,7 @@
         <v>45811.34578703704</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -45901,7 +45901,7 @@
         <v>45174</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -45958,7 +45958,7 @@
         <v>44987.34981481481</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -46020,7 +46020,7 @@
         <v>45741.38347222222</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -46077,7 +46077,7 @@
         <v>45111</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -46139,7 +46139,7 @@
         <v>45813.64590277777</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -46196,7 +46196,7 @@
         <v>45485</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -46258,7 +46258,7 @@
         <v>45485</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -46320,7 +46320,7 @@
         <v>45485</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -46382,7 +46382,7 @@
         <v>45813.47074074074</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -46439,7 +46439,7 @@
         <v>45253.55737268519</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -46496,7 +46496,7 @@
         <v>44565.31975694445</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -46558,7 +46558,7 @@
         <v>44565</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -46620,7 +46620,7 @@
         <v>44316</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -46677,7 +46677,7 @@
         <v>45813.48734953703</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -46734,7 +46734,7 @@
         <v>45406.64024305555</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -46796,7 +46796,7 @@
         <v>45642.35256944445</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -46853,7 +46853,7 @@
         <v>45751.63266203704</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -46915,7 +46915,7 @@
         <v>44924.61315972222</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -46977,7 +46977,7 @@
         <v>45303</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -47034,7 +47034,7 @@
         <v>45238.64153935185</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -47091,7 +47091,7 @@
         <v>45265</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -47148,7 +47148,7 @@
         <v>45859</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -47205,7 +47205,7 @@
         <v>45506.3637962963</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -47262,7 +47262,7 @@
         <v>45195.35877314815</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -47319,7 +47319,7 @@
         <v>45195.3878125</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -47376,7 +47376,7 @@
         <v>44883</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -47433,7 +47433,7 @@
         <v>45459</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -47490,7 +47490,7 @@
         <v>45817.33819444444</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -47552,7 +47552,7 @@
         <v>45849</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -47609,7 +47609,7 @@
         <v>45624.57098379629</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -47666,7 +47666,7 @@
         <v>45817.62439814815</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -47723,7 +47723,7 @@
         <v>45817.594375</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -47785,7 +47785,7 @@
         <v>45218.58609953704</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -47842,7 +47842,7 @@
         <v>44914</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -47924,7 +47924,7 @@
         <v>44928.48072916667</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -47986,7 +47986,7 @@
         <v>45531.78386574074</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -48043,7 +48043,7 @@
         <v>45678.37956018518</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -48100,7 +48100,7 @@
         <v>45097</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -48162,7 +48162,7 @@
         <v>45202</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -48224,7 +48224,7 @@
         <v>45362.65903935185</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -48281,7 +48281,7 @@
         <v>45751.69827546296</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -48343,7 +48343,7 @@
         <v>45721.33868055556</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -48400,7 +48400,7 @@
         <v>45474.54432870371</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -48457,7 +48457,7 @@
         <v>45820.64821759259</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -48514,7 +48514,7 @@
         <v>44924.59140046296</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -48576,7 +48576,7 @@
         <v>44726</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -48633,7 +48633,7 @@
         <v>44423</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -48690,7 +48690,7 @@
         <v>44182</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -48747,7 +48747,7 @@
         <v>44665</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -48804,7 +48804,7 @@
         <v>45173</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -48866,7 +48866,7 @@
         <v>45866.40701388889</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -48923,7 +48923,7 @@
         <v>45866.62908564815</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -48980,7 +48980,7 @@
         <v>45821.77903935185</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -49037,7 +49037,7 @@
         <v>45821.57201388889</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -49099,7 +49099,7 @@
         <v>45723.58140046296</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -49156,7 +49156,7 @@
         <v>45245</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -49213,7 +49213,7 @@
         <v>44229</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -49275,7 +49275,7 @@
         <v>44225</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -49332,7 +49332,7 @@
         <v>45791</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -49389,7 +49389,7 @@
         <v>45867.55305555555</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -49446,7 +49446,7 @@
         <v>45867.55642361111</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -49508,7 +49508,7 @@
         <v>45868.639375</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -49565,7 +49565,7 @@
         <v>44631.37701388889</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -49627,7 +49627,7 @@
         <v>44631.42353009259</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -49689,7 +49689,7 @@
         <v>44914</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -49746,7 +49746,7 @@
         <v>45607.44832175926</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -49808,7 +49808,7 @@
         <v>44698</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -49870,7 +49870,7 @@
         <v>45617</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -49932,7 +49932,7 @@
         <v>45212</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -49989,7 +49989,7 @@
         <v>45826.43267361111</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -50051,7 +50051,7 @@
         <v>44925</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -50113,7 +50113,7 @@
         <v>45691</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -50175,7 +50175,7 @@
         <v>45691</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -50237,7 +50237,7 @@
         <v>45827.42467592593</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -50299,7 +50299,7 @@
         <v>45827</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -50356,7 +50356,7 @@
         <v>45869.61858796296</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -50413,7 +50413,7 @@
         <v>45869.62335648148</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -50470,7 +50470,7 @@
         <v>45827.41753472222</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -50532,7 +50532,7 @@
         <v>45546.54530092593</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -50589,7 +50589,7 @@
         <v>44162.65819444445</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -50651,7 +50651,7 @@
         <v>45510</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -50708,7 +50708,7 @@
         <v>44180</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -50765,7 +50765,7 @@
         <v>45869.61069444445</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -50822,7 +50822,7 @@
         <v>45758.49096064815</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -50884,7 +50884,7 @@
         <v>45568</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -50946,7 +50946,7 @@
         <v>45873.59511574074</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -51008,7 +51008,7 @@
         <v>45754.67329861111</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -51065,7 +51065,7 @@
         <v>45397.64855324074</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -51122,7 +51122,7 @@
         <v>44818</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -51179,7 +51179,7 @@
         <v>45622.64627314815</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -51236,7 +51236,7 @@
         <v>45755</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -51293,7 +51293,7 @@
         <v>45832.64047453704</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -51350,7 +51350,7 @@
         <v>45831</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -51412,7 +51412,7 @@
         <v>45687.53689814815</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -51469,7 +51469,7 @@
         <v>45630.5731712963</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -51531,7 +51531,7 @@
         <v>45432</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -51593,7 +51593,7 @@
         <v>44242</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -51650,7 +51650,7 @@
         <v>44939.45376157408</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -51707,7 +51707,7 @@
         <v>44994</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -51764,7 +51764,7 @@
         <v>45832</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -51826,7 +51826,7 @@
         <v>45874.64513888889</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -51883,7 +51883,7 @@
         <v>45832</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -51945,7 +51945,7 @@
         <v>45832.3859837963</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -52007,7 +52007,7 @@
         <v>45832</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -52069,7 +52069,7 @@
         <v>45442</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -52131,7 +52131,7 @@
         <v>45874.64199074074</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -52188,7 +52188,7 @@
         <v>45576.48657407407</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -52250,7 +52250,7 @@
         <v>45834.51079861111</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -52312,7 +52312,7 @@
         <v>45876.39362268519</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -52374,7 +52374,7 @@
         <v>45834.38173611111</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -52431,7 +52431,7 @@
         <v>45560</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -52488,7 +52488,7 @@
         <v>45875.5196875</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -52545,7 +52545,7 @@
         <v>45834.69577546296</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -52602,7 +52602,7 @@
         <v>45834.71440972222</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -52659,7 +52659,7 @@
         <v>44916</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -52716,7 +52716,7 @@
         <v>44440</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -52773,7 +52773,7 @@
         <v>45834</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -52835,7 +52835,7 @@
         <v>45833</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -52897,7 +52897,7 @@
         <v>45876.50833333333</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -52959,7 +52959,7 @@
         <v>45118.3959375</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -53021,7 +53021,7 @@
         <v>45833.36467592593</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -53083,7 +53083,7 @@
         <v>45833.6081712963</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -53145,7 +53145,7 @@
         <v>45833</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -53207,7 +53207,7 @@
         <v>44977.44643518519</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -53269,7 +53269,7 @@
         <v>45875.47854166666</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -53331,7 +53331,7 @@
         <v>45833</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -53393,7 +53393,7 @@
         <v>45834.6568287037</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -53450,7 +53450,7 @@
         <v>45834</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -53507,7 +53507,7 @@
         <v>45834</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -53569,7 +53569,7 @@
         <v>45834.7087962963</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -53626,7 +53626,7 @@
         <v>45876.51233796297</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -53688,7 +53688,7 @@
         <v>45733.59667824074</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -53750,7 +53750,7 @@
         <v>45876.49113425926</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -53807,7 +53807,7 @@
         <v>45098.48666666666</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -53869,7 +53869,7 @@
         <v>44957</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -53931,7 +53931,7 @@
         <v>44925</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -53988,7 +53988,7 @@
         <v>45835.55998842593</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -54050,7 +54050,7 @@
         <v>44258</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -54107,7 +54107,7 @@
         <v>45496.67342592592</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -54169,7 +54169,7 @@
         <v>45834.80229166667</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -54226,7 +54226,7 @@
         <v>45496.66903935185</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -54288,7 +54288,7 @@
         <v>45509</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -54350,7 +54350,7 @@
         <v>44958</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -54412,7 +54412,7 @@
         <v>45835.5583912037</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -54474,7 +54474,7 @@
         <v>45743.38449074074</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -54531,7 +54531,7 @@
         <v>45880.37472222222</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -54588,7 +54588,7 @@
         <v>45835.57069444445</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -54645,7 +54645,7 @@
         <v>45688.67932870371</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -54707,7 +54707,7 @@
         <v>45562.65759259259</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -54769,7 +54769,7 @@
         <v>45775.36587962963</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -54826,7 +54826,7 @@
         <v>45775.36589120371</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -54883,7 +54883,7 @@
         <v>45634.65831018519</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -54940,7 +54940,7 @@
         <v>45839.5658912037</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -54997,7 +54997,7 @@
         <v>44483</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -55054,7 +55054,7 @@
         <v>45061.36835648148</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -55111,7 +55111,7 @@
         <v>45728</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -55168,7 +55168,7 @@
         <v>45733.43663194445</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -55230,7 +55230,7 @@
         <v>45881.46869212963</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -55287,7 +55287,7 @@
         <v>45881.6609375</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -55344,7 +55344,7 @@
         <v>45881.36469907407</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -55401,7 +55401,7 @@
         <v>44985</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -55463,7 +55463,7 @@
         <v>44475</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -55520,7 +55520,7 @@
         <v>45664.56502314815</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -55577,7 +55577,7 @@
         <v>45575.6125925926</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -55639,7 +55639,7 @@
         <v>45882.64755787037</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -55701,7 +55701,7 @@
         <v>45881.64365740741</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -55758,7 +55758,7 @@
         <v>45840.64394675926</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -55820,7 +55820,7 @@
         <v>45882.63179398148</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -55882,7 +55882,7 @@
         <v>45881.43114583333</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -55939,7 +55939,7 @@
         <v>45484.48854166667</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -56001,7 +56001,7 @@
         <v>45488</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -56058,7 +56058,7 @@
         <v>44858</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -56115,7 +56115,7 @@
         <v>45288.58685185185</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -56172,7 +56172,7 @@
         <v>45595.5666550926</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -56229,7 +56229,7 @@
         <v>44953</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -56286,7 +56286,7 @@
         <v>45547.59543981482</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -56343,7 +56343,7 @@
         <v>45841.69273148148</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -56400,7 +56400,7 @@
         <v>45509.5980787037</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -56462,7 +56462,7 @@
         <v>45841.46512731481</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -56524,7 +56524,7 @@
         <v>44531.43927083333</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -56586,7 +56586,7 @@
         <v>45203</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -56643,7 +56643,7 @@
         <v>45208</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -56700,7 +56700,7 @@
         <v>45772.46951388889</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -56762,7 +56762,7 @@
         <v>45841.45137731481</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -56819,7 +56819,7 @@
         <v>44381</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -56876,7 +56876,7 @@
         <v>45768.30814814815</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -56938,7 +56938,7 @@
         <v>45883.40538194445</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -56995,7 +56995,7 @@
         <v>45656.51157407407</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -57057,7 +57057,7 @@
         <v>45841.4312037037</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -57114,7 +57114,7 @@
         <v>45884.55263888889</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -57176,7 +57176,7 @@
         <v>44964</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -57233,7 +57233,7 @@
         <v>45842.48990740741</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -57290,7 +57290,7 @@
         <v>45883.4108912037</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -57347,7 +57347,7 @@
         <v>45883.51854166666</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -57404,7 +57404,7 @@
         <v>45883.35789351852</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -57461,7 +57461,7 @@
         <v>45533.75398148148</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -57518,7 +57518,7 @@
         <v>45883.58944444444</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -57580,7 +57580,7 @@
         <v>45622</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -57637,7 +57637,7 @@
         <v>45705.32456018519</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -57694,7 +57694,7 @@
         <v>45209.45420138889</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -57751,7 +57751,7 @@
         <v>44225</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -57808,7 +57808,7 @@
         <v>44925.59333333333</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -57870,7 +57870,7 @@
         <v>45385</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -57927,7 +57927,7 @@
         <v>44216</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -57989,7 +57989,7 @@
         <v>44151</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -58046,7 +58046,7 @@
         <v>44169</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -58103,7 +58103,7 @@
         <v>44126</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -58160,7 +58160,7 @@
         <v>44985.61403935185</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -58222,7 +58222,7 @@
         <v>45604.31657407407</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -58284,7 +58284,7 @@
         <v>45345</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -58346,7 +58346,7 @@
         <v>45751.34636574074</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -58408,7 +58408,7 @@
         <v>45740.57487268518</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -58470,7 +58470,7 @@
         <v>44784.60677083334</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -58532,7 +58532,7 @@
         <v>45433</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -58589,7 +58589,7 @@
         <v>44827</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -58646,7 +58646,7 @@
         <v>45580.92037037037</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -58703,7 +58703,7 @@
         <v>44280</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -58760,7 +58760,7 @@
         <v>45166.34795138889</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -58817,7 +58817,7 @@
         <v>44928</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -58879,7 +58879,7 @@
         <v>45622.64012731481</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -58941,7 +58941,7 @@
         <v>45478.44497685185</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -59003,7 +59003,7 @@
         <v>45432</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -59065,7 +59065,7 @@
         <v>45622.45239583333</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -59127,7 +59127,7 @@
         <v>45638</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -59189,7 +59189,7 @@
         <v>45603</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -59251,7 +59251,7 @@
         <v>45107</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -59308,7 +59308,7 @@
         <v>45611.4021875</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -59365,7 +59365,7 @@
         <v>45622</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -59427,7 +59427,7 @@
         <v>45618</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -59484,7 +59484,7 @@
         <v>44987.35637731481</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -59546,7 +59546,7 @@
         <v>44987</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -59608,7 +59608,7 @@
         <v>45569.48626157407</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -59665,7 +59665,7 @@
         <v>45670.4570949074</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -59727,7 +59727,7 @@
         <v>45477.62255787037</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -59789,7 +59789,7 @@
         <v>45632</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -59846,7 +59846,7 @@
         <v>45666</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -59908,7 +59908,7 @@
         <v>45610.55846064815</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -59970,7 +59970,7 @@
         <v>45159.46996527778</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -60032,7 +60032,7 @@
         <v>45624.63614583333</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -60094,7 +60094,7 @@
         <v>44925.60457175926</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -60156,7 +60156,7 @@
         <v>44925.64309027778</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -60218,7 +60218,7 @@
         <v>45041</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -60275,7 +60275,7 @@
         <v>45041</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -60332,7 +60332,7 @@
         <v>44550.39550925926</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -60389,7 +60389,7 @@
         <v>45791</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -60446,7 +60446,7 @@
         <v>45533.67138888889</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -60503,7 +60503,7 @@
         <v>45758.69638888889</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -60560,7 +60560,7 @@
         <v>44722</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -60617,7 +60617,7 @@
         <v>45159</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -60679,7 +60679,7 @@
         <v>45159</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -60741,7 +60741,7 @@
         <v>45644</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -60798,7 +60798,7 @@
         <v>44314</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -60855,7 +60855,7 @@
         <v>44998</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -60912,7 +60912,7 @@
         <v>45154</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -60969,7 +60969,7 @@
         <v>45496.67178240741</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -61031,7 +61031,7 @@
         <v>45282.64012731481</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -61093,7 +61093,7 @@
         <v>45673.65925925926</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -61155,7 +61155,7 @@
         <v>45420.44414351852</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -61217,7 +61217,7 @@
         <v>45582.49792824074</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -61279,7 +61279,7 @@
         <v>45170.46923611111</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -61341,7 +61341,7 @@
         <v>45677.43028935185</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -61398,7 +61398,7 @@
         <v>44460.44315972222</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -61460,7 +61460,7 @@
         <v>44091</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -61517,7 +61517,7 @@
         <v>45239.43173611111</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -61579,7 +61579,7 @@
         <v>45719.40480324074</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -61636,7 +61636,7 @@
         <v>45624.36090277778</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -61693,7 +61693,7 @@
         <v>45617.89371527778</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -61750,7 +61750,7 @@
         <v>45621</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -61812,7 +61812,7 @@
         <v>45154</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -61869,7 +61869,7 @@
         <v>45719.45215277778</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -61926,7 +61926,7 @@
         <v>45604.66936342593</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -61983,7 +61983,7 @@
         <v>45020</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -62040,7 +62040,7 @@
         <v>45118.91633101852</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -62097,7 +62097,7 @@
         <v>45119</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -62154,7 +62154,7 @@
         <v>44708.48859953704</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -62216,7 +62216,7 @@
         <v>45632.65197916667</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -62273,7 +62273,7 @@
         <v>44872</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -62330,7 +62330,7 @@
         <v>44209</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -62392,7 +62392,7 @@
         <v>45075.59358796296</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -62454,7 +62454,7 @@
         <v>45740.36546296296</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -62516,7 +62516,7 @@
         <v>45685.52405092592</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -62578,7 +62578,7 @@
         <v>45685.5349074074</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -62640,7 +62640,7 @@
         <v>45147</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -62697,7 +62697,7 @@
         <v>45659.57361111111</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -62759,7 +62759,7 @@
         <v>45672.61748842592</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -62816,7 +62816,7 @@
         <v>45063</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -62873,7 +62873,7 @@
         <v>45390</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -62930,7 +62930,7 @@
         <v>45630.62513888889</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -62987,7 +62987,7 @@
         <v>45631.39950231482</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -63049,7 +63049,7 @@
         <v>45735.60342592592</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -63106,7 +63106,7 @@
         <v>45707</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -63163,7 +63163,7 @@
         <v>45719.45277777778</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -63220,7 +63220,7 @@
         <v>45764.44861111111</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -63282,7 +63282,7 @@
         <v>45727.35621527778</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -63344,7 +63344,7 @@
         <v>45510</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -63406,7 +63406,7 @@
         <v>45484.65768518519</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -63468,7 +63468,7 @@
         <v>45763.4178587963</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -63525,7 +63525,7 @@
         <v>45351</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -63582,7 +63582,7 @@
         <v>45575</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -63639,7 +63639,7 @@
         <v>45691</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -63701,7 +63701,7 @@
         <v>45691</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -63763,7 +63763,7 @@
         <v>45621</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -63820,7 +63820,7 @@
         <v>45621</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -63877,7 +63877,7 @@
         <v>45485</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -63934,7 +63934,7 @@
         <v>45616.49530092593</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -63991,7 +63991,7 @@
         <v>45154</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -64048,7 +64048,7 @@
         <v>45643.56899305555</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -64110,7 +64110,7 @@
         <v>45688.46570601852</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -64172,7 +64172,7 @@
         <v>44928.36418981481</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -64234,7 +64234,7 @@
         <v>44231</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -64296,7 +64296,7 @@
         <v>45707</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -64353,7 +64353,7 @@
         <v>44155</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -64410,7 +64410,7 @@
         <v>44795</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -64467,7 +64467,7 @@
         <v>44088</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -64524,7 +64524,7 @@
         <v>45642</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -64581,7 +64581,7 @@
         <v>45742.42793981481</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -64643,7 +64643,7 @@
         <v>45705.72106481482</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -64700,7 +64700,7 @@
         <v>45484.58422453704</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -64762,7 +64762,7 @@
         <v>44385</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -64819,7 +64819,7 @@
         <v>45371.66217592593</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -64881,7 +64881,7 @@
         <v>44757.37524305555</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -64938,7 +64938,7 @@
         <v>45764.44825231482</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -65000,7 +65000,7 @@
         <v>45485</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -65062,7 +65062,7 @@
         <v>45485</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -65124,7 +65124,7 @@
         <v>44886</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -65186,7 +65186,7 @@
         <v>44435</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -65248,7 +65248,7 @@
         <v>45572.60001157408</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -65305,7 +65305,7 @@
         <v>45303.5047337963</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -65362,7 +65362,7 @@
         <v>45735.57390046296</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -65419,7 +65419,7 @@
         <v>45737.3787962963</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -65476,7 +65476,7 @@
         <v>45119.38151620371</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -65538,7 +65538,7 @@
         <v>45665.59925925926</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -65595,7 +65595,7 @@
         <v>45768.29469907407</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -65657,7 +65657,7 @@
         <v>45768.30260416667</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -65719,7 +65719,7 @@
         <v>45768.30388888889</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -65781,7 +65781,7 @@
         <v>45593.6821412037</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -65838,7 +65838,7 @@
         <v>45593.68434027778</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -65895,7 +65895,7 @@
         <v>45685.50063657408</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -65957,7 +65957,7 @@
         <v>45687.54329861111</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -66014,7 +66014,7 @@
         <v>45625.56934027778</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -66076,7 +66076,7 @@
         <v>45063</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -66133,7 +66133,7 @@
         <v>44474.59423611111</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -66190,7 +66190,7 @@
         <v>45274</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -66247,7 +66247,7 @@
         <v>45743.61899305556</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -66304,7 +66304,7 @@
         <v>45743.62116898148</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -66361,7 +66361,7 @@
         <v>45764</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -66418,7 +66418,7 @@
         <v>45411.44549768518</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -66480,7 +66480,7 @@
         <v>45303.5187037037</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -66537,7 +66537,7 @@
         <v>45754.35055555555</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -66594,7 +66594,7 @@
         <v>45539.43545138889</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -66651,7 +66651,7 @@
         <v>45204</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -66708,7 +66708,7 @@
         <v>45688.6749537037</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -66770,7 +66770,7 @@
         <v>45635.42027777778</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -66832,7 +66832,7 @@
         <v>44827</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -66889,7 +66889,7 @@
         <v>44827</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -66946,7 +66946,7 @@
         <v>45728.61006944445</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -67003,7 +67003,7 @@
         <v>45238.46430555556</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -67060,7 +67060,7 @@
         <v>45670</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -67122,7 +67122,7 @@
         <v>45611.38759259259</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -67179,7 +67179,7 @@
         <v>44642</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -67241,7 +67241,7 @@
         <v>45532</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -67298,7 +67298,7 @@
         <v>45244</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -67355,7 +67355,7 @@
         <v>44886</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -67417,7 +67417,7 @@
         <v>45758.66108796297</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -67474,7 +67474,7 @@
         <v>45758.69123842593</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -67531,7 +67531,7 @@
         <v>45252.48409722222</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -67588,7 +67588,7 @@
         <v>45252</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -67645,7 +67645,7 @@
         <v>44853</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -67702,7 +67702,7 @@
         <v>44925.33584490741</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -67764,7 +67764,7 @@
         <v>45667</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -67821,7 +67821,7 @@
         <v>45509</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -67883,7 +67883,7 @@
         <v>45706</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -67940,7 +67940,7 @@
         <v>45303.52626157407</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -67997,7 +67997,7 @@
         <v>45741.39084490741</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -68054,7 +68054,7 @@
         <v>44985.6125</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -68116,7 +68116,7 @@
         <v>45719.48778935185</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -68173,7 +68173,7 @@
         <v>45574.66106481481</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -68230,7 +68230,7 @@
         <v>45763.4266087963</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -68287,7 +68287,7 @@
         <v>45264.92637731481</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -68344,7 +68344,7 @@
         <v>45345.65929398148</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -68406,7 +68406,7 @@
         <v>45688.6769212963</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -68468,7 +68468,7 @@
         <v>45439.43106481482</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -68530,7 +68530,7 @@
         <v>44972.57449074074</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -68587,7 +68587,7 @@
         <v>44484.55535879629</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -68644,7 +68644,7 @@
         <v>45229.92739583334</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -68701,7 +68701,7 @@
         <v>45260.59042824074</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -68758,7 +68758,7 @@
         <v>45075.59148148148</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -68820,7 +68820,7 @@
         <v>45063.92605324074</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -68877,7 +68877,7 @@
         <v>45575.60996527778</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -68939,7 +68939,7 @@
         <v>44889.56582175926</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -68996,7 +68996,7 @@
         <v>45531.66196759259</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -69058,7 +69058,7 @@
         <v>44928</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -69120,7 +69120,7 @@
         <v>44928</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -69182,7 +69182,7 @@
         <v>45290.39024305555</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -69239,7 +69239,7 @@
         <v>45731.69629629629</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -69296,7 +69296,7 @@
         <v>45460.48582175926</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -69353,7 +69353,7 @@
         <v>45680.42497685185</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -69410,7 +69410,7 @@
         <v>44819.56722222222</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -69467,7 +69467,7 @@
         <v>45631.63091435185</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -69524,7 +69524,7 @@
         <v>45153.42725694444</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -69586,7 +69586,7 @@
         <v>44854</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -69648,7 +69648,7 @@
         <v>45568</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -69710,7 +69710,7 @@
         <v>45751.65657407408</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -69772,7 +69772,7 @@
         <v>45685</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -69834,7 +69834,7 @@
         <v>45477.66773148148</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -69896,7 +69896,7 @@
         <v>45338</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -69958,7 +69958,7 @@
         <v>45496.59202546296</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -70020,7 +70020,7 @@
         <v>45756</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -70077,7 +70077,7 @@
         <v>45257</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -70134,7 +70134,7 @@
         <v>45601.58355324074</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -70191,7 +70191,7 @@
         <v>45447.35144675926</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -70248,7 +70248,7 @@
         <v>45429.39</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -70305,7 +70305,7 @@
         <v>45054</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -70367,7 +70367,7 @@
         <v>45761.61501157407</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -70429,7 +70429,7 @@
         <v>45637.39587962963</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -70491,7 +70491,7 @@
         <v>45559.43645833333</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -70553,7 +70553,7 @@
         <v>45517.69590277778</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -70615,7 +70615,7 @@
         <v>45635.4916087963</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -70672,7 +70672,7 @@
         <v>45012</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -70734,7 +70734,7 @@
         <v>45590.31899305555</v>
       </c>
       <c r="C1075" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
@@ -70791,7 +70791,7 @@
         <v>45607</v>
       </c>
       <c r="C1076" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
@@ -70848,7 +70848,7 @@
         <v>44571</v>
       </c>
       <c r="C1077" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
@@ -70905,7 +70905,7 @@
         <v>45642.41907407407</v>
       </c>
       <c r="C1078" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1078" t="inlineStr">
         <is>
@@ -70962,7 +70962,7 @@
         <v>45049.59826388889</v>
       </c>
       <c r="C1079" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1079" t="inlineStr">
         <is>
@@ -71019,7 +71019,7 @@
         <v>45579.59980324074</v>
       </c>
       <c r="C1080" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
@@ -71076,7 +71076,7 @@
         <v>45632</v>
       </c>
       <c r="C1081" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1081" t="inlineStr">
         <is>
@@ -71133,7 +71133,7 @@
         <v>45632</v>
       </c>
       <c r="C1082" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1082" t="inlineStr">
         <is>

--- a/Översikt HÄRJEDALEN.xlsx
+++ b/Översikt HÄRJEDALEN.xlsx
@@ -567,7 +567,7 @@
         <v>45513</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         <v>45763</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>44785</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>44790</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>44553</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>44837</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>44844</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>44749</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>44406</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>45691</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>44182</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>44154.40430555555</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>45761.58262731481</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>45531</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>44831</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>44496.94013888889</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>45667</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
         <v>44865.57574074074</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>45180</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
         <v>44650</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>45250</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>45351</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3043,7 +3043,7 @@
         <v>44200</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>44193</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>45554</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         <v>45631</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         <v>45544.35653935185</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>44501</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3681,7 +3681,7 @@
         <v>44182</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>44690</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>44487</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
         <v>45631</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>45625.49736111111</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4211,7 +4211,7 @@
         <v>44406</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         <v>45544</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4409,7 +4409,7 @@
         <v>44440</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4506,7 +4506,7 @@
         <v>45837</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         <v>45106</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>45217</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>45571</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         <v>44774</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>44357</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         <v>45457.38396990741</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5212,7 +5212,7 @@
         <v>45175</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
         <v>45544</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         <v>45198</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5527,7 +5527,7 @@
         <v>45531</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         <v>45477.46537037037</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
         <v>45694</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>45411</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>45833.43898148148</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>44553</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>45471.59034722222</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
         <v>44517</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6320,7 +6320,7 @@
         <v>45614.45413194445</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6426,7 +6426,7 @@
         <v>44406</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6523,7 +6523,7 @@
         <v>44553</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6620,7 +6620,7 @@
         <v>44377</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
         <v>45426</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6808,7 +6808,7 @@
         <v>45741.82913194445</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6900,7 +6900,7 @@
         <v>45677.45212962963</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         <v>44430</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7092,7 +7092,7 @@
         <v>44553</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         <v>45715</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7288,7 +7288,7 @@
         <v>45007</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         <v>45531.45444444445</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7483,7 +7483,7 @@
         <v>44242</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7573,7 +7573,7 @@
         <v>45616.6450462963</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7671,7 +7671,7 @@
         <v>45568</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7766,7 +7766,7 @@
         <v>45559</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7865,7 +7865,7 @@
         <v>45772.51116898148</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7960,7 +7960,7 @@
         <v>45719</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
         <v>45574</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8148,7 +8148,7 @@
         <v>45625.45384259259</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8251,7 +8251,7 @@
         <v>45869</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8345,7 +8345,7 @@
         <v>44882</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8438,7 +8438,7 @@
         <v>44517</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8527,7 +8527,7 @@
         <v>45243</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8620,7 +8620,7 @@
         <v>44979</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8709,7 +8709,7 @@
         <v>45432.94736111111</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8807,7 +8807,7 @@
         <v>44430</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8908,7 +8908,7 @@
         <v>44294</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>44294</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9084,7 +9084,7 @@
         <v>44977</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9181,7 +9181,7 @@
         <v>45694</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9269,7 +9269,7 @@
         <v>45467.47204861111</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9362,7 +9362,7 @@
         <v>45085</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9454,7 +9454,7 @@
         <v>44377</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9546,7 +9546,7 @@
         <v>45559.38894675926</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9643,7 +9643,7 @@
         <v>44957</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9735,7 +9735,7 @@
         <v>45531.45752314815</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         <v>45537.45818287037</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9920,7 +9920,7 @@
         <v>45007</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10013,7 +10013,7 @@
         <v>45838.73927083334</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10106,7 +10106,7 @@
         <v>45506.35658564815</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10198,7 +10198,7 @@
         <v>44476</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10290,7 +10290,7 @@
         <v>45552</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10378,7 +10378,7 @@
         <v>44475</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
         <v>44441</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10552,7 +10552,7 @@
         <v>44475</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10639,7 +10639,7 @@
         <v>44475</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10726,7 +10726,7 @@
         <v>44713</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10826,7 +10826,7 @@
         <v>45791</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10913,7 +10913,7 @@
         <v>45800.3484375</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11005,7 +11005,7 @@
         <v>45617</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11101,7 +11101,7 @@
         <v>44107</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11197,7 +11197,7 @@
         <v>45821.56523148148</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11289,7 +11289,7 @@
         <v>45841.41003472222</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>45468</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         <v>45849.35011574074</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11550,7 +11550,7 @@
         <v>44180</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>44074</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11738,7 +11738,7 @@
         <v>44186</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11829,7 +11829,7 @@
         <v>44677</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11920,7 +11920,7 @@
         <v>44286</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12006,7 +12006,7 @@
         <v>44221</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12092,7 +12092,7 @@
         <v>44475</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12178,7 +12178,7 @@
         <v>44866.46503472222</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12273,7 +12273,7 @@
         <v>45772.51070601852</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12364,7 +12364,7 @@
         <v>45191</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12455,7 +12455,7 @@
         <v>44853</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12545,7 +12545,7 @@
         <v>45786.66594907407</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12636,7 +12636,7 @@
         <v>45786.67016203704</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12727,7 +12727,7 @@
         <v>45786.6768287037</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12818,7 +12818,7 @@
         <v>45786.6590625</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12909,7 +12909,7 @@
         <v>45786.65452546296</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13000,7 +13000,7 @@
         <v>44987</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13095,7 +13095,7 @@
         <v>45786.67261574074</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13186,7 +13186,7 @@
         <v>44449</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13272,7 +13272,7 @@
         <v>45772.36488425926</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13367,7 +13367,7 @@
         <v>45644.56555555556</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>45153</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13552,7 +13552,7 @@
         <v>45595.58056712963</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13643,7 +13643,7 @@
         <v>45694</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13729,7 +13729,7 @@
         <v>45805.73822916667</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13820,7 +13820,7 @@
         <v>45833</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -13906,7 +13906,7 @@
         <v>45035</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14001,7 +14001,7 @@
         <v>44955</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
         <v>45880.37559027778</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14177,7 +14177,7 @@
         <v>45621</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14272,7 +14272,7 @@
         <v>45552</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14362,7 +14362,7 @@
         <v>45538</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14453,7 +14453,7 @@
         <v>44475</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14539,7 +14539,7 @@
         <v>44096</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14629,7 +14629,7 @@
         <v>44475</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14714,7 +14714,7 @@
         <v>44321</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -14804,7 +14804,7 @@
         <v>44475</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -14889,7 +14889,7 @@
         <v>44475</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -14974,7 +14974,7 @@
         <v>44113</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15059,7 +15059,7 @@
         <v>44105</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15144,7 +15144,7 @@
         <v>45538.57630787037</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15233,7 +15233,7 @@
         <v>45621.47555555555</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15323,7 +15323,7 @@
         <v>45603</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15413,7 +15413,7 @@
         <v>44475</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -15498,7 +15498,7 @@
         <v>45729.64623842593</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
         <v>45345</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -15678,7 +15678,7 @@
         <v>44769.48783564815</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -15768,7 +15768,7 @@
         <v>45111</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -15858,7 +15858,7 @@
         <v>45638.33607638889</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -15948,7 +15948,7 @@
         <v>45714.55248842593</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16042,7 +16042,7 @@
         <v>45320</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16127,7 +16127,7 @@
         <v>45308</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -16216,7 +16216,7 @@
         <v>45457.38677083333</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -16306,7 +16306,7 @@
         <v>45540.69512731482</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -16396,7 +16396,7 @@
         <v>45800.63043981481</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -16490,7 +16490,7 @@
         <v>45805.66601851852</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -16584,7 +16584,7 @@
         <v>45791</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -16669,7 +16669,7 @@
         <v>45805.73546296296</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -16759,7 +16759,7 @@
         <v>45617</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -16853,7 +16853,7 @@
         <v>45454.62443287037</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -16938,7 +16938,7 @@
         <v>45812.82244212963</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17028,7 +17028,7 @@
         <v>45672.50416666667</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17113,7 +17113,7 @@
         <v>45835.7499537037</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -17203,7 +17203,7 @@
         <v>45838.773125</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -17293,7 +17293,7 @@
         <v>45869</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -17378,7 +17378,7 @@
         <v>45889.56214120371</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -17468,7 +17468,7 @@
         <v>45758.70164351852</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -17553,7 +17553,7 @@
         <v>45875</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -17642,7 +17642,7 @@
         <v>44320</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -17699,7 +17699,7 @@
         <v>44316</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -17756,7 +17756,7 @@
         <v>44320</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -17818,7 +17818,7 @@
         <v>44105</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -17875,7 +17875,7 @@
         <v>44810</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -17937,7 +17937,7 @@
         <v>44727.70908564814</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -17999,7 +17999,7 @@
         <v>44430</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -18061,7 +18061,7 @@
         <v>44543</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -18118,7 +18118,7 @@
         <v>44614</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -18180,7 +18180,7 @@
         <v>44404</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -18237,7 +18237,7 @@
         <v>44417.38271990741</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -18294,7 +18294,7 @@
         <v>44417.38614583333</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -18351,7 +18351,7 @@
         <v>44497</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -18408,7 +18408,7 @@
         <v>44475</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -18465,7 +18465,7 @@
         <v>44361</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -18522,7 +18522,7 @@
         <v>44540</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -18584,7 +18584,7 @@
         <v>44531</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -18641,7 +18641,7 @@
         <v>44600</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -18698,7 +18698,7 @@
         <v>44475</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -18755,7 +18755,7 @@
         <v>44385.93652777778</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -18817,7 +18817,7 @@
         <v>44475</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>44406</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -18931,7 +18931,7 @@
         <v>44854</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -18988,7 +18988,7 @@
         <v>44538</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -19050,7 +19050,7 @@
         <v>44102</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -19107,7 +19107,7 @@
         <v>44823</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -19169,7 +19169,7 @@
         <v>44316</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -19226,7 +19226,7 @@
         <v>44424</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -19283,7 +19283,7 @@
         <v>44483</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -19340,7 +19340,7 @@
         <v>44421</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -19397,7 +19397,7 @@
         <v>44418</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -19459,7 +19459,7 @@
         <v>44488</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -19521,7 +19521,7 @@
         <v>44132</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -19578,7 +19578,7 @@
         <v>44603</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -19640,7 +19640,7 @@
         <v>44418</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -19702,7 +19702,7 @@
         <v>44564.6747337963</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -19764,7 +19764,7 @@
         <v>44361</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -19826,7 +19826,7 @@
         <v>44615</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -19888,7 +19888,7 @@
         <v>44466.81701388889</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -19945,7 +19945,7 @@
         <v>44218</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -20002,7 +20002,7 @@
         <v>44286</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -20059,7 +20059,7 @@
         <v>44475</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -20116,7 +20116,7 @@
         <v>44475</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -20173,7 +20173,7 @@
         <v>44410.74284722222</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -20230,7 +20230,7 @@
         <v>44631</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -20292,7 +20292,7 @@
         <v>44631.41535879629</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>44728</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -20411,7 +20411,7 @@
         <v>44810</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -20473,7 +20473,7 @@
         <v>44417.37519675926</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -20530,7 +20530,7 @@
         <v>44344</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -20587,7 +20587,7 @@
         <v>44174</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -20644,7 +20644,7 @@
         <v>44084</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -20706,7 +20706,7 @@
         <v>44475</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -20763,7 +20763,7 @@
         <v>44078</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -20820,7 +20820,7 @@
         <v>44179</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -20877,7 +20877,7 @@
         <v>44258</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -20934,7 +20934,7 @@
         <v>44424</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -20991,7 +20991,7 @@
         <v>44424</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -21048,7 +21048,7 @@
         <v>44818</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -21105,7 +21105,7 @@
         <v>44770.53315972222</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -21162,7 +21162,7 @@
         <v>44690</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -21219,7 +21219,7 @@
         <v>44285</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -21276,7 +21276,7 @@
         <v>44286</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -21333,7 +21333,7 @@
         <v>44792.68023148148</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -21390,7 +21390,7 @@
         <v>44385.93658564815</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -21452,7 +21452,7 @@
         <v>44243.63096064814</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -21509,7 +21509,7 @@
         <v>44298</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -21566,7 +21566,7 @@
         <v>44183</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -21623,7 +21623,7 @@
         <v>44319</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -21680,7 +21680,7 @@
         <v>44316</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -21737,7 +21737,7 @@
         <v>44316</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -21794,7 +21794,7 @@
         <v>44126</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -21851,7 +21851,7 @@
         <v>44825</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -21908,7 +21908,7 @@
         <v>44174</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -21965,7 +21965,7 @@
         <v>44154</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -22027,7 +22027,7 @@
         <v>44396</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -22084,7 +22084,7 @@
         <v>44475</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -22141,7 +22141,7 @@
         <v>44127</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -22203,7 +22203,7 @@
         <v>44475</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -22260,7 +22260,7 @@
         <v>44475</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -22317,7 +22317,7 @@
         <v>44475</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -22374,7 +22374,7 @@
         <v>44475</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -22431,7 +22431,7 @@
         <v>44544</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -22493,7 +22493,7 @@
         <v>44420.33096064815</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -22550,7 +22550,7 @@
         <v>44188</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -22612,7 +22612,7 @@
         <v>44483.36435185185</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -22669,7 +22669,7 @@
         <v>44417</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -22726,7 +22726,7 @@
         <v>44181</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -22788,7 +22788,7 @@
         <v>44426.45706018519</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -22845,7 +22845,7 @@
         <v>44859</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -22907,7 +22907,7 @@
         <v>44473</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -22964,7 +22964,7 @@
         <v>44314</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -23021,7 +23021,7 @@
         <v>44727.71858796296</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -23083,7 +23083,7 @@
         <v>44335.4837962963</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -23140,7 +23140,7 @@
         <v>44475</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -23197,7 +23197,7 @@
         <v>44543</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -23259,7 +23259,7 @@
         <v>44475</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -23316,7 +23316,7 @@
         <v>44475</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -23373,7 +23373,7 @@
         <v>44481.67951388889</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -23430,7 +23430,7 @@
         <v>44725</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -23492,7 +23492,7 @@
         <v>44631.37421296296</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -23554,7 +23554,7 @@
         <v>44230</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -23611,7 +23611,7 @@
         <v>44538</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -23673,7 +23673,7 @@
         <v>44855.60383101852</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -23730,7 +23730,7 @@
         <v>44133</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -23792,7 +23792,7 @@
         <v>44631.45398148148</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -23854,7 +23854,7 @@
         <v>44417.37207175926</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -23911,7 +23911,7 @@
         <v>44768.44859953703</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -23968,7 +23968,7 @@
         <v>44475</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -24025,7 +24025,7 @@
         <v>44475</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -24082,7 +24082,7 @@
         <v>44475</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -24139,7 +24139,7 @@
         <v>44475</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -24196,7 +24196,7 @@
         <v>44368</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -24253,7 +24253,7 @@
         <v>44403</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -24310,7 +24310,7 @@
         <v>44886.62578703704</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -24367,7 +24367,7 @@
         <v>44886.629375</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -24424,7 +24424,7 @@
         <v>44838</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -24486,7 +24486,7 @@
         <v>44708.46081018518</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -24548,7 +24548,7 @@
         <v>44684</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -24610,7 +24610,7 @@
         <v>44126</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -24672,7 +24672,7 @@
         <v>44540.56034722222</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -24729,7 +24729,7 @@
         <v>44872</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -24791,7 +24791,7 @@
         <v>44169</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -24848,7 +24848,7 @@
         <v>44531</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -24905,7 +24905,7 @@
         <v>44180</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -24962,7 +24962,7 @@
         <v>44207</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -25024,7 +25024,7 @@
         <v>44742</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -25086,7 +25086,7 @@
         <v>44270</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -25143,7 +25143,7 @@
         <v>44166</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -25205,7 +25205,7 @@
         <v>44531</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -25262,7 +25262,7 @@
         <v>44531</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -25319,7 +25319,7 @@
         <v>44788.67976851852</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -25381,7 +25381,7 @@
         <v>44316</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -25438,7 +25438,7 @@
         <v>44413</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -25495,7 +25495,7 @@
         <v>44316</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -25552,7 +25552,7 @@
         <v>44627.36047453704</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -25614,7 +25614,7 @@
         <v>44389</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -25676,7 +25676,7 @@
         <v>44188</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -25733,7 +25733,7 @@
         <v>45484.58422453704</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -25795,7 +25795,7 @@
         <v>44825</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -25852,7 +25852,7 @@
         <v>44361</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -25909,7 +25909,7 @@
         <v>44530.40607638889</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -25966,7 +25966,7 @@
         <v>44889.56582175926</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -26023,7 +26023,7 @@
         <v>45740.36546296296</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -26085,7 +26085,7 @@
         <v>44706.66417824074</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -26147,7 +26147,7 @@
         <v>45240</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -26204,7 +26204,7 @@
         <v>45634.65831018519</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -26261,7 +26261,7 @@
         <v>45687.54329861111</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -26318,7 +26318,7 @@
         <v>44475</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -26375,7 +26375,7 @@
         <v>44803</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -26432,7 +26432,7 @@
         <v>45706</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -26489,7 +26489,7 @@
         <v>44285</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -26546,7 +26546,7 @@
         <v>44258</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -26603,7 +26603,7 @@
         <v>44377</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -26660,7 +26660,7 @@
         <v>45772.69290509259</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -26722,7 +26722,7 @@
         <v>44155</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -26779,7 +26779,7 @@
         <v>45763.41402777778</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -26836,7 +26836,7 @@
         <v>45740.57487268518</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -26898,7 +26898,7 @@
         <v>45579.59980324074</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -26955,7 +26955,7 @@
         <v>44242</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -27012,7 +27012,7 @@
         <v>44643.81518518519</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -27069,7 +27069,7 @@
         <v>45252</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -27126,7 +27126,7 @@
         <v>44925</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -27183,7 +27183,7 @@
         <v>45624.36090277778</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -27240,7 +27240,7 @@
         <v>45614.47960648148</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -27297,7 +27297,7 @@
         <v>45758.49096064815</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -27359,7 +27359,7 @@
         <v>45096.62344907408</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -27421,7 +27421,7 @@
         <v>45733.43663194445</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -27483,7 +27483,7 @@
         <v>44088</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -27540,7 +27540,7 @@
         <v>44925</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -27602,7 +27602,7 @@
         <v>45595.5666550926</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -27659,7 +27659,7 @@
         <v>45362.67293981482</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -27716,7 +27716,7 @@
         <v>45607</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -27773,7 +27773,7 @@
         <v>45579.57390046296</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -27835,7 +27835,7 @@
         <v>45420.44414351852</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -27897,7 +27897,7 @@
         <v>44872</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -27954,7 +27954,7 @@
         <v>45741.45597222223</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -28011,7 +28011,7 @@
         <v>45667</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -28068,7 +28068,7 @@
         <v>45195.35877314815</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -28125,7 +28125,7 @@
         <v>45617.89371527778</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -28182,7 +28182,7 @@
         <v>45775.36587962963</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -28239,7 +28239,7 @@
         <v>45119.39105324074</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -28301,7 +28301,7 @@
         <v>45685</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -28363,7 +28363,7 @@
         <v>45510</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -28420,7 +28420,7 @@
         <v>45622.64012731481</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -28482,7 +28482,7 @@
         <v>45756</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -28539,7 +28539,7 @@
         <v>45635.33439814814</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -28601,7 +28601,7 @@
         <v>45439.43106481482</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -28663,7 +28663,7 @@
         <v>44531.43927083333</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -28725,7 +28725,7 @@
         <v>45688.67935185185</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -28787,7 +28787,7 @@
         <v>45574.66106481481</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -28844,7 +28844,7 @@
         <v>45575</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -28901,7 +28901,7 @@
         <v>44784.60677083334</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -28963,7 +28963,7 @@
         <v>45754.35055555555</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -29020,7 +29020,7 @@
         <v>45506.36534722222</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -29077,7 +29077,7 @@
         <v>45772.46965277778</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -29139,7 +29139,7 @@
         <v>45772.46988425926</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -29201,7 +29201,7 @@
         <v>45632.64769675926</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -29258,7 +29258,7 @@
         <v>45106</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -29320,7 +29320,7 @@
         <v>45603</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -29382,7 +29382,7 @@
         <v>45603</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -29444,7 +29444,7 @@
         <v>44475</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -29501,7 +29501,7 @@
         <v>44300</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -29558,7 +29558,7 @@
         <v>45459</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -29615,7 +29615,7 @@
         <v>45345.66555555556</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -29677,7 +29677,7 @@
         <v>45664.56502314815</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -29734,7 +29734,7 @@
         <v>45575.60996527778</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -29796,7 +29796,7 @@
         <v>45303.5047337963</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -29853,7 +29853,7 @@
         <v>44985.61403935185</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -29915,7 +29915,7 @@
         <v>45743.38449074074</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -29972,7 +29972,7 @@
         <v>45637</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -30029,7 +30029,7 @@
         <v>45721.33868055556</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -30086,7 +30086,7 @@
         <v>45688.67932870371</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -30148,7 +30148,7 @@
         <v>45685.5349074074</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -30210,7 +30210,7 @@
         <v>45290.39024305555</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -30267,7 +30267,7 @@
         <v>44795</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -30324,7 +30324,7 @@
         <v>45572.60001157408</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -30381,7 +30381,7 @@
         <v>45607.44832175926</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -30443,7 +30443,7 @@
         <v>45580.92037037037</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -30500,7 +30500,7 @@
         <v>45568</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -30562,7 +30562,7 @@
         <v>45768.30814814815</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -30624,7 +30624,7 @@
         <v>45635.42027777778</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -30686,7 +30686,7 @@
         <v>45350</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -30743,7 +30743,7 @@
         <v>45351</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -30800,7 +30800,7 @@
         <v>45075.59358796296</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -30862,7 +30862,7 @@
         <v>45729.65261574074</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -30924,7 +30924,7 @@
         <v>45691</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -30986,7 +30986,7 @@
         <v>45569.48626157407</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -31043,7 +31043,7 @@
         <v>45691</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -31105,7 +31105,7 @@
         <v>44914</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -31162,7 +31162,7 @@
         <v>45764</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -31219,7 +31219,7 @@
         <v>44472</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -31276,7 +31276,7 @@
         <v>45672.61748842592</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -31333,7 +31333,7 @@
         <v>44977.44643518519</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -31395,7 +31395,7 @@
         <v>44316</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -31452,7 +31452,7 @@
         <v>44280</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -31509,7 +31509,7 @@
         <v>45338</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -31571,7 +31571,7 @@
         <v>45432</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -31633,7 +31633,7 @@
         <v>45659.57361111111</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -31695,7 +31695,7 @@
         <v>44381</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -31752,7 +31752,7 @@
         <v>45762.55899305556</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -31809,7 +31809,7 @@
         <v>45604.31657407407</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -31871,7 +31871,7 @@
         <v>45280</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -31928,7 +31928,7 @@
         <v>44732</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -31985,7 +31985,7 @@
         <v>45345.35003472222</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -32047,7 +32047,7 @@
         <v>45758.69638888889</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -32104,7 +32104,7 @@
         <v>45617</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -32166,7 +32166,7 @@
         <v>45496.59202546296</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -32228,7 +32228,7 @@
         <v>45677.44273148148</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -32285,7 +32285,7 @@
         <v>44916</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -32342,7 +32342,7 @@
         <v>45719.45215277778</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -32399,7 +32399,7 @@
         <v>45621</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -32456,7 +32456,7 @@
         <v>45621</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -32513,7 +32513,7 @@
         <v>45645.48079861111</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -32575,7 +32575,7 @@
         <v>44953</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -32632,7 +32632,7 @@
         <v>45111</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -32689,7 +32689,7 @@
         <v>45257</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -32751,7 +32751,7 @@
         <v>45622</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -32813,7 +32813,7 @@
         <v>44126</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -32870,7 +32870,7 @@
         <v>44483</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -32927,7 +32927,7 @@
         <v>45537.60471064815</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -32989,7 +32989,7 @@
         <v>44925.64049768518</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -33051,7 +33051,7 @@
         <v>45642.33616898148</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -33108,7 +33108,7 @@
         <v>45741.38347222222</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -33165,7 +33165,7 @@
         <v>45505</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -33222,7 +33222,7 @@
         <v>45728.44329861111</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -33284,7 +33284,7 @@
         <v>44726</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -33341,7 +33341,7 @@
         <v>45442</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -33403,7 +33403,7 @@
         <v>45728.49267361111</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -33465,7 +33465,7 @@
         <v>45604.33195601852</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -33527,7 +33527,7 @@
         <v>45575</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -33584,7 +33584,7 @@
         <v>45603</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -33646,7 +33646,7 @@
         <v>45540.4264699074</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -33708,7 +33708,7 @@
         <v>45643.56899305555</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -33770,7 +33770,7 @@
         <v>45719.40480324074</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -33827,7 +33827,7 @@
         <v>45547.59543981482</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -33884,7 +33884,7 @@
         <v>45560</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -33941,7 +33941,7 @@
         <v>44162.65819444445</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -34003,7 +34003,7 @@
         <v>45751.69827546296</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -34065,7 +34065,7 @@
         <v>45582.49792824074</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -34127,7 +34127,7 @@
         <v>44167</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -34184,7 +34184,7 @@
         <v>45303.52626157407</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -34241,7 +34241,7 @@
         <v>45119.38151620371</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -34303,7 +34303,7 @@
         <v>45061.61002314815</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -34365,7 +34365,7 @@
         <v>45517.38320601852</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -34422,7 +34422,7 @@
         <v>45260.35777777778</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -34479,7 +34479,7 @@
         <v>45645.47609953704</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -34541,7 +34541,7 @@
         <v>45471.66556712963</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -34603,7 +34603,7 @@
         <v>44928</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -34665,7 +34665,7 @@
         <v>44928</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -34727,7 +34727,7 @@
         <v>45243.63798611111</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -34784,7 +34784,7 @@
         <v>44827</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -34841,7 +34841,7 @@
         <v>44827</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -34898,7 +34898,7 @@
         <v>45635.4916087963</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -34955,7 +34955,7 @@
         <v>45688.46570601852</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -35017,7 +35017,7 @@
         <v>45604.66936342593</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -35074,7 +35074,7 @@
         <v>45411.44549768518</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -35136,7 +35136,7 @@
         <v>45776.43898148148</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -35193,7 +35193,7 @@
         <v>44985.6125</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -35255,7 +35255,7 @@
         <v>45776.69569444445</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -35312,7 +35312,7 @@
         <v>45768.29469907407</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -35374,7 +35374,7 @@
         <v>45768.30260416667</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -35436,7 +35436,7 @@
         <v>45768.30388888889</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -35498,7 +35498,7 @@
         <v>45485</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -35560,7 +35560,7 @@
         <v>45485</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -35622,7 +35622,7 @@
         <v>45611.38759259259</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -35679,7 +35679,7 @@
         <v>45484.66521990741</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -35741,7 +35741,7 @@
         <v>45506.36702546296</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -35798,7 +35798,7 @@
         <v>45779.41844907407</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -35860,7 +35860,7 @@
         <v>45779.38211805555</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -35922,7 +35922,7 @@
         <v>45779.50886574074</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -35984,7 +35984,7 @@
         <v>45779.51943287037</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -36046,7 +36046,7 @@
         <v>45779.52488425926</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -36108,7 +36108,7 @@
         <v>45020</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -36165,7 +36165,7 @@
         <v>45779.50052083333</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -36227,7 +36227,7 @@
         <v>45737</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -36284,7 +36284,7 @@
         <v>45779.47704861111</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -36346,7 +36346,7 @@
         <v>45614.62445601852</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -36408,7 +36408,7 @@
         <v>45779.51357638889</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -36470,7 +36470,7 @@
         <v>45779.48611111111</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -36532,7 +36532,7 @@
         <v>45791</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -36589,7 +36589,7 @@
         <v>45707</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -36646,7 +36646,7 @@
         <v>45707</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -36703,7 +36703,7 @@
         <v>45483.47572916667</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -36760,7 +36760,7 @@
         <v>45743.61899305556</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -36817,7 +36817,7 @@
         <v>45743.62116898148</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -36874,7 +36874,7 @@
         <v>45783.68547453704</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -36936,7 +36936,7 @@
         <v>45618.35961805555</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -36993,7 +36993,7 @@
         <v>45782.41581018519</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -37050,7 +37050,7 @@
         <v>45751.63266203704</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -37112,7 +37112,7 @@
         <v>45118.47491898148</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -37174,7 +37174,7 @@
         <v>45782.42744212963</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -37231,7 +37231,7 @@
         <v>44999.60127314815</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -37288,7 +37288,7 @@
         <v>45665.59925925926</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -37345,7 +37345,7 @@
         <v>45666</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -37407,7 +37407,7 @@
         <v>45147</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -37464,7 +37464,7 @@
         <v>45457.92854166667</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -37521,7 +37521,7 @@
         <v>45387</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -37578,7 +37578,7 @@
         <v>45785.33164351852</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -37635,7 +37635,7 @@
         <v>45785.34165509259</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -37692,7 +37692,7 @@
         <v>44924.59140046296</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -37754,7 +37754,7 @@
         <v>45677.43028935185</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -37811,7 +37811,7 @@
         <v>45784.59012731481</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -37873,7 +37873,7 @@
         <v>45119.38675925926</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -37935,7 +37935,7 @@
         <v>45670.34313657408</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -37992,7 +37992,7 @@
         <v>45632.64078703704</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -38049,7 +38049,7 @@
         <v>45642</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -38106,7 +38106,7 @@
         <v>44312</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -38163,7 +38163,7 @@
         <v>45345.65929398148</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -38225,7 +38225,7 @@
         <v>45453.6619212963</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -38282,7 +38282,7 @@
         <v>45569.6909837963</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -38339,7 +38339,7 @@
         <v>44853.41693287037</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -38396,7 +38396,7 @@
         <v>45673.65925925926</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -38458,7 +38458,7 @@
         <v>45705.32643518518</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -38515,7 +38515,7 @@
         <v>45173</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -38577,7 +38577,7 @@
         <v>45533.67138888889</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -38634,7 +38634,7 @@
         <v>45196</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -38696,7 +38696,7 @@
         <v>45279.57732638889</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -38753,7 +38753,7 @@
         <v>45733.59667824074</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -38815,7 +38815,7 @@
         <v>45209.45420138889</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -38872,7 +38872,7 @@
         <v>45159.46996527778</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -38934,7 +38934,7 @@
         <v>45786.66425925926</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -38996,7 +38996,7 @@
         <v>45630.5731712963</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -39058,7 +39058,7 @@
         <v>45568</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -39120,7 +39120,7 @@
         <v>45432</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -39182,7 +39182,7 @@
         <v>44708.48859953704</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -39244,7 +39244,7 @@
         <v>45786.66853009259</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -39306,7 +39306,7 @@
         <v>45510</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -39368,7 +39368,7 @@
         <v>45531.78386574074</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -39425,7 +39425,7 @@
         <v>44957</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -39487,7 +39487,7 @@
         <v>44638.44958333333</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -39544,7 +39544,7 @@
         <v>45737.37006944444</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -39601,7 +39601,7 @@
         <v>45216</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -39658,7 +39658,7 @@
         <v>45559</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -39715,7 +39715,7 @@
         <v>45786.66209490741</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -39777,7 +39777,7 @@
         <v>45484.65768518519</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -39839,7 +39839,7 @@
         <v>44348</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -39896,7 +39896,7 @@
         <v>45786.66032407407</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -39958,7 +39958,7 @@
         <v>45264.92637731481</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -40015,7 +40015,7 @@
         <v>45546.54530092593</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -40072,7 +40072,7 @@
         <v>44474.59423611111</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -40129,7 +40129,7 @@
         <v>45406</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -40191,7 +40191,7 @@
         <v>44424</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -40248,7 +40248,7 @@
         <v>44823.84673611111</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -40305,7 +40305,7 @@
         <v>44209</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -40367,7 +40367,7 @@
         <v>45790.43</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -40429,7 +40429,7 @@
         <v>44928</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -40491,7 +40491,7 @@
         <v>44928.48072916667</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -40553,7 +40553,7 @@
         <v>44985</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -40615,7 +40615,7 @@
         <v>44631.37701388889</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -40677,7 +40677,7 @@
         <v>45397.64855324074</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -40734,7 +40734,7 @@
         <v>45205</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -40791,7 +40791,7 @@
         <v>45517.39274305556</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -40853,7 +40853,7 @@
         <v>45474.54432870371</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -40910,7 +40910,7 @@
         <v>45790.87653935186</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -40967,7 +40967,7 @@
         <v>44925.60457175926</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -41029,7 +41029,7 @@
         <v>44925.64309027778</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -41091,7 +41091,7 @@
         <v>44928.36418981481</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -41153,7 +41153,7 @@
         <v>45792.64795138889</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -41210,7 +41210,7 @@
         <v>45792.50942129629</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -41272,7 +41272,7 @@
         <v>45159</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -41334,7 +41334,7 @@
         <v>45159</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -41396,7 +41396,7 @@
         <v>44423</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -41453,7 +41453,7 @@
         <v>45408</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -41510,7 +41510,7 @@
         <v>44153</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -41567,7 +41567,7 @@
         <v>45793.41994212963</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -41629,7 +41629,7 @@
         <v>45484.57285879629</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -41691,7 +41691,7 @@
         <v>45063</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -41748,7 +41748,7 @@
         <v>45792.65047453704</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -41805,7 +41805,7 @@
         <v>45642</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -41862,7 +41862,7 @@
         <v>45644.56674768519</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -41924,7 +41924,7 @@
         <v>45685.52405092592</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -41986,7 +41986,7 @@
         <v>45607</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -42048,7 +42048,7 @@
         <v>45632.65197916667</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -42105,7 +42105,7 @@
         <v>45631</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -42167,7 +42167,7 @@
         <v>44435</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -42229,7 +42229,7 @@
         <v>45754.67329861111</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -42286,7 +42286,7 @@
         <v>45742.42793981481</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -42348,7 +42348,7 @@
         <v>44231</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -42410,7 +42410,7 @@
         <v>45644.50141203704</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -42472,7 +42472,7 @@
         <v>45569</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -42534,7 +42534,7 @@
         <v>44225</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -42591,7 +42591,7 @@
         <v>45772.46951388889</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -42653,7 +42653,7 @@
         <v>45303.5187037037</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -42710,7 +42710,7 @@
         <v>44939.45376157408</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -42767,7 +42767,7 @@
         <v>45740.44842592593</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -42829,7 +42829,7 @@
         <v>45618.35097222222</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -42886,7 +42886,7 @@
         <v>45796.39770833333</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -42943,7 +42943,7 @@
         <v>45631</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -43005,7 +43005,7 @@
         <v>45791</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -43062,7 +43062,7 @@
         <v>45796.57802083333</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -43119,7 +43119,7 @@
         <v>45588.56039351852</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -43176,7 +43176,7 @@
         <v>45797.37096064815</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -43233,7 +43233,7 @@
         <v>45118.91633101852</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -43290,7 +43290,7 @@
         <v>45533.75398148148</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -43347,7 +43347,7 @@
         <v>44924.61315972222</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -43409,7 +43409,7 @@
         <v>45719.45277777778</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -43466,7 +43466,7 @@
         <v>45621</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -43528,7 +43528,7 @@
         <v>45212</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -43585,7 +43585,7 @@
         <v>45728.61006944445</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -43642,7 +43642,7 @@
         <v>45830</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -43699,7 +43699,7 @@
         <v>45830</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -43756,7 +43756,7 @@
         <v>45830</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -43813,7 +43813,7 @@
         <v>45730</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -43870,7 +43870,7 @@
         <v>45453.6672800926</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -43927,7 +43927,7 @@
         <v>45768.29289351852</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -43989,7 +43989,7 @@
         <v>45768.30086805556</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -44051,7 +44051,7 @@
         <v>45799.64804398148</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -44113,7 +44113,7 @@
         <v>45674.57393518519</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -44170,7 +44170,7 @@
         <v>45517.69590277778</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -44232,7 +44232,7 @@
         <v>45063.92605324074</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -44289,7 +44289,7 @@
         <v>44827</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -44346,7 +44346,7 @@
         <v>44958</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -44408,7 +44408,7 @@
         <v>45496.67178240741</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -44470,7 +44470,7 @@
         <v>45642.35256944445</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -44527,7 +44527,7 @@
         <v>45685.50063657408</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -44589,7 +44589,7 @@
         <v>45063</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -44646,7 +44646,7 @@
         <v>45799.4658912037</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -44708,7 +44708,7 @@
         <v>45799.46642361111</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -44765,7 +44765,7 @@
         <v>45830</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -44822,7 +44822,7 @@
         <v>44075</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -44879,7 +44879,7 @@
         <v>45638.416875</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -44941,7 +44941,7 @@
         <v>45799.43550925926</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -45003,7 +45003,7 @@
         <v>45799.47225694444</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -45065,7 +45065,7 @@
         <v>44886</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -45127,7 +45127,7 @@
         <v>45531.66196759259</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -45189,7 +45189,7 @@
         <v>45509.5980787037</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -45251,7 +45251,7 @@
         <v>45429.39</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -45308,7 +45308,7 @@
         <v>44460.44315972222</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -45370,7 +45370,7 @@
         <v>45477.62255787037</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -45432,7 +45432,7 @@
         <v>45799.45770833334</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -45494,7 +45494,7 @@
         <v>45484.48854166667</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -45556,7 +45556,7 @@
         <v>45345</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -45618,7 +45618,7 @@
         <v>45407.36894675926</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -45680,7 +45680,7 @@
         <v>45799.57883101852</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -45737,7 +45737,7 @@
         <v>45799.43086805556</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -45799,7 +45799,7 @@
         <v>44153</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -45861,7 +45861,7 @@
         <v>45800.64065972222</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -45923,7 +45923,7 @@
         <v>45630.62513888889</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -45980,7 +45980,7 @@
         <v>45624.36858796296</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -46037,7 +46037,7 @@
         <v>45803.37480324074</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -46094,7 +46094,7 @@
         <v>44757.37524305555</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -46151,7 +46151,7 @@
         <v>45631.39950231482</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -46213,7 +46213,7 @@
         <v>45751.65657407408</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -46275,7 +46275,7 @@
         <v>45237.5815162037</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -46332,7 +46332,7 @@
         <v>44082</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -46394,7 +46394,7 @@
         <v>45625.56934027778</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -46456,7 +46456,7 @@
         <v>45837</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -46513,7 +46513,7 @@
         <v>45834</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -46570,7 +46570,7 @@
         <v>45800.63738425926</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -46632,7 +46632,7 @@
         <v>45800.37524305555</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -46694,7 +46694,7 @@
         <v>45800.58859953703</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -46751,7 +46751,7 @@
         <v>45800.59567129629</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -46813,7 +46813,7 @@
         <v>45800.64719907408</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -46875,7 +46875,7 @@
         <v>45800.65341435185</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -46937,7 +46937,7 @@
         <v>45800.42797453704</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -46994,7 +46994,7 @@
         <v>45800.44090277778</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -47051,7 +47051,7 @@
         <v>45800.66043981481</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -47113,7 +47113,7 @@
         <v>45800.33436342593</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -47175,7 +47175,7 @@
         <v>45800.3425</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -47237,7 +47237,7 @@
         <v>45800.44868055556</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -47299,7 +47299,7 @@
         <v>45800.4687962963</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -47361,7 +47361,7 @@
         <v>45800.56222222222</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -47423,7 +47423,7 @@
         <v>45800.46069444445</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -47485,7 +47485,7 @@
         <v>45800.56995370371</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -47547,7 +47547,7 @@
         <v>45800.35670138889</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -47609,7 +47609,7 @@
         <v>45803.37258101852</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -47666,7 +47666,7 @@
         <v>45800.48060185185</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -47728,7 +47728,7 @@
         <v>45800.3503587963</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -47790,7 +47790,7 @@
         <v>45800.50431712963</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -47852,7 +47852,7 @@
         <v>45800.60508101852</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -47914,7 +47914,7 @@
         <v>45800.56313657408</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -47971,7 +47971,7 @@
         <v>45800.57837962963</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -48033,7 +48033,7 @@
         <v>45800.3787037037</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -48095,7 +48095,7 @@
         <v>45800.41883101852</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -48157,7 +48157,7 @@
         <v>45800.48515046296</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -48219,7 +48219,7 @@
         <v>44883</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -48276,7 +48276,7 @@
         <v>45275</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -48333,7 +48333,7 @@
         <v>45804.589375</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -48390,7 +48390,7 @@
         <v>45539.43545138889</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -48447,7 +48447,7 @@
         <v>44169</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -48504,7 +48504,7 @@
         <v>45061.36835648148</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -48561,7 +48561,7 @@
         <v>45433</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -48618,7 +48618,7 @@
         <v>44091</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -48675,7 +48675,7 @@
         <v>44728</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -48737,7 +48737,7 @@
         <v>45593.6821412037</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -48794,7 +48794,7 @@
         <v>45593.68434027778</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -48851,7 +48851,7 @@
         <v>45804.5813425926</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -48913,7 +48913,7 @@
         <v>45805.53280092592</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -48975,7 +48975,7 @@
         <v>45345.34219907408</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -49037,7 +49037,7 @@
         <v>45345.47642361111</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -49099,7 +49099,7 @@
         <v>45562.65759259259</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -49161,7 +49161,7 @@
         <v>45685</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -49223,7 +49223,7 @@
         <v>45345</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -49285,7 +49285,7 @@
         <v>45097</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -49347,7 +49347,7 @@
         <v>45807.58393518518</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -49409,7 +49409,7 @@
         <v>45485</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -49466,7 +49466,7 @@
         <v>45807.47479166667</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -49528,7 +49528,7 @@
         <v>45807.3409837963</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -49590,7 +49590,7 @@
         <v>45807.35476851852</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -49652,7 +49652,7 @@
         <v>45807.41287037037</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -49714,7 +49714,7 @@
         <v>45807.42212962963</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -49776,7 +49776,7 @@
         <v>45170.46923611111</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -49838,7 +49838,7 @@
         <v>45807.49436342593</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -49900,7 +49900,7 @@
         <v>45807.56403935186</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -49962,7 +49962,7 @@
         <v>45807.65438657408</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -50024,7 +50024,7 @@
         <v>45807.60333333333</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -50086,7 +50086,7 @@
         <v>45807.55893518519</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -50148,7 +50148,7 @@
         <v>45807.36304398148</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -50210,7 +50210,7 @@
         <v>45807.49045138889</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -50272,7 +50272,7 @@
         <v>45807.5684375</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -50334,7 +50334,7 @@
         <v>45807.63334490741</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -50396,7 +50396,7 @@
         <v>45807.45288194445</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -50458,7 +50458,7 @@
         <v>45617</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -50520,7 +50520,7 @@
         <v>45576.48657407407</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -50582,7 +50582,7 @@
         <v>45617</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -50644,7 +50644,7 @@
         <v>45616.49530092593</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -50701,7 +50701,7 @@
         <v>45041</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -50758,7 +50758,7 @@
         <v>45618</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -50815,7 +50815,7 @@
         <v>45807.41717592593</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -50877,7 +50877,7 @@
         <v>45807.43461805556</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -50939,7 +50939,7 @@
         <v>45807.44070601852</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -51001,7 +51001,7 @@
         <v>45807.44608796296</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -51063,7 +51063,7 @@
         <v>45807.49832175926</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -51125,7 +51125,7 @@
         <v>45807.58868055556</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -51187,7 +51187,7 @@
         <v>45807.59407407408</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -51249,7 +51249,7 @@
         <v>45532</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -51306,7 +51306,7 @@
         <v>45853.28325231482</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -51363,7 +51363,7 @@
         <v>44987.35637731481</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -51425,7 +51425,7 @@
         <v>44987</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -51487,7 +51487,7 @@
         <v>45852</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -51544,7 +51544,7 @@
         <v>45646</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -51601,7 +51601,7 @@
         <v>45622</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -51663,7 +51663,7 @@
         <v>45811.34564814815</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -51725,7 +51725,7 @@
         <v>45477.66773148148</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -51787,7 +51787,7 @@
         <v>44631.42353009259</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -51849,7 +51849,7 @@
         <v>45478.44497685185</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -51911,7 +51911,7 @@
         <v>45107</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -51968,7 +51968,7 @@
         <v>45481.3330787037</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -52030,7 +52030,7 @@
         <v>45601.58355324074</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -52087,7 +52087,7 @@
         <v>44858</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -52144,7 +52144,7 @@
         <v>45154</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -52201,7 +52201,7 @@
         <v>45610.55846064815</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -52263,7 +52263,7 @@
         <v>45811.34540509259</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -52325,7 +52325,7 @@
         <v>45853.62415509259</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -52387,7 +52387,7 @@
         <v>45852.48290509259</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -52444,7 +52444,7 @@
         <v>45811.34578703704</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -52506,7 +52506,7 @@
         <v>45853.61865740741</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -52563,7 +52563,7 @@
         <v>45496.67342592592</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -52625,7 +52625,7 @@
         <v>45764.44825231482</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -52687,7 +52687,7 @@
         <v>45764.44861111111</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -52749,7 +52749,7 @@
         <v>44853</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -52806,7 +52806,7 @@
         <v>44550.39550925926</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -52863,7 +52863,7 @@
         <v>45265</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -52920,7 +52920,7 @@
         <v>44925.59333333333</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -52982,7 +52982,7 @@
         <v>44818</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -53039,7 +53039,7 @@
         <v>44957</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -53101,7 +53101,7 @@
         <v>45177.9224537037</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -53158,7 +53158,7 @@
         <v>45195.61476851852</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -53215,7 +53215,7 @@
         <v>45154</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -53272,7 +53272,7 @@
         <v>45385</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -53329,7 +53329,7 @@
         <v>45854.40662037037</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -53391,7 +53391,7 @@
         <v>45111</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -53453,7 +53453,7 @@
         <v>45688.6749537037</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -53515,7 +53515,7 @@
         <v>45813.48734953703</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -53572,7 +53572,7 @@
         <v>45813.47074074074</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -53629,7 +53629,7 @@
         <v>44854</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -53691,7 +53691,7 @@
         <v>45280</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -53748,7 +53748,7 @@
         <v>45670.66085648148</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -53805,7 +53805,7 @@
         <v>45406.64024305555</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -53867,7 +53867,7 @@
         <v>45813.64590277777</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -53924,7 +53924,7 @@
         <v>45496.66903935185</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -53986,7 +53986,7 @@
         <v>45334</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -54048,7 +54048,7 @@
         <v>45509</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -54110,7 +54110,7 @@
         <v>45509</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -54172,7 +54172,7 @@
         <v>45685</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -54229,7 +54229,7 @@
         <v>45635.35274305556</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -54291,7 +54291,7 @@
         <v>45733</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -54348,7 +54348,7 @@
         <v>45854.44850694444</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -54410,7 +54410,7 @@
         <v>45854.44864583333</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -54472,7 +54472,7 @@
         <v>45506.3637962963</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -54529,7 +54529,7 @@
         <v>44475</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -54586,7 +54586,7 @@
         <v>45166.34795138889</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -54643,7 +54643,7 @@
         <v>44985</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -54705,7 +54705,7 @@
         <v>45559.43645833333</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -54767,7 +54767,7 @@
         <v>45665.563125</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -54829,7 +54829,7 @@
         <v>45362.64613425926</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -54886,7 +54886,7 @@
         <v>45362.65407407407</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -54943,7 +54943,7 @@
         <v>45817.33819444444</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -55005,7 +55005,7 @@
         <v>45483.47207175926</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -55062,7 +55062,7 @@
         <v>45817.62439814815</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -55119,7 +55119,7 @@
         <v>45203</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -55176,7 +55176,7 @@
         <v>45817.594375</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -55238,7 +55238,7 @@
         <v>45656.51157407407</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -55300,7 +55300,7 @@
         <v>45197.46966435185</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -55357,7 +55357,7 @@
         <v>45218.58609953704</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -55414,7 +55414,7 @@
         <v>45859</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -55471,7 +55471,7 @@
         <v>45680.42497685185</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -55528,7 +55528,7 @@
         <v>44722</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -55585,7 +55585,7 @@
         <v>44914</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -55667,7 +55667,7 @@
         <v>45485.42287037037</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -55724,7 +55724,7 @@
         <v>45485</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -55781,7 +55781,7 @@
         <v>45485.44258101852</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -55843,7 +55843,7 @@
         <v>45509.6427662037</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -55905,7 +55905,7 @@
         <v>45098.48666666666</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -55967,7 +55967,7 @@
         <v>45208</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -56024,7 +56024,7 @@
         <v>45303</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -56081,7 +56081,7 @@
         <v>45119</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -56138,7 +56138,7 @@
         <v>44312</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -56195,7 +56195,7 @@
         <v>44082</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -56257,7 +56257,7 @@
         <v>45260.59042824074</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -56314,7 +56314,7 @@
         <v>44883</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -56371,7 +56371,7 @@
         <v>45821.57201388889</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -56433,7 +56433,7 @@
         <v>45820.64821759259</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -56490,7 +56490,7 @@
         <v>45741.39084490741</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -56547,7 +56547,7 @@
         <v>45624.57098379629</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -56604,7 +56604,7 @@
         <v>45678.37956018518</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -56661,7 +56661,7 @@
         <v>45590.31899305555</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -56718,7 +56718,7 @@
         <v>44305</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -56775,7 +56775,7 @@
         <v>45622.64627314815</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -56832,7 +56832,7 @@
         <v>45485</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -56894,7 +56894,7 @@
         <v>45371.66217592593</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -56956,7 +56956,7 @@
         <v>45821.77903935185</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -57013,7 +57013,7 @@
         <v>45274</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -57070,7 +57070,7 @@
         <v>45154</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -57127,7 +57127,7 @@
         <v>45867.55305555555</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -57184,7 +57184,7 @@
         <v>45723.58140046296</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -57241,7 +57241,7 @@
         <v>45867.55642361111</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -57303,7 +57303,7 @@
         <v>45488</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -57360,7 +57360,7 @@
         <v>45238.64153935185</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -57417,7 +57417,7 @@
         <v>45866.40701388889</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -57474,7 +57474,7 @@
         <v>45866.62908564815</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -57531,7 +57531,7 @@
         <v>45827.41753472222</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -57593,7 +57593,7 @@
         <v>45826.43267361111</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -57655,7 +57655,7 @@
         <v>45075.59148148148</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -57717,7 +57717,7 @@
         <v>44091</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -57774,7 +57774,7 @@
         <v>45687.53689814815</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -57831,7 +57831,7 @@
         <v>45153.42725694444</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -57893,7 +57893,7 @@
         <v>45485</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -57955,7 +57955,7 @@
         <v>45485</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -58017,7 +58017,7 @@
         <v>45827</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -58074,7 +58074,7 @@
         <v>45691</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -58136,7 +58136,7 @@
         <v>45691</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -58198,7 +58198,7 @@
         <v>45509</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -58260,7 +58260,7 @@
         <v>45868.639375</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -58317,7 +58317,7 @@
         <v>45244</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -58374,7 +58374,7 @@
         <v>45159.60288194445</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -58431,7 +58431,7 @@
         <v>45763.4266087963</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -58488,7 +58488,7 @@
         <v>45791</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -58545,7 +58545,7 @@
         <v>45593.67809027778</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -58602,7 +58602,7 @@
         <v>45170.46134259259</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -58664,7 +58664,7 @@
         <v>45827.42467592593</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -58726,7 +58726,7 @@
         <v>45485</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -58783,7 +58783,7 @@
         <v>45735.60342592592</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -58840,7 +58840,7 @@
         <v>44987.34981481481</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -58902,7 +58902,7 @@
         <v>45460.47969907407</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -58959,7 +58959,7 @@
         <v>45460.48582175926</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -59016,7 +59016,7 @@
         <v>44180</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -59073,7 +59073,7 @@
         <v>45478.48700231482</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -59135,7 +59135,7 @@
         <v>45873.59511574074</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -59197,7 +59197,7 @@
         <v>45231</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -59254,7 +59254,7 @@
         <v>45345.4940625</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -59316,7 +59316,7 @@
         <v>45831</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -59378,7 +59378,7 @@
         <v>45582.59753472222</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -59440,7 +59440,7 @@
         <v>45875.5196875</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -59497,7 +59497,7 @@
         <v>45345.48181712963</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -59559,7 +59559,7 @@
         <v>45874.64199074074</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -59616,7 +59616,7 @@
         <v>45439.62893518519</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -59673,7 +59673,7 @@
         <v>45735.57390046296</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -59730,7 +59730,7 @@
         <v>45054</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -59792,7 +59792,7 @@
         <v>44642</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -59854,7 +59854,7 @@
         <v>45429</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -59911,7 +59911,7 @@
         <v>45874.64513888889</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -59968,7 +59968,7 @@
         <v>45832</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -60030,7 +60030,7 @@
         <v>45833</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -60092,7 +60092,7 @@
         <v>45833</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -60154,7 +60154,7 @@
         <v>45875.47854166666</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -60216,7 +60216,7 @@
         <v>45832</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -60278,7 +60278,7 @@
         <v>45833.36467592593</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -60340,7 +60340,7 @@
         <v>44385</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -60397,7 +60397,7 @@
         <v>45832.64047453704</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -60454,7 +60454,7 @@
         <v>45832.3859837963</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -60516,7 +60516,7 @@
         <v>45833</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -60578,7 +60578,7 @@
         <v>45833.6081712963</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -60640,7 +60640,7 @@
         <v>45342</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -60697,7 +60697,7 @@
         <v>44862</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -60759,7 +60759,7 @@
         <v>45832</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -60821,7 +60821,7 @@
         <v>45834.80229166667</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -60878,7 +60878,7 @@
         <v>45835.55998842593</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -60940,7 +60940,7 @@
         <v>45835.57069444445</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -60997,7 +60997,7 @@
         <v>45705.32456018519</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -61054,7 +61054,7 @@
         <v>45834</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -61116,7 +61116,7 @@
         <v>45834.7087962963</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -61173,7 +61173,7 @@
         <v>45834</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -61235,7 +61235,7 @@
         <v>45622.45239583333</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -61297,7 +61297,7 @@
         <v>45834.38173611111</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -61354,7 +61354,7 @@
         <v>45288.58685185185</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -61411,7 +61411,7 @@
         <v>44819.56722222222</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -61468,7 +61468,7 @@
         <v>45834.69577546296</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -61525,7 +61525,7 @@
         <v>45071.92488425926</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -61582,7 +61582,7 @@
         <v>45638</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -61644,7 +61644,7 @@
         <v>44886</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -61706,7 +61706,7 @@
         <v>45467</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -61763,7 +61763,7 @@
         <v>45642.41907407407</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -61820,7 +61820,7 @@
         <v>45204</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -61877,7 +61877,7 @@
         <v>45252.45481481482</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -61934,7 +61934,7 @@
         <v>45252.48409722222</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -61991,7 +61991,7 @@
         <v>45041</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -62048,7 +62048,7 @@
         <v>45245</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -62105,7 +62105,7 @@
         <v>45688.6769212963</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -62167,7 +62167,7 @@
         <v>45835.5583912037</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -62229,7 +62229,7 @@
         <v>45834.6568287037</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -62286,7 +62286,7 @@
         <v>45834</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -62343,7 +62343,7 @@
         <v>45215</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -62400,7 +62400,7 @@
         <v>45876.49113425926</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -62457,7 +62457,7 @@
         <v>45876.39362268519</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -62519,7 +62519,7 @@
         <v>45834.51079861111</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -62581,7 +62581,7 @@
         <v>45610.56706018518</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -62643,7 +62643,7 @@
         <v>45085</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -62700,7 +62700,7 @@
         <v>45834.71440972222</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -62757,7 +62757,7 @@
         <v>45881.36469907407</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -62814,7 +62814,7 @@
         <v>45390</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -62871,7 +62871,7 @@
         <v>45484</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -62933,7 +62933,7 @@
         <v>45881.6609375</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -62990,7 +62990,7 @@
         <v>45406</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -63052,7 +63052,7 @@
         <v>45670</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -63114,7 +63114,7 @@
         <v>45719.48778935185</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -63171,7 +63171,7 @@
         <v>45202</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -63233,7 +63233,7 @@
         <v>45839.5658912037</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -63290,7 +63290,7 @@
         <v>45644</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -63347,7 +63347,7 @@
         <v>44216</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -63409,7 +63409,7 @@
         <v>44216</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -63471,7 +63471,7 @@
         <v>45611.4021875</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -63528,7 +63528,7 @@
         <v>45881.46869212963</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -63585,7 +63585,7 @@
         <v>45881.43114583333</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -63642,7 +63642,7 @@
         <v>45118.3959375</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -63704,7 +63704,7 @@
         <v>45881.64365740741</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -63761,7 +63761,7 @@
         <v>45362.65903935185</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -63818,7 +63818,7 @@
         <v>45775.36589120371</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -63875,7 +63875,7 @@
         <v>45685.38901620371</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -63937,7 +63937,7 @@
         <v>44571</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -63994,7 +63994,7 @@
         <v>45173</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -64051,7 +64051,7 @@
         <v>45880.37472222222</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -64108,7 +64108,7 @@
         <v>45840.64394675926</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -64170,7 +64170,7 @@
         <v>45883.4108912037</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -64227,7 +64227,7 @@
         <v>44182</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -64284,7 +64284,7 @@
         <v>45883.35789351852</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -64341,7 +64341,7 @@
         <v>44998</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -64398,7 +64398,7 @@
         <v>44151</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -64455,7 +64455,7 @@
         <v>45575.6125925926</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -64517,7 +64517,7 @@
         <v>45882.64755787037</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -64579,7 +64579,7 @@
         <v>45883.51854166666</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -64636,7 +64636,7 @@
         <v>45882.63179398148</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -64698,7 +64698,7 @@
         <v>45841.69273148148</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -64755,7 +64755,7 @@
         <v>45705.72106481482</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -64812,7 +64812,7 @@
         <v>45883.40538194445</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -64869,7 +64869,7 @@
         <v>45841.4312037037</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -64926,7 +64926,7 @@
         <v>45841.46512731481</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -64988,7 +64988,7 @@
         <v>44708.45504629629</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -65050,7 +65050,7 @@
         <v>45883.58944444444</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -65112,7 +65112,7 @@
         <v>45568</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -65174,7 +65174,7 @@
         <v>45841.45137731481</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -65231,7 +65231,7 @@
         <v>45239.43173611111</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -65293,7 +65293,7 @@
         <v>44214</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -65355,7 +65355,7 @@
         <v>45845.6920949074</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -65417,7 +65417,7 @@
         <v>45772.36106481482</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -65479,7 +65479,7 @@
         <v>45569</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -65541,7 +65541,7 @@
         <v>45876</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -65603,7 +65603,7 @@
         <v>45667</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -65665,7 +65665,7 @@
         <v>45887.59913194444</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -65727,7 +65727,7 @@
         <v>45225.58005787037</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -65784,7 +65784,7 @@
         <v>45569</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -65846,7 +65846,7 @@
         <v>44314</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -65903,7 +65903,7 @@
         <v>44925.33584490741</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -65965,7 +65965,7 @@
         <v>44925</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -66022,7 +66022,7 @@
         <v>45049.59826388889</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -66079,7 +66079,7 @@
         <v>45632</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -66136,7 +66136,7 @@
         <v>45845.55270833334</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -66193,7 +66193,7 @@
         <v>45632</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -66250,7 +66250,7 @@
         <v>45568</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -66312,7 +66312,7 @@
         <v>45621</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -66374,7 +66374,7 @@
         <v>45170.4643287037</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -66436,7 +66436,7 @@
         <v>45887.50216435185</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -66498,7 +66498,7 @@
         <v>45568</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -66560,7 +66560,7 @@
         <v>45730</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -66617,7 +66617,7 @@
         <v>45622</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -66674,7 +66674,7 @@
         <v>45730</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -66731,7 +66731,7 @@
         <v>45842.48990740741</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -66788,7 +66788,7 @@
         <v>45755</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -66845,7 +66845,7 @@
         <v>45637.39587962963</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -66907,7 +66907,7 @@
         <v>45560.33311342593</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -66969,7 +66969,7 @@
         <v>45684.51006944444</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -67026,7 +67026,7 @@
         <v>45632</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -67083,7 +67083,7 @@
         <v>45728</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -67140,7 +67140,7 @@
         <v>44698</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -67202,7 +67202,7 @@
         <v>45869</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -67259,7 +67259,7 @@
         <v>45884.55263888889</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -67321,7 +67321,7 @@
         <v>45604.32543981481</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -67383,7 +67383,7 @@
         <v>45569</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -67445,7 +67445,7 @@
         <v>45447.35144675926</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -67502,7 +67502,7 @@
         <v>45845.60496527778</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -67559,7 +67559,7 @@
         <v>45885</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -67616,7 +67616,7 @@
         <v>45876</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -67678,7 +67678,7 @@
         <v>45869</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -67735,7 +67735,7 @@
         <v>45869</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -67792,7 +67792,7 @@
         <v>45845.55259259259</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -67849,7 +67849,7 @@
         <v>45845.55266203704</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -67906,7 +67906,7 @@
         <v>44484.55535879629</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -67963,7 +67963,7 @@
         <v>45238.46430555556</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -68020,7 +68020,7 @@
         <v>45631.63091435185</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -68077,7 +68077,7 @@
         <v>45888.59509259259</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -68134,7 +68134,7 @@
         <v>44229</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -68196,7 +68196,7 @@
         <v>44225</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -68253,7 +68253,7 @@
         <v>45727.35621527778</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -68315,7 +68315,7 @@
         <v>45012</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -68377,7 +68377,7 @@
         <v>45861</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -68439,7 +68439,7 @@
         <v>45254</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -68496,7 +68496,7 @@
         <v>45847.58865740741</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -68558,7 +68558,7 @@
         <v>44565.31975694445</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -68620,7 +68620,7 @@
         <v>45737.3787962963</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -68677,7 +68677,7 @@
         <v>45888.78833333333</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -68734,7 +68734,7 @@
         <v>45888.78960648148</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -68791,7 +68791,7 @@
         <v>44565</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -68853,7 +68853,7 @@
         <v>45505</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -68915,7 +68915,7 @@
         <v>45888.78539351852</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -68972,7 +68972,7 @@
         <v>45253.55737268519</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -69029,7 +69029,7 @@
         <v>45889.40916666666</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -69086,7 +69086,7 @@
         <v>45889.41715277778</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -69143,7 +69143,7 @@
         <v>45362.67789351852</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -69200,7 +69200,7 @@
         <v>44972.57449074074</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -69257,7 +69257,7 @@
         <v>45257</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -69314,7 +69314,7 @@
         <v>45848.45113425926</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -69376,7 +69376,7 @@
         <v>45758.66108796297</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -69433,7 +69433,7 @@
         <v>45758.69123842593</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -69490,7 +69490,7 @@
         <v>45670.4570949074</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -69552,7 +69552,7 @@
         <v>45848.65003472222</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -69609,7 +69609,7 @@
         <v>45688.67145833333</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -69671,7 +69671,7 @@
         <v>44665</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -69728,7 +69728,7 @@
         <v>45849</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -69785,7 +69785,7 @@
         <v>45282.64012731481</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -69847,7 +69847,7 @@
         <v>45848</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -69909,7 +69909,7 @@
         <v>45848.57644675926</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -69971,7 +69971,7 @@
         <v>45848.6568287037</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -70028,7 +70028,7 @@
         <v>45848.68640046296</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -70090,7 +70090,7 @@
         <v>45848.62873842593</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -70147,7 +70147,7 @@
         <v>45848.639375</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -70204,7 +70204,7 @@
         <v>44987.35282407407</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -70266,7 +70266,7 @@
         <v>45848.35400462963</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -70323,7 +70323,7 @@
         <v>45768.29630787037</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -70385,7 +70385,7 @@
         <v>45768.30954861111</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -70447,7 +70447,7 @@
         <v>44440</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -70504,7 +70504,7 @@
         <v>44628.36402777778</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -70561,7 +70561,7 @@
         <v>45195.3878125</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -70618,7 +70618,7 @@
         <v>44994</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -70675,7 +70675,7 @@
         <v>45351</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -70732,7 +70732,7 @@
         <v>44414.58354166667</v>
       </c>
       <c r="C1075" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
@@ -70789,7 +70789,7 @@
         <v>45229.92739583334</v>
       </c>
       <c r="C1076" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
@@ -70846,7 +70846,7 @@
         <v>45751.34636574074</v>
       </c>
       <c r="C1077" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
@@ -70908,7 +70908,7 @@
         <v>45731.69629629629</v>
       </c>
       <c r="C1078" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1078" t="inlineStr">
         <is>
@@ -70965,7 +70965,7 @@
         <v>45763.4178587963</v>
       </c>
       <c r="C1079" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1079" t="inlineStr">
         <is>
@@ -71022,7 +71022,7 @@
         <v>45509</v>
       </c>
       <c r="C1080" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
@@ -71084,7 +71084,7 @@
         <v>45733.38637731481</v>
       </c>
       <c r="C1081" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1081" t="inlineStr">
         <is>
@@ -71141,7 +71141,7 @@
         <v>45174</v>
       </c>
       <c r="C1082" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1082" t="inlineStr">
         <is>
@@ -71198,7 +71198,7 @@
         <v>45624.63614583333</v>
       </c>
       <c r="C1083" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1083" t="inlineStr">
         <is>
@@ -71260,7 +71260,7 @@
         <v>45041</v>
       </c>
       <c r="C1084" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1084" t="inlineStr">
         <is>
@@ -71317,7 +71317,7 @@
         <v>45491.5859375</v>
       </c>
       <c r="C1085" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1085" t="inlineStr">
         <is>
@@ -71374,7 +71374,7 @@
         <v>45632</v>
       </c>
       <c r="C1086" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1086" t="inlineStr">
         <is>
@@ -71431,7 +71431,7 @@
         <v>45509</v>
       </c>
       <c r="C1087" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1087" t="inlineStr">
         <is>
@@ -71493,7 +71493,7 @@
         <v>45687.65449074074</v>
       </c>
       <c r="C1088" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1088" t="inlineStr">
         <is>
@@ -71555,7 +71555,7 @@
         <v>44708</v>
       </c>
       <c r="C1089" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1089" t="inlineStr">
         <is>
@@ -71617,7 +71617,7 @@
         <v>44964</v>
       </c>
       <c r="C1090" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1090" t="inlineStr">
         <is>
@@ -71674,7 +71674,7 @@
         <v>45761.61501157407</v>
       </c>
       <c r="C1091" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1091" t="inlineStr">
         <is>

--- a/Översikt HÄRJEDALEN.xlsx
+++ b/Översikt HÄRJEDALEN.xlsx
@@ -567,7 +567,7 @@
         <v>45513</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         <v>45763</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>44785</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>44790</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>44553</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>44837</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>44844</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>44749</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>44406</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>45691</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>44182</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>44154.40430555555</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>45761.58262731481</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>45531</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>44831</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>44496.94013888889</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>45667</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
         <v>44865.57574074074</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>45180</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
         <v>44650</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>45250</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>45351</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3043,7 +3043,7 @@
         <v>44200</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>44193</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>45554</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         <v>45631</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         <v>45544.35653935185</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>44501</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3681,7 +3681,7 @@
         <v>44182</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>44690</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>44487</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
         <v>45631</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>45625.49736111111</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4211,7 +4211,7 @@
         <v>44406</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         <v>45544</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4409,7 +4409,7 @@
         <v>44440</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4506,7 +4506,7 @@
         <v>45837</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         <v>45106</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>45217</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>45571</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         <v>44774</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>44357</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         <v>45457.38396990741</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5212,7 +5212,7 @@
         <v>45175</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
         <v>45544</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         <v>45198</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5527,7 +5527,7 @@
         <v>45531</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         <v>45477.46537037037</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
         <v>45694</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>45411</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>45833.43898148148</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>44553</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>45471.59034722222</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
         <v>44517</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6320,7 +6320,7 @@
         <v>45614.45413194445</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6426,7 +6426,7 @@
         <v>44406</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6523,7 +6523,7 @@
         <v>44553</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6620,7 +6620,7 @@
         <v>44377</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
         <v>45426</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6808,7 +6808,7 @@
         <v>45741.82913194445</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6900,7 +6900,7 @@
         <v>45677.45212962963</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         <v>44430</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7092,7 +7092,7 @@
         <v>44553</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         <v>45715</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7288,7 +7288,7 @@
         <v>45007</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         <v>45531.45444444445</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7483,7 +7483,7 @@
         <v>44242</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7573,7 +7573,7 @@
         <v>45616.6450462963</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7671,7 +7671,7 @@
         <v>45568</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7766,7 +7766,7 @@
         <v>45559</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7865,7 +7865,7 @@
         <v>45772.51116898148</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7960,7 +7960,7 @@
         <v>45719</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
         <v>45574</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8148,7 +8148,7 @@
         <v>45625.45384259259</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8251,7 +8251,7 @@
         <v>45869</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8345,7 +8345,7 @@
         <v>44882</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8438,7 +8438,7 @@
         <v>44517</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8527,7 +8527,7 @@
         <v>45243</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8620,7 +8620,7 @@
         <v>44979</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8709,7 +8709,7 @@
         <v>45432.94736111111</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8807,7 +8807,7 @@
         <v>44430</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8908,7 +8908,7 @@
         <v>44294</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>44294</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9084,7 +9084,7 @@
         <v>44977</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9181,7 +9181,7 @@
         <v>45694</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9269,7 +9269,7 @@
         <v>45467.47204861111</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9362,7 +9362,7 @@
         <v>45085</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9454,7 +9454,7 @@
         <v>44377</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9546,7 +9546,7 @@
         <v>45559.38894675926</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9643,7 +9643,7 @@
         <v>44957</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9735,7 +9735,7 @@
         <v>45531.45752314815</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         <v>45537.45818287037</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9920,7 +9920,7 @@
         <v>45007</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10013,7 +10013,7 @@
         <v>45838.73927083334</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10106,7 +10106,7 @@
         <v>45506.35658564815</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10198,7 +10198,7 @@
         <v>44476</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10290,7 +10290,7 @@
         <v>45552</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10378,7 +10378,7 @@
         <v>44475</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
         <v>44441</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10552,7 +10552,7 @@
         <v>44475</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10639,7 +10639,7 @@
         <v>44475</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10726,7 +10726,7 @@
         <v>44713</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10826,7 +10826,7 @@
         <v>45791</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10913,7 +10913,7 @@
         <v>45800.3484375</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11005,7 +11005,7 @@
         <v>45617</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11101,7 +11101,7 @@
         <v>44107</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11197,7 +11197,7 @@
         <v>45821.56523148148</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11289,7 +11289,7 @@
         <v>45841.41003472222</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>45468</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         <v>45849.35011574074</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11550,7 +11550,7 @@
         <v>44180</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>44074</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11738,7 +11738,7 @@
         <v>44186</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11829,7 +11829,7 @@
         <v>44677</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11920,7 +11920,7 @@
         <v>44286</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12006,7 +12006,7 @@
         <v>44221</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12092,7 +12092,7 @@
         <v>44475</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12178,7 +12178,7 @@
         <v>44866.46503472222</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12273,7 +12273,7 @@
         <v>45772.51070601852</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12364,7 +12364,7 @@
         <v>45191</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12455,7 +12455,7 @@
         <v>44853</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12545,7 +12545,7 @@
         <v>45786.66594907407</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12636,7 +12636,7 @@
         <v>45786.67016203704</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12727,7 +12727,7 @@
         <v>45786.6768287037</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12818,7 +12818,7 @@
         <v>45786.6590625</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12909,7 +12909,7 @@
         <v>45786.65452546296</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13000,7 +13000,7 @@
         <v>44987</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13095,7 +13095,7 @@
         <v>45786.67261574074</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13186,7 +13186,7 @@
         <v>44449</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13272,7 +13272,7 @@
         <v>45772.36488425926</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13367,7 +13367,7 @@
         <v>45644.56555555556</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>45153</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13552,7 +13552,7 @@
         <v>45595.58056712963</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13643,7 +13643,7 @@
         <v>45694</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13729,7 +13729,7 @@
         <v>45805.73822916667</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13820,7 +13820,7 @@
         <v>45833</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -13906,7 +13906,7 @@
         <v>45035</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14001,7 +14001,7 @@
         <v>44955</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
         <v>45880.37559027778</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14177,7 +14177,7 @@
         <v>45621</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14272,7 +14272,7 @@
         <v>45552</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14362,7 +14362,7 @@
         <v>45538</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14453,7 +14453,7 @@
         <v>44475</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14539,7 +14539,7 @@
         <v>44096</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14629,7 +14629,7 @@
         <v>44475</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14714,7 +14714,7 @@
         <v>44321</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -14804,7 +14804,7 @@
         <v>44475</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -14889,7 +14889,7 @@
         <v>44475</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -14974,7 +14974,7 @@
         <v>44113</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15059,7 +15059,7 @@
         <v>44105</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15144,7 +15144,7 @@
         <v>45538.57630787037</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15233,7 +15233,7 @@
         <v>45621.47555555555</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15323,7 +15323,7 @@
         <v>45603</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15413,7 +15413,7 @@
         <v>44475</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -15498,7 +15498,7 @@
         <v>45729.64623842593</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
         <v>45345</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -15678,7 +15678,7 @@
         <v>44769.48783564815</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -15768,7 +15768,7 @@
         <v>45111</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -15858,7 +15858,7 @@
         <v>45638.33607638889</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -15948,7 +15948,7 @@
         <v>45714.55248842593</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16042,7 +16042,7 @@
         <v>45320</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16127,7 +16127,7 @@
         <v>45308</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -16216,7 +16216,7 @@
         <v>45457.38677083333</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -16306,7 +16306,7 @@
         <v>45540.69512731482</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -16396,7 +16396,7 @@
         <v>45800.63043981481</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -16490,7 +16490,7 @@
         <v>45805.66601851852</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -16584,7 +16584,7 @@
         <v>45791</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -16669,7 +16669,7 @@
         <v>45805.73546296296</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -16759,7 +16759,7 @@
         <v>45617</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -16853,7 +16853,7 @@
         <v>45454.62443287037</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -16938,7 +16938,7 @@
         <v>45812.82244212963</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17028,7 +17028,7 @@
         <v>45672.50416666667</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17113,7 +17113,7 @@
         <v>45835.7499537037</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -17203,7 +17203,7 @@
         <v>45838.773125</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -17293,7 +17293,7 @@
         <v>45869</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -17378,7 +17378,7 @@
         <v>45889.56214120371</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -17468,7 +17468,7 @@
         <v>45758.70164351852</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -17553,7 +17553,7 @@
         <v>45875</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -17642,7 +17642,7 @@
         <v>44320</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -17699,7 +17699,7 @@
         <v>44316</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -17756,7 +17756,7 @@
         <v>44320</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -17818,7 +17818,7 @@
         <v>44105</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -17875,7 +17875,7 @@
         <v>44810</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -17937,7 +17937,7 @@
         <v>44727.70908564814</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -17999,7 +17999,7 @@
         <v>44430</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -18061,7 +18061,7 @@
         <v>44543</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -18118,7 +18118,7 @@
         <v>44614</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -18180,7 +18180,7 @@
         <v>44404</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -18237,7 +18237,7 @@
         <v>44417.38271990741</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -18294,7 +18294,7 @@
         <v>44417.38614583333</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -18351,7 +18351,7 @@
         <v>44497</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -18408,7 +18408,7 @@
         <v>44475</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -18465,7 +18465,7 @@
         <v>44361</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -18522,7 +18522,7 @@
         <v>44540</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -18584,7 +18584,7 @@
         <v>44531</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -18641,7 +18641,7 @@
         <v>44600</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -18698,7 +18698,7 @@
         <v>44475</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -18755,7 +18755,7 @@
         <v>44385.93652777778</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -18817,7 +18817,7 @@
         <v>44475</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>44406</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -18931,7 +18931,7 @@
         <v>44854</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -18988,7 +18988,7 @@
         <v>44538</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -19050,7 +19050,7 @@
         <v>44102</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -19107,7 +19107,7 @@
         <v>44823</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -19169,7 +19169,7 @@
         <v>44316</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -19226,7 +19226,7 @@
         <v>44424</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -19283,7 +19283,7 @@
         <v>44483</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -19340,7 +19340,7 @@
         <v>44421</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -19397,7 +19397,7 @@
         <v>44418</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -19459,7 +19459,7 @@
         <v>44488</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -19521,7 +19521,7 @@
         <v>44132</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -19578,7 +19578,7 @@
         <v>44603</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -19640,7 +19640,7 @@
         <v>44418</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -19702,7 +19702,7 @@
         <v>44564.6747337963</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -19764,7 +19764,7 @@
         <v>44361</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -19826,7 +19826,7 @@
         <v>44615</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -19888,7 +19888,7 @@
         <v>44466.81701388889</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -19945,7 +19945,7 @@
         <v>44218</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -20002,7 +20002,7 @@
         <v>44286</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -20059,7 +20059,7 @@
         <v>44475</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -20116,7 +20116,7 @@
         <v>44475</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -20173,7 +20173,7 @@
         <v>44410.74284722222</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -20230,7 +20230,7 @@
         <v>44631</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -20292,7 +20292,7 @@
         <v>44631.41535879629</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>44728</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -20411,7 +20411,7 @@
         <v>44810</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -20473,7 +20473,7 @@
         <v>44417.37519675926</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -20530,7 +20530,7 @@
         <v>44344</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -20587,7 +20587,7 @@
         <v>44174</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -20644,7 +20644,7 @@
         <v>44084</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -20706,7 +20706,7 @@
         <v>44475</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -20763,7 +20763,7 @@
         <v>44078</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -20820,7 +20820,7 @@
         <v>44179</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -20877,7 +20877,7 @@
         <v>44258</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -20934,7 +20934,7 @@
         <v>44424</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -20991,7 +20991,7 @@
         <v>44424</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -21048,7 +21048,7 @@
         <v>44818</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -21105,7 +21105,7 @@
         <v>44770.53315972222</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -21162,7 +21162,7 @@
         <v>44690</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -21219,7 +21219,7 @@
         <v>44285</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -21276,7 +21276,7 @@
         <v>44286</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -21333,7 +21333,7 @@
         <v>44792.68023148148</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -21390,7 +21390,7 @@
         <v>44385.93658564815</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -21452,7 +21452,7 @@
         <v>44243.63096064814</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -21509,7 +21509,7 @@
         <v>44298</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -21566,7 +21566,7 @@
         <v>44183</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -21623,7 +21623,7 @@
         <v>44319</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -21680,7 +21680,7 @@
         <v>44316</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -21737,7 +21737,7 @@
         <v>44316</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -21794,7 +21794,7 @@
         <v>44126</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -21851,7 +21851,7 @@
         <v>44825</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -21908,7 +21908,7 @@
         <v>44174</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -21965,7 +21965,7 @@
         <v>44154</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -22027,7 +22027,7 @@
         <v>44396</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -22084,7 +22084,7 @@
         <v>44475</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -22141,7 +22141,7 @@
         <v>44127</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -22203,7 +22203,7 @@
         <v>44475</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -22260,7 +22260,7 @@
         <v>44475</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -22317,7 +22317,7 @@
         <v>44475</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -22374,7 +22374,7 @@
         <v>44475</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -22431,7 +22431,7 @@
         <v>44544</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -22493,7 +22493,7 @@
         <v>44420.33096064815</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -22550,7 +22550,7 @@
         <v>44188</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -22612,7 +22612,7 @@
         <v>44483.36435185185</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -22669,7 +22669,7 @@
         <v>44417</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -22726,7 +22726,7 @@
         <v>44181</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -22788,7 +22788,7 @@
         <v>44426.45706018519</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -22845,7 +22845,7 @@
         <v>44859</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -22907,7 +22907,7 @@
         <v>44473</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -22964,7 +22964,7 @@
         <v>44314</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -23021,7 +23021,7 @@
         <v>44727.71858796296</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -23083,7 +23083,7 @@
         <v>44335.4837962963</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -23140,7 +23140,7 @@
         <v>44475</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -23197,7 +23197,7 @@
         <v>44543</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -23259,7 +23259,7 @@
         <v>44475</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -23316,7 +23316,7 @@
         <v>44475</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -23373,7 +23373,7 @@
         <v>44481.67951388889</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -23430,7 +23430,7 @@
         <v>44725</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -23492,7 +23492,7 @@
         <v>44631.37421296296</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -23554,7 +23554,7 @@
         <v>44230</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -23611,7 +23611,7 @@
         <v>44538</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -23673,7 +23673,7 @@
         <v>44855.60383101852</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -23730,7 +23730,7 @@
         <v>44133</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -23792,7 +23792,7 @@
         <v>44631.45398148148</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -23854,7 +23854,7 @@
         <v>44417.37207175926</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -23911,7 +23911,7 @@
         <v>44768.44859953703</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -23968,7 +23968,7 @@
         <v>44475</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -24025,7 +24025,7 @@
         <v>44475</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -24082,7 +24082,7 @@
         <v>44475</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -24139,7 +24139,7 @@
         <v>44475</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -24196,7 +24196,7 @@
         <v>44368</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -24253,7 +24253,7 @@
         <v>44403</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -24310,7 +24310,7 @@
         <v>44886.62578703704</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -24367,7 +24367,7 @@
         <v>44886.629375</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -24424,7 +24424,7 @@
         <v>44838</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -24486,7 +24486,7 @@
         <v>44708.46081018518</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -24548,7 +24548,7 @@
         <v>44684</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -24610,7 +24610,7 @@
         <v>44126</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -24672,7 +24672,7 @@
         <v>44540.56034722222</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -24729,7 +24729,7 @@
         <v>44872</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -24791,7 +24791,7 @@
         <v>44169</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -24848,7 +24848,7 @@
         <v>44531</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -24905,7 +24905,7 @@
         <v>44180</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -24962,7 +24962,7 @@
         <v>44207</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -25024,7 +25024,7 @@
         <v>44742</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -25086,7 +25086,7 @@
         <v>44270</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -25143,7 +25143,7 @@
         <v>44166</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -25205,7 +25205,7 @@
         <v>44531</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -25262,7 +25262,7 @@
         <v>44531</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -25319,7 +25319,7 @@
         <v>44788.67976851852</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -25381,7 +25381,7 @@
         <v>44316</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -25438,7 +25438,7 @@
         <v>44413</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -25495,7 +25495,7 @@
         <v>44316</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -25552,7 +25552,7 @@
         <v>44627.36047453704</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -25614,7 +25614,7 @@
         <v>44389</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -25676,7 +25676,7 @@
         <v>44188</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -25733,7 +25733,7 @@
         <v>45484.58422453704</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -25795,7 +25795,7 @@
         <v>44825</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -25852,7 +25852,7 @@
         <v>44361</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -25909,7 +25909,7 @@
         <v>44530.40607638889</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -25966,7 +25966,7 @@
         <v>44889.56582175926</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -26023,7 +26023,7 @@
         <v>45740.36546296296</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -26085,7 +26085,7 @@
         <v>44706.66417824074</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -26147,7 +26147,7 @@
         <v>45240</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -26204,7 +26204,7 @@
         <v>45634.65831018519</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -26261,7 +26261,7 @@
         <v>45687.54329861111</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -26318,7 +26318,7 @@
         <v>44475</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -26375,7 +26375,7 @@
         <v>44803</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -26432,7 +26432,7 @@
         <v>45706</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -26489,7 +26489,7 @@
         <v>44285</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -26546,7 +26546,7 @@
         <v>44258</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -26603,7 +26603,7 @@
         <v>44377</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -26660,7 +26660,7 @@
         <v>45772.69290509259</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -26722,7 +26722,7 @@
         <v>44155</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -26779,7 +26779,7 @@
         <v>45763.41402777778</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -26836,7 +26836,7 @@
         <v>45740.57487268518</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -26898,7 +26898,7 @@
         <v>45579.59980324074</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -26955,7 +26955,7 @@
         <v>44242</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -27012,7 +27012,7 @@
         <v>44643.81518518519</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -27069,7 +27069,7 @@
         <v>45252</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -27126,7 +27126,7 @@
         <v>44925</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -27183,7 +27183,7 @@
         <v>45624.36090277778</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -27240,7 +27240,7 @@
         <v>45614.47960648148</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -27297,7 +27297,7 @@
         <v>45758.49096064815</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -27359,7 +27359,7 @@
         <v>45096.62344907408</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -27421,7 +27421,7 @@
         <v>45733.43663194445</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -27483,7 +27483,7 @@
         <v>44088</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -27540,7 +27540,7 @@
         <v>44925</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -27602,7 +27602,7 @@
         <v>45595.5666550926</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -27659,7 +27659,7 @@
         <v>45362.67293981482</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -27716,7 +27716,7 @@
         <v>45607</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -27773,7 +27773,7 @@
         <v>45579.57390046296</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -27835,7 +27835,7 @@
         <v>45420.44414351852</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -27897,7 +27897,7 @@
         <v>44872</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -27954,7 +27954,7 @@
         <v>45741.45597222223</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -28011,7 +28011,7 @@
         <v>45667</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -28068,7 +28068,7 @@
         <v>45195.35877314815</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -28125,7 +28125,7 @@
         <v>45617.89371527778</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -28182,7 +28182,7 @@
         <v>45775.36587962963</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -28239,7 +28239,7 @@
         <v>45119.39105324074</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -28301,7 +28301,7 @@
         <v>45685</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -28363,7 +28363,7 @@
         <v>45510</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -28420,7 +28420,7 @@
         <v>45622.64012731481</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -28482,7 +28482,7 @@
         <v>45756</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -28539,7 +28539,7 @@
         <v>45635.33439814814</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -28601,7 +28601,7 @@
         <v>45439.43106481482</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -28663,7 +28663,7 @@
         <v>44531.43927083333</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -28725,7 +28725,7 @@
         <v>45688.67935185185</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -28787,7 +28787,7 @@
         <v>45574.66106481481</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -28844,7 +28844,7 @@
         <v>45575</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -28901,7 +28901,7 @@
         <v>44784.60677083334</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -28963,7 +28963,7 @@
         <v>45754.35055555555</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -29020,7 +29020,7 @@
         <v>45506.36534722222</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -29077,7 +29077,7 @@
         <v>45772.46965277778</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -29139,7 +29139,7 @@
         <v>45772.46988425926</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -29201,7 +29201,7 @@
         <v>45632.64769675926</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -29258,7 +29258,7 @@
         <v>45106</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -29320,7 +29320,7 @@
         <v>45603</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -29382,7 +29382,7 @@
         <v>45603</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -29444,7 +29444,7 @@
         <v>44475</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -29501,7 +29501,7 @@
         <v>44300</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -29558,7 +29558,7 @@
         <v>45459</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -29615,7 +29615,7 @@
         <v>45345.66555555556</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -29677,7 +29677,7 @@
         <v>45664.56502314815</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -29734,7 +29734,7 @@
         <v>45575.60996527778</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -29796,7 +29796,7 @@
         <v>45303.5047337963</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -29853,7 +29853,7 @@
         <v>44985.61403935185</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -29915,7 +29915,7 @@
         <v>45743.38449074074</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -29972,7 +29972,7 @@
         <v>45637</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -30029,7 +30029,7 @@
         <v>45721.33868055556</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -30086,7 +30086,7 @@
         <v>45688.67932870371</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -30148,7 +30148,7 @@
         <v>45685.5349074074</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -30210,7 +30210,7 @@
         <v>45290.39024305555</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -30267,7 +30267,7 @@
         <v>44795</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -30324,7 +30324,7 @@
         <v>45572.60001157408</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -30381,7 +30381,7 @@
         <v>45607.44832175926</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -30443,7 +30443,7 @@
         <v>45580.92037037037</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -30500,7 +30500,7 @@
         <v>45568</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -30562,7 +30562,7 @@
         <v>45768.30814814815</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -30624,7 +30624,7 @@
         <v>45635.42027777778</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -30686,7 +30686,7 @@
         <v>45350</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -30743,7 +30743,7 @@
         <v>45351</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -30800,7 +30800,7 @@
         <v>45075.59358796296</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -30862,7 +30862,7 @@
         <v>45729.65261574074</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -30924,7 +30924,7 @@
         <v>45691</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -30986,7 +30986,7 @@
         <v>45569.48626157407</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -31043,7 +31043,7 @@
         <v>45691</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -31105,7 +31105,7 @@
         <v>44914</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -31162,7 +31162,7 @@
         <v>45764</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -31219,7 +31219,7 @@
         <v>44472</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -31276,7 +31276,7 @@
         <v>45672.61748842592</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -31333,7 +31333,7 @@
         <v>44977.44643518519</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -31395,7 +31395,7 @@
         <v>44316</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -31452,7 +31452,7 @@
         <v>44280</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -31509,7 +31509,7 @@
         <v>45338</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -31571,7 +31571,7 @@
         <v>45432</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -31633,7 +31633,7 @@
         <v>45659.57361111111</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -31695,7 +31695,7 @@
         <v>44381</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -31752,7 +31752,7 @@
         <v>45762.55899305556</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -31809,7 +31809,7 @@
         <v>45604.31657407407</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -31871,7 +31871,7 @@
         <v>45280</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -31928,7 +31928,7 @@
         <v>44732</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -31985,7 +31985,7 @@
         <v>45345.35003472222</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -32047,7 +32047,7 @@
         <v>45758.69638888889</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -32104,7 +32104,7 @@
         <v>45617</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -32166,7 +32166,7 @@
         <v>45496.59202546296</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -32228,7 +32228,7 @@
         <v>45677.44273148148</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -32285,7 +32285,7 @@
         <v>44916</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -32342,7 +32342,7 @@
         <v>45719.45215277778</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -32399,7 +32399,7 @@
         <v>45621</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -32456,7 +32456,7 @@
         <v>45621</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -32513,7 +32513,7 @@
         <v>45645.48079861111</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -32575,7 +32575,7 @@
         <v>44953</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -32632,7 +32632,7 @@
         <v>45111</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -32689,7 +32689,7 @@
         <v>45257</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -32751,7 +32751,7 @@
         <v>45622</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -32813,7 +32813,7 @@
         <v>44126</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -32870,7 +32870,7 @@
         <v>44483</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -32927,7 +32927,7 @@
         <v>45537.60471064815</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -32989,7 +32989,7 @@
         <v>44925.64049768518</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -33051,7 +33051,7 @@
         <v>45642.33616898148</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -33108,7 +33108,7 @@
         <v>45741.38347222222</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -33165,7 +33165,7 @@
         <v>45505</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -33222,7 +33222,7 @@
         <v>45728.44329861111</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -33284,7 +33284,7 @@
         <v>44726</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -33341,7 +33341,7 @@
         <v>45442</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -33403,7 +33403,7 @@
         <v>45728.49267361111</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -33465,7 +33465,7 @@
         <v>45604.33195601852</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -33527,7 +33527,7 @@
         <v>45575</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -33584,7 +33584,7 @@
         <v>45603</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -33646,7 +33646,7 @@
         <v>45540.4264699074</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -33708,7 +33708,7 @@
         <v>45643.56899305555</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -33770,7 +33770,7 @@
         <v>45719.40480324074</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -33827,7 +33827,7 @@
         <v>45547.59543981482</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -33884,7 +33884,7 @@
         <v>45560</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -33941,7 +33941,7 @@
         <v>44162.65819444445</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -34003,7 +34003,7 @@
         <v>45751.69827546296</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -34065,7 +34065,7 @@
         <v>45582.49792824074</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -34127,7 +34127,7 @@
         <v>44167</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -34184,7 +34184,7 @@
         <v>45303.52626157407</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -34241,7 +34241,7 @@
         <v>45119.38151620371</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -34303,7 +34303,7 @@
         <v>45061.61002314815</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -34365,7 +34365,7 @@
         <v>45517.38320601852</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -34422,7 +34422,7 @@
         <v>45260.35777777778</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -34479,7 +34479,7 @@
         <v>45645.47609953704</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -34541,7 +34541,7 @@
         <v>45471.66556712963</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -34603,7 +34603,7 @@
         <v>44928</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -34665,7 +34665,7 @@
         <v>44928</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -34727,7 +34727,7 @@
         <v>45243.63798611111</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -34784,7 +34784,7 @@
         <v>44827</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -34841,7 +34841,7 @@
         <v>44827</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -34898,7 +34898,7 @@
         <v>45635.4916087963</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -34955,7 +34955,7 @@
         <v>45688.46570601852</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -35017,7 +35017,7 @@
         <v>45604.66936342593</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -35074,7 +35074,7 @@
         <v>45411.44549768518</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -35136,7 +35136,7 @@
         <v>45776.43898148148</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -35193,7 +35193,7 @@
         <v>44985.6125</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -35255,7 +35255,7 @@
         <v>45776.69569444445</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -35312,7 +35312,7 @@
         <v>45768.29469907407</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -35374,7 +35374,7 @@
         <v>45768.30260416667</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -35436,7 +35436,7 @@
         <v>45768.30388888889</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -35498,7 +35498,7 @@
         <v>45485</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -35560,7 +35560,7 @@
         <v>45485</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -35622,7 +35622,7 @@
         <v>45611.38759259259</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -35679,7 +35679,7 @@
         <v>45484.66521990741</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -35741,7 +35741,7 @@
         <v>45506.36702546296</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -35798,7 +35798,7 @@
         <v>45779.41844907407</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -35860,7 +35860,7 @@
         <v>45779.38211805555</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -35922,7 +35922,7 @@
         <v>45779.50886574074</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -35984,7 +35984,7 @@
         <v>45779.51943287037</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -36046,7 +36046,7 @@
         <v>45779.52488425926</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -36108,7 +36108,7 @@
         <v>45020</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -36165,7 +36165,7 @@
         <v>45779.50052083333</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -36227,7 +36227,7 @@
         <v>45737</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -36284,7 +36284,7 @@
         <v>45779.47704861111</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -36346,7 +36346,7 @@
         <v>45614.62445601852</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -36408,7 +36408,7 @@
         <v>45779.51357638889</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -36470,7 +36470,7 @@
         <v>45779.48611111111</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -36532,7 +36532,7 @@
         <v>45791</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -36589,7 +36589,7 @@
         <v>45707</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -36646,7 +36646,7 @@
         <v>45707</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -36703,7 +36703,7 @@
         <v>45483.47572916667</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -36760,7 +36760,7 @@
         <v>45743.61899305556</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -36817,7 +36817,7 @@
         <v>45743.62116898148</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -36874,7 +36874,7 @@
         <v>45783.68547453704</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -36936,7 +36936,7 @@
         <v>45618.35961805555</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -36993,7 +36993,7 @@
         <v>45782.41581018519</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -37050,7 +37050,7 @@
         <v>45751.63266203704</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -37112,7 +37112,7 @@
         <v>45118.47491898148</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -37174,7 +37174,7 @@
         <v>45782.42744212963</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -37231,7 +37231,7 @@
         <v>44999.60127314815</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -37288,7 +37288,7 @@
         <v>45665.59925925926</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -37345,7 +37345,7 @@
         <v>45666</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -37407,7 +37407,7 @@
         <v>45147</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -37464,7 +37464,7 @@
         <v>45457.92854166667</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -37521,7 +37521,7 @@
         <v>45387</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -37578,7 +37578,7 @@
         <v>45785.33164351852</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -37635,7 +37635,7 @@
         <v>45785.34165509259</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -37692,7 +37692,7 @@
         <v>44924.59140046296</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -37754,7 +37754,7 @@
         <v>45677.43028935185</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -37811,7 +37811,7 @@
         <v>45784.59012731481</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -37873,7 +37873,7 @@
         <v>45119.38675925926</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -37935,7 +37935,7 @@
         <v>45670.34313657408</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -37992,7 +37992,7 @@
         <v>45632.64078703704</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -38049,7 +38049,7 @@
         <v>45642</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -38106,7 +38106,7 @@
         <v>44312</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -38163,7 +38163,7 @@
         <v>45345.65929398148</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -38225,7 +38225,7 @@
         <v>45453.6619212963</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -38282,7 +38282,7 @@
         <v>45569.6909837963</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -38339,7 +38339,7 @@
         <v>44853.41693287037</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -38396,7 +38396,7 @@
         <v>45673.65925925926</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -38458,7 +38458,7 @@
         <v>45705.32643518518</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -38515,7 +38515,7 @@
         <v>45173</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -38577,7 +38577,7 @@
         <v>45533.67138888889</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -38634,7 +38634,7 @@
         <v>45196</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -38696,7 +38696,7 @@
         <v>45279.57732638889</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -38753,7 +38753,7 @@
         <v>45733.59667824074</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -38815,7 +38815,7 @@
         <v>45209.45420138889</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -38872,7 +38872,7 @@
         <v>45159.46996527778</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -38934,7 +38934,7 @@
         <v>45786.66425925926</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -38996,7 +38996,7 @@
         <v>45630.5731712963</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -39058,7 +39058,7 @@
         <v>45568</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -39120,7 +39120,7 @@
         <v>45432</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -39182,7 +39182,7 @@
         <v>44708.48859953704</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -39244,7 +39244,7 @@
         <v>45786.66853009259</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -39306,7 +39306,7 @@
         <v>45510</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -39368,7 +39368,7 @@
         <v>45531.78386574074</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -39425,7 +39425,7 @@
         <v>44957</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -39487,7 +39487,7 @@
         <v>44638.44958333333</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -39544,7 +39544,7 @@
         <v>45737.37006944444</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -39601,7 +39601,7 @@
         <v>45216</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -39658,7 +39658,7 @@
         <v>45559</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -39715,7 +39715,7 @@
         <v>45786.66209490741</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -39777,7 +39777,7 @@
         <v>45484.65768518519</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -39839,7 +39839,7 @@
         <v>44348</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -39896,7 +39896,7 @@
         <v>45786.66032407407</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -39958,7 +39958,7 @@
         <v>45264.92637731481</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -40015,7 +40015,7 @@
         <v>45546.54530092593</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -40072,7 +40072,7 @@
         <v>44474.59423611111</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -40129,7 +40129,7 @@
         <v>45406</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -40191,7 +40191,7 @@
         <v>44424</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -40248,7 +40248,7 @@
         <v>44823.84673611111</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -40305,7 +40305,7 @@
         <v>44209</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -40367,7 +40367,7 @@
         <v>45790.43</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -40429,7 +40429,7 @@
         <v>44928</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -40491,7 +40491,7 @@
         <v>44928.48072916667</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -40553,7 +40553,7 @@
         <v>44985</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -40615,7 +40615,7 @@
         <v>44631.37701388889</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -40677,7 +40677,7 @@
         <v>45397.64855324074</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -40734,7 +40734,7 @@
         <v>45205</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -40791,7 +40791,7 @@
         <v>45517.39274305556</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -40853,7 +40853,7 @@
         <v>45474.54432870371</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -40910,7 +40910,7 @@
         <v>45790.87653935186</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -40967,7 +40967,7 @@
         <v>44925.60457175926</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -41029,7 +41029,7 @@
         <v>44925.64309027778</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -41091,7 +41091,7 @@
         <v>44928.36418981481</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -41153,7 +41153,7 @@
         <v>45792.64795138889</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -41210,7 +41210,7 @@
         <v>45792.50942129629</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -41272,7 +41272,7 @@
         <v>45159</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -41334,7 +41334,7 @@
         <v>45159</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -41396,7 +41396,7 @@
         <v>44423</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -41453,7 +41453,7 @@
         <v>45408</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -41510,7 +41510,7 @@
         <v>44153</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -41567,7 +41567,7 @@
         <v>45793.41994212963</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -41629,7 +41629,7 @@
         <v>45484.57285879629</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -41691,7 +41691,7 @@
         <v>45063</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -41748,7 +41748,7 @@
         <v>45792.65047453704</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -41805,7 +41805,7 @@
         <v>45642</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -41862,7 +41862,7 @@
         <v>45644.56674768519</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -41924,7 +41924,7 @@
         <v>45685.52405092592</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -41986,7 +41986,7 @@
         <v>45607</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -42048,7 +42048,7 @@
         <v>45632.65197916667</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -42105,7 +42105,7 @@
         <v>45631</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -42167,7 +42167,7 @@
         <v>44435</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -42229,7 +42229,7 @@
         <v>45754.67329861111</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -42286,7 +42286,7 @@
         <v>45742.42793981481</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -42348,7 +42348,7 @@
         <v>44231</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -42410,7 +42410,7 @@
         <v>45644.50141203704</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -42472,7 +42472,7 @@
         <v>45569</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -42534,7 +42534,7 @@
         <v>44225</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -42591,7 +42591,7 @@
         <v>45772.46951388889</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -42653,7 +42653,7 @@
         <v>45303.5187037037</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -42710,7 +42710,7 @@
         <v>44939.45376157408</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -42767,7 +42767,7 @@
         <v>45740.44842592593</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -42829,7 +42829,7 @@
         <v>45618.35097222222</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -42886,7 +42886,7 @@
         <v>45796.39770833333</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -42943,7 +42943,7 @@
         <v>45631</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -43005,7 +43005,7 @@
         <v>45791</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -43062,7 +43062,7 @@
         <v>45796.57802083333</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -43119,7 +43119,7 @@
         <v>45588.56039351852</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -43176,7 +43176,7 @@
         <v>45797.37096064815</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -43233,7 +43233,7 @@
         <v>45118.91633101852</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -43290,7 +43290,7 @@
         <v>45533.75398148148</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -43347,7 +43347,7 @@
         <v>44924.61315972222</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -43409,7 +43409,7 @@
         <v>45719.45277777778</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -43466,7 +43466,7 @@
         <v>45621</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -43528,7 +43528,7 @@
         <v>45212</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -43585,7 +43585,7 @@
         <v>45728.61006944445</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -43642,7 +43642,7 @@
         <v>45830</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -43699,7 +43699,7 @@
         <v>45830</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -43756,7 +43756,7 @@
         <v>45830</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -43813,7 +43813,7 @@
         <v>45730</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -43870,7 +43870,7 @@
         <v>45453.6672800926</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -43927,7 +43927,7 @@
         <v>45768.29289351852</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -43989,7 +43989,7 @@
         <v>45768.30086805556</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -44051,7 +44051,7 @@
         <v>45799.64804398148</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -44113,7 +44113,7 @@
         <v>45674.57393518519</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -44170,7 +44170,7 @@
         <v>45517.69590277778</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -44232,7 +44232,7 @@
         <v>45063.92605324074</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -44289,7 +44289,7 @@
         <v>44827</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -44346,7 +44346,7 @@
         <v>44958</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -44408,7 +44408,7 @@
         <v>45496.67178240741</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -44470,7 +44470,7 @@
         <v>45642.35256944445</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -44527,7 +44527,7 @@
         <v>45685.50063657408</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -44589,7 +44589,7 @@
         <v>45063</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -44646,7 +44646,7 @@
         <v>45799.4658912037</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -44708,7 +44708,7 @@
         <v>45799.46642361111</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -44765,7 +44765,7 @@
         <v>45830</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -44822,7 +44822,7 @@
         <v>44075</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -44879,7 +44879,7 @@
         <v>45638.416875</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -44941,7 +44941,7 @@
         <v>45799.43550925926</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -45003,7 +45003,7 @@
         <v>45799.47225694444</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -45065,7 +45065,7 @@
         <v>44886</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -45127,7 +45127,7 @@
         <v>45531.66196759259</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -45189,7 +45189,7 @@
         <v>45509.5980787037</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -45251,7 +45251,7 @@
         <v>45429.39</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -45308,7 +45308,7 @@
         <v>44460.44315972222</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -45370,7 +45370,7 @@
         <v>45477.62255787037</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -45432,7 +45432,7 @@
         <v>45799.45770833334</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -45494,7 +45494,7 @@
         <v>45484.48854166667</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -45556,7 +45556,7 @@
         <v>45345</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -45618,7 +45618,7 @@
         <v>45407.36894675926</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -45680,7 +45680,7 @@
         <v>45799.57883101852</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -45737,7 +45737,7 @@
         <v>45799.43086805556</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -45799,7 +45799,7 @@
         <v>44153</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -45861,7 +45861,7 @@
         <v>45800.64065972222</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -45923,7 +45923,7 @@
         <v>45630.62513888889</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -45980,7 +45980,7 @@
         <v>45624.36858796296</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -46037,7 +46037,7 @@
         <v>45803.37480324074</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -46094,7 +46094,7 @@
         <v>44757.37524305555</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -46151,7 +46151,7 @@
         <v>45631.39950231482</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -46213,7 +46213,7 @@
         <v>45751.65657407408</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -46275,7 +46275,7 @@
         <v>45237.5815162037</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -46332,7 +46332,7 @@
         <v>44082</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -46394,7 +46394,7 @@
         <v>45625.56934027778</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -46456,7 +46456,7 @@
         <v>45837</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -46513,7 +46513,7 @@
         <v>45834</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -46570,7 +46570,7 @@
         <v>45800.63738425926</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -46632,7 +46632,7 @@
         <v>45800.37524305555</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -46694,7 +46694,7 @@
         <v>45800.58859953703</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -46751,7 +46751,7 @@
         <v>45800.59567129629</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -46813,7 +46813,7 @@
         <v>45800.64719907408</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -46875,7 +46875,7 @@
         <v>45800.65341435185</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -46937,7 +46937,7 @@
         <v>45800.42797453704</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -46994,7 +46994,7 @@
         <v>45800.44090277778</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -47051,7 +47051,7 @@
         <v>45800.66043981481</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -47113,7 +47113,7 @@
         <v>45800.33436342593</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -47175,7 +47175,7 @@
         <v>45800.3425</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -47237,7 +47237,7 @@
         <v>45800.44868055556</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -47299,7 +47299,7 @@
         <v>45800.4687962963</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -47361,7 +47361,7 @@
         <v>45800.56222222222</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -47423,7 +47423,7 @@
         <v>45800.46069444445</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -47485,7 +47485,7 @@
         <v>45800.56995370371</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -47547,7 +47547,7 @@
         <v>45800.35670138889</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -47609,7 +47609,7 @@
         <v>45803.37258101852</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -47666,7 +47666,7 @@
         <v>45800.48060185185</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -47728,7 +47728,7 @@
         <v>45800.3503587963</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -47790,7 +47790,7 @@
         <v>45800.50431712963</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -47852,7 +47852,7 @@
         <v>45800.60508101852</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -47914,7 +47914,7 @@
         <v>45800.56313657408</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -47971,7 +47971,7 @@
         <v>45800.57837962963</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -48033,7 +48033,7 @@
         <v>45800.3787037037</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -48095,7 +48095,7 @@
         <v>45800.41883101852</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -48157,7 +48157,7 @@
         <v>45800.48515046296</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -48219,7 +48219,7 @@
         <v>44883</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -48276,7 +48276,7 @@
         <v>45275</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -48333,7 +48333,7 @@
         <v>45804.589375</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -48390,7 +48390,7 @@
         <v>45539.43545138889</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -48447,7 +48447,7 @@
         <v>44169</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -48504,7 +48504,7 @@
         <v>45061.36835648148</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -48561,7 +48561,7 @@
         <v>45433</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -48618,7 +48618,7 @@
         <v>44091</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -48675,7 +48675,7 @@
         <v>44728</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -48737,7 +48737,7 @@
         <v>45593.6821412037</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -48794,7 +48794,7 @@
         <v>45593.68434027778</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -48851,7 +48851,7 @@
         <v>45804.5813425926</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -48913,7 +48913,7 @@
         <v>45805.53280092592</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -48975,7 +48975,7 @@
         <v>45345.34219907408</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -49037,7 +49037,7 @@
         <v>45345.47642361111</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -49099,7 +49099,7 @@
         <v>45562.65759259259</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -49161,7 +49161,7 @@
         <v>45685</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -49223,7 +49223,7 @@
         <v>45345</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -49285,7 +49285,7 @@
         <v>45097</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -49347,7 +49347,7 @@
         <v>45807.58393518518</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -49409,7 +49409,7 @@
         <v>45485</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -49466,7 +49466,7 @@
         <v>45807.47479166667</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -49528,7 +49528,7 @@
         <v>45807.3409837963</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -49590,7 +49590,7 @@
         <v>45807.35476851852</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -49652,7 +49652,7 @@
         <v>45807.41287037037</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -49714,7 +49714,7 @@
         <v>45807.42212962963</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -49776,7 +49776,7 @@
         <v>45170.46923611111</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -49838,7 +49838,7 @@
         <v>45807.49436342593</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -49900,7 +49900,7 @@
         <v>45807.56403935186</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -49962,7 +49962,7 @@
         <v>45807.65438657408</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -50024,7 +50024,7 @@
         <v>45807.60333333333</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -50086,7 +50086,7 @@
         <v>45807.55893518519</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -50148,7 +50148,7 @@
         <v>45807.36304398148</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -50210,7 +50210,7 @@
         <v>45807.49045138889</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -50272,7 +50272,7 @@
         <v>45807.5684375</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -50334,7 +50334,7 @@
         <v>45807.63334490741</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -50396,7 +50396,7 @@
         <v>45807.45288194445</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -50458,7 +50458,7 @@
         <v>45617</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -50520,7 +50520,7 @@
         <v>45576.48657407407</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -50582,7 +50582,7 @@
         <v>45617</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -50644,7 +50644,7 @@
         <v>45616.49530092593</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -50701,7 +50701,7 @@
         <v>45041</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -50758,7 +50758,7 @@
         <v>45618</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -50815,7 +50815,7 @@
         <v>45807.41717592593</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -50877,7 +50877,7 @@
         <v>45807.43461805556</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -50939,7 +50939,7 @@
         <v>45807.44070601852</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -51001,7 +51001,7 @@
         <v>45807.44608796296</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -51063,7 +51063,7 @@
         <v>45807.49832175926</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -51125,7 +51125,7 @@
         <v>45807.58868055556</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -51187,7 +51187,7 @@
         <v>45807.59407407408</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -51249,7 +51249,7 @@
         <v>45532</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -51306,7 +51306,7 @@
         <v>45853.28325231482</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -51363,7 +51363,7 @@
         <v>44987.35637731481</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -51425,7 +51425,7 @@
         <v>44987</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -51487,7 +51487,7 @@
         <v>45852</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -51544,7 +51544,7 @@
         <v>45646</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -51601,7 +51601,7 @@
         <v>45622</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -51663,7 +51663,7 @@
         <v>45811.34564814815</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -51725,7 +51725,7 @@
         <v>45477.66773148148</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -51787,7 +51787,7 @@
         <v>44631.42353009259</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -51849,7 +51849,7 @@
         <v>45478.44497685185</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -51911,7 +51911,7 @@
         <v>45107</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -51968,7 +51968,7 @@
         <v>45481.3330787037</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -52030,7 +52030,7 @@
         <v>45601.58355324074</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -52087,7 +52087,7 @@
         <v>44858</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -52144,7 +52144,7 @@
         <v>45154</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -52201,7 +52201,7 @@
         <v>45610.55846064815</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -52263,7 +52263,7 @@
         <v>45811.34540509259</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -52325,7 +52325,7 @@
         <v>45853.62415509259</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -52387,7 +52387,7 @@
         <v>45852.48290509259</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -52444,7 +52444,7 @@
         <v>45811.34578703704</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -52506,7 +52506,7 @@
         <v>45853.61865740741</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -52563,7 +52563,7 @@
         <v>45496.67342592592</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -52625,7 +52625,7 @@
         <v>45764.44825231482</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -52687,7 +52687,7 @@
         <v>45764.44861111111</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -52749,7 +52749,7 @@
         <v>44853</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -52806,7 +52806,7 @@
         <v>44550.39550925926</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -52863,7 +52863,7 @@
         <v>45265</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -52920,7 +52920,7 @@
         <v>44925.59333333333</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -52982,7 +52982,7 @@
         <v>44818</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -53039,7 +53039,7 @@
         <v>44957</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -53101,7 +53101,7 @@
         <v>45177.9224537037</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -53158,7 +53158,7 @@
         <v>45195.61476851852</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -53215,7 +53215,7 @@
         <v>45154</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -53272,7 +53272,7 @@
         <v>45385</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -53329,7 +53329,7 @@
         <v>45854.40662037037</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -53391,7 +53391,7 @@
         <v>45111</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -53453,7 +53453,7 @@
         <v>45688.6749537037</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -53515,7 +53515,7 @@
         <v>45813.48734953703</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -53572,7 +53572,7 @@
         <v>45813.47074074074</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -53629,7 +53629,7 @@
         <v>44854</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -53691,7 +53691,7 @@
         <v>45280</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -53748,7 +53748,7 @@
         <v>45670.66085648148</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -53805,7 +53805,7 @@
         <v>45406.64024305555</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -53867,7 +53867,7 @@
         <v>45813.64590277777</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -53924,7 +53924,7 @@
         <v>45496.66903935185</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -53986,7 +53986,7 @@
         <v>45334</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -54048,7 +54048,7 @@
         <v>45509</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -54110,7 +54110,7 @@
         <v>45509</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -54172,7 +54172,7 @@
         <v>45685</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -54229,7 +54229,7 @@
         <v>45635.35274305556</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -54291,7 +54291,7 @@
         <v>45733</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -54348,7 +54348,7 @@
         <v>45854.44850694444</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -54410,7 +54410,7 @@
         <v>45854.44864583333</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -54472,7 +54472,7 @@
         <v>45506.3637962963</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -54529,7 +54529,7 @@
         <v>44475</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -54586,7 +54586,7 @@
         <v>45166.34795138889</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -54643,7 +54643,7 @@
         <v>44985</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -54705,7 +54705,7 @@
         <v>45559.43645833333</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -54767,7 +54767,7 @@
         <v>45665.563125</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -54829,7 +54829,7 @@
         <v>45362.64613425926</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -54886,7 +54886,7 @@
         <v>45362.65407407407</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -54943,7 +54943,7 @@
         <v>45817.33819444444</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -55005,7 +55005,7 @@
         <v>45483.47207175926</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -55062,7 +55062,7 @@
         <v>45817.62439814815</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -55119,7 +55119,7 @@
         <v>45203</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -55176,7 +55176,7 @@
         <v>45817.594375</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -55238,7 +55238,7 @@
         <v>45656.51157407407</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -55300,7 +55300,7 @@
         <v>45197.46966435185</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -55357,7 +55357,7 @@
         <v>45218.58609953704</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -55414,7 +55414,7 @@
         <v>45859</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -55471,7 +55471,7 @@
         <v>45680.42497685185</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -55528,7 +55528,7 @@
         <v>44722</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -55585,7 +55585,7 @@
         <v>44914</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -55667,7 +55667,7 @@
         <v>45485.42287037037</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -55724,7 +55724,7 @@
         <v>45485</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -55781,7 +55781,7 @@
         <v>45485.44258101852</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -55843,7 +55843,7 @@
         <v>45509.6427662037</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -55905,7 +55905,7 @@
         <v>45098.48666666666</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -55967,7 +55967,7 @@
         <v>45208</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -56024,7 +56024,7 @@
         <v>45303</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -56081,7 +56081,7 @@
         <v>45119</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -56138,7 +56138,7 @@
         <v>44312</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -56195,7 +56195,7 @@
         <v>44082</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -56257,7 +56257,7 @@
         <v>45260.59042824074</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -56314,7 +56314,7 @@
         <v>44883</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -56371,7 +56371,7 @@
         <v>45821.57201388889</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -56433,7 +56433,7 @@
         <v>45820.64821759259</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -56490,7 +56490,7 @@
         <v>45741.39084490741</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -56547,7 +56547,7 @@
         <v>45624.57098379629</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -56604,7 +56604,7 @@
         <v>45678.37956018518</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -56661,7 +56661,7 @@
         <v>45590.31899305555</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -56718,7 +56718,7 @@
         <v>44305</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -56775,7 +56775,7 @@
         <v>45622.64627314815</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -56832,7 +56832,7 @@
         <v>45485</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -56894,7 +56894,7 @@
         <v>45371.66217592593</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -56956,7 +56956,7 @@
         <v>45821.77903935185</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -57013,7 +57013,7 @@
         <v>45274</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -57070,7 +57070,7 @@
         <v>45154</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -57127,7 +57127,7 @@
         <v>45867.55305555555</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -57184,7 +57184,7 @@
         <v>45723.58140046296</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -57241,7 +57241,7 @@
         <v>45867.55642361111</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -57303,7 +57303,7 @@
         <v>45488</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -57360,7 +57360,7 @@
         <v>45238.64153935185</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -57417,7 +57417,7 @@
         <v>45866.40701388889</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -57474,7 +57474,7 @@
         <v>45866.62908564815</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -57531,7 +57531,7 @@
         <v>45827.41753472222</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -57593,7 +57593,7 @@
         <v>45826.43267361111</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -57655,7 +57655,7 @@
         <v>45075.59148148148</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -57717,7 +57717,7 @@
         <v>44091</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -57774,7 +57774,7 @@
         <v>45687.53689814815</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -57831,7 +57831,7 @@
         <v>45153.42725694444</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -57893,7 +57893,7 @@
         <v>45485</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -57955,7 +57955,7 @@
         <v>45485</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -58017,7 +58017,7 @@
         <v>45827</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -58074,7 +58074,7 @@
         <v>45691</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -58136,7 +58136,7 @@
         <v>45691</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -58198,7 +58198,7 @@
         <v>45509</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -58260,7 +58260,7 @@
         <v>45868.639375</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -58317,7 +58317,7 @@
         <v>45244</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -58374,7 +58374,7 @@
         <v>45159.60288194445</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -58431,7 +58431,7 @@
         <v>45763.4266087963</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -58488,7 +58488,7 @@
         <v>45791</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -58545,7 +58545,7 @@
         <v>45593.67809027778</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -58602,7 +58602,7 @@
         <v>45170.46134259259</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -58664,7 +58664,7 @@
         <v>45827.42467592593</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -58726,7 +58726,7 @@
         <v>45485</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -58783,7 +58783,7 @@
         <v>45735.60342592592</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -58840,7 +58840,7 @@
         <v>44987.34981481481</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -58902,7 +58902,7 @@
         <v>45460.47969907407</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -58959,7 +58959,7 @@
         <v>45460.48582175926</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -59016,7 +59016,7 @@
         <v>44180</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -59073,7 +59073,7 @@
         <v>45478.48700231482</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -59135,7 +59135,7 @@
         <v>45873.59511574074</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -59197,7 +59197,7 @@
         <v>45231</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -59254,7 +59254,7 @@
         <v>45345.4940625</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -59316,7 +59316,7 @@
         <v>45831</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -59378,7 +59378,7 @@
         <v>45582.59753472222</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -59440,7 +59440,7 @@
         <v>45875.5196875</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -59497,7 +59497,7 @@
         <v>45345.48181712963</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -59559,7 +59559,7 @@
         <v>45874.64199074074</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -59616,7 +59616,7 @@
         <v>45439.62893518519</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -59673,7 +59673,7 @@
         <v>45735.57390046296</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -59730,7 +59730,7 @@
         <v>45054</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -59792,7 +59792,7 @@
         <v>44642</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -59854,7 +59854,7 @@
         <v>45429</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -59911,7 +59911,7 @@
         <v>45874.64513888889</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -59968,7 +59968,7 @@
         <v>45832</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -60030,7 +60030,7 @@
         <v>45833</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -60092,7 +60092,7 @@
         <v>45833</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -60154,7 +60154,7 @@
         <v>45875.47854166666</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -60216,7 +60216,7 @@
         <v>45832</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -60278,7 +60278,7 @@
         <v>45833.36467592593</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -60340,7 +60340,7 @@
         <v>44385</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -60397,7 +60397,7 @@
         <v>45832.64047453704</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -60454,7 +60454,7 @@
         <v>45832.3859837963</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -60516,7 +60516,7 @@
         <v>45833</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -60578,7 +60578,7 @@
         <v>45833.6081712963</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -60640,7 +60640,7 @@
         <v>45342</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -60697,7 +60697,7 @@
         <v>44862</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -60759,7 +60759,7 @@
         <v>45832</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -60821,7 +60821,7 @@
         <v>45834.80229166667</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -60878,7 +60878,7 @@
         <v>45835.55998842593</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -60940,7 +60940,7 @@
         <v>45835.57069444445</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -60997,7 +60997,7 @@
         <v>45705.32456018519</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -61054,7 +61054,7 @@
         <v>45834</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -61116,7 +61116,7 @@
         <v>45834.7087962963</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -61173,7 +61173,7 @@
         <v>45834</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -61235,7 +61235,7 @@
         <v>45622.45239583333</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -61297,7 +61297,7 @@
         <v>45834.38173611111</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -61354,7 +61354,7 @@
         <v>45288.58685185185</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -61411,7 +61411,7 @@
         <v>44819.56722222222</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -61468,7 +61468,7 @@
         <v>45834.69577546296</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -61525,7 +61525,7 @@
         <v>45071.92488425926</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -61582,7 +61582,7 @@
         <v>45638</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -61644,7 +61644,7 @@
         <v>44886</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -61706,7 +61706,7 @@
         <v>45467</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -61763,7 +61763,7 @@
         <v>45642.41907407407</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -61820,7 +61820,7 @@
         <v>45204</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -61877,7 +61877,7 @@
         <v>45252.45481481482</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -61934,7 +61934,7 @@
         <v>45252.48409722222</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -61991,7 +61991,7 @@
         <v>45041</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -62048,7 +62048,7 @@
         <v>45245</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -62105,7 +62105,7 @@
         <v>45688.6769212963</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -62167,7 +62167,7 @@
         <v>45835.5583912037</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -62229,7 +62229,7 @@
         <v>45834.6568287037</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -62286,7 +62286,7 @@
         <v>45834</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -62343,7 +62343,7 @@
         <v>45215</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -62400,7 +62400,7 @@
         <v>45876.49113425926</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -62457,7 +62457,7 @@
         <v>45876.39362268519</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -62519,7 +62519,7 @@
         <v>45834.51079861111</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -62581,7 +62581,7 @@
         <v>45610.56706018518</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -62643,7 +62643,7 @@
         <v>45085</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -62700,7 +62700,7 @@
         <v>45834.71440972222</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -62757,7 +62757,7 @@
         <v>45881.36469907407</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -62814,7 +62814,7 @@
         <v>45390</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -62871,7 +62871,7 @@
         <v>45484</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -62933,7 +62933,7 @@
         <v>45881.6609375</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -62990,7 +62990,7 @@
         <v>45406</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -63052,7 +63052,7 @@
         <v>45670</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -63114,7 +63114,7 @@
         <v>45719.48778935185</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -63171,7 +63171,7 @@
         <v>45202</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -63233,7 +63233,7 @@
         <v>45839.5658912037</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -63290,7 +63290,7 @@
         <v>45644</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -63347,7 +63347,7 @@
         <v>44216</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -63409,7 +63409,7 @@
         <v>44216</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -63471,7 +63471,7 @@
         <v>45611.4021875</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -63528,7 +63528,7 @@
         <v>45881.46869212963</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -63585,7 +63585,7 @@
         <v>45881.43114583333</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -63642,7 +63642,7 @@
         <v>45118.3959375</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -63704,7 +63704,7 @@
         <v>45881.64365740741</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -63761,7 +63761,7 @@
         <v>45362.65903935185</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -63818,7 +63818,7 @@
         <v>45775.36589120371</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -63875,7 +63875,7 @@
         <v>45685.38901620371</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -63937,7 +63937,7 @@
         <v>44571</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -63994,7 +63994,7 @@
         <v>45173</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -64051,7 +64051,7 @@
         <v>45880.37472222222</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -64108,7 +64108,7 @@
         <v>45840.64394675926</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -64170,7 +64170,7 @@
         <v>45883.4108912037</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -64227,7 +64227,7 @@
         <v>44182</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -64284,7 +64284,7 @@
         <v>45883.35789351852</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -64341,7 +64341,7 @@
         <v>44998</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -64398,7 +64398,7 @@
         <v>44151</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -64455,7 +64455,7 @@
         <v>45575.6125925926</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -64517,7 +64517,7 @@
         <v>45882.64755787037</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -64579,7 +64579,7 @@
         <v>45883.51854166666</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -64636,7 +64636,7 @@
         <v>45882.63179398148</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -64698,7 +64698,7 @@
         <v>45841.69273148148</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -64755,7 +64755,7 @@
         <v>45705.72106481482</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -64812,7 +64812,7 @@
         <v>45883.40538194445</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -64869,7 +64869,7 @@
         <v>45841.4312037037</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -64926,7 +64926,7 @@
         <v>45841.46512731481</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -64988,7 +64988,7 @@
         <v>44708.45504629629</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -65050,7 +65050,7 @@
         <v>45883.58944444444</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -65112,7 +65112,7 @@
         <v>45568</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -65174,7 +65174,7 @@
         <v>45841.45137731481</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -65231,7 +65231,7 @@
         <v>45239.43173611111</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -65293,7 +65293,7 @@
         <v>44214</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -65355,7 +65355,7 @@
         <v>45845.6920949074</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -65417,7 +65417,7 @@
         <v>45772.36106481482</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -65479,7 +65479,7 @@
         <v>45569</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -65541,7 +65541,7 @@
         <v>45876</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -65603,7 +65603,7 @@
         <v>45667</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -65665,7 +65665,7 @@
         <v>45887.59913194444</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -65727,7 +65727,7 @@
         <v>45225.58005787037</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -65784,7 +65784,7 @@
         <v>45569</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -65846,7 +65846,7 @@
         <v>44314</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -65903,7 +65903,7 @@
         <v>44925.33584490741</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -65965,7 +65965,7 @@
         <v>44925</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -66022,7 +66022,7 @@
         <v>45049.59826388889</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -66079,7 +66079,7 @@
         <v>45632</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -66136,7 +66136,7 @@
         <v>45845.55270833334</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -66193,7 +66193,7 @@
         <v>45632</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -66250,7 +66250,7 @@
         <v>45568</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -66312,7 +66312,7 @@
         <v>45621</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -66374,7 +66374,7 @@
         <v>45170.4643287037</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -66436,7 +66436,7 @@
         <v>45887.50216435185</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -66498,7 +66498,7 @@
         <v>45568</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -66560,7 +66560,7 @@
         <v>45730</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -66617,7 +66617,7 @@
         <v>45622</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -66674,7 +66674,7 @@
         <v>45730</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -66731,7 +66731,7 @@
         <v>45842.48990740741</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -66788,7 +66788,7 @@
         <v>45755</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -66845,7 +66845,7 @@
         <v>45637.39587962963</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -66907,7 +66907,7 @@
         <v>45560.33311342593</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -66969,7 +66969,7 @@
         <v>45684.51006944444</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -67026,7 +67026,7 @@
         <v>45632</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -67083,7 +67083,7 @@
         <v>45728</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -67140,7 +67140,7 @@
         <v>44698</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -67202,7 +67202,7 @@
         <v>45869</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -67259,7 +67259,7 @@
         <v>45884.55263888889</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -67321,7 +67321,7 @@
         <v>45604.32543981481</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -67383,7 +67383,7 @@
         <v>45569</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -67445,7 +67445,7 @@
         <v>45447.35144675926</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -67502,7 +67502,7 @@
         <v>45845.60496527778</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -67559,7 +67559,7 @@
         <v>45885</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -67616,7 +67616,7 @@
         <v>45876</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -67678,7 +67678,7 @@
         <v>45869</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -67735,7 +67735,7 @@
         <v>45869</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -67792,7 +67792,7 @@
         <v>45845.55259259259</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -67849,7 +67849,7 @@
         <v>45845.55266203704</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -67906,7 +67906,7 @@
         <v>44484.55535879629</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -67963,7 +67963,7 @@
         <v>45238.46430555556</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -68020,7 +68020,7 @@
         <v>45631.63091435185</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -68077,7 +68077,7 @@
         <v>45888.59509259259</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -68134,7 +68134,7 @@
         <v>44229</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -68196,7 +68196,7 @@
         <v>44225</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -68253,7 +68253,7 @@
         <v>45727.35621527778</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -68315,7 +68315,7 @@
         <v>45012</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -68377,7 +68377,7 @@
         <v>45861</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -68439,7 +68439,7 @@
         <v>45254</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -68496,7 +68496,7 @@
         <v>45847.58865740741</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -68558,7 +68558,7 @@
         <v>44565.31975694445</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -68620,7 +68620,7 @@
         <v>45737.3787962963</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -68677,7 +68677,7 @@
         <v>45888.78833333333</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -68734,7 +68734,7 @@
         <v>45888.78960648148</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -68791,7 +68791,7 @@
         <v>44565</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -68853,7 +68853,7 @@
         <v>45505</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -68915,7 +68915,7 @@
         <v>45888.78539351852</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -68972,7 +68972,7 @@
         <v>45253.55737268519</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -69029,7 +69029,7 @@
         <v>45889.40916666666</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -69086,7 +69086,7 @@
         <v>45889.41715277778</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -69143,7 +69143,7 @@
         <v>45362.67789351852</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -69200,7 +69200,7 @@
         <v>44972.57449074074</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -69257,7 +69257,7 @@
         <v>45257</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -69314,7 +69314,7 @@
         <v>45848.45113425926</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -69376,7 +69376,7 @@
         <v>45758.66108796297</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -69433,7 +69433,7 @@
         <v>45758.69123842593</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -69490,7 +69490,7 @@
         <v>45670.4570949074</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -69552,7 +69552,7 @@
         <v>45848.65003472222</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -69609,7 +69609,7 @@
         <v>45688.67145833333</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -69671,7 +69671,7 @@
         <v>44665</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -69728,7 +69728,7 @@
         <v>45849</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -69785,7 +69785,7 @@
         <v>45282.64012731481</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -69847,7 +69847,7 @@
         <v>45848</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -69909,7 +69909,7 @@
         <v>45848.57644675926</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -69971,7 +69971,7 @@
         <v>45848.6568287037</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -70028,7 +70028,7 @@
         <v>45848.68640046296</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -70090,7 +70090,7 @@
         <v>45848.62873842593</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -70147,7 +70147,7 @@
         <v>45848.639375</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -70204,7 +70204,7 @@
         <v>44987.35282407407</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -70266,7 +70266,7 @@
         <v>45848.35400462963</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -70323,7 +70323,7 @@
         <v>45768.29630787037</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -70385,7 +70385,7 @@
         <v>45768.30954861111</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -70447,7 +70447,7 @@
         <v>44440</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -70504,7 +70504,7 @@
         <v>44628.36402777778</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -70561,7 +70561,7 @@
         <v>45195.3878125</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -70618,7 +70618,7 @@
         <v>44994</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -70675,7 +70675,7 @@
         <v>45351</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -70732,7 +70732,7 @@
         <v>44414.58354166667</v>
       </c>
       <c r="C1075" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
@@ -70789,7 +70789,7 @@
         <v>45229.92739583334</v>
       </c>
       <c r="C1076" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
@@ -70846,7 +70846,7 @@
         <v>45751.34636574074</v>
       </c>
       <c r="C1077" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
@@ -70908,7 +70908,7 @@
         <v>45731.69629629629</v>
       </c>
       <c r="C1078" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1078" t="inlineStr">
         <is>
@@ -70965,7 +70965,7 @@
         <v>45763.4178587963</v>
       </c>
       <c r="C1079" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1079" t="inlineStr">
         <is>
@@ -71022,7 +71022,7 @@
         <v>45509</v>
       </c>
       <c r="C1080" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
@@ -71084,7 +71084,7 @@
         <v>45733.38637731481</v>
       </c>
       <c r="C1081" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1081" t="inlineStr">
         <is>
@@ -71141,7 +71141,7 @@
         <v>45174</v>
       </c>
       <c r="C1082" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1082" t="inlineStr">
         <is>
@@ -71198,7 +71198,7 @@
         <v>45624.63614583333</v>
       </c>
       <c r="C1083" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1083" t="inlineStr">
         <is>
@@ -71260,7 +71260,7 @@
         <v>45041</v>
       </c>
       <c r="C1084" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1084" t="inlineStr">
         <is>
@@ -71317,7 +71317,7 @@
         <v>45491.5859375</v>
       </c>
       <c r="C1085" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1085" t="inlineStr">
         <is>
@@ -71374,7 +71374,7 @@
         <v>45632</v>
       </c>
       <c r="C1086" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1086" t="inlineStr">
         <is>
@@ -71431,7 +71431,7 @@
         <v>45509</v>
       </c>
       <c r="C1087" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1087" t="inlineStr">
         <is>
@@ -71493,7 +71493,7 @@
         <v>45687.65449074074</v>
       </c>
       <c r="C1088" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1088" t="inlineStr">
         <is>
@@ -71555,7 +71555,7 @@
         <v>44708</v>
       </c>
       <c r="C1089" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1089" t="inlineStr">
         <is>
@@ -71617,7 +71617,7 @@
         <v>44964</v>
       </c>
       <c r="C1090" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1090" t="inlineStr">
         <is>
@@ -71674,7 +71674,7 @@
         <v>45761.61501157407</v>
       </c>
       <c r="C1091" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1091" t="inlineStr">
         <is>

--- a/Översikt HÄRJEDALEN.xlsx
+++ b/Översikt HÄRJEDALEN.xlsx
@@ -567,7 +567,7 @@
         <v>45513</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         <v>45763</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>44785</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>44790</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>44553</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>44837</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>44844</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>44749</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>44406</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>45691</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>44182</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>44154.40430555555</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>45531</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>45761.58262731481</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>44831</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>44496.94013888889</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>44865.57574074074</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
         <v>45667</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>44650</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2727,7 +2727,7 @@
         <v>45250</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>45351</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>45180</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3043,7 +3043,7 @@
         <v>44200</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>45631</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>45554</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>44690</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
         <v>44501</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
         <v>44193</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         <v>44182</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>45544.35653935185</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>44487</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
         <v>45631</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>44440</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>45625.49736111111</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         <v>44406</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         <v>45544</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4506,7 +4506,7 @@
         <v>45106</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         <v>45837</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>45217</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>45571</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         <v>44774</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>44357</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         <v>45544</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>45198</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5315,7 +5315,7 @@
         <v>45457.38396990741</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         <v>45175</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5527,7 +5527,7 @@
         <v>45531</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         <v>45411</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         <v>45833.43898148148</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>45477.46537037037</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5929,7 +5929,7 @@
         <v>45694</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>44553</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>45471.59034722222</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
         <v>44406</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
         <v>45614.45413194445</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6430,7 +6430,7 @@
         <v>44517</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6523,7 +6523,7 @@
         <v>44553</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6620,7 +6620,7 @@
         <v>44377</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
         <v>45426</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6808,7 +6808,7 @@
         <v>45677.45212962963</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         <v>45741.82913194445</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         <v>44430</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7092,7 +7092,7 @@
         <v>44553</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         <v>45007</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7288,7 +7288,7 @@
         <v>45715</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         <v>45531.45444444445</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7483,7 +7483,7 @@
         <v>44242</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7573,7 +7573,7 @@
         <v>45625.45384259259</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7676,7 +7676,7 @@
         <v>45772.51116898148</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7771,7 +7771,7 @@
         <v>45616.6450462963</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7869,7 +7869,7 @@
         <v>45568</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7964,7 +7964,7 @@
         <v>45719</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8058,7 +8058,7 @@
         <v>45869</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8152,7 +8152,7 @@
         <v>45559</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8251,7 +8251,7 @@
         <v>45574</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8345,7 +8345,7 @@
         <v>45432.94736111111</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8443,7 +8443,7 @@
         <v>45243</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         <v>44517</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
         <v>44882</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8718,7 +8718,7 @@
         <v>44979</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8807,7 +8807,7 @@
         <v>44430</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8908,7 +8908,7 @@
         <v>44294</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>44294</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9084,7 +9084,7 @@
         <v>45694</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         <v>44476</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>45467.47204861111</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9357,7 +9357,7 @@
         <v>45559.38894675926</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9454,7 +9454,7 @@
         <v>45537.45818287037</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9551,7 +9551,7 @@
         <v>44977</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9648,7 +9648,7 @@
         <v>44957</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9740,7 +9740,7 @@
         <v>45838.73927083334</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9833,7 +9833,7 @@
         <v>45883.35789351852</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9925,7 +9925,7 @@
         <v>45552</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10013,7 +10013,7 @@
         <v>45666</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10110,7 +10110,7 @@
         <v>45007</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
         <v>45531.45752314815</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10291,7 +10291,7 @@
         <v>45085</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10383,7 +10383,7 @@
         <v>45506.35658564815</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10475,7 +10475,7 @@
         <v>44377</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10567,7 +10567,7 @@
         <v>44475</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10654,7 +10654,7 @@
         <v>44441</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10741,7 +10741,7 @@
         <v>44475</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10828,7 +10828,7 @@
         <v>44475</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10915,7 +10915,7 @@
         <v>44713</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11015,7 +11015,7 @@
         <v>45468</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11102,7 +11102,7 @@
         <v>44074</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11198,7 +11198,7 @@
         <v>45791</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11285,7 +11285,7 @@
         <v>45800.3484375</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11377,7 +11377,7 @@
         <v>44107</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11473,7 +11473,7 @@
         <v>45617</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         <v>45821.56523148148</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11661,7 +11661,7 @@
         <v>45841.41003472222</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11748,7 +11748,7 @@
         <v>45849.35011574074</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11835,7 +11835,7 @@
         <v>44180</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11927,7 +11927,7 @@
         <v>44186</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12018,7 +12018,7 @@
         <v>44677</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12109,7 +12109,7 @@
         <v>44286</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12195,7 +12195,7 @@
         <v>44475</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12281,7 +12281,7 @@
         <v>45772.51070601852</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12372,7 +12372,7 @@
         <v>45538</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12463,7 +12463,7 @@
         <v>45035</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12558,7 +12558,7 @@
         <v>45786.6590625</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12649,7 +12649,7 @@
         <v>45786.66594907407</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12740,7 +12740,7 @@
         <v>45786.65452546296</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12831,7 +12831,7 @@
         <v>45786.6768287037</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12922,7 +12922,7 @@
         <v>45786.67261574074</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13013,7 +13013,7 @@
         <v>45786.67016203704</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13104,7 +13104,7 @@
         <v>44987</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13199,7 +13199,7 @@
         <v>45805.73822916667</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13290,7 +13290,7 @@
         <v>45644.56555555556</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13385,7 +13385,7 @@
         <v>45833</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13471,7 +13471,7 @@
         <v>44475</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13557,7 +13557,7 @@
         <v>44221</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13643,7 +13643,7 @@
         <v>45621</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13738,7 +13738,7 @@
         <v>45191</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13829,7 +13829,7 @@
         <v>45880.37559027778</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -13915,7 +13915,7 @@
         <v>45772.36488425926</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14010,7 +14010,7 @@
         <v>45552</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14100,7 +14100,7 @@
         <v>44853</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14190,7 +14190,7 @@
         <v>44866.46503472222</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14285,7 +14285,7 @@
         <v>44955</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14375,7 +14375,7 @@
         <v>45595.58056712963</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14466,7 +14466,7 @@
         <v>45694</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14552,7 +14552,7 @@
         <v>45153</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14642,7 +14642,7 @@
         <v>44449</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14728,7 +14728,7 @@
         <v>44096</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -14818,7 +14818,7 @@
         <v>44475</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -14903,7 +14903,7 @@
         <v>44321</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -14993,7 +14993,7 @@
         <v>44475</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15078,7 +15078,7 @@
         <v>44475</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15163,7 +15163,7 @@
         <v>44113</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15248,7 +15248,7 @@
         <v>44105</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15333,7 +15333,7 @@
         <v>44769.48783564815</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15423,7 +15423,7 @@
         <v>45729.64623842593</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -15513,7 +15513,7 @@
         <v>45345</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -15603,7 +15603,7 @@
         <v>45457.38677083333</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -15693,7 +15693,7 @@
         <v>45320</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -15778,7 +15778,7 @@
         <v>45621.47555555555</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -15868,7 +15868,7 @@
         <v>45714.55248842593</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -15962,7 +15962,7 @@
         <v>45800.63043981481</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16056,7 +16056,7 @@
         <v>45538.57630787037</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16145,7 +16145,7 @@
         <v>45805.66601851852</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -16239,7 +16239,7 @@
         <v>45805.73546296296</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -16329,7 +16329,7 @@
         <v>45603</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -16419,7 +16419,7 @@
         <v>45617</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -16513,7 +16513,7 @@
         <v>45454.62443287037</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -16598,7 +16598,7 @@
         <v>45111</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -16688,7 +16688,7 @@
         <v>45812.82244212963</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -16778,7 +16778,7 @@
         <v>45638.33607638889</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -16868,7 +16868,7 @@
         <v>44475</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -16953,7 +16953,7 @@
         <v>45791</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>45835.7499537037</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17128,7 +17128,7 @@
         <v>45838.773125</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -17218,7 +17218,7 @@
         <v>45869</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -17303,7 +17303,7 @@
         <v>45889.56214120371</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -17393,7 +17393,7 @@
         <v>45875</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -17482,7 +17482,7 @@
         <v>45758.70164351852</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -17567,7 +17567,7 @@
         <v>45308</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -17656,7 +17656,7 @@
         <v>45540.69512731482</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -17746,7 +17746,7 @@
         <v>45672.50416666667</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -17831,7 +17831,7 @@
         <v>44320</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -17888,7 +17888,7 @@
         <v>44316</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
         <v>44320</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -18007,7 +18007,7 @@
         <v>44105</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -18064,7 +18064,7 @@
         <v>44810</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -18126,7 +18126,7 @@
         <v>44727.70908564814</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -18188,7 +18188,7 @@
         <v>44430</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -18250,7 +18250,7 @@
         <v>44543</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -18307,7 +18307,7 @@
         <v>44614</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -18369,7 +18369,7 @@
         <v>44404</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -18426,7 +18426,7 @@
         <v>44417.38271990741</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -18483,7 +18483,7 @@
         <v>44417.38614583333</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -18540,7 +18540,7 @@
         <v>44497</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -18597,7 +18597,7 @@
         <v>44475</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -18654,7 +18654,7 @@
         <v>44531</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -18711,7 +18711,7 @@
         <v>44361</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -18768,7 +18768,7 @@
         <v>44600</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -18825,7 +18825,7 @@
         <v>44540</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -18887,7 +18887,7 @@
         <v>44475</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -18944,7 +18944,7 @@
         <v>44385.93652777778</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -19006,7 +19006,7 @@
         <v>44538</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -19068,7 +19068,7 @@
         <v>44475</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -19125,7 +19125,7 @@
         <v>44406</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -19182,7 +19182,7 @@
         <v>44854</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -19239,7 +19239,7 @@
         <v>44102</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -19296,7 +19296,7 @@
         <v>44823</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -19358,7 +19358,7 @@
         <v>44424</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -19415,7 +19415,7 @@
         <v>44316</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -19472,7 +19472,7 @@
         <v>44483</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -19529,7 +19529,7 @@
         <v>44421</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -19586,7 +19586,7 @@
         <v>44418</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -19648,7 +19648,7 @@
         <v>44488</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -19710,7 +19710,7 @@
         <v>44603</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -19772,7 +19772,7 @@
         <v>44132</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -19829,7 +19829,7 @@
         <v>44179</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -19886,7 +19886,7 @@
         <v>44418</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -19948,7 +19948,7 @@
         <v>44564.6747337963</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -20010,7 +20010,7 @@
         <v>44361</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -20072,7 +20072,7 @@
         <v>44615</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -20134,7 +20134,7 @@
         <v>44466.81701388889</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -20191,7 +20191,7 @@
         <v>44218</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -20248,7 +20248,7 @@
         <v>44286</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -20305,7 +20305,7 @@
         <v>44475</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -20362,7 +20362,7 @@
         <v>44475</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -20419,7 +20419,7 @@
         <v>44410.74284722222</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -20476,7 +20476,7 @@
         <v>44631</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -20538,7 +20538,7 @@
         <v>44810</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -20600,7 +20600,7 @@
         <v>44631.41535879629</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -20662,7 +20662,7 @@
         <v>44728</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -20719,7 +20719,7 @@
         <v>44417.37519675926</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -20776,7 +20776,7 @@
         <v>44344</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -20833,7 +20833,7 @@
         <v>44174</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -20890,7 +20890,7 @@
         <v>44084</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -20952,7 +20952,7 @@
         <v>44475</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -21009,7 +21009,7 @@
         <v>44078</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -21066,7 +21066,7 @@
         <v>44424</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -21123,7 +21123,7 @@
         <v>44424</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -21180,7 +21180,7 @@
         <v>44258</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -21237,7 +21237,7 @@
         <v>44818</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -21294,7 +21294,7 @@
         <v>44770.53315972222</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -21351,7 +21351,7 @@
         <v>44690</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -21408,7 +21408,7 @@
         <v>44286</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -21465,7 +21465,7 @@
         <v>44285</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -21522,7 +21522,7 @@
         <v>44385.93658564815</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -21584,7 +21584,7 @@
         <v>44792.68023148148</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -21641,7 +21641,7 @@
         <v>44243.63096064814</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -21698,7 +21698,7 @@
         <v>44298</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -21755,7 +21755,7 @@
         <v>44183</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -21812,7 +21812,7 @@
         <v>44319</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -21869,7 +21869,7 @@
         <v>44316</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -21926,7 +21926,7 @@
         <v>44316</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -21983,7 +21983,7 @@
         <v>44126</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -22040,7 +22040,7 @@
         <v>44825</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -22097,7 +22097,7 @@
         <v>44174</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -22154,7 +22154,7 @@
         <v>44154</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -22216,7 +22216,7 @@
         <v>44396</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -22273,7 +22273,7 @@
         <v>44475</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -22330,7 +22330,7 @@
         <v>44127</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -22392,7 +22392,7 @@
         <v>44475</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -22449,7 +22449,7 @@
         <v>44475</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -22506,7 +22506,7 @@
         <v>44475</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -22563,7 +22563,7 @@
         <v>44475</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -22620,7 +22620,7 @@
         <v>44544</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -22682,7 +22682,7 @@
         <v>44420.33096064815</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -22739,7 +22739,7 @@
         <v>44188</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -22801,7 +22801,7 @@
         <v>44483.36435185185</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -22858,7 +22858,7 @@
         <v>44417</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -22915,7 +22915,7 @@
         <v>44181</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -22977,7 +22977,7 @@
         <v>44426.45706018519</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -23034,7 +23034,7 @@
         <v>44859</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -23096,7 +23096,7 @@
         <v>44473</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -23153,7 +23153,7 @@
         <v>44314</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -23210,7 +23210,7 @@
         <v>44335.4837962963</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -23267,7 +23267,7 @@
         <v>44727.71858796296</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -23329,7 +23329,7 @@
         <v>44475</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -23386,7 +23386,7 @@
         <v>44543</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -23448,7 +23448,7 @@
         <v>44475</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -23505,7 +23505,7 @@
         <v>44475</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -23562,7 +23562,7 @@
         <v>44725</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -23624,7 +23624,7 @@
         <v>44481.67951388889</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -23681,7 +23681,7 @@
         <v>44855.60383101852</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -23738,7 +23738,7 @@
         <v>44631.45398148148</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -23800,7 +23800,7 @@
         <v>44133</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -23862,7 +23862,7 @@
         <v>44417.37207175926</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -23919,7 +23919,7 @@
         <v>44631.37421296296</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -23981,7 +23981,7 @@
         <v>44768.44859953703</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -24038,7 +24038,7 @@
         <v>44230</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -24095,7 +24095,7 @@
         <v>44538</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -24157,7 +24157,7 @@
         <v>44368</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -24214,7 +24214,7 @@
         <v>44403</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -24271,7 +24271,7 @@
         <v>44886.62578703704</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -24328,7 +24328,7 @@
         <v>44886.629375</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -24385,7 +24385,7 @@
         <v>44838</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -24447,7 +24447,7 @@
         <v>44126</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -24509,7 +24509,7 @@
         <v>44475</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -24566,7 +24566,7 @@
         <v>44475</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -24623,7 +24623,7 @@
         <v>44475</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -24680,7 +24680,7 @@
         <v>44475</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -24737,7 +24737,7 @@
         <v>44540.56034722222</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -24794,7 +24794,7 @@
         <v>44872</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -24856,7 +24856,7 @@
         <v>44742</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -24918,7 +24918,7 @@
         <v>44166</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -24980,7 +24980,7 @@
         <v>44708.46081018518</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -25042,7 +25042,7 @@
         <v>44684</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -25104,7 +25104,7 @@
         <v>44531</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -25161,7 +25161,7 @@
         <v>44188</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -25218,7 +25218,7 @@
         <v>44270</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -25275,7 +25275,7 @@
         <v>44531</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -25332,7 +25332,7 @@
         <v>44531</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -25389,7 +25389,7 @@
         <v>44169</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -25446,7 +25446,7 @@
         <v>44530.40607638889</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -25503,7 +25503,7 @@
         <v>44788.67976851852</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -25565,7 +25565,7 @@
         <v>44180</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -25622,7 +25622,7 @@
         <v>44413</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -25679,7 +25679,7 @@
         <v>44207</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -25741,7 +25741,7 @@
         <v>44706.66417824074</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -25803,7 +25803,7 @@
         <v>44475</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -25860,7 +25860,7 @@
         <v>44316</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -25917,7 +25917,7 @@
         <v>44803</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -25974,7 +25974,7 @@
         <v>44389</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -26036,7 +26036,7 @@
         <v>44316</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -26093,7 +26093,7 @@
         <v>44285</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -26150,7 +26150,7 @@
         <v>44377</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -26207,7 +26207,7 @@
         <v>44627.36047453704</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -26269,7 +26269,7 @@
         <v>45071.92488425926</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -26326,7 +26326,7 @@
         <v>45772.36106481482</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -26388,7 +26388,7 @@
         <v>45684.51006944444</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -26445,7 +26445,7 @@
         <v>44825</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -26502,7 +26502,7 @@
         <v>45345.66555555556</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -26564,7 +26564,7 @@
         <v>45471.66556712963</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -26626,7 +26626,7 @@
         <v>45705.32643518518</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -26683,7 +26683,7 @@
         <v>45362.64613425926</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -26740,7 +26740,7 @@
         <v>45362.65407407407</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -26797,7 +26797,7 @@
         <v>45362.67789351852</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -26854,7 +26854,7 @@
         <v>45579.57390046296</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -26916,7 +26916,7 @@
         <v>44643.81518518519</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -26973,7 +26973,7 @@
         <v>45280</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -27030,7 +27030,7 @@
         <v>44999.60127314815</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -27087,7 +27087,7 @@
         <v>45772.46965277778</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -27149,7 +27149,7 @@
         <v>45772.46988425926</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -27211,7 +27211,7 @@
         <v>44216</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -27273,7 +27273,7 @@
         <v>44300</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -27330,7 +27330,7 @@
         <v>45604.32543981481</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -27392,7 +27392,7 @@
         <v>45406</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -27454,7 +27454,7 @@
         <v>45406</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -27516,7 +27516,7 @@
         <v>44823.84673611111</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -27573,7 +27573,7 @@
         <v>44361</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -27630,7 +27630,7 @@
         <v>45342</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -27687,7 +27687,7 @@
         <v>45688.67935185185</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -27749,7 +27749,7 @@
         <v>45688.67145833333</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -27811,7 +27811,7 @@
         <v>44312</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -27868,7 +27868,7 @@
         <v>45603</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -27930,7 +27930,7 @@
         <v>45741.45597222223</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -27987,7 +27987,7 @@
         <v>45119.39105324074</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -28049,7 +28049,7 @@
         <v>45733.38637731481</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -28106,7 +28106,7 @@
         <v>45085</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -28163,7 +28163,7 @@
         <v>45509</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -28225,7 +28225,7 @@
         <v>45729.65261574074</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -28287,7 +28287,7 @@
         <v>45687.65449074074</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -28349,7 +28349,7 @@
         <v>45106</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -28411,7 +28411,7 @@
         <v>45484.66521990741</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -28473,7 +28473,7 @@
         <v>45740.44842592593</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -28535,7 +28535,7 @@
         <v>45776.69569444445</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -28592,7 +28592,7 @@
         <v>45575</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -28649,7 +28649,7 @@
         <v>45776.43898148148</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -28706,7 +28706,7 @@
         <v>44862</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -28768,7 +28768,7 @@
         <v>45243.63798611111</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -28825,7 +28825,7 @@
         <v>44472</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -28882,7 +28882,7 @@
         <v>45254</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -28939,7 +28939,7 @@
         <v>45345.35003472222</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -29001,7 +29001,7 @@
         <v>45779.48611111111</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -29063,7 +29063,7 @@
         <v>45429</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -29120,7 +29120,7 @@
         <v>45460.47969907407</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -29177,7 +29177,7 @@
         <v>45407.36894675926</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -29239,7 +29239,7 @@
         <v>45779.38211805555</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -29301,7 +29301,7 @@
         <v>45779.47704861111</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -29363,7 +29363,7 @@
         <v>45779.50052083333</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -29425,7 +29425,7 @@
         <v>45779.41844907407</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -29487,7 +29487,7 @@
         <v>45737</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -29544,7 +29544,7 @@
         <v>45782.41581018519</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -29601,7 +29601,7 @@
         <v>45779.50886574074</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -29663,7 +29663,7 @@
         <v>45779.51943287037</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -29725,7 +29725,7 @@
         <v>45779.52488425926</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -29787,7 +29787,7 @@
         <v>45537.60471064815</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -29849,7 +29849,7 @@
         <v>45782.42744212963</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -29906,7 +29906,7 @@
         <v>45779.51357638889</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -29968,7 +29968,7 @@
         <v>44414.58354166667</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -30025,7 +30025,7 @@
         <v>44167</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -30082,7 +30082,7 @@
         <v>45784.59012731481</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -30144,7 +30144,7 @@
         <v>45618.35961805555</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -30201,7 +30201,7 @@
         <v>45783.68547453704</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -30263,7 +30263,7 @@
         <v>45632.64078703704</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -30320,7 +30320,7 @@
         <v>45768.29630787037</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -30382,7 +30382,7 @@
         <v>45768.30954861111</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -30444,7 +30444,7 @@
         <v>45483.47572916667</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -30501,7 +30501,7 @@
         <v>44312</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -30558,7 +30558,7 @@
         <v>45642</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -30615,7 +30615,7 @@
         <v>45569.6909837963</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -30672,7 +30672,7 @@
         <v>45763.41402777778</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -30729,7 +30729,7 @@
         <v>45786.66032407407</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -30791,7 +30791,7 @@
         <v>45786.66853009259</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -30853,7 +30853,7 @@
         <v>45275</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -30910,7 +30910,7 @@
         <v>45568</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -30972,7 +30972,7 @@
         <v>44082</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -31034,7 +31034,7 @@
         <v>44925</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -31091,7 +31091,7 @@
         <v>44732</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -31148,7 +31148,7 @@
         <v>45453.6619212963</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -31205,7 +31205,7 @@
         <v>45260.35777777778</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -31262,7 +31262,7 @@
         <v>45786.66209490741</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -31324,7 +31324,7 @@
         <v>45670.34313657408</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -31381,7 +31381,7 @@
         <v>45560.33311342593</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -31443,7 +31443,7 @@
         <v>45540.4264699074</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -31505,7 +31505,7 @@
         <v>44925.64049768518</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -31567,7 +31567,7 @@
         <v>45786.66425925926</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -31629,7 +31629,7 @@
         <v>45387</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -31686,7 +31686,7 @@
         <v>45457.92854166667</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -31743,7 +31743,7 @@
         <v>45785.34165509259</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -31800,7 +31800,7 @@
         <v>45785.33164351852</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -31857,7 +31857,7 @@
         <v>45588.56039351852</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -31914,7 +31914,7 @@
         <v>44348</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -31971,7 +31971,7 @@
         <v>45257</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -32033,7 +32033,7 @@
         <v>45610.56706018518</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -32095,7 +32095,7 @@
         <v>45790.43</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -32157,7 +32157,7 @@
         <v>45279.57732638889</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -32214,7 +32214,7 @@
         <v>44883</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -32271,7 +32271,7 @@
         <v>45509</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -32333,7 +32333,7 @@
         <v>44091</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -32390,7 +32390,7 @@
         <v>44985</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -32452,7 +32452,7 @@
         <v>44853.41693287037</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -32509,7 +32509,7 @@
         <v>45252.45481481482</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -32566,7 +32566,7 @@
         <v>44957</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -32628,7 +32628,7 @@
         <v>45582.59753472222</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -32690,7 +32690,7 @@
         <v>44475</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -32747,7 +32747,7 @@
         <v>45096.62344907408</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -32809,7 +32809,7 @@
         <v>45792.64795138889</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -32866,7 +32866,7 @@
         <v>45177.9224537037</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -32923,7 +32923,7 @@
         <v>45632</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -32980,7 +32980,7 @@
         <v>45624.36858796296</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -33037,7 +33037,7 @@
         <v>45790.87653935186</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -33094,7 +33094,7 @@
         <v>45484.57285879629</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -33156,7 +33156,7 @@
         <v>44153</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -33213,7 +33213,7 @@
         <v>45638.416875</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -33275,7 +33275,7 @@
         <v>45792.65047453704</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -33332,7 +33332,7 @@
         <v>45607</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -33394,7 +33394,7 @@
         <v>44987.35282407407</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -33456,7 +33456,7 @@
         <v>45517.39274305556</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -33518,7 +33518,7 @@
         <v>45772.69290509259</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -33580,7 +33580,7 @@
         <v>45792.50942129629</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -33642,7 +33642,7 @@
         <v>45485</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -33699,7 +33699,7 @@
         <v>45041</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -33756,7 +33756,7 @@
         <v>44424</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -33813,7 +33813,7 @@
         <v>45173</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -33870,7 +33870,7 @@
         <v>45170.4643287037</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -33932,7 +33932,7 @@
         <v>45618.35097222222</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -33989,7 +33989,7 @@
         <v>45467</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -34046,7 +34046,7 @@
         <v>45637</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -34103,7 +34103,7 @@
         <v>45484</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -34165,7 +34165,7 @@
         <v>45481.3330787037</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -34227,7 +34227,7 @@
         <v>45796.39770833333</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -34284,7 +34284,7 @@
         <v>45506.36534722222</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -34341,7 +34341,7 @@
         <v>45478.48700231482</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -34403,7 +34403,7 @@
         <v>45491.5859375</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -34460,7 +34460,7 @@
         <v>45793.41994212963</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -34522,7 +34522,7 @@
         <v>45559</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -34579,7 +34579,7 @@
         <v>45604.33195601852</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -34641,7 +34641,7 @@
         <v>44082</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -34703,7 +34703,7 @@
         <v>45506.36702546296</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -34760,7 +34760,7 @@
         <v>45796.57802083333</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -34817,7 +34817,7 @@
         <v>45453.6672800926</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -34874,7 +34874,7 @@
         <v>45509</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -34936,7 +34936,7 @@
         <v>45509.6427662037</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -34998,7 +34998,7 @@
         <v>45635.33439814814</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -35060,7 +35060,7 @@
         <v>45631</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -35122,7 +35122,7 @@
         <v>45621</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -35184,7 +35184,7 @@
         <v>44987.34981481481</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -35246,7 +35246,7 @@
         <v>45674.57393518519</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -35303,7 +35303,7 @@
         <v>45569</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -35365,7 +35365,7 @@
         <v>44075</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -35422,7 +35422,7 @@
         <v>45632.64769675926</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -35479,7 +35479,7 @@
         <v>45483.47207175926</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -35536,7 +35536,7 @@
         <v>45631</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -35598,7 +35598,7 @@
         <v>45485</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -35660,7 +35660,7 @@
         <v>45485</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -35722,7 +35722,7 @@
         <v>45593.67809027778</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -35779,7 +35779,7 @@
         <v>45791</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -35836,7 +35836,7 @@
         <v>45797.37096064815</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -35893,7 +35893,7 @@
         <v>45485</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -35955,7 +35955,7 @@
         <v>45800.58859953703</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -36012,7 +36012,7 @@
         <v>45800.59567129629</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -36074,7 +36074,7 @@
         <v>45800.64719907408</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -36136,7 +36136,7 @@
         <v>44628.36402777778</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -36193,7 +36193,7 @@
         <v>45800.56313657408</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -36250,7 +36250,7 @@
         <v>45800.57837962963</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -36312,7 +36312,7 @@
         <v>45830</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -36369,7 +36369,7 @@
         <v>45800.48060185185</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -36431,7 +36431,7 @@
         <v>45799.64804398148</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -36493,7 +36493,7 @@
         <v>45837</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -36550,7 +36550,7 @@
         <v>45253.55737268519</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -36607,7 +36607,7 @@
         <v>45800.3787037037</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -36669,7 +36669,7 @@
         <v>44565.31975694445</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -36731,7 +36731,7 @@
         <v>44565</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -36793,7 +36793,7 @@
         <v>45834</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -36850,7 +36850,7 @@
         <v>45800.44868055556</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -36912,7 +36912,7 @@
         <v>45800.4687962963</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -36974,7 +36974,7 @@
         <v>45800.50431712963</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -37036,7 +37036,7 @@
         <v>44316</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -37093,7 +37093,7 @@
         <v>45642.35256944445</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -37150,7 +37150,7 @@
         <v>45800.56222222222</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -37212,7 +37212,7 @@
         <v>45799.57883101852</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -37269,7 +37269,7 @@
         <v>45799.45770833334</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -37331,7 +37331,7 @@
         <v>45830</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -37388,7 +37388,7 @@
         <v>45830</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -37445,7 +37445,7 @@
         <v>45800.65341435185</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -37507,7 +37507,7 @@
         <v>45799.47225694444</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -37569,7 +37569,7 @@
         <v>45644.50141203704</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -37631,7 +37631,7 @@
         <v>45800.33436342593</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -37693,7 +37693,7 @@
         <v>45800.3425</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -37755,7 +37755,7 @@
         <v>44924.61315972222</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -37817,7 +37817,7 @@
         <v>45345.47642361111</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -37879,7 +37879,7 @@
         <v>45345.48181712963</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -37941,7 +37941,7 @@
         <v>45345.4940625</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -38003,7 +38003,7 @@
         <v>45799.43550925926</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -38065,7 +38065,7 @@
         <v>45800.46069444445</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -38127,7 +38127,7 @@
         <v>45800.48515046296</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -38189,7 +38189,7 @@
         <v>45800.56995370371</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -38251,7 +38251,7 @@
         <v>45665.563125</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -38313,7 +38313,7 @@
         <v>45800.37524305555</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -38375,7 +38375,7 @@
         <v>45800.42797453704</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -38432,7 +38432,7 @@
         <v>45800.44090277778</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -38489,7 +38489,7 @@
         <v>45800.64065972222</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -38551,7 +38551,7 @@
         <v>45237.5815162037</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -38608,7 +38608,7 @@
         <v>45800.63738425926</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -38670,7 +38670,7 @@
         <v>45830</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -38727,7 +38727,7 @@
         <v>45800.60508101852</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -38789,7 +38789,7 @@
         <v>45800.66043981481</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -38851,7 +38851,7 @@
         <v>45799.4658912037</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -38913,7 +38913,7 @@
         <v>45799.46642361111</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -38970,7 +38970,7 @@
         <v>45800.3503587963</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -39032,7 +39032,7 @@
         <v>45800.35670138889</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -39094,7 +39094,7 @@
         <v>45362.67293981482</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -39151,7 +39151,7 @@
         <v>45800.41883101852</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -39213,7 +39213,7 @@
         <v>45799.43086805556</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -39275,7 +39275,7 @@
         <v>45614.47960648148</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -39332,7 +39332,7 @@
         <v>44305</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -39389,7 +39389,7 @@
         <v>45804.5813425926</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -39451,7 +39451,7 @@
         <v>45803.37258101852</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -39508,7 +39508,7 @@
         <v>45517.38320601852</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -39565,7 +39565,7 @@
         <v>45345</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -39627,7 +39627,7 @@
         <v>45804.589375</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -39684,7 +39684,7 @@
         <v>45624.57098379629</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -39741,7 +39741,7 @@
         <v>45803.37480324074</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -39798,7 +39798,7 @@
         <v>45685</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -39860,7 +39860,7 @@
         <v>44914</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -39942,7 +39942,7 @@
         <v>44928.48072916667</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -40004,7 +40004,7 @@
         <v>45531.78386574074</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -40061,7 +40061,7 @@
         <v>45805.53280092592</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -40123,7 +40123,7 @@
         <v>45097</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -40185,7 +40185,7 @@
         <v>45202</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -40247,7 +40247,7 @@
         <v>45362.65903935185</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -40304,7 +40304,7 @@
         <v>45644.56674768519</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -40366,7 +40366,7 @@
         <v>44924.59140046296</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -40428,7 +40428,7 @@
         <v>45635.35274305556</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -40490,7 +40490,7 @@
         <v>45485.42287037037</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -40547,7 +40547,7 @@
         <v>45485</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -40604,7 +40604,7 @@
         <v>45485.44258101852</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -40666,7 +40666,7 @@
         <v>45159.60288194445</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -40723,7 +40723,7 @@
         <v>45807.60333333333</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -40785,7 +40785,7 @@
         <v>45807.58868055556</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -40847,7 +40847,7 @@
         <v>45603</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -40909,7 +40909,7 @@
         <v>45617</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -40971,7 +40971,7 @@
         <v>45807.59407407408</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -41033,7 +41033,7 @@
         <v>45807.41287037037</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -41095,7 +41095,7 @@
         <v>45807.42212962963</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -41157,7 +41157,7 @@
         <v>45807.45288194445</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -41219,7 +41219,7 @@
         <v>45807.49436342593</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -41281,7 +41281,7 @@
         <v>45807.49832175926</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -41343,7 +41343,7 @@
         <v>45622</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -41405,7 +41405,7 @@
         <v>45807.58393518518</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -41467,7 +41467,7 @@
         <v>45807.36304398148</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -41529,7 +41529,7 @@
         <v>45807.41717592593</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -41591,7 +41591,7 @@
         <v>45807.43461805556</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -41653,7 +41653,7 @@
         <v>45807.44070601852</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -41715,7 +41715,7 @@
         <v>45807.44608796296</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -41777,7 +41777,7 @@
         <v>45225.58005787037</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -41834,7 +41834,7 @@
         <v>45807.63334490741</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -41896,7 +41896,7 @@
         <v>45807.47479166667</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -41958,7 +41958,7 @@
         <v>45807.49045138889</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -42020,7 +42020,7 @@
         <v>45408</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -42077,7 +42077,7 @@
         <v>45646</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -42134,7 +42134,7 @@
         <v>45807.65438657408</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -42196,7 +42196,7 @@
         <v>45807.3409837963</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -42258,7 +42258,7 @@
         <v>45807.35476851852</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -42320,7 +42320,7 @@
         <v>45807.55893518519</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -42382,7 +42382,7 @@
         <v>44153</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -42444,7 +42444,7 @@
         <v>45807.5684375</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -42506,7 +42506,7 @@
         <v>45350</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -42563,7 +42563,7 @@
         <v>45351</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -42620,7 +42620,7 @@
         <v>45345.34219907408</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -42682,7 +42682,7 @@
         <v>45617</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -42744,7 +42744,7 @@
         <v>44631.37701388889</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -42806,7 +42806,7 @@
         <v>45730</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -42863,7 +42863,7 @@
         <v>44631.42353009259</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -42925,7 +42925,7 @@
         <v>45807.56403935186</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -42987,7 +42987,7 @@
         <v>45170.46134259259</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -43049,7 +43049,7 @@
         <v>45737.37006944444</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -43106,7 +43106,7 @@
         <v>44914</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -43163,7 +43163,7 @@
         <v>45334</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -43225,7 +43225,7 @@
         <v>45685</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -43282,7 +43282,7 @@
         <v>45607.44832175926</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -43344,7 +43344,7 @@
         <v>44698</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -43406,7 +43406,7 @@
         <v>45617</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -43468,7 +43468,7 @@
         <v>45280</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -43525,7 +43525,7 @@
         <v>45811.34540509259</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -43587,7 +43587,7 @@
         <v>45212</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -43644,7 +43644,7 @@
         <v>44925</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -43706,7 +43706,7 @@
         <v>45811.34564814815</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -43768,7 +43768,7 @@
         <v>45691</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -43830,7 +43830,7 @@
         <v>45691</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -43892,7 +43892,7 @@
         <v>45733</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -43949,7 +43949,7 @@
         <v>45111</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -44006,7 +44006,7 @@
         <v>45811.34578703704</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -44068,7 +44068,7 @@
         <v>45768.29289351852</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -44130,7 +44130,7 @@
         <v>45768.30086805556</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -44192,7 +44192,7 @@
         <v>45119.38675925926</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -44254,7 +44254,7 @@
         <v>45111</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -44316,7 +44316,7 @@
         <v>45546.54530092593</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -44373,7 +44373,7 @@
         <v>45813.64590277777</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -44430,7 +44430,7 @@
         <v>44638.44958333333</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -44487,7 +44487,7 @@
         <v>45813.47074074074</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -44544,7 +44544,7 @@
         <v>44162.65819444445</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -44606,7 +44606,7 @@
         <v>45510</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -44663,7 +44663,7 @@
         <v>45813.48734953703</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -44720,7 +44720,7 @@
         <v>45406.64024305555</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -44782,7 +44782,7 @@
         <v>45642.33616898148</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -44839,7 +44839,7 @@
         <v>45061.61002314815</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -44901,7 +44901,7 @@
         <v>45758.49096064815</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -44963,7 +44963,7 @@
         <v>45568</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -45025,7 +45025,7 @@
         <v>45303</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -45082,7 +45082,7 @@
         <v>45754.67329861111</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -45139,7 +45139,7 @@
         <v>45622.64627314815</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -45196,7 +45196,7 @@
         <v>45859</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -45253,7 +45253,7 @@
         <v>45506.3637962963</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -45310,7 +45310,7 @@
         <v>45687.53689814815</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -45367,7 +45367,7 @@
         <v>45432</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -45429,7 +45429,7 @@
         <v>45762.55899305556</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -45486,7 +45486,7 @@
         <v>44242</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -45543,7 +45543,7 @@
         <v>44939.45376157408</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -45600,7 +45600,7 @@
         <v>44994</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -45657,7 +45657,7 @@
         <v>44883</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -45714,7 +45714,7 @@
         <v>45817.33819444444</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -45776,7 +45776,7 @@
         <v>45576.48657407407</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -45838,7 +45838,7 @@
         <v>45817.62439814815</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -45895,7 +45895,7 @@
         <v>45231</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -45952,7 +45952,7 @@
         <v>45817.594375</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -46014,7 +46014,7 @@
         <v>45685.38901620371</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -46076,7 +46076,7 @@
         <v>45677.44273148148</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -46133,7 +46133,7 @@
         <v>45678.37956018518</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -46190,7 +46190,7 @@
         <v>45439.62893518519</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -46247,7 +46247,7 @@
         <v>45560</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -46304,7 +46304,7 @@
         <v>44916</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -46361,7 +46361,7 @@
         <v>44440</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -46418,7 +46418,7 @@
         <v>45195.61476851852</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -46475,7 +46475,7 @@
         <v>44977.44643518519</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -46537,7 +46537,7 @@
         <v>44957</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -46599,7 +46599,7 @@
         <v>45820.64821759259</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -46656,7 +46656,7 @@
         <v>45240</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -46713,7 +46713,7 @@
         <v>45215</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -46770,7 +46770,7 @@
         <v>44258</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -46827,7 +46827,7 @@
         <v>45496.66903935185</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -46889,7 +46889,7 @@
         <v>45196</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -46951,7 +46951,7 @@
         <v>45866.40701388889</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -47008,7 +47008,7 @@
         <v>45562.65759259259</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -47070,7 +47070,7 @@
         <v>45866.62908564815</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -47127,7 +47127,7 @@
         <v>45634.65831018519</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -47184,7 +47184,7 @@
         <v>45821.77903935185</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -47241,7 +47241,7 @@
         <v>45061.36835648148</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -47298,7 +47298,7 @@
         <v>45728</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -47355,7 +47355,7 @@
         <v>45821.57201388889</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -47417,7 +47417,7 @@
         <v>44708.45504629629</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -47479,7 +47479,7 @@
         <v>44708</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -47541,7 +47541,7 @@
         <v>45733.43663194445</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -47603,7 +47603,7 @@
         <v>45118.47491898148</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -47665,7 +47665,7 @@
         <v>44985</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -47727,7 +47727,7 @@
         <v>44475</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -47784,7 +47784,7 @@
         <v>45791</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -47841,7 +47841,7 @@
         <v>45867.55305555555</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -47898,7 +47898,7 @@
         <v>45867.55642361111</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -47960,7 +47960,7 @@
         <v>45575.6125925926</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -48022,7 +48022,7 @@
         <v>45868.639375</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -48079,7 +48079,7 @@
         <v>45216</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -48136,7 +48136,7 @@
         <v>45595.5666550926</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -48193,7 +48193,7 @@
         <v>44953</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -48250,7 +48250,7 @@
         <v>45826.43267361111</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -48312,7 +48312,7 @@
         <v>45728.44329861111</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -48374,7 +48374,7 @@
         <v>45728.49267361111</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -48436,7 +48436,7 @@
         <v>45505</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -48493,7 +48493,7 @@
         <v>45505</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -48555,7 +48555,7 @@
         <v>44531.43927083333</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -48617,7 +48617,7 @@
         <v>45645.47609953704</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -48679,7 +48679,7 @@
         <v>45203</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -48736,7 +48736,7 @@
         <v>45827.42467592593</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -48798,7 +48798,7 @@
         <v>45208</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -48855,7 +48855,7 @@
         <v>45772.46951388889</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -48917,7 +48917,7 @@
         <v>45827</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -48974,7 +48974,7 @@
         <v>45827.41753472222</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -49036,7 +49036,7 @@
         <v>44214</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -49098,7 +49098,7 @@
         <v>45205</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -49155,7 +49155,7 @@
         <v>45614.62445601852</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -49217,7 +49217,7 @@
         <v>44180</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -49274,7 +49274,7 @@
         <v>44728</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -49336,7 +49336,7 @@
         <v>45873.59511574074</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -49398,7 +49398,7 @@
         <v>45670.66085648148</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -49455,7 +49455,7 @@
         <v>45533.75398148148</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -49512,7 +49512,7 @@
         <v>45832.64047453704</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -49569,7 +49569,7 @@
         <v>45831</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -49631,7 +49631,7 @@
         <v>45705.32456018519</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -49688,7 +49688,7 @@
         <v>45197.46966435185</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -49745,7 +49745,7 @@
         <v>45209.45420138889</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -49802,7 +49802,7 @@
         <v>44225</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -49859,7 +49859,7 @@
         <v>45832</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -49921,7 +49921,7 @@
         <v>45874.64513888889</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -49978,7 +49978,7 @@
         <v>45832</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -50040,7 +50040,7 @@
         <v>45832.3859837963</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -50102,7 +50102,7 @@
         <v>45832</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -50164,7 +50164,7 @@
         <v>45874.64199074074</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -50221,7 +50221,7 @@
         <v>45174</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -50278,7 +50278,7 @@
         <v>45741.38347222222</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -50335,7 +50335,7 @@
         <v>45834.51079861111</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -50397,7 +50397,7 @@
         <v>45876.39362268519</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -50459,7 +50459,7 @@
         <v>45834.38173611111</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -50516,7 +50516,7 @@
         <v>45875.5196875</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -50573,7 +50573,7 @@
         <v>45834.69577546296</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -50630,7 +50630,7 @@
         <v>45834.71440972222</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -50687,7 +50687,7 @@
         <v>45604.31657407407</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -50749,7 +50749,7 @@
         <v>45834</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -50811,7 +50811,7 @@
         <v>45833</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -50873,7 +50873,7 @@
         <v>45751.63266203704</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -50935,7 +50935,7 @@
         <v>45238.64153935185</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -50992,7 +50992,7 @@
         <v>45265</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -51049,7 +51049,7 @@
         <v>45345</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -51111,7 +51111,7 @@
         <v>45195.35877314815</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -51168,7 +51168,7 @@
         <v>45195.3878125</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -51225,7 +51225,7 @@
         <v>45459</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -51282,7 +51282,7 @@
         <v>45751.34636574074</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -51344,7 +51344,7 @@
         <v>45740.57487268518</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -51406,7 +51406,7 @@
         <v>44784.60677083334</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -51468,7 +51468,7 @@
         <v>45833.36467592593</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -51530,7 +51530,7 @@
         <v>45218.58609953704</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -51587,7 +51587,7 @@
         <v>44827</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -51644,7 +51644,7 @@
         <v>45751.69827546296</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -51706,7 +51706,7 @@
         <v>45721.33868055556</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -51763,7 +51763,7 @@
         <v>45833.6081712963</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -51825,7 +51825,7 @@
         <v>45833</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -51887,7 +51887,7 @@
         <v>45875.47854166666</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -51949,7 +51949,7 @@
         <v>45833</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -52011,7 +52011,7 @@
         <v>45834.6568287037</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -52068,7 +52068,7 @@
         <v>45834</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -52125,7 +52125,7 @@
         <v>45834</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -52187,7 +52187,7 @@
         <v>45834.7087962963</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -52244,7 +52244,7 @@
         <v>45876.49113425926</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -52301,7 +52301,7 @@
         <v>45580.92037037037</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -52358,7 +52358,7 @@
         <v>45474.54432870371</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -52415,7 +52415,7 @@
         <v>44280</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -52472,7 +52472,7 @@
         <v>45835.55998842593</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -52534,7 +52534,7 @@
         <v>45834.80229166667</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -52591,7 +52591,7 @@
         <v>44726</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -52648,7 +52648,7 @@
         <v>45835.5583912037</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -52710,7 +52710,7 @@
         <v>44423</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -52767,7 +52767,7 @@
         <v>45622.64012731481</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -52829,7 +52829,7 @@
         <v>45478.44497685185</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -52891,7 +52891,7 @@
         <v>45880.37472222222</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -52948,7 +52948,7 @@
         <v>45835.57069444445</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -53005,7 +53005,7 @@
         <v>44182</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -53062,7 +53062,7 @@
         <v>44665</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -53119,7 +53119,7 @@
         <v>45173</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -53181,7 +53181,7 @@
         <v>45839.5658912037</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -53238,7 +53238,7 @@
         <v>45622.45239583333</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -53300,7 +53300,7 @@
         <v>45638</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -53362,7 +53362,7 @@
         <v>45881.46869212963</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -53419,7 +53419,7 @@
         <v>45603</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -53481,7 +53481,7 @@
         <v>45723.58140046296</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -53538,7 +53538,7 @@
         <v>45107</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -53595,7 +53595,7 @@
         <v>45611.4021875</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -53652,7 +53652,7 @@
         <v>45622</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -53714,7 +53714,7 @@
         <v>45881.6609375</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -53771,7 +53771,7 @@
         <v>45618</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -53828,7 +53828,7 @@
         <v>45245</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -53885,7 +53885,7 @@
         <v>45881.36469907407</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -53942,7 +53942,7 @@
         <v>44229</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -54004,7 +54004,7 @@
         <v>44225</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -54061,7 +54061,7 @@
         <v>45882.64755787037</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -54123,7 +54123,7 @@
         <v>45881.64365740741</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -54180,7 +54180,7 @@
         <v>45840.64394675926</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -54242,7 +54242,7 @@
         <v>45882.63179398148</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -54304,7 +54304,7 @@
         <v>45881.43114583333</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -54361,7 +54361,7 @@
         <v>45841.69273148148</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -54418,7 +54418,7 @@
         <v>45841.46512731481</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -54480,7 +54480,7 @@
         <v>45397.64855324074</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -54537,7 +54537,7 @@
         <v>44818</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -54594,7 +54594,7 @@
         <v>45569.48626157407</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -54651,7 +54651,7 @@
         <v>45841.45137731481</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -54708,7 +54708,7 @@
         <v>45883.40538194445</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -54765,7 +54765,7 @@
         <v>45841.4312037037</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -54822,7 +54822,7 @@
         <v>45884.55263888889</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -54884,7 +54884,7 @@
         <v>45630.5731712963</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -54946,7 +54946,7 @@
         <v>45842.48990740741</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -55003,7 +55003,7 @@
         <v>45883.4108912037</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -55060,7 +55060,7 @@
         <v>45883.51854166666</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -55117,7 +55117,7 @@
         <v>45883.58944444444</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -55179,7 +55179,7 @@
         <v>45632</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -55236,7 +55236,7 @@
         <v>45568</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -55298,7 +55298,7 @@
         <v>45442</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -55360,7 +55360,7 @@
         <v>45569</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -55422,7 +55422,7 @@
         <v>45888.78833333333</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -55479,7 +55479,7 @@
         <v>45888.78960648148</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -55536,7 +55536,7 @@
         <v>45569</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -55598,7 +55598,7 @@
         <v>45869</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -55655,7 +55655,7 @@
         <v>45876</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -55717,7 +55717,7 @@
         <v>45667</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -55779,7 +55779,7 @@
         <v>45845.60496527778</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -55836,7 +55836,7 @@
         <v>45869</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -55893,7 +55893,7 @@
         <v>45876</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -55955,7 +55955,7 @@
         <v>45845.6920949074</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -56017,7 +56017,7 @@
         <v>45610.55846064815</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -56079,7 +56079,7 @@
         <v>45888.78539351852</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -56136,7 +56136,7 @@
         <v>45159.46996527778</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -56198,7 +56198,7 @@
         <v>44925.60457175926</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -56260,7 +56260,7 @@
         <v>44925.64309027778</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -56322,7 +56322,7 @@
         <v>45845.55270833334</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -56379,7 +56379,7 @@
         <v>45845.55266203704</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -56436,7 +56436,7 @@
         <v>45730</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -56493,7 +56493,7 @@
         <v>45568</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -56555,7 +56555,7 @@
         <v>45755</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -56612,7 +56612,7 @@
         <v>45622</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -56669,7 +56669,7 @@
         <v>45845.55259259259</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -56726,7 +56726,7 @@
         <v>45887.50216435185</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -56788,7 +56788,7 @@
         <v>45887.59913194444</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -56850,7 +56850,7 @@
         <v>45730</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -56907,7 +56907,7 @@
         <v>45888.59509259259</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -56964,7 +56964,7 @@
         <v>45569</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -57026,7 +57026,7 @@
         <v>45533.67138888889</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -57083,7 +57083,7 @@
         <v>45848.57644675926</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -57145,7 +57145,7 @@
         <v>45758.69638888889</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -57202,7 +57202,7 @@
         <v>45861</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -57264,7 +57264,7 @@
         <v>45889.40916666666</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -57321,7 +57321,7 @@
         <v>45889.41715277778</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -57378,7 +57378,7 @@
         <v>45848.62873842593</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -57435,7 +57435,7 @@
         <v>45848.639375</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -57492,7 +57492,7 @@
         <v>45848.6568287037</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -57549,7 +57549,7 @@
         <v>45848.68640046296</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -57611,7 +57611,7 @@
         <v>45848</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -57673,7 +57673,7 @@
         <v>45848.35400462963</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -57730,7 +57730,7 @@
         <v>45159</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -57792,7 +57792,7 @@
         <v>45159</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -57854,7 +57854,7 @@
         <v>45644</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -57911,7 +57911,7 @@
         <v>44314</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -57968,7 +57968,7 @@
         <v>45118.3959375</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -58030,7 +58030,7 @@
         <v>44998</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -58087,7 +58087,7 @@
         <v>45848.45113425926</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -58149,7 +58149,7 @@
         <v>45848.65003472222</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -58206,7 +58206,7 @@
         <v>45847.58865740741</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -58268,7 +58268,7 @@
         <v>45733.59667824074</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -58330,7 +58330,7 @@
         <v>45098.48666666666</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -58392,7 +58392,7 @@
         <v>44925</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -58449,7 +58449,7 @@
         <v>45852</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -58506,7 +58506,7 @@
         <v>45892.53184027778</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -58563,7 +58563,7 @@
         <v>45496.67342592592</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -58625,7 +58625,7 @@
         <v>45582.49792824074</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -58687,7 +58687,7 @@
         <v>45509</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -58749,7 +58749,7 @@
         <v>44958</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -58811,7 +58811,7 @@
         <v>45894.65869212963</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -58868,7 +58868,7 @@
         <v>45170.46923611111</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -58930,7 +58930,7 @@
         <v>45743.38449074074</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -58987,7 +58987,7 @@
         <v>45894.64358796296</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -59049,7 +59049,7 @@
         <v>45688.67932870371</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -59111,7 +59111,7 @@
         <v>44091</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -59168,7 +59168,7 @@
         <v>45852.48290509259</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -59225,7 +59225,7 @@
         <v>45849</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -59282,7 +59282,7 @@
         <v>45719.40480324074</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -59339,7 +59339,7 @@
         <v>45775.36587962963</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -59396,7 +59396,7 @@
         <v>45775.36589120371</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -59453,7 +59453,7 @@
         <v>45896.49959490741</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -59510,7 +59510,7 @@
         <v>45617.89371527778</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -59567,7 +59567,7 @@
         <v>45621</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -59629,7 +59629,7 @@
         <v>45853.61865740741</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -59686,7 +59686,7 @@
         <v>45853.62415509259</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -59748,7 +59748,7 @@
         <v>45853.28325231482</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -59805,7 +59805,7 @@
         <v>45154</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -59862,7 +59862,7 @@
         <v>45719.45215277778</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -59919,7 +59919,7 @@
         <v>45604.66936342593</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -59976,7 +59976,7 @@
         <v>45118.91633101852</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -60033,7 +60033,7 @@
         <v>45119</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -60090,7 +60090,7 @@
         <v>45854.40662037037</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -60152,7 +60152,7 @@
         <v>44708.48859953704</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -60214,7 +60214,7 @@
         <v>45632.65197916667</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -60271,7 +60271,7 @@
         <v>44483</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -60328,7 +60328,7 @@
         <v>45896.49821759259</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -60385,7 +60385,7 @@
         <v>44209</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -60447,7 +60447,7 @@
         <v>45664.56502314815</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -60504,7 +60504,7 @@
         <v>45895.29387731481</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -60566,7 +60566,7 @@
         <v>45740.36546296296</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -60628,7 +60628,7 @@
         <v>45854.44850694444</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -60690,7 +60690,7 @@
         <v>45854.44864583333</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -60752,7 +60752,7 @@
         <v>45484.48854166667</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -60814,7 +60814,7 @@
         <v>45147</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -60871,7 +60871,7 @@
         <v>45488</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -60928,7 +60928,7 @@
         <v>45897.44645833333</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -60990,7 +60990,7 @@
         <v>45898.55296296296</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -61052,7 +61052,7 @@
         <v>44858</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -61109,7 +61109,7 @@
         <v>45659.57361111111</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -61171,7 +61171,7 @@
         <v>45288.58685185185</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -61228,7 +61228,7 @@
         <v>45898.38625</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -61285,7 +61285,7 @@
         <v>45898.40267361111</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -61347,7 +61347,7 @@
         <v>45898.40481481481</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -61404,7 +61404,7 @@
         <v>45063</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -61461,7 +61461,7 @@
         <v>45898.41540509259</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -61518,7 +61518,7 @@
         <v>45670</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -61580,7 +61580,7 @@
         <v>45630.62513888889</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -61637,7 +61637,7 @@
         <v>45547.59543981482</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -61694,7 +61694,7 @@
         <v>45631.39950231482</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -61756,7 +61756,7 @@
         <v>45885</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -61813,7 +61813,7 @@
         <v>45509.5980787037</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -61875,7 +61875,7 @@
         <v>45869</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -61932,7 +61932,7 @@
         <v>45707</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -61989,7 +61989,7 @@
         <v>44381</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -62046,7 +62046,7 @@
         <v>45768.30814814815</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -62108,7 +62108,7 @@
         <v>45764.44861111111</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -62170,7 +62170,7 @@
         <v>45727.35621527778</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -62232,7 +62232,7 @@
         <v>45510</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -62294,7 +62294,7 @@
         <v>45656.51157407407</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -62356,7 +62356,7 @@
         <v>45484.65768518519</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -62418,7 +62418,7 @@
         <v>44964</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -62475,7 +62475,7 @@
         <v>45691</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -62537,7 +62537,7 @@
         <v>45691</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -62599,7 +62599,7 @@
         <v>45621</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -62656,7 +62656,7 @@
         <v>45621</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -62713,7 +62713,7 @@
         <v>45485</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -62770,7 +62770,7 @@
         <v>45643.56899305555</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -62832,7 +62832,7 @@
         <v>44928.36418981481</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -62894,7 +62894,7 @@
         <v>44231</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -62956,7 +62956,7 @@
         <v>45707</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -63013,7 +63013,7 @@
         <v>44795</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -63070,7 +63070,7 @@
         <v>44088</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -63127,7 +63127,7 @@
         <v>45742.42793981481</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -63189,7 +63189,7 @@
         <v>45705.72106481482</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -63246,7 +63246,7 @@
         <v>44385</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -63303,7 +63303,7 @@
         <v>44925.59333333333</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -63365,7 +63365,7 @@
         <v>45385</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -63422,7 +63422,7 @@
         <v>44757.37524305555</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -63479,7 +63479,7 @@
         <v>45764.44825231482</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -63541,7 +63541,7 @@
         <v>44216</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -63603,7 +63603,7 @@
         <v>45485</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -63665,7 +63665,7 @@
         <v>44151</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -63722,7 +63722,7 @@
         <v>45485</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -63784,7 +63784,7 @@
         <v>44435</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -63846,7 +63846,7 @@
         <v>44169</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -63903,7 +63903,7 @@
         <v>44126</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -63960,7 +63960,7 @@
         <v>45572.60001157408</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -64017,7 +64017,7 @@
         <v>44985.61403935185</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -64079,7 +64079,7 @@
         <v>45737.3787962963</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -64136,7 +64136,7 @@
         <v>45768.29469907407</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -64198,7 +64198,7 @@
         <v>45768.30260416667</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -64260,7 +64260,7 @@
         <v>45768.30388888889</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -64322,7 +64322,7 @@
         <v>45685.50063657408</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -64384,7 +64384,7 @@
         <v>45687.54329861111</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -64441,7 +64441,7 @@
         <v>45063</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -64498,7 +64498,7 @@
         <v>44474.59423611111</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -64555,7 +64555,7 @@
         <v>45743.61899305556</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -64612,7 +64612,7 @@
         <v>45743.62116898148</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -64669,7 +64669,7 @@
         <v>45433</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -64726,7 +64726,7 @@
         <v>45764</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -64783,7 +64783,7 @@
         <v>45754.35055555555</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -64840,7 +64840,7 @@
         <v>45539.43545138889</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -64897,7 +64897,7 @@
         <v>45204</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -64954,7 +64954,7 @@
         <v>45688.6749537037</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -65016,7 +65016,7 @@
         <v>44827</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -65073,7 +65073,7 @@
         <v>44827</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -65130,7 +65130,7 @@
         <v>45238.46430555556</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -65187,7 +65187,7 @@
         <v>45166.34795138889</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -65244,7 +65244,7 @@
         <v>44928</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -65306,7 +65306,7 @@
         <v>45432</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -65368,7 +65368,7 @@
         <v>44987.35637731481</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -65430,7 +65430,7 @@
         <v>44987</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -65492,7 +65492,7 @@
         <v>45532</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -65549,7 +65549,7 @@
         <v>44886</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -65611,7 +65611,7 @@
         <v>45758.66108796297</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -65668,7 +65668,7 @@
         <v>45758.69123842593</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -65725,7 +65725,7 @@
         <v>45670.4570949074</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -65787,7 +65787,7 @@
         <v>44853</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -65844,7 +65844,7 @@
         <v>44925.33584490741</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -65906,7 +65906,7 @@
         <v>45706</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -65963,7 +65963,7 @@
         <v>45741.39084490741</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -66020,7 +66020,7 @@
         <v>45477.62255787037</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -66082,7 +66082,7 @@
         <v>44985.6125</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -66144,7 +66144,7 @@
         <v>45763.4266087963</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -66201,7 +66201,7 @@
         <v>45345.65929398148</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -66263,7 +66263,7 @@
         <v>45688.6769212963</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -66325,7 +66325,7 @@
         <v>45439.43106481482</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -66387,7 +66387,7 @@
         <v>44972.57449074074</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -66444,7 +66444,7 @@
         <v>44484.55535879629</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -66501,7 +66501,7 @@
         <v>45229.92739583334</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -66558,7 +66558,7 @@
         <v>45624.63614583333</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -66620,7 +66620,7 @@
         <v>45041</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -66677,7 +66677,7 @@
         <v>45041</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -66734,7 +66734,7 @@
         <v>44889.56582175926</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -66791,7 +66791,7 @@
         <v>45531.66196759259</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -66853,7 +66853,7 @@
         <v>44928</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -66915,7 +66915,7 @@
         <v>44550.39550925926</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -66972,7 +66972,7 @@
         <v>44928</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -67034,7 +67034,7 @@
         <v>45791</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -67091,7 +67091,7 @@
         <v>45731.69629629629</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -67148,7 +67148,7 @@
         <v>44819.56722222222</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -67205,7 +67205,7 @@
         <v>45631.63091435185</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -67262,7 +67262,7 @@
         <v>44722</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -67319,7 +67319,7 @@
         <v>44854</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -67381,7 +67381,7 @@
         <v>45751.65657407408</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -67443,7 +67443,7 @@
         <v>45338</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -67505,7 +67505,7 @@
         <v>45496.59202546296</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -67567,7 +67567,7 @@
         <v>45756</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -67624,7 +67624,7 @@
         <v>45154</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -67681,7 +67681,7 @@
         <v>45496.67178240741</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -67743,7 +67743,7 @@
         <v>45282.64012731481</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -67805,7 +67805,7 @@
         <v>45673.65925925926</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -67867,7 +67867,7 @@
         <v>45420.44414351852</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -67929,7 +67929,7 @@
         <v>45677.43028935185</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -67986,7 +67986,7 @@
         <v>44460.44315972222</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -68048,7 +68048,7 @@
         <v>45447.35144675926</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -68105,7 +68105,7 @@
         <v>45239.43173611111</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -68167,7 +68167,7 @@
         <v>45054</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -68229,7 +68229,7 @@
         <v>45761.61501157407</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -68291,7 +68291,7 @@
         <v>45637.39587962963</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -68353,7 +68353,7 @@
         <v>45559.43645833333</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -68415,7 +68415,7 @@
         <v>45517.69590277778</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -68477,7 +68477,7 @@
         <v>45624.36090277778</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -68534,7 +68534,7 @@
         <v>45590.31899305555</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -68591,7 +68591,7 @@
         <v>45642.41907407407</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -68648,7 +68648,7 @@
         <v>45049.59826388889</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -68705,7 +68705,7 @@
         <v>45020</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -68762,7 +68762,7 @@
         <v>44872</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -68819,7 +68819,7 @@
         <v>45075.59358796296</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -68881,7 +68881,7 @@
         <v>45685.52405092592</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -68943,7 +68943,7 @@
         <v>45685.5349074074</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -69005,7 +69005,7 @@
         <v>45672.61748842592</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -69062,7 +69062,7 @@
         <v>45390</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -69119,7 +69119,7 @@
         <v>45735.60342592592</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -69176,7 +69176,7 @@
         <v>45719.45277777778</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -69233,7 +69233,7 @@
         <v>45763.4178587963</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -69290,7 +69290,7 @@
         <v>45351</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -69347,7 +69347,7 @@
         <v>45575</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -69404,7 +69404,7 @@
         <v>45616.49530092593</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -69461,7 +69461,7 @@
         <v>45154</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -69518,7 +69518,7 @@
         <v>45688.46570601852</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -69580,7 +69580,7 @@
         <v>44155</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -69637,7 +69637,7 @@
         <v>45642</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -69694,7 +69694,7 @@
         <v>45484.58422453704</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -69756,7 +69756,7 @@
         <v>45371.66217592593</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -69818,7 +69818,7 @@
         <v>44886</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -69880,7 +69880,7 @@
         <v>45303.5047337963</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -69937,7 +69937,7 @@
         <v>45735.57390046296</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -69994,7 +69994,7 @@
         <v>45119.38151620371</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -70056,7 +70056,7 @@
         <v>45665.59925925926</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -70113,7 +70113,7 @@
         <v>45593.6821412037</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -70170,7 +70170,7 @@
         <v>45593.68434027778</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -70227,7 +70227,7 @@
         <v>45625.56934027778</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -70289,7 +70289,7 @@
         <v>45274</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -70346,7 +70346,7 @@
         <v>45411.44549768518</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -70408,7 +70408,7 @@
         <v>45303.5187037037</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -70465,7 +70465,7 @@
         <v>45635.42027777778</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -70527,7 +70527,7 @@
         <v>45728.61006944445</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -70584,7 +70584,7 @@
         <v>45611.38759259259</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -70641,7 +70641,7 @@
         <v>44642</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -70703,7 +70703,7 @@
         <v>45244</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -70760,7 +70760,7 @@
         <v>45252.48409722222</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -70817,7 +70817,7 @@
         <v>45252</v>
       </c>
       <c r="C1075" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
@@ -70874,7 +70874,7 @@
         <v>45667</v>
       </c>
       <c r="C1076" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
@@ -70931,7 +70931,7 @@
         <v>45509</v>
       </c>
       <c r="C1077" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
@@ -70993,7 +70993,7 @@
         <v>45303.52626157407</v>
       </c>
       <c r="C1078" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1078" t="inlineStr">
         <is>
@@ -71050,7 +71050,7 @@
         <v>45719.48778935185</v>
       </c>
       <c r="C1079" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1079" t="inlineStr">
         <is>
@@ -71107,7 +71107,7 @@
         <v>45574.66106481481</v>
       </c>
       <c r="C1080" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
@@ -71164,7 +71164,7 @@
         <v>45264.92637731481</v>
       </c>
       <c r="C1081" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1081" t="inlineStr">
         <is>
@@ -71221,7 +71221,7 @@
         <v>45260.59042824074</v>
       </c>
       <c r="C1082" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1082" t="inlineStr">
         <is>
@@ -71278,7 +71278,7 @@
         <v>45075.59148148148</v>
       </c>
       <c r="C1083" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1083" t="inlineStr">
         <is>
@@ -71340,7 +71340,7 @@
         <v>45063.92605324074</v>
       </c>
       <c r="C1084" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1084" t="inlineStr">
         <is>
@@ -71397,7 +71397,7 @@
         <v>45575.60996527778</v>
       </c>
       <c r="C1085" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1085" t="inlineStr">
         <is>
@@ -71459,7 +71459,7 @@
         <v>45290.39024305555</v>
       </c>
       <c r="C1086" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1086" t="inlineStr">
         <is>
@@ -71516,7 +71516,7 @@
         <v>45460.48582175926</v>
       </c>
       <c r="C1087" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1087" t="inlineStr">
         <is>
@@ -71573,7 +71573,7 @@
         <v>45680.42497685185</v>
       </c>
       <c r="C1088" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1088" t="inlineStr">
         <is>
@@ -71630,7 +71630,7 @@
         <v>45153.42725694444</v>
       </c>
       <c r="C1089" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1089" t="inlineStr">
         <is>
@@ -71692,7 +71692,7 @@
         <v>45568</v>
       </c>
       <c r="C1090" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1090" t="inlineStr">
         <is>
@@ -71754,7 +71754,7 @@
         <v>45685</v>
       </c>
       <c r="C1091" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1091" t="inlineStr">
         <is>
@@ -71816,7 +71816,7 @@
         <v>45477.66773148148</v>
       </c>
       <c r="C1092" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1092" t="inlineStr">
         <is>
@@ -71878,7 +71878,7 @@
         <v>45257</v>
       </c>
       <c r="C1093" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1093" t="inlineStr">
         <is>
@@ -71935,7 +71935,7 @@
         <v>45601.58355324074</v>
       </c>
       <c r="C1094" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1094" t="inlineStr">
         <is>
@@ -71992,7 +71992,7 @@
         <v>45429.39</v>
       </c>
       <c r="C1095" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1095" t="inlineStr">
         <is>
@@ -72049,7 +72049,7 @@
         <v>45635.4916087963</v>
       </c>
       <c r="C1096" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1096" t="inlineStr">
         <is>
@@ -72106,7 +72106,7 @@
         <v>45012</v>
       </c>
       <c r="C1097" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1097" t="inlineStr">
         <is>
@@ -72168,7 +72168,7 @@
         <v>45607</v>
       </c>
       <c r="C1098" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1098" t="inlineStr">
         <is>
@@ -72225,7 +72225,7 @@
         <v>44571</v>
       </c>
       <c r="C1099" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1099" t="inlineStr">
         <is>
@@ -72282,7 +72282,7 @@
         <v>45579.59980324074</v>
       </c>
       <c r="C1100" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1100" t="inlineStr">
         <is>
@@ -72339,7 +72339,7 @@
         <v>45632</v>
       </c>
       <c r="C1101" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1101" t="inlineStr">
         <is>
@@ -72396,7 +72396,7 @@
         <v>45632</v>
       </c>
       <c r="C1102" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1102" t="inlineStr">
         <is>

--- a/Översikt HÄRJEDALEN.xlsx
+++ b/Översikt HÄRJEDALEN.xlsx
@@ -567,7 +567,7 @@
         <v>45513</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         <v>45763</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>44785</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>44790</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>44553</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>44837</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>44844</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>44749</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>44406</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>45691</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>44182</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>44154.40430555555</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>45531</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>45761.58262731481</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>44831</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>44496.94013888889</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>44865.57574074074</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
         <v>45667</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>44650</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2727,7 +2727,7 @@
         <v>45250</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>45351</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>45180</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3043,7 +3043,7 @@
         <v>44200</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>45631</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>45554</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>44690</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
         <v>44501</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
         <v>44193</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         <v>44182</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>45544.35653935185</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>44487</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
         <v>45631</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>44440</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>45625.49736111111</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         <v>44406</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         <v>45544</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4506,7 +4506,7 @@
         <v>45106</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         <v>45837</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>45217</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>45571</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         <v>44774</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>44357</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         <v>45544</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>45198</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5315,7 +5315,7 @@
         <v>45457.38396990741</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         <v>45175</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5527,7 +5527,7 @@
         <v>45531</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         <v>45411</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         <v>45833.43898148148</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>45477.46537037037</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5929,7 +5929,7 @@
         <v>45694</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>44553</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>45471.59034722222</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
         <v>44406</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
         <v>45614.45413194445</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6430,7 +6430,7 @@
         <v>44517</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6523,7 +6523,7 @@
         <v>44553</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6620,7 +6620,7 @@
         <v>44377</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
         <v>45426</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6808,7 +6808,7 @@
         <v>45677.45212962963</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         <v>45741.82913194445</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         <v>44430</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7092,7 +7092,7 @@
         <v>44553</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         <v>45007</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7288,7 +7288,7 @@
         <v>45715</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         <v>45531.45444444445</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7483,7 +7483,7 @@
         <v>44242</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7573,7 +7573,7 @@
         <v>45625.45384259259</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7676,7 +7676,7 @@
         <v>45772.51116898148</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7771,7 +7771,7 @@
         <v>45616.6450462963</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7869,7 +7869,7 @@
         <v>45568</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7964,7 +7964,7 @@
         <v>45719</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8058,7 +8058,7 @@
         <v>45869</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8152,7 +8152,7 @@
         <v>45559</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8251,7 +8251,7 @@
         <v>45574</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8345,7 +8345,7 @@
         <v>45432.94736111111</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8443,7 +8443,7 @@
         <v>45243</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         <v>44517</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
         <v>44882</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8718,7 +8718,7 @@
         <v>44979</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8807,7 +8807,7 @@
         <v>44430</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8908,7 +8908,7 @@
         <v>44294</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>44294</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9084,7 +9084,7 @@
         <v>45694</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         <v>44476</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>45467.47204861111</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9357,7 +9357,7 @@
         <v>45559.38894675926</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9454,7 +9454,7 @@
         <v>45537.45818287037</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9551,7 +9551,7 @@
         <v>44977</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9648,7 +9648,7 @@
         <v>44957</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9740,7 +9740,7 @@
         <v>45838.73927083334</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9833,7 +9833,7 @@
         <v>45883.35789351852</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9925,7 +9925,7 @@
         <v>45552</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10013,7 +10013,7 @@
         <v>45666</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10110,7 +10110,7 @@
         <v>45007</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
         <v>45531.45752314815</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10291,7 +10291,7 @@
         <v>45085</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10383,7 +10383,7 @@
         <v>45506.35658564815</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10475,7 +10475,7 @@
         <v>44377</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10567,7 +10567,7 @@
         <v>44475</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10654,7 +10654,7 @@
         <v>44441</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10741,7 +10741,7 @@
         <v>44475</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10828,7 +10828,7 @@
         <v>44475</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10915,7 +10915,7 @@
         <v>44713</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11015,7 +11015,7 @@
         <v>45468</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11102,7 +11102,7 @@
         <v>44074</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11198,7 +11198,7 @@
         <v>45791</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11285,7 +11285,7 @@
         <v>45800.3484375</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11377,7 +11377,7 @@
         <v>44107</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11473,7 +11473,7 @@
         <v>45617</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         <v>45821.56523148148</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11661,7 +11661,7 @@
         <v>45841.41003472222</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11748,7 +11748,7 @@
         <v>45849.35011574074</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11835,7 +11835,7 @@
         <v>44180</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11927,7 +11927,7 @@
         <v>44186</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12018,7 +12018,7 @@
         <v>44677</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12109,7 +12109,7 @@
         <v>44286</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12195,7 +12195,7 @@
         <v>44475</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12281,7 +12281,7 @@
         <v>45772.51070601852</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12372,7 +12372,7 @@
         <v>45538</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12463,7 +12463,7 @@
         <v>45035</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12558,7 +12558,7 @@
         <v>45786.6590625</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12649,7 +12649,7 @@
         <v>45786.66594907407</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12740,7 +12740,7 @@
         <v>45786.65452546296</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12831,7 +12831,7 @@
         <v>45786.6768287037</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12922,7 +12922,7 @@
         <v>45786.67261574074</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13013,7 +13013,7 @@
         <v>45786.67016203704</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13104,7 +13104,7 @@
         <v>44987</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13199,7 +13199,7 @@
         <v>45805.73822916667</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13290,7 +13290,7 @@
         <v>45644.56555555556</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13385,7 +13385,7 @@
         <v>45833</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13471,7 +13471,7 @@
         <v>44475</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13557,7 +13557,7 @@
         <v>44221</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13643,7 +13643,7 @@
         <v>45621</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13738,7 +13738,7 @@
         <v>45191</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13829,7 +13829,7 @@
         <v>45880.37559027778</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -13915,7 +13915,7 @@
         <v>45772.36488425926</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14010,7 +14010,7 @@
         <v>45552</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14100,7 +14100,7 @@
         <v>44853</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14190,7 +14190,7 @@
         <v>44866.46503472222</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14285,7 +14285,7 @@
         <v>44955</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14375,7 +14375,7 @@
         <v>45595.58056712963</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14466,7 +14466,7 @@
         <v>45694</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14552,7 +14552,7 @@
         <v>45153</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14642,7 +14642,7 @@
         <v>44449</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14728,7 +14728,7 @@
         <v>44096</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -14818,7 +14818,7 @@
         <v>44475</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -14903,7 +14903,7 @@
         <v>44321</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -14993,7 +14993,7 @@
         <v>44475</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15078,7 +15078,7 @@
         <v>44475</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15163,7 +15163,7 @@
         <v>44113</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15248,7 +15248,7 @@
         <v>44105</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15333,7 +15333,7 @@
         <v>44769.48783564815</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15423,7 +15423,7 @@
         <v>45729.64623842593</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -15513,7 +15513,7 @@
         <v>45345</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -15603,7 +15603,7 @@
         <v>45457.38677083333</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -15693,7 +15693,7 @@
         <v>45320</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -15778,7 +15778,7 @@
         <v>45621.47555555555</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -15868,7 +15868,7 @@
         <v>45714.55248842593</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -15962,7 +15962,7 @@
         <v>45800.63043981481</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16056,7 +16056,7 @@
         <v>45538.57630787037</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16145,7 +16145,7 @@
         <v>45805.66601851852</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -16239,7 +16239,7 @@
         <v>45805.73546296296</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -16329,7 +16329,7 @@
         <v>45603</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -16419,7 +16419,7 @@
         <v>45617</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -16513,7 +16513,7 @@
         <v>45454.62443287037</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -16598,7 +16598,7 @@
         <v>45111</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -16688,7 +16688,7 @@
         <v>45812.82244212963</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -16778,7 +16778,7 @@
         <v>45638.33607638889</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -16868,7 +16868,7 @@
         <v>44475</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -16953,7 +16953,7 @@
         <v>45791</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>45835.7499537037</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17128,7 +17128,7 @@
         <v>45838.773125</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -17218,7 +17218,7 @@
         <v>45869</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -17303,7 +17303,7 @@
         <v>45889.56214120371</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -17393,7 +17393,7 @@
         <v>45875</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -17482,7 +17482,7 @@
         <v>45758.70164351852</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -17567,7 +17567,7 @@
         <v>45308</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -17656,7 +17656,7 @@
         <v>45540.69512731482</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -17746,7 +17746,7 @@
         <v>45672.50416666667</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -17831,7 +17831,7 @@
         <v>44320</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -17888,7 +17888,7 @@
         <v>44316</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
         <v>44320</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -18007,7 +18007,7 @@
         <v>44105</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -18064,7 +18064,7 @@
         <v>44810</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -18126,7 +18126,7 @@
         <v>44727.70908564814</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -18188,7 +18188,7 @@
         <v>44430</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -18250,7 +18250,7 @@
         <v>44543</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -18307,7 +18307,7 @@
         <v>44614</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -18369,7 +18369,7 @@
         <v>44404</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -18426,7 +18426,7 @@
         <v>44417.38271990741</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -18483,7 +18483,7 @@
         <v>44417.38614583333</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -18540,7 +18540,7 @@
         <v>44497</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -18597,7 +18597,7 @@
         <v>44475</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -18654,7 +18654,7 @@
         <v>44531</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -18711,7 +18711,7 @@
         <v>44361</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -18768,7 +18768,7 @@
         <v>44600</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -18825,7 +18825,7 @@
         <v>44540</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -18887,7 +18887,7 @@
         <v>44475</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -18944,7 +18944,7 @@
         <v>44385.93652777778</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -19006,7 +19006,7 @@
         <v>44538</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -19068,7 +19068,7 @@
         <v>44475</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -19125,7 +19125,7 @@
         <v>44406</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -19182,7 +19182,7 @@
         <v>44854</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -19239,7 +19239,7 @@
         <v>44102</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -19296,7 +19296,7 @@
         <v>44823</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -19358,7 +19358,7 @@
         <v>44424</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -19415,7 +19415,7 @@
         <v>44316</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -19472,7 +19472,7 @@
         <v>44483</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -19529,7 +19529,7 @@
         <v>44421</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -19586,7 +19586,7 @@
         <v>44418</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -19648,7 +19648,7 @@
         <v>44488</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -19710,7 +19710,7 @@
         <v>44603</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -19772,7 +19772,7 @@
         <v>44132</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -19829,7 +19829,7 @@
         <v>44179</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -19886,7 +19886,7 @@
         <v>44418</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -19948,7 +19948,7 @@
         <v>44564.6747337963</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -20010,7 +20010,7 @@
         <v>44361</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -20072,7 +20072,7 @@
         <v>44615</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -20134,7 +20134,7 @@
         <v>44466.81701388889</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -20191,7 +20191,7 @@
         <v>44218</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -20248,7 +20248,7 @@
         <v>44286</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -20305,7 +20305,7 @@
         <v>44475</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -20362,7 +20362,7 @@
         <v>44475</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -20419,7 +20419,7 @@
         <v>44410.74284722222</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -20476,7 +20476,7 @@
         <v>44631</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -20538,7 +20538,7 @@
         <v>44810</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -20600,7 +20600,7 @@
         <v>44631.41535879629</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -20662,7 +20662,7 @@
         <v>44728</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -20719,7 +20719,7 @@
         <v>44417.37519675926</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -20776,7 +20776,7 @@
         <v>44344</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -20833,7 +20833,7 @@
         <v>44174</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -20890,7 +20890,7 @@
         <v>44084</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -20952,7 +20952,7 @@
         <v>44475</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -21009,7 +21009,7 @@
         <v>44078</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -21066,7 +21066,7 @@
         <v>44424</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -21123,7 +21123,7 @@
         <v>44424</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -21180,7 +21180,7 @@
         <v>44258</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -21237,7 +21237,7 @@
         <v>44818</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -21294,7 +21294,7 @@
         <v>44770.53315972222</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -21351,7 +21351,7 @@
         <v>44690</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -21408,7 +21408,7 @@
         <v>44286</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -21465,7 +21465,7 @@
         <v>44285</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -21522,7 +21522,7 @@
         <v>44385.93658564815</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -21584,7 +21584,7 @@
         <v>44792.68023148148</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -21641,7 +21641,7 @@
         <v>44243.63096064814</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -21698,7 +21698,7 @@
         <v>44298</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -21755,7 +21755,7 @@
         <v>44183</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -21812,7 +21812,7 @@
         <v>44319</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -21869,7 +21869,7 @@
         <v>44316</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -21926,7 +21926,7 @@
         <v>44316</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -21983,7 +21983,7 @@
         <v>44126</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -22040,7 +22040,7 @@
         <v>44825</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -22097,7 +22097,7 @@
         <v>44174</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -22154,7 +22154,7 @@
         <v>44154</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -22216,7 +22216,7 @@
         <v>44396</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -22273,7 +22273,7 @@
         <v>44475</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -22330,7 +22330,7 @@
         <v>44127</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -22392,7 +22392,7 @@
         <v>44475</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -22449,7 +22449,7 @@
         <v>44475</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -22506,7 +22506,7 @@
         <v>44475</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -22563,7 +22563,7 @@
         <v>44475</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -22620,7 +22620,7 @@
         <v>44544</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -22682,7 +22682,7 @@
         <v>44420.33096064815</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -22739,7 +22739,7 @@
         <v>44188</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -22801,7 +22801,7 @@
         <v>44483.36435185185</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -22858,7 +22858,7 @@
         <v>44417</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -22915,7 +22915,7 @@
         <v>44181</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -22977,7 +22977,7 @@
         <v>44426.45706018519</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -23034,7 +23034,7 @@
         <v>44859</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -23096,7 +23096,7 @@
         <v>44473</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -23153,7 +23153,7 @@
         <v>44314</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -23210,7 +23210,7 @@
         <v>44335.4837962963</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -23267,7 +23267,7 @@
         <v>44727.71858796296</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -23329,7 +23329,7 @@
         <v>44475</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -23386,7 +23386,7 @@
         <v>44543</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -23448,7 +23448,7 @@
         <v>44475</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -23505,7 +23505,7 @@
         <v>44475</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -23562,7 +23562,7 @@
         <v>44725</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -23624,7 +23624,7 @@
         <v>44481.67951388889</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -23681,7 +23681,7 @@
         <v>44855.60383101852</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -23738,7 +23738,7 @@
         <v>44631.45398148148</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -23800,7 +23800,7 @@
         <v>44133</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -23862,7 +23862,7 @@
         <v>44417.37207175926</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -23919,7 +23919,7 @@
         <v>44631.37421296296</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -23981,7 +23981,7 @@
         <v>44768.44859953703</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -24038,7 +24038,7 @@
         <v>44230</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -24095,7 +24095,7 @@
         <v>44538</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -24157,7 +24157,7 @@
         <v>44368</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -24214,7 +24214,7 @@
         <v>44403</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -24271,7 +24271,7 @@
         <v>44886.62578703704</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -24328,7 +24328,7 @@
         <v>44886.629375</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -24385,7 +24385,7 @@
         <v>44838</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -24447,7 +24447,7 @@
         <v>44126</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -24509,7 +24509,7 @@
         <v>44475</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -24566,7 +24566,7 @@
         <v>44475</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -24623,7 +24623,7 @@
         <v>44475</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -24680,7 +24680,7 @@
         <v>44475</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -24737,7 +24737,7 @@
         <v>44540.56034722222</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -24794,7 +24794,7 @@
         <v>44872</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -24856,7 +24856,7 @@
         <v>44742</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -24918,7 +24918,7 @@
         <v>44166</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -24980,7 +24980,7 @@
         <v>44708.46081018518</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -25042,7 +25042,7 @@
         <v>44684</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -25104,7 +25104,7 @@
         <v>44531</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -25161,7 +25161,7 @@
         <v>44188</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -25218,7 +25218,7 @@
         <v>44270</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -25275,7 +25275,7 @@
         <v>44531</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -25332,7 +25332,7 @@
         <v>44531</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -25389,7 +25389,7 @@
         <v>44169</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -25446,7 +25446,7 @@
         <v>44530.40607638889</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -25503,7 +25503,7 @@
         <v>44788.67976851852</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -25565,7 +25565,7 @@
         <v>44180</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -25622,7 +25622,7 @@
         <v>44413</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -25679,7 +25679,7 @@
         <v>44207</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -25741,7 +25741,7 @@
         <v>44706.66417824074</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -25803,7 +25803,7 @@
         <v>44475</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -25860,7 +25860,7 @@
         <v>44316</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -25917,7 +25917,7 @@
         <v>44803</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -25974,7 +25974,7 @@
         <v>44389</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -26036,7 +26036,7 @@
         <v>44316</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -26093,7 +26093,7 @@
         <v>44285</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -26150,7 +26150,7 @@
         <v>44377</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -26207,7 +26207,7 @@
         <v>44627.36047453704</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -26269,7 +26269,7 @@
         <v>45071.92488425926</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -26326,7 +26326,7 @@
         <v>45772.36106481482</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -26388,7 +26388,7 @@
         <v>45684.51006944444</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -26445,7 +26445,7 @@
         <v>44825</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -26502,7 +26502,7 @@
         <v>45345.66555555556</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -26564,7 +26564,7 @@
         <v>45471.66556712963</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -26626,7 +26626,7 @@
         <v>45705.32643518518</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -26683,7 +26683,7 @@
         <v>45362.64613425926</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -26740,7 +26740,7 @@
         <v>45362.65407407407</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -26797,7 +26797,7 @@
         <v>45362.67789351852</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -26854,7 +26854,7 @@
         <v>45579.57390046296</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -26916,7 +26916,7 @@
         <v>44643.81518518519</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -26973,7 +26973,7 @@
         <v>45280</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -27030,7 +27030,7 @@
         <v>44999.60127314815</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -27087,7 +27087,7 @@
         <v>45772.46965277778</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -27149,7 +27149,7 @@
         <v>45772.46988425926</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -27211,7 +27211,7 @@
         <v>44216</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -27273,7 +27273,7 @@
         <v>44300</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -27330,7 +27330,7 @@
         <v>45604.32543981481</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -27392,7 +27392,7 @@
         <v>45406</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -27454,7 +27454,7 @@
         <v>45406</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -27516,7 +27516,7 @@
         <v>44823.84673611111</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -27573,7 +27573,7 @@
         <v>44361</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -27630,7 +27630,7 @@
         <v>45342</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -27687,7 +27687,7 @@
         <v>45688.67935185185</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -27749,7 +27749,7 @@
         <v>45688.67145833333</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -27811,7 +27811,7 @@
         <v>44312</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -27868,7 +27868,7 @@
         <v>45603</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -27930,7 +27930,7 @@
         <v>45741.45597222223</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -27987,7 +27987,7 @@
         <v>45119.39105324074</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -28049,7 +28049,7 @@
         <v>45733.38637731481</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -28106,7 +28106,7 @@
         <v>45085</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -28163,7 +28163,7 @@
         <v>45509</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -28225,7 +28225,7 @@
         <v>45729.65261574074</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -28287,7 +28287,7 @@
         <v>45687.65449074074</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -28349,7 +28349,7 @@
         <v>45106</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -28411,7 +28411,7 @@
         <v>45484.66521990741</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -28473,7 +28473,7 @@
         <v>45740.44842592593</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -28535,7 +28535,7 @@
         <v>45776.69569444445</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -28592,7 +28592,7 @@
         <v>45575</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -28649,7 +28649,7 @@
         <v>45776.43898148148</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -28706,7 +28706,7 @@
         <v>44862</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -28768,7 +28768,7 @@
         <v>45243.63798611111</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -28825,7 +28825,7 @@
         <v>44472</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -28882,7 +28882,7 @@
         <v>45254</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -28939,7 +28939,7 @@
         <v>45345.35003472222</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -29001,7 +29001,7 @@
         <v>45779.48611111111</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -29063,7 +29063,7 @@
         <v>45429</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -29120,7 +29120,7 @@
         <v>45460.47969907407</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -29177,7 +29177,7 @@
         <v>45407.36894675926</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -29239,7 +29239,7 @@
         <v>45779.38211805555</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -29301,7 +29301,7 @@
         <v>45779.47704861111</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -29363,7 +29363,7 @@
         <v>45779.50052083333</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -29425,7 +29425,7 @@
         <v>45779.41844907407</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -29487,7 +29487,7 @@
         <v>45737</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -29544,7 +29544,7 @@
         <v>45782.41581018519</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -29601,7 +29601,7 @@
         <v>45779.50886574074</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -29663,7 +29663,7 @@
         <v>45779.51943287037</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -29725,7 +29725,7 @@
         <v>45779.52488425926</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -29787,7 +29787,7 @@
         <v>45537.60471064815</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -29849,7 +29849,7 @@
         <v>45782.42744212963</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -29906,7 +29906,7 @@
         <v>45779.51357638889</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -29968,7 +29968,7 @@
         <v>44414.58354166667</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -30025,7 +30025,7 @@
         <v>44167</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -30082,7 +30082,7 @@
         <v>45784.59012731481</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -30144,7 +30144,7 @@
         <v>45618.35961805555</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -30201,7 +30201,7 @@
         <v>45783.68547453704</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -30263,7 +30263,7 @@
         <v>45632.64078703704</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -30320,7 +30320,7 @@
         <v>45768.29630787037</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -30382,7 +30382,7 @@
         <v>45768.30954861111</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -30444,7 +30444,7 @@
         <v>45483.47572916667</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -30501,7 +30501,7 @@
         <v>44312</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -30558,7 +30558,7 @@
         <v>45642</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -30615,7 +30615,7 @@
         <v>45569.6909837963</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -30672,7 +30672,7 @@
         <v>45763.41402777778</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -30729,7 +30729,7 @@
         <v>45786.66032407407</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -30791,7 +30791,7 @@
         <v>45786.66853009259</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -30853,7 +30853,7 @@
         <v>45275</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -30910,7 +30910,7 @@
         <v>45568</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -30972,7 +30972,7 @@
         <v>44082</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -31034,7 +31034,7 @@
         <v>44925</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -31091,7 +31091,7 @@
         <v>44732</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -31148,7 +31148,7 @@
         <v>45453.6619212963</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -31205,7 +31205,7 @@
         <v>45260.35777777778</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -31262,7 +31262,7 @@
         <v>45786.66209490741</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -31324,7 +31324,7 @@
         <v>45670.34313657408</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -31381,7 +31381,7 @@
         <v>45560.33311342593</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -31443,7 +31443,7 @@
         <v>45540.4264699074</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -31505,7 +31505,7 @@
         <v>44925.64049768518</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -31567,7 +31567,7 @@
         <v>45786.66425925926</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -31629,7 +31629,7 @@
         <v>45387</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -31686,7 +31686,7 @@
         <v>45457.92854166667</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -31743,7 +31743,7 @@
         <v>45785.34165509259</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -31800,7 +31800,7 @@
         <v>45785.33164351852</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -31857,7 +31857,7 @@
         <v>45588.56039351852</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -31914,7 +31914,7 @@
         <v>44348</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -31971,7 +31971,7 @@
         <v>45257</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -32033,7 +32033,7 @@
         <v>45610.56706018518</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -32095,7 +32095,7 @@
         <v>45790.43</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -32157,7 +32157,7 @@
         <v>45279.57732638889</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -32214,7 +32214,7 @@
         <v>44883</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -32271,7 +32271,7 @@
         <v>45509</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -32333,7 +32333,7 @@
         <v>44091</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -32390,7 +32390,7 @@
         <v>44985</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -32452,7 +32452,7 @@
         <v>44853.41693287037</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -32509,7 +32509,7 @@
         <v>45252.45481481482</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -32566,7 +32566,7 @@
         <v>44957</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -32628,7 +32628,7 @@
         <v>45582.59753472222</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -32690,7 +32690,7 @@
         <v>44475</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -32747,7 +32747,7 @@
         <v>45096.62344907408</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -32809,7 +32809,7 @@
         <v>45792.64795138889</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -32866,7 +32866,7 @@
         <v>45177.9224537037</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -32923,7 +32923,7 @@
         <v>45632</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -32980,7 +32980,7 @@
         <v>45624.36858796296</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -33037,7 +33037,7 @@
         <v>45790.87653935186</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -33094,7 +33094,7 @@
         <v>45484.57285879629</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -33156,7 +33156,7 @@
         <v>44153</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -33213,7 +33213,7 @@
         <v>45638.416875</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -33275,7 +33275,7 @@
         <v>45792.65047453704</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -33332,7 +33332,7 @@
         <v>45607</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -33394,7 +33394,7 @@
         <v>44987.35282407407</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -33456,7 +33456,7 @@
         <v>45517.39274305556</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -33518,7 +33518,7 @@
         <v>45772.69290509259</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -33580,7 +33580,7 @@
         <v>45792.50942129629</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -33642,7 +33642,7 @@
         <v>45485</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -33699,7 +33699,7 @@
         <v>45041</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -33756,7 +33756,7 @@
         <v>44424</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -33813,7 +33813,7 @@
         <v>45173</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -33870,7 +33870,7 @@
         <v>45170.4643287037</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -33932,7 +33932,7 @@
         <v>45618.35097222222</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -33989,7 +33989,7 @@
         <v>45467</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -34046,7 +34046,7 @@
         <v>45637</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -34103,7 +34103,7 @@
         <v>45484</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -34165,7 +34165,7 @@
         <v>45481.3330787037</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -34227,7 +34227,7 @@
         <v>45796.39770833333</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -34284,7 +34284,7 @@
         <v>45506.36534722222</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -34341,7 +34341,7 @@
         <v>45478.48700231482</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -34403,7 +34403,7 @@
         <v>45491.5859375</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -34460,7 +34460,7 @@
         <v>45793.41994212963</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -34522,7 +34522,7 @@
         <v>45559</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -34579,7 +34579,7 @@
         <v>45604.33195601852</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -34641,7 +34641,7 @@
         <v>44082</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -34703,7 +34703,7 @@
         <v>45506.36702546296</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -34760,7 +34760,7 @@
         <v>45796.57802083333</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -34817,7 +34817,7 @@
         <v>45453.6672800926</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -34874,7 +34874,7 @@
         <v>45509</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -34936,7 +34936,7 @@
         <v>45509.6427662037</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -34998,7 +34998,7 @@
         <v>45635.33439814814</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -35060,7 +35060,7 @@
         <v>45631</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -35122,7 +35122,7 @@
         <v>45621</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -35184,7 +35184,7 @@
         <v>44987.34981481481</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -35246,7 +35246,7 @@
         <v>45674.57393518519</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -35303,7 +35303,7 @@
         <v>45569</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -35365,7 +35365,7 @@
         <v>44075</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -35422,7 +35422,7 @@
         <v>45632.64769675926</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -35479,7 +35479,7 @@
         <v>45483.47207175926</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -35536,7 +35536,7 @@
         <v>45631</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -35598,7 +35598,7 @@
         <v>45485</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -35660,7 +35660,7 @@
         <v>45485</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -35722,7 +35722,7 @@
         <v>45593.67809027778</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -35779,7 +35779,7 @@
         <v>45791</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -35836,7 +35836,7 @@
         <v>45797.37096064815</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -35893,7 +35893,7 @@
         <v>45485</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -35955,7 +35955,7 @@
         <v>45800.58859953703</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -36012,7 +36012,7 @@
         <v>45800.59567129629</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -36074,7 +36074,7 @@
         <v>45800.64719907408</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -36136,7 +36136,7 @@
         <v>44628.36402777778</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -36193,7 +36193,7 @@
         <v>45800.56313657408</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -36250,7 +36250,7 @@
         <v>45800.57837962963</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -36312,7 +36312,7 @@
         <v>45830</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -36369,7 +36369,7 @@
         <v>45800.48060185185</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -36431,7 +36431,7 @@
         <v>45799.64804398148</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -36493,7 +36493,7 @@
         <v>45837</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -36550,7 +36550,7 @@
         <v>45253.55737268519</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -36607,7 +36607,7 @@
         <v>45800.3787037037</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -36669,7 +36669,7 @@
         <v>44565.31975694445</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -36731,7 +36731,7 @@
         <v>44565</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -36793,7 +36793,7 @@
         <v>45834</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -36850,7 +36850,7 @@
         <v>45800.44868055556</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -36912,7 +36912,7 @@
         <v>45800.4687962963</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -36974,7 +36974,7 @@
         <v>45800.50431712963</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -37036,7 +37036,7 @@
         <v>44316</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -37093,7 +37093,7 @@
         <v>45642.35256944445</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -37150,7 +37150,7 @@
         <v>45800.56222222222</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -37212,7 +37212,7 @@
         <v>45799.57883101852</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -37269,7 +37269,7 @@
         <v>45799.45770833334</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -37331,7 +37331,7 @@
         <v>45830</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -37388,7 +37388,7 @@
         <v>45830</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -37445,7 +37445,7 @@
         <v>45800.65341435185</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -37507,7 +37507,7 @@
         <v>45799.47225694444</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -37569,7 +37569,7 @@
         <v>45644.50141203704</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -37631,7 +37631,7 @@
         <v>45800.33436342593</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -37693,7 +37693,7 @@
         <v>45800.3425</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -37755,7 +37755,7 @@
         <v>44924.61315972222</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -37817,7 +37817,7 @@
         <v>45345.47642361111</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -37879,7 +37879,7 @@
         <v>45345.48181712963</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -37941,7 +37941,7 @@
         <v>45345.4940625</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -38003,7 +38003,7 @@
         <v>45799.43550925926</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -38065,7 +38065,7 @@
         <v>45800.46069444445</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -38127,7 +38127,7 @@
         <v>45800.48515046296</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -38189,7 +38189,7 @@
         <v>45800.56995370371</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -38251,7 +38251,7 @@
         <v>45665.563125</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -38313,7 +38313,7 @@
         <v>45800.37524305555</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -38375,7 +38375,7 @@
         <v>45800.42797453704</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -38432,7 +38432,7 @@
         <v>45800.44090277778</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -38489,7 +38489,7 @@
         <v>45800.64065972222</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -38551,7 +38551,7 @@
         <v>45237.5815162037</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -38608,7 +38608,7 @@
         <v>45800.63738425926</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -38670,7 +38670,7 @@
         <v>45830</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -38727,7 +38727,7 @@
         <v>45800.60508101852</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -38789,7 +38789,7 @@
         <v>45800.66043981481</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -38851,7 +38851,7 @@
         <v>45799.4658912037</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -38913,7 +38913,7 @@
         <v>45799.46642361111</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -38970,7 +38970,7 @@
         <v>45800.3503587963</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -39032,7 +39032,7 @@
         <v>45800.35670138889</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -39094,7 +39094,7 @@
         <v>45362.67293981482</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -39151,7 +39151,7 @@
         <v>45800.41883101852</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -39213,7 +39213,7 @@
         <v>45799.43086805556</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -39275,7 +39275,7 @@
         <v>45614.47960648148</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -39332,7 +39332,7 @@
         <v>44305</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -39389,7 +39389,7 @@
         <v>45804.5813425926</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -39451,7 +39451,7 @@
         <v>45803.37258101852</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -39508,7 +39508,7 @@
         <v>45517.38320601852</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -39565,7 +39565,7 @@
         <v>45345</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -39627,7 +39627,7 @@
         <v>45804.589375</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -39684,7 +39684,7 @@
         <v>45624.57098379629</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -39741,7 +39741,7 @@
         <v>45803.37480324074</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -39798,7 +39798,7 @@
         <v>45685</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -39860,7 +39860,7 @@
         <v>44914</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -39942,7 +39942,7 @@
         <v>44928.48072916667</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -40004,7 +40004,7 @@
         <v>45531.78386574074</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -40061,7 +40061,7 @@
         <v>45805.53280092592</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -40123,7 +40123,7 @@
         <v>45097</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -40185,7 +40185,7 @@
         <v>45202</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -40247,7 +40247,7 @@
         <v>45362.65903935185</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -40304,7 +40304,7 @@
         <v>45644.56674768519</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -40366,7 +40366,7 @@
         <v>44924.59140046296</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -40428,7 +40428,7 @@
         <v>45635.35274305556</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -40490,7 +40490,7 @@
         <v>45485.42287037037</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -40547,7 +40547,7 @@
         <v>45485</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -40604,7 +40604,7 @@
         <v>45485.44258101852</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -40666,7 +40666,7 @@
         <v>45159.60288194445</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -40723,7 +40723,7 @@
         <v>45807.60333333333</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -40785,7 +40785,7 @@
         <v>45807.58868055556</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -40847,7 +40847,7 @@
         <v>45603</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -40909,7 +40909,7 @@
         <v>45617</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -40971,7 +40971,7 @@
         <v>45807.59407407408</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -41033,7 +41033,7 @@
         <v>45807.41287037037</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -41095,7 +41095,7 @@
         <v>45807.42212962963</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -41157,7 +41157,7 @@
         <v>45807.45288194445</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -41219,7 +41219,7 @@
         <v>45807.49436342593</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -41281,7 +41281,7 @@
         <v>45807.49832175926</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -41343,7 +41343,7 @@
         <v>45622</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -41405,7 +41405,7 @@
         <v>45807.58393518518</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -41467,7 +41467,7 @@
         <v>45807.36304398148</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -41529,7 +41529,7 @@
         <v>45807.41717592593</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -41591,7 +41591,7 @@
         <v>45807.43461805556</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -41653,7 +41653,7 @@
         <v>45807.44070601852</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -41715,7 +41715,7 @@
         <v>45807.44608796296</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -41777,7 +41777,7 @@
         <v>45225.58005787037</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -41834,7 +41834,7 @@
         <v>45807.63334490741</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -41896,7 +41896,7 @@
         <v>45807.47479166667</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -41958,7 +41958,7 @@
         <v>45807.49045138889</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -42020,7 +42020,7 @@
         <v>45408</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -42077,7 +42077,7 @@
         <v>45646</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -42134,7 +42134,7 @@
         <v>45807.65438657408</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -42196,7 +42196,7 @@
         <v>45807.3409837963</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -42258,7 +42258,7 @@
         <v>45807.35476851852</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -42320,7 +42320,7 @@
         <v>45807.55893518519</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -42382,7 +42382,7 @@
         <v>44153</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -42444,7 +42444,7 @@
         <v>45807.5684375</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -42506,7 +42506,7 @@
         <v>45350</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -42563,7 +42563,7 @@
         <v>45351</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -42620,7 +42620,7 @@
         <v>45345.34219907408</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -42682,7 +42682,7 @@
         <v>45617</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -42744,7 +42744,7 @@
         <v>44631.37701388889</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -42806,7 +42806,7 @@
         <v>45730</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -42863,7 +42863,7 @@
         <v>44631.42353009259</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -42925,7 +42925,7 @@
         <v>45807.56403935186</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -42987,7 +42987,7 @@
         <v>45170.46134259259</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -43049,7 +43049,7 @@
         <v>45737.37006944444</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -43106,7 +43106,7 @@
         <v>44914</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -43163,7 +43163,7 @@
         <v>45334</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -43225,7 +43225,7 @@
         <v>45685</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -43282,7 +43282,7 @@
         <v>45607.44832175926</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -43344,7 +43344,7 @@
         <v>44698</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -43406,7 +43406,7 @@
         <v>45617</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -43468,7 +43468,7 @@
         <v>45280</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -43525,7 +43525,7 @@
         <v>45811.34540509259</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -43587,7 +43587,7 @@
         <v>45212</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -43644,7 +43644,7 @@
         <v>44925</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -43706,7 +43706,7 @@
         <v>45811.34564814815</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -43768,7 +43768,7 @@
         <v>45691</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -43830,7 +43830,7 @@
         <v>45691</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -43892,7 +43892,7 @@
         <v>45733</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -43949,7 +43949,7 @@
         <v>45111</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -44006,7 +44006,7 @@
         <v>45811.34578703704</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -44068,7 +44068,7 @@
         <v>45768.29289351852</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -44130,7 +44130,7 @@
         <v>45768.30086805556</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -44192,7 +44192,7 @@
         <v>45119.38675925926</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -44254,7 +44254,7 @@
         <v>45111</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -44316,7 +44316,7 @@
         <v>45546.54530092593</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -44373,7 +44373,7 @@
         <v>45813.64590277777</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -44430,7 +44430,7 @@
         <v>44638.44958333333</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -44487,7 +44487,7 @@
         <v>45813.47074074074</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -44544,7 +44544,7 @@
         <v>44162.65819444445</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -44606,7 +44606,7 @@
         <v>45510</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -44663,7 +44663,7 @@
         <v>45813.48734953703</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -44720,7 +44720,7 @@
         <v>45406.64024305555</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -44782,7 +44782,7 @@
         <v>45642.33616898148</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -44839,7 +44839,7 @@
         <v>45061.61002314815</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -44901,7 +44901,7 @@
         <v>45758.49096064815</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -44963,7 +44963,7 @@
         <v>45568</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -45025,7 +45025,7 @@
         <v>45303</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -45082,7 +45082,7 @@
         <v>45754.67329861111</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -45139,7 +45139,7 @@
         <v>45622.64627314815</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -45196,7 +45196,7 @@
         <v>45859</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -45253,7 +45253,7 @@
         <v>45506.3637962963</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -45310,7 +45310,7 @@
         <v>45687.53689814815</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -45367,7 +45367,7 @@
         <v>45432</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -45429,7 +45429,7 @@
         <v>45762.55899305556</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -45486,7 +45486,7 @@
         <v>44242</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -45543,7 +45543,7 @@
         <v>44939.45376157408</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -45600,7 +45600,7 @@
         <v>44994</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -45657,7 +45657,7 @@
         <v>44883</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -45714,7 +45714,7 @@
         <v>45817.33819444444</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -45776,7 +45776,7 @@
         <v>45576.48657407407</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -45838,7 +45838,7 @@
         <v>45817.62439814815</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -45895,7 +45895,7 @@
         <v>45231</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -45952,7 +45952,7 @@
         <v>45817.594375</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -46014,7 +46014,7 @@
         <v>45685.38901620371</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -46076,7 +46076,7 @@
         <v>45677.44273148148</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -46133,7 +46133,7 @@
         <v>45678.37956018518</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -46190,7 +46190,7 @@
         <v>45439.62893518519</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -46247,7 +46247,7 @@
         <v>45560</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -46304,7 +46304,7 @@
         <v>44916</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -46361,7 +46361,7 @@
         <v>44440</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -46418,7 +46418,7 @@
         <v>45195.61476851852</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -46475,7 +46475,7 @@
         <v>44977.44643518519</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -46537,7 +46537,7 @@
         <v>44957</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -46599,7 +46599,7 @@
         <v>45820.64821759259</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -46656,7 +46656,7 @@
         <v>45240</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -46713,7 +46713,7 @@
         <v>45215</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -46770,7 +46770,7 @@
         <v>44258</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -46827,7 +46827,7 @@
         <v>45496.66903935185</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -46889,7 +46889,7 @@
         <v>45196</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -46951,7 +46951,7 @@
         <v>45866.40701388889</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -47008,7 +47008,7 @@
         <v>45562.65759259259</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -47070,7 +47070,7 @@
         <v>45866.62908564815</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -47127,7 +47127,7 @@
         <v>45634.65831018519</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -47184,7 +47184,7 @@
         <v>45821.77903935185</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -47241,7 +47241,7 @@
         <v>45061.36835648148</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -47298,7 +47298,7 @@
         <v>45728</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -47355,7 +47355,7 @@
         <v>45821.57201388889</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -47417,7 +47417,7 @@
         <v>44708.45504629629</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -47479,7 +47479,7 @@
         <v>44708</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -47541,7 +47541,7 @@
         <v>45733.43663194445</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -47603,7 +47603,7 @@
         <v>45118.47491898148</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -47665,7 +47665,7 @@
         <v>44985</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -47727,7 +47727,7 @@
         <v>44475</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -47784,7 +47784,7 @@
         <v>45791</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -47841,7 +47841,7 @@
         <v>45867.55305555555</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -47898,7 +47898,7 @@
         <v>45867.55642361111</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -47960,7 +47960,7 @@
         <v>45575.6125925926</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -48022,7 +48022,7 @@
         <v>45868.639375</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -48079,7 +48079,7 @@
         <v>45216</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -48136,7 +48136,7 @@
         <v>45595.5666550926</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -48193,7 +48193,7 @@
         <v>44953</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -48250,7 +48250,7 @@
         <v>45826.43267361111</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -48312,7 +48312,7 @@
         <v>45728.44329861111</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -48374,7 +48374,7 @@
         <v>45728.49267361111</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -48436,7 +48436,7 @@
         <v>45505</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -48493,7 +48493,7 @@
         <v>45505</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -48555,7 +48555,7 @@
         <v>44531.43927083333</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -48617,7 +48617,7 @@
         <v>45645.47609953704</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -48679,7 +48679,7 @@
         <v>45203</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -48736,7 +48736,7 @@
         <v>45827.42467592593</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -48798,7 +48798,7 @@
         <v>45208</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -48855,7 +48855,7 @@
         <v>45772.46951388889</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -48917,7 +48917,7 @@
         <v>45827</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -48974,7 +48974,7 @@
         <v>45827.41753472222</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -49036,7 +49036,7 @@
         <v>44214</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -49098,7 +49098,7 @@
         <v>45205</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -49155,7 +49155,7 @@
         <v>45614.62445601852</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -49217,7 +49217,7 @@
         <v>44180</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -49274,7 +49274,7 @@
         <v>44728</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -49336,7 +49336,7 @@
         <v>45873.59511574074</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -49398,7 +49398,7 @@
         <v>45670.66085648148</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -49455,7 +49455,7 @@
         <v>45533.75398148148</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -49512,7 +49512,7 @@
         <v>45832.64047453704</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -49569,7 +49569,7 @@
         <v>45831</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -49631,7 +49631,7 @@
         <v>45705.32456018519</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -49688,7 +49688,7 @@
         <v>45197.46966435185</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -49745,7 +49745,7 @@
         <v>45209.45420138889</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -49802,7 +49802,7 @@
         <v>44225</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -49859,7 +49859,7 @@
         <v>45832</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -49921,7 +49921,7 @@
         <v>45874.64513888889</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -49978,7 +49978,7 @@
         <v>45832</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -50040,7 +50040,7 @@
         <v>45832.3859837963</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -50102,7 +50102,7 @@
         <v>45832</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -50164,7 +50164,7 @@
         <v>45874.64199074074</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -50221,7 +50221,7 @@
         <v>45174</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -50278,7 +50278,7 @@
         <v>45741.38347222222</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -50335,7 +50335,7 @@
         <v>45834.51079861111</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -50397,7 +50397,7 @@
         <v>45876.39362268519</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -50459,7 +50459,7 @@
         <v>45834.38173611111</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -50516,7 +50516,7 @@
         <v>45875.5196875</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -50573,7 +50573,7 @@
         <v>45834.69577546296</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -50630,7 +50630,7 @@
         <v>45834.71440972222</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -50687,7 +50687,7 @@
         <v>45604.31657407407</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -50749,7 +50749,7 @@
         <v>45834</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -50811,7 +50811,7 @@
         <v>45833</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -50873,7 +50873,7 @@
         <v>45751.63266203704</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -50935,7 +50935,7 @@
         <v>45238.64153935185</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -50992,7 +50992,7 @@
         <v>45265</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -51049,7 +51049,7 @@
         <v>45345</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -51111,7 +51111,7 @@
         <v>45195.35877314815</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -51168,7 +51168,7 @@
         <v>45195.3878125</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -51225,7 +51225,7 @@
         <v>45459</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -51282,7 +51282,7 @@
         <v>45751.34636574074</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -51344,7 +51344,7 @@
         <v>45740.57487268518</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -51406,7 +51406,7 @@
         <v>44784.60677083334</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -51468,7 +51468,7 @@
         <v>45833.36467592593</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -51530,7 +51530,7 @@
         <v>45218.58609953704</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -51587,7 +51587,7 @@
         <v>44827</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -51644,7 +51644,7 @@
         <v>45751.69827546296</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -51706,7 +51706,7 @@
         <v>45721.33868055556</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -51763,7 +51763,7 @@
         <v>45833.6081712963</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -51825,7 +51825,7 @@
         <v>45833</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -51887,7 +51887,7 @@
         <v>45875.47854166666</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -51949,7 +51949,7 @@
         <v>45833</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -52011,7 +52011,7 @@
         <v>45834.6568287037</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -52068,7 +52068,7 @@
         <v>45834</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -52125,7 +52125,7 @@
         <v>45834</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -52187,7 +52187,7 @@
         <v>45834.7087962963</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -52244,7 +52244,7 @@
         <v>45876.49113425926</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -52301,7 +52301,7 @@
         <v>45580.92037037037</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -52358,7 +52358,7 @@
         <v>45474.54432870371</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -52415,7 +52415,7 @@
         <v>44280</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -52472,7 +52472,7 @@
         <v>45835.55998842593</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -52534,7 +52534,7 @@
         <v>45834.80229166667</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -52591,7 +52591,7 @@
         <v>44726</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -52648,7 +52648,7 @@
         <v>45835.5583912037</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -52710,7 +52710,7 @@
         <v>44423</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -52767,7 +52767,7 @@
         <v>45622.64012731481</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -52829,7 +52829,7 @@
         <v>45478.44497685185</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -52891,7 +52891,7 @@
         <v>45880.37472222222</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -52948,7 +52948,7 @@
         <v>45835.57069444445</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -53005,7 +53005,7 @@
         <v>44182</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -53062,7 +53062,7 @@
         <v>44665</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -53119,7 +53119,7 @@
         <v>45173</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -53181,7 +53181,7 @@
         <v>45839.5658912037</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -53238,7 +53238,7 @@
         <v>45622.45239583333</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -53300,7 +53300,7 @@
         <v>45638</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -53362,7 +53362,7 @@
         <v>45881.46869212963</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -53419,7 +53419,7 @@
         <v>45603</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -53481,7 +53481,7 @@
         <v>45723.58140046296</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -53538,7 +53538,7 @@
         <v>45107</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -53595,7 +53595,7 @@
         <v>45611.4021875</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -53652,7 +53652,7 @@
         <v>45622</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -53714,7 +53714,7 @@
         <v>45881.6609375</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -53771,7 +53771,7 @@
         <v>45618</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -53828,7 +53828,7 @@
         <v>45245</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -53885,7 +53885,7 @@
         <v>45881.36469907407</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -53942,7 +53942,7 @@
         <v>44229</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -54004,7 +54004,7 @@
         <v>44225</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -54061,7 +54061,7 @@
         <v>45882.64755787037</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -54123,7 +54123,7 @@
         <v>45881.64365740741</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -54180,7 +54180,7 @@
         <v>45840.64394675926</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -54242,7 +54242,7 @@
         <v>45882.63179398148</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -54304,7 +54304,7 @@
         <v>45881.43114583333</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -54361,7 +54361,7 @@
         <v>45841.69273148148</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -54418,7 +54418,7 @@
         <v>45841.46512731481</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -54480,7 +54480,7 @@
         <v>45397.64855324074</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -54537,7 +54537,7 @@
         <v>44818</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -54594,7 +54594,7 @@
         <v>45569.48626157407</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -54651,7 +54651,7 @@
         <v>45841.45137731481</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -54708,7 +54708,7 @@
         <v>45883.40538194445</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -54765,7 +54765,7 @@
         <v>45841.4312037037</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -54822,7 +54822,7 @@
         <v>45884.55263888889</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -54884,7 +54884,7 @@
         <v>45630.5731712963</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -54946,7 +54946,7 @@
         <v>45842.48990740741</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -55003,7 +55003,7 @@
         <v>45883.4108912037</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -55060,7 +55060,7 @@
         <v>45883.51854166666</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -55117,7 +55117,7 @@
         <v>45883.58944444444</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -55179,7 +55179,7 @@
         <v>45632</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -55236,7 +55236,7 @@
         <v>45568</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -55298,7 +55298,7 @@
         <v>45442</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -55360,7 +55360,7 @@
         <v>45569</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -55422,7 +55422,7 @@
         <v>45888.78833333333</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -55479,7 +55479,7 @@
         <v>45888.78960648148</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -55536,7 +55536,7 @@
         <v>45569</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -55598,7 +55598,7 @@
         <v>45869</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -55655,7 +55655,7 @@
         <v>45876</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -55717,7 +55717,7 @@
         <v>45667</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -55779,7 +55779,7 @@
         <v>45845.60496527778</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -55836,7 +55836,7 @@
         <v>45869</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -55893,7 +55893,7 @@
         <v>45876</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -55955,7 +55955,7 @@
         <v>45845.6920949074</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -56017,7 +56017,7 @@
         <v>45610.55846064815</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -56079,7 +56079,7 @@
         <v>45888.78539351852</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -56136,7 +56136,7 @@
         <v>45159.46996527778</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -56198,7 +56198,7 @@
         <v>44925.60457175926</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -56260,7 +56260,7 @@
         <v>44925.64309027778</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -56322,7 +56322,7 @@
         <v>45845.55270833334</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -56379,7 +56379,7 @@
         <v>45845.55266203704</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -56436,7 +56436,7 @@
         <v>45730</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -56493,7 +56493,7 @@
         <v>45568</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -56555,7 +56555,7 @@
         <v>45755</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -56612,7 +56612,7 @@
         <v>45622</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -56669,7 +56669,7 @@
         <v>45845.55259259259</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -56726,7 +56726,7 @@
         <v>45887.50216435185</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -56788,7 +56788,7 @@
         <v>45887.59913194444</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -56850,7 +56850,7 @@
         <v>45730</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -56907,7 +56907,7 @@
         <v>45888.59509259259</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -56964,7 +56964,7 @@
         <v>45569</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -57026,7 +57026,7 @@
         <v>45533.67138888889</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -57083,7 +57083,7 @@
         <v>45848.57644675926</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -57145,7 +57145,7 @@
         <v>45758.69638888889</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -57202,7 +57202,7 @@
         <v>45861</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -57264,7 +57264,7 @@
         <v>45889.40916666666</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -57321,7 +57321,7 @@
         <v>45889.41715277778</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -57378,7 +57378,7 @@
         <v>45848.62873842593</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -57435,7 +57435,7 @@
         <v>45848.639375</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -57492,7 +57492,7 @@
         <v>45848.6568287037</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -57549,7 +57549,7 @@
         <v>45848.68640046296</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -57611,7 +57611,7 @@
         <v>45848</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -57673,7 +57673,7 @@
         <v>45848.35400462963</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -57730,7 +57730,7 @@
         <v>45159</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -57792,7 +57792,7 @@
         <v>45159</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -57854,7 +57854,7 @@
         <v>45644</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -57911,7 +57911,7 @@
         <v>44314</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -57968,7 +57968,7 @@
         <v>45118.3959375</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -58030,7 +58030,7 @@
         <v>44998</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -58087,7 +58087,7 @@
         <v>45848.45113425926</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -58149,7 +58149,7 @@
         <v>45848.65003472222</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -58206,7 +58206,7 @@
         <v>45847.58865740741</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -58268,7 +58268,7 @@
         <v>45733.59667824074</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -58330,7 +58330,7 @@
         <v>45098.48666666666</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -58392,7 +58392,7 @@
         <v>44925</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -58449,7 +58449,7 @@
         <v>45852</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -58506,7 +58506,7 @@
         <v>45892.53184027778</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -58563,7 +58563,7 @@
         <v>45496.67342592592</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -58625,7 +58625,7 @@
         <v>45582.49792824074</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -58687,7 +58687,7 @@
         <v>45509</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -58749,7 +58749,7 @@
         <v>44958</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -58811,7 +58811,7 @@
         <v>45894.65869212963</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -58868,7 +58868,7 @@
         <v>45170.46923611111</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -58930,7 +58930,7 @@
         <v>45743.38449074074</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -58987,7 +58987,7 @@
         <v>45894.64358796296</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -59049,7 +59049,7 @@
         <v>45688.67932870371</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -59111,7 +59111,7 @@
         <v>44091</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -59168,7 +59168,7 @@
         <v>45852.48290509259</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -59225,7 +59225,7 @@
         <v>45849</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -59282,7 +59282,7 @@
         <v>45719.40480324074</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -59339,7 +59339,7 @@
         <v>45775.36587962963</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -59396,7 +59396,7 @@
         <v>45775.36589120371</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -59453,7 +59453,7 @@
         <v>45896.49959490741</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -59510,7 +59510,7 @@
         <v>45617.89371527778</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -59567,7 +59567,7 @@
         <v>45621</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -59629,7 +59629,7 @@
         <v>45853.61865740741</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -59686,7 +59686,7 @@
         <v>45853.62415509259</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -59748,7 +59748,7 @@
         <v>45853.28325231482</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -59805,7 +59805,7 @@
         <v>45154</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -59862,7 +59862,7 @@
         <v>45719.45215277778</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -59919,7 +59919,7 @@
         <v>45604.66936342593</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -59976,7 +59976,7 @@
         <v>45118.91633101852</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -60033,7 +60033,7 @@
         <v>45119</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -60090,7 +60090,7 @@
         <v>45854.40662037037</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -60152,7 +60152,7 @@
         <v>44708.48859953704</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -60214,7 +60214,7 @@
         <v>45632.65197916667</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -60271,7 +60271,7 @@
         <v>44483</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -60328,7 +60328,7 @@
         <v>45896.49821759259</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -60385,7 +60385,7 @@
         <v>44209</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -60447,7 +60447,7 @@
         <v>45664.56502314815</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -60504,7 +60504,7 @@
         <v>45895.29387731481</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -60566,7 +60566,7 @@
         <v>45740.36546296296</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -60628,7 +60628,7 @@
         <v>45854.44850694444</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -60690,7 +60690,7 @@
         <v>45854.44864583333</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -60752,7 +60752,7 @@
         <v>45484.48854166667</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -60814,7 +60814,7 @@
         <v>45147</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -60871,7 +60871,7 @@
         <v>45488</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -60928,7 +60928,7 @@
         <v>45897.44645833333</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -60990,7 +60990,7 @@
         <v>45898.55296296296</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -61052,7 +61052,7 @@
         <v>44858</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -61109,7 +61109,7 @@
         <v>45659.57361111111</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -61171,7 +61171,7 @@
         <v>45288.58685185185</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -61228,7 +61228,7 @@
         <v>45898.38625</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -61285,7 +61285,7 @@
         <v>45898.40267361111</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -61347,7 +61347,7 @@
         <v>45898.40481481481</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -61404,7 +61404,7 @@
         <v>45063</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -61461,7 +61461,7 @@
         <v>45898.41540509259</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -61518,7 +61518,7 @@
         <v>45670</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -61580,7 +61580,7 @@
         <v>45630.62513888889</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -61637,7 +61637,7 @@
         <v>45547.59543981482</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -61694,7 +61694,7 @@
         <v>45631.39950231482</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -61756,7 +61756,7 @@
         <v>45885</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -61813,7 +61813,7 @@
         <v>45509.5980787037</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -61875,7 +61875,7 @@
         <v>45869</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -61932,7 +61932,7 @@
         <v>45707</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -61989,7 +61989,7 @@
         <v>44381</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -62046,7 +62046,7 @@
         <v>45768.30814814815</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -62108,7 +62108,7 @@
         <v>45764.44861111111</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -62170,7 +62170,7 @@
         <v>45727.35621527778</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -62232,7 +62232,7 @@
         <v>45510</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -62294,7 +62294,7 @@
         <v>45656.51157407407</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -62356,7 +62356,7 @@
         <v>45484.65768518519</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -62418,7 +62418,7 @@
         <v>44964</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -62475,7 +62475,7 @@
         <v>45691</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -62537,7 +62537,7 @@
         <v>45691</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -62599,7 +62599,7 @@
         <v>45621</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -62656,7 +62656,7 @@
         <v>45621</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -62713,7 +62713,7 @@
         <v>45485</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -62770,7 +62770,7 @@
         <v>45643.56899305555</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -62832,7 +62832,7 @@
         <v>44928.36418981481</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -62894,7 +62894,7 @@
         <v>44231</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -62956,7 +62956,7 @@
         <v>45707</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -63013,7 +63013,7 @@
         <v>44795</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -63070,7 +63070,7 @@
         <v>44088</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -63127,7 +63127,7 @@
         <v>45742.42793981481</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -63189,7 +63189,7 @@
         <v>45705.72106481482</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -63246,7 +63246,7 @@
         <v>44385</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -63303,7 +63303,7 @@
         <v>44925.59333333333</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -63365,7 +63365,7 @@
         <v>45385</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -63422,7 +63422,7 @@
         <v>44757.37524305555</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -63479,7 +63479,7 @@
         <v>45764.44825231482</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -63541,7 +63541,7 @@
         <v>44216</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -63603,7 +63603,7 @@
         <v>45485</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -63665,7 +63665,7 @@
         <v>44151</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -63722,7 +63722,7 @@
         <v>45485</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -63784,7 +63784,7 @@
         <v>44435</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -63846,7 +63846,7 @@
         <v>44169</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -63903,7 +63903,7 @@
         <v>44126</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -63960,7 +63960,7 @@
         <v>45572.60001157408</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -64017,7 +64017,7 @@
         <v>44985.61403935185</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -64079,7 +64079,7 @@
         <v>45737.3787962963</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -64136,7 +64136,7 @@
         <v>45768.29469907407</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -64198,7 +64198,7 @@
         <v>45768.30260416667</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -64260,7 +64260,7 @@
         <v>45768.30388888889</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -64322,7 +64322,7 @@
         <v>45685.50063657408</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -64384,7 +64384,7 @@
         <v>45687.54329861111</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -64441,7 +64441,7 @@
         <v>45063</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -64498,7 +64498,7 @@
         <v>44474.59423611111</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -64555,7 +64555,7 @@
         <v>45743.61899305556</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -64612,7 +64612,7 @@
         <v>45743.62116898148</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -64669,7 +64669,7 @@
         <v>45433</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -64726,7 +64726,7 @@
         <v>45764</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -64783,7 +64783,7 @@
         <v>45754.35055555555</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -64840,7 +64840,7 @@
         <v>45539.43545138889</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -64897,7 +64897,7 @@
         <v>45204</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -64954,7 +64954,7 @@
         <v>45688.6749537037</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -65016,7 +65016,7 @@
         <v>44827</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -65073,7 +65073,7 @@
         <v>44827</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -65130,7 +65130,7 @@
         <v>45238.46430555556</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -65187,7 +65187,7 @@
         <v>45166.34795138889</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -65244,7 +65244,7 @@
         <v>44928</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -65306,7 +65306,7 @@
         <v>45432</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -65368,7 +65368,7 @@
         <v>44987.35637731481</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -65430,7 +65430,7 @@
         <v>44987</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -65492,7 +65492,7 @@
         <v>45532</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -65549,7 +65549,7 @@
         <v>44886</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -65611,7 +65611,7 @@
         <v>45758.66108796297</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -65668,7 +65668,7 @@
         <v>45758.69123842593</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -65725,7 +65725,7 @@
         <v>45670.4570949074</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -65787,7 +65787,7 @@
         <v>44853</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -65844,7 +65844,7 @@
         <v>44925.33584490741</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -65906,7 +65906,7 @@
         <v>45706</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -65963,7 +65963,7 @@
         <v>45741.39084490741</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -66020,7 +66020,7 @@
         <v>45477.62255787037</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -66082,7 +66082,7 @@
         <v>44985.6125</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -66144,7 +66144,7 @@
         <v>45763.4266087963</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -66201,7 +66201,7 @@
         <v>45345.65929398148</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -66263,7 +66263,7 @@
         <v>45688.6769212963</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -66325,7 +66325,7 @@
         <v>45439.43106481482</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -66387,7 +66387,7 @@
         <v>44972.57449074074</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -66444,7 +66444,7 @@
         <v>44484.55535879629</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -66501,7 +66501,7 @@
         <v>45229.92739583334</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -66558,7 +66558,7 @@
         <v>45624.63614583333</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -66620,7 +66620,7 @@
         <v>45041</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -66677,7 +66677,7 @@
         <v>45041</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -66734,7 +66734,7 @@
         <v>44889.56582175926</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -66791,7 +66791,7 @@
         <v>45531.66196759259</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -66853,7 +66853,7 @@
         <v>44928</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -66915,7 +66915,7 @@
         <v>44550.39550925926</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -66972,7 +66972,7 @@
         <v>44928</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -67034,7 +67034,7 @@
         <v>45791</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -67091,7 +67091,7 @@
         <v>45731.69629629629</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -67148,7 +67148,7 @@
         <v>44819.56722222222</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -67205,7 +67205,7 @@
         <v>45631.63091435185</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -67262,7 +67262,7 @@
         <v>44722</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -67319,7 +67319,7 @@
         <v>44854</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -67381,7 +67381,7 @@
         <v>45751.65657407408</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -67443,7 +67443,7 @@
         <v>45338</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -67505,7 +67505,7 @@
         <v>45496.59202546296</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -67567,7 +67567,7 @@
         <v>45756</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -67624,7 +67624,7 @@
         <v>45154</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -67681,7 +67681,7 @@
         <v>45496.67178240741</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -67743,7 +67743,7 @@
         <v>45282.64012731481</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -67805,7 +67805,7 @@
         <v>45673.65925925926</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -67867,7 +67867,7 @@
         <v>45420.44414351852</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -67929,7 +67929,7 @@
         <v>45677.43028935185</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -67986,7 +67986,7 @@
         <v>44460.44315972222</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -68048,7 +68048,7 @@
         <v>45447.35144675926</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -68105,7 +68105,7 @@
         <v>45239.43173611111</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -68167,7 +68167,7 @@
         <v>45054</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -68229,7 +68229,7 @@
         <v>45761.61501157407</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -68291,7 +68291,7 @@
         <v>45637.39587962963</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -68353,7 +68353,7 @@
         <v>45559.43645833333</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -68415,7 +68415,7 @@
         <v>45517.69590277778</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -68477,7 +68477,7 @@
         <v>45624.36090277778</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -68534,7 +68534,7 @@
         <v>45590.31899305555</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -68591,7 +68591,7 @@
         <v>45642.41907407407</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -68648,7 +68648,7 @@
         <v>45049.59826388889</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -68705,7 +68705,7 @@
         <v>45020</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -68762,7 +68762,7 @@
         <v>44872</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -68819,7 +68819,7 @@
         <v>45075.59358796296</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -68881,7 +68881,7 @@
         <v>45685.52405092592</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -68943,7 +68943,7 @@
         <v>45685.5349074074</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -69005,7 +69005,7 @@
         <v>45672.61748842592</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -69062,7 +69062,7 @@
         <v>45390</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -69119,7 +69119,7 @@
         <v>45735.60342592592</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -69176,7 +69176,7 @@
         <v>45719.45277777778</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -69233,7 +69233,7 @@
         <v>45763.4178587963</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -69290,7 +69290,7 @@
         <v>45351</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -69347,7 +69347,7 @@
         <v>45575</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -69404,7 +69404,7 @@
         <v>45616.49530092593</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -69461,7 +69461,7 @@
         <v>45154</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -69518,7 +69518,7 @@
         <v>45688.46570601852</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -69580,7 +69580,7 @@
         <v>44155</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -69637,7 +69637,7 @@
         <v>45642</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -69694,7 +69694,7 @@
         <v>45484.58422453704</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -69756,7 +69756,7 @@
         <v>45371.66217592593</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -69818,7 +69818,7 @@
         <v>44886</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -69880,7 +69880,7 @@
         <v>45303.5047337963</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -69937,7 +69937,7 @@
         <v>45735.57390046296</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -69994,7 +69994,7 @@
         <v>45119.38151620371</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -70056,7 +70056,7 @@
         <v>45665.59925925926</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -70113,7 +70113,7 @@
         <v>45593.6821412037</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -70170,7 +70170,7 @@
         <v>45593.68434027778</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -70227,7 +70227,7 @@
         <v>45625.56934027778</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -70289,7 +70289,7 @@
         <v>45274</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -70346,7 +70346,7 @@
         <v>45411.44549768518</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -70408,7 +70408,7 @@
         <v>45303.5187037037</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -70465,7 +70465,7 @@
         <v>45635.42027777778</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -70527,7 +70527,7 @@
         <v>45728.61006944445</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -70584,7 +70584,7 @@
         <v>45611.38759259259</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -70641,7 +70641,7 @@
         <v>44642</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -70703,7 +70703,7 @@
         <v>45244</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -70760,7 +70760,7 @@
         <v>45252.48409722222</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -70817,7 +70817,7 @@
         <v>45252</v>
       </c>
       <c r="C1075" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
@@ -70874,7 +70874,7 @@
         <v>45667</v>
       </c>
       <c r="C1076" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
@@ -70931,7 +70931,7 @@
         <v>45509</v>
       </c>
       <c r="C1077" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
@@ -70993,7 +70993,7 @@
         <v>45303.52626157407</v>
       </c>
       <c r="C1078" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1078" t="inlineStr">
         <is>
@@ -71050,7 +71050,7 @@
         <v>45719.48778935185</v>
       </c>
       <c r="C1079" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1079" t="inlineStr">
         <is>
@@ -71107,7 +71107,7 @@
         <v>45574.66106481481</v>
       </c>
       <c r="C1080" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
@@ -71164,7 +71164,7 @@
         <v>45264.92637731481</v>
       </c>
       <c r="C1081" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1081" t="inlineStr">
         <is>
@@ -71221,7 +71221,7 @@
         <v>45260.59042824074</v>
       </c>
       <c r="C1082" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1082" t="inlineStr">
         <is>
@@ -71278,7 +71278,7 @@
         <v>45075.59148148148</v>
       </c>
       <c r="C1083" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1083" t="inlineStr">
         <is>
@@ -71340,7 +71340,7 @@
         <v>45063.92605324074</v>
       </c>
       <c r="C1084" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1084" t="inlineStr">
         <is>
@@ -71397,7 +71397,7 @@
         <v>45575.60996527778</v>
       </c>
       <c r="C1085" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1085" t="inlineStr">
         <is>
@@ -71459,7 +71459,7 @@
         <v>45290.39024305555</v>
       </c>
       <c r="C1086" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1086" t="inlineStr">
         <is>
@@ -71516,7 +71516,7 @@
         <v>45460.48582175926</v>
       </c>
       <c r="C1087" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1087" t="inlineStr">
         <is>
@@ -71573,7 +71573,7 @@
         <v>45680.42497685185</v>
       </c>
       <c r="C1088" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1088" t="inlineStr">
         <is>
@@ -71630,7 +71630,7 @@
         <v>45153.42725694444</v>
       </c>
       <c r="C1089" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1089" t="inlineStr">
         <is>
@@ -71692,7 +71692,7 @@
         <v>45568</v>
       </c>
       <c r="C1090" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1090" t="inlineStr">
         <is>
@@ -71754,7 +71754,7 @@
         <v>45685</v>
       </c>
       <c r="C1091" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1091" t="inlineStr">
         <is>
@@ -71816,7 +71816,7 @@
         <v>45477.66773148148</v>
       </c>
       <c r="C1092" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1092" t="inlineStr">
         <is>
@@ -71878,7 +71878,7 @@
         <v>45257</v>
       </c>
       <c r="C1093" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1093" t="inlineStr">
         <is>
@@ -71935,7 +71935,7 @@
         <v>45601.58355324074</v>
       </c>
       <c r="C1094" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1094" t="inlineStr">
         <is>
@@ -71992,7 +71992,7 @@
         <v>45429.39</v>
       </c>
       <c r="C1095" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1095" t="inlineStr">
         <is>
@@ -72049,7 +72049,7 @@
         <v>45635.4916087963</v>
       </c>
       <c r="C1096" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1096" t="inlineStr">
         <is>
@@ -72106,7 +72106,7 @@
         <v>45012</v>
       </c>
       <c r="C1097" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1097" t="inlineStr">
         <is>
@@ -72168,7 +72168,7 @@
         <v>45607</v>
       </c>
       <c r="C1098" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1098" t="inlineStr">
         <is>
@@ -72225,7 +72225,7 @@
         <v>44571</v>
       </c>
       <c r="C1099" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1099" t="inlineStr">
         <is>
@@ -72282,7 +72282,7 @@
         <v>45579.59980324074</v>
       </c>
       <c r="C1100" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1100" t="inlineStr">
         <is>
@@ -72339,7 +72339,7 @@
         <v>45632</v>
       </c>
       <c r="C1101" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1101" t="inlineStr">
         <is>
@@ -72396,7 +72396,7 @@
         <v>45632</v>
       </c>
       <c r="C1102" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1102" t="inlineStr">
         <is>

--- a/Översikt HÄRJEDALEN.xlsx
+++ b/Översikt HÄRJEDALEN.xlsx
@@ -567,7 +567,7 @@
         <v>45513</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         <v>45763</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>44785</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>44790</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>44553</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>44837</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>44844</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>44749</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>44406</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>45691</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>44182</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>44154.40430555555</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>45761.58262731481</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>45531</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>44831</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>44496.94013888889</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>45667</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
         <v>44865.57574074074</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>45180</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
         <v>44650</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>45250</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>45351</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3043,7 +3043,7 @@
         <v>44200</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>44193</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>45554</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         <v>45631</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         <v>45544.35653935185</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>44501</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3681,7 +3681,7 @@
         <v>44182</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>44690</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>44487</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
         <v>45631</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>45903.62199074074</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>45625.49736111111</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>44440</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
         <v>44406</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4508,7 +4508,7 @@
         <v>45544</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4609,7 +4609,7 @@
         <v>45837</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         <v>45217</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
         <v>45106</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4913,7 +4913,7 @@
         <v>45571</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5013,7 +5013,7 @@
         <v>44774</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>44357</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5211,7 +5211,7 @@
         <v>45457.38396990741</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5315,7 +5315,7 @@
         <v>45544</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5414,7 +5414,7 @@
         <v>45198</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>45175</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5630,7 +5630,7 @@
         <v>45471.59034722222</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5733,7 +5733,7 @@
         <v>45531</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5831,7 +5831,7 @@
         <v>45477.46537037037</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>45411</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6032,7 +6032,7 @@
         <v>45833.43898148148</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6135,7 +6135,7 @@
         <v>45694</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         <v>44553</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6331,7 +6331,7 @@
         <v>44517</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>44406</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6521,7 +6521,7 @@
         <v>45614.45413194445</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6627,7 +6627,7 @@
         <v>44553</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6724,7 +6724,7 @@
         <v>44377</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
         <v>45741.82913194445</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         <v>45677.45212962963</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7008,7 +7008,7 @@
         <v>45426</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7100,7 +7100,7 @@
         <v>44430</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         <v>44553</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7292,7 +7292,7 @@
         <v>45715</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>45531.45444444445</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7487,7 +7487,7 @@
         <v>45007</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7587,7 +7587,7 @@
         <v>44242</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7677,7 +7677,7 @@
         <v>45616.6450462963</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7775,7 +7775,7 @@
         <v>45568</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7870,7 +7870,7 @@
         <v>45559</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7969,7 +7969,7 @@
         <v>45772.51116898148</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8064,7 +8064,7 @@
         <v>45869</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8158,7 +8158,7 @@
         <v>45719</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8252,7 +8252,7 @@
         <v>45574</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
         <v>45625.45384259259</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         <v>44882</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8542,7 +8542,7 @@
         <v>45432.94736111111</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>44517</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8729,7 +8729,7 @@
         <v>44979</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8818,7 +8818,7 @@
         <v>45243</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8911,7 +8911,7 @@
         <v>44430</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9012,7 +9012,7 @@
         <v>44294</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         <v>44294</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9188,7 +9188,7 @@
         <v>45666</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         <v>45467.47204861111</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9378,7 +9378,7 @@
         <v>44957</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9470,7 +9470,7 @@
         <v>45838.73927083334</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9563,7 +9563,7 @@
         <v>44377</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9655,7 +9655,7 @@
         <v>45883.35789351852</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9747,7 +9747,7 @@
         <v>45085</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9839,7 +9839,7 @@
         <v>45694</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9927,7 +9927,7 @@
         <v>44977</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>45537.45818287037</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10121,7 +10121,7 @@
         <v>45552</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10209,7 +10209,7 @@
         <v>45531.45752314815</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10297,7 +10297,7 @@
         <v>45559.38894675926</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10394,7 +10394,7 @@
         <v>45007</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10487,7 +10487,7 @@
         <v>45506.35658564815</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10579,7 +10579,7 @@
         <v>44476</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10671,7 +10671,7 @@
         <v>44475</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10758,7 +10758,7 @@
         <v>44441</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10845,7 +10845,7 @@
         <v>44475</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10932,7 +10932,7 @@
         <v>44475</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11019,7 +11019,7 @@
         <v>44713</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11119,7 +11119,7 @@
         <v>45791</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11206,7 +11206,7 @@
         <v>45800.3484375</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11298,7 +11298,7 @@
         <v>45617</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11394,7 +11394,7 @@
         <v>45821.56523148148</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11486,7 +11486,7 @@
         <v>45841.41003472222</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11573,7 +11573,7 @@
         <v>45849.35011574074</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11660,7 +11660,7 @@
         <v>44107</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11756,7 +11756,7 @@
         <v>45468</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11843,7 +11843,7 @@
         <v>44180</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>44186</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12026,7 +12026,7 @@
         <v>44677</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12117,7 +12117,7 @@
         <v>44286</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12203,7 +12203,7 @@
         <v>44866.46503472222</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12298,7 +12298,7 @@
         <v>45772.51070601852</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12389,7 +12389,7 @@
         <v>45191</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>45786.66594907407</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12571,7 +12571,7 @@
         <v>45786.67016203704</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12662,7 +12662,7 @@
         <v>45786.6768287037</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12753,7 +12753,7 @@
         <v>45786.6590625</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12844,7 +12844,7 @@
         <v>45786.65452546296</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12935,7 +12935,7 @@
         <v>45786.67261574074</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13026,7 +13026,7 @@
         <v>44853</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13116,7 +13116,7 @@
         <v>44449</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13202,7 +13202,7 @@
         <v>45644.56555555556</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13297,7 +13297,7 @@
         <v>45153</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
         <v>44987</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13482,7 +13482,7 @@
         <v>45772.36488425926</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13577,7 +13577,7 @@
         <v>45805.73822916667</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13668,7 +13668,7 @@
         <v>45595.58056712963</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13759,7 +13759,7 @@
         <v>45833</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13845,7 +13845,7 @@
         <v>45035</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -13940,7 +13940,7 @@
         <v>44955</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14030,7 +14030,7 @@
         <v>45880.37559027778</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14116,7 +14116,7 @@
         <v>45694</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14202,7 +14202,7 @@
         <v>45552</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14292,7 +14292,7 @@
         <v>45621</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14387,7 +14387,7 @@
         <v>44475</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14473,7 +14473,7 @@
         <v>45538</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14564,7 +14564,7 @@
         <v>44221</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14650,7 +14650,7 @@
         <v>44475</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14736,7 +14736,7 @@
         <v>44096</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -14826,7 +14826,7 @@
         <v>44475</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -14911,7 +14911,7 @@
         <v>44475</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -14996,7 +14996,7 @@
         <v>44475</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15081,7 +15081,7 @@
         <v>44321</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15171,7 +15171,7 @@
         <v>44105</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15256,7 +15256,7 @@
         <v>44113</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15341,7 +15341,7 @@
         <v>44769.48783564815</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15431,7 +15431,7 @@
         <v>45638.33607638889</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -15521,7 +15521,7 @@
         <v>45729.64623842593</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -15611,7 +15611,7 @@
         <v>45320</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -15696,7 +15696,7 @@
         <v>45111</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -15786,7 +15786,7 @@
         <v>45714.55248842593</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -15880,7 +15880,7 @@
         <v>45308</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -15969,7 +15969,7 @@
         <v>45457.38677083333</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16059,7 +16059,7 @@
         <v>45540.69512731482</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16149,7 +16149,7 @@
         <v>45800.63043981481</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -16243,7 +16243,7 @@
         <v>45805.66601851852</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -16337,7 +16337,7 @@
         <v>45805.73546296296</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -16427,7 +16427,7 @@
         <v>45617</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -16521,7 +16521,7 @@
         <v>45454.62443287037</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -16606,7 +16606,7 @@
         <v>45812.82244212963</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -16696,7 +16696,7 @@
         <v>45791</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -16781,7 +16781,7 @@
         <v>45835.7499537037</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -16871,7 +16871,7 @@
         <v>45838.773125</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -16961,7 +16961,7 @@
         <v>45869</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17046,7 +17046,7 @@
         <v>45672.50416666667</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17131,7 +17131,7 @@
         <v>45889.56214120371</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -17221,7 +17221,7 @@
         <v>45875</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -17310,7 +17310,7 @@
         <v>45758.70164351852</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -17395,7 +17395,7 @@
         <v>45538.57630787037</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -17484,7 +17484,7 @@
         <v>45621.47555555555</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -17574,7 +17574,7 @@
         <v>45345</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -17664,7 +17664,7 @@
         <v>45603</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -17754,7 +17754,7 @@
         <v>44475</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -17839,7 +17839,7 @@
         <v>44320</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -17896,7 +17896,7 @@
         <v>44316</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -17953,7 +17953,7 @@
         <v>44320</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -18015,7 +18015,7 @@
         <v>44105</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -18072,7 +18072,7 @@
         <v>44810</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -18134,7 +18134,7 @@
         <v>44727.70908564814</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -18196,7 +18196,7 @@
         <v>44430</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -18258,7 +18258,7 @@
         <v>44543</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -18315,7 +18315,7 @@
         <v>44614</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -18377,7 +18377,7 @@
         <v>44404</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -18434,7 +18434,7 @@
         <v>44417.38271990741</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -18491,7 +18491,7 @@
         <v>44417.38614583333</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -18548,7 +18548,7 @@
         <v>44497</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -18605,7 +18605,7 @@
         <v>44475</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -18662,7 +18662,7 @@
         <v>44361</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -18719,7 +18719,7 @@
         <v>44540</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -18781,7 +18781,7 @@
         <v>44531</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -18838,7 +18838,7 @@
         <v>44475</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -18895,7 +18895,7 @@
         <v>44385.93652777778</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -18957,7 +18957,7 @@
         <v>44600</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -19014,7 +19014,7 @@
         <v>44406</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -19071,7 +19071,7 @@
         <v>44475</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -19128,7 +19128,7 @@
         <v>44538</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -19190,7 +19190,7 @@
         <v>44854</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -19247,7 +19247,7 @@
         <v>44102</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -19304,7 +19304,7 @@
         <v>44424</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -19361,7 +19361,7 @@
         <v>44823</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -19423,7 +19423,7 @@
         <v>44316</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -19480,7 +19480,7 @@
         <v>44483</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -19537,7 +19537,7 @@
         <v>44421</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -19594,7 +19594,7 @@
         <v>44418</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -19656,7 +19656,7 @@
         <v>44488</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -19718,7 +19718,7 @@
         <v>44603</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -19780,7 +19780,7 @@
         <v>44132</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -19837,7 +19837,7 @@
         <v>44179</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -19894,7 +19894,7 @@
         <v>44418</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -19956,7 +19956,7 @@
         <v>44564.6747337963</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -20018,7 +20018,7 @@
         <v>44361</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -20080,7 +20080,7 @@
         <v>44615</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -20142,7 +20142,7 @@
         <v>44466.81701388889</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -20199,7 +20199,7 @@
         <v>44218</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -20256,7 +20256,7 @@
         <v>44286</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -20313,7 +20313,7 @@
         <v>44475</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -20370,7 +20370,7 @@
         <v>44475</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -20427,7 +20427,7 @@
         <v>44410.74284722222</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -20484,7 +20484,7 @@
         <v>44631</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -20546,7 +20546,7 @@
         <v>44631.41535879629</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -20608,7 +20608,7 @@
         <v>44810</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -20670,7 +20670,7 @@
         <v>44728</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -20727,7 +20727,7 @@
         <v>44417.37519675926</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -20784,7 +20784,7 @@
         <v>44344</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -20841,7 +20841,7 @@
         <v>44174</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -20898,7 +20898,7 @@
         <v>44084</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -20960,7 +20960,7 @@
         <v>44475</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -21017,7 +21017,7 @@
         <v>44258</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -21074,7 +21074,7 @@
         <v>44424</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -21131,7 +21131,7 @@
         <v>44424</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -21188,7 +21188,7 @@
         <v>44818</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -21245,7 +21245,7 @@
         <v>44770.53315972222</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -21302,7 +21302,7 @@
         <v>44690</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -21359,7 +21359,7 @@
         <v>44286</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -21416,7 +21416,7 @@
         <v>44285</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -21473,7 +21473,7 @@
         <v>44792.68023148148</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -21530,7 +21530,7 @@
         <v>44385.93658564815</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -21592,7 +21592,7 @@
         <v>44243.63096064814</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -21649,7 +21649,7 @@
         <v>44298</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -21706,7 +21706,7 @@
         <v>44183</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -21763,7 +21763,7 @@
         <v>44319</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -21820,7 +21820,7 @@
         <v>44316</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -21877,7 +21877,7 @@
         <v>44316</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -21934,7 +21934,7 @@
         <v>44126</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -21991,7 +21991,7 @@
         <v>44825</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -22048,7 +22048,7 @@
         <v>44174</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -22105,7 +22105,7 @@
         <v>44154</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -22167,7 +22167,7 @@
         <v>44396</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -22224,7 +22224,7 @@
         <v>44475</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -22281,7 +22281,7 @@
         <v>44127</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -22343,7 +22343,7 @@
         <v>44475</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -22400,7 +22400,7 @@
         <v>44475</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -22457,7 +22457,7 @@
         <v>44475</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -22514,7 +22514,7 @@
         <v>44475</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -22571,7 +22571,7 @@
         <v>44420.33096064815</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -22628,7 +22628,7 @@
         <v>44544</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -22690,7 +22690,7 @@
         <v>44188</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -22752,7 +22752,7 @@
         <v>44483.36435185185</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -22809,7 +22809,7 @@
         <v>44417</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -22866,7 +22866,7 @@
         <v>44181</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -22928,7 +22928,7 @@
         <v>44426.45706018519</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -22985,7 +22985,7 @@
         <v>44859</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -23047,7 +23047,7 @@
         <v>44473</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -23104,7 +23104,7 @@
         <v>44314</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -23161,7 +23161,7 @@
         <v>44335.4837962963</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -23218,7 +23218,7 @@
         <v>44475</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -23275,7 +23275,7 @@
         <v>44543</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -23337,7 +23337,7 @@
         <v>44475</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -23394,7 +23394,7 @@
         <v>44475</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -23451,7 +23451,7 @@
         <v>44725</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -23513,7 +23513,7 @@
         <v>44631.45398148148</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -23575,7 +23575,7 @@
         <v>44417.37207175926</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -23632,7 +23632,7 @@
         <v>44855.60383101852</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -23689,7 +23689,7 @@
         <v>44481.67951388889</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -23746,7 +23746,7 @@
         <v>44133</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -23808,7 +23808,7 @@
         <v>44768.44859953703</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -23865,7 +23865,7 @@
         <v>44631.37421296296</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -23927,7 +23927,7 @@
         <v>44368</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -23984,7 +23984,7 @@
         <v>44403</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -24041,7 +24041,7 @@
         <v>44126</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -24103,7 +24103,7 @@
         <v>44538</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -24165,7 +24165,7 @@
         <v>44886.62578703704</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -24222,7 +24222,7 @@
         <v>44886.629375</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -24279,7 +24279,7 @@
         <v>44838</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -24341,7 +24341,7 @@
         <v>44540.56034722222</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -24398,7 +24398,7 @@
         <v>44872</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -24460,7 +24460,7 @@
         <v>44230</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -24517,7 +24517,7 @@
         <v>44742</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -24579,7 +24579,7 @@
         <v>44475</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -24636,7 +24636,7 @@
         <v>44475</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -24693,7 +24693,7 @@
         <v>44475</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -24750,7 +24750,7 @@
         <v>44475</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -24807,7 +24807,7 @@
         <v>44166</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -24869,7 +24869,7 @@
         <v>44708.46081018518</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -24931,7 +24931,7 @@
         <v>44684</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -24993,7 +24993,7 @@
         <v>44270</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -25050,7 +25050,7 @@
         <v>44169</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -25107,7 +25107,7 @@
         <v>44788.67976851852</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -25169,7 +25169,7 @@
         <v>44180</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -25226,7 +25226,7 @@
         <v>44531</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -25283,7 +25283,7 @@
         <v>44207</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -25345,7 +25345,7 @@
         <v>44531</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -25402,7 +25402,7 @@
         <v>44531</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -25459,7 +25459,7 @@
         <v>44316</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -25516,7 +25516,7 @@
         <v>44413</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -25573,7 +25573,7 @@
         <v>44316</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -25630,7 +25630,7 @@
         <v>44188</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -25687,7 +25687,7 @@
         <v>44389</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -25749,7 +25749,7 @@
         <v>44530.40607638889</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -25806,7 +25806,7 @@
         <v>44706.66417824074</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -25868,7 +25868,7 @@
         <v>44627.36047453704</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -25930,7 +25930,7 @@
         <v>44475</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -25987,7 +25987,7 @@
         <v>45617.89371527778</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -26044,7 +26044,7 @@
         <v>45119.39105324074</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -26106,7 +26106,7 @@
         <v>44803</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -26163,7 +26163,7 @@
         <v>45685</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -26225,7 +26225,7 @@
         <v>44285</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -26282,7 +26282,7 @@
         <v>44377</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -26339,7 +26339,7 @@
         <v>44825</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -26396,7 +26396,7 @@
         <v>44361</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -26453,7 +26453,7 @@
         <v>44727.71858796296</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -26515,7 +26515,7 @@
         <v>45740.36546296296</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -26577,7 +26577,7 @@
         <v>45634.65831018519</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -26634,7 +26634,7 @@
         <v>45687.54329861111</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -26691,7 +26691,7 @@
         <v>44300</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -26748,7 +26748,7 @@
         <v>45706</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -26805,7 +26805,7 @@
         <v>44483</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -26862,7 +26862,7 @@
         <v>45345.66555555556</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -26924,7 +26924,7 @@
         <v>45664.56502314815</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -26981,7 +26981,7 @@
         <v>45575.60996527778</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -27043,7 +27043,7 @@
         <v>45505</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -27100,7 +27100,7 @@
         <v>45560</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -27157,7 +27157,7 @@
         <v>44162.65819444445</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -27219,7 +27219,7 @@
         <v>45751.69827546296</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -27281,7 +27281,7 @@
         <v>45582.49792824074</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -27343,7 +27343,7 @@
         <v>44985.61403935185</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -27405,7 +27405,7 @@
         <v>45637</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -27462,7 +27462,7 @@
         <v>45604.33195601852</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -27524,7 +27524,7 @@
         <v>45575</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -27581,7 +27581,7 @@
         <v>45603</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -27643,7 +27643,7 @@
         <v>45776.43898148148</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -27700,7 +27700,7 @@
         <v>45776.69569444445</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -27757,7 +27757,7 @@
         <v>45721.33868055556</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -27814,7 +27814,7 @@
         <v>45688.67932870371</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -27876,7 +27876,7 @@
         <v>45719.40480324074</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -27933,7 +27933,7 @@
         <v>45547.59543981482</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -27990,7 +27990,7 @@
         <v>45779.41844907407</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -28052,7 +28052,7 @@
         <v>45779.38211805555</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -28114,7 +28114,7 @@
         <v>45779.50886574074</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -28176,7 +28176,7 @@
         <v>45779.51943287037</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -28238,7 +28238,7 @@
         <v>45779.52488425926</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -28300,7 +28300,7 @@
         <v>45779.50052083333</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -28362,7 +28362,7 @@
         <v>45737</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -28419,7 +28419,7 @@
         <v>45779.47704861111</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -28481,7 +28481,7 @@
         <v>45779.51357638889</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -28543,7 +28543,7 @@
         <v>45779.48611111111</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -28605,7 +28605,7 @@
         <v>45483.47572916667</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -28662,7 +28662,7 @@
         <v>45607.44832175926</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -28724,7 +28724,7 @@
         <v>45580.92037037037</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -28781,7 +28781,7 @@
         <v>45768.30814814815</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -28843,7 +28843,7 @@
         <v>45635.42027777778</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -28905,7 +28905,7 @@
         <v>45783.68547453704</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -28967,7 +28967,7 @@
         <v>45350</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -29024,7 +29024,7 @@
         <v>45351</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -29081,7 +29081,7 @@
         <v>45303.52626157407</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -29138,7 +29138,7 @@
         <v>45618.35961805555</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -29195,7 +29195,7 @@
         <v>45782.41581018519</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
         <v>45782.42744212963</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -29309,7 +29309,7 @@
         <v>45729.65261574074</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -29371,7 +29371,7 @@
         <v>45569.48626157407</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -29428,7 +29428,7 @@
         <v>45119.38151620371</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -29490,7 +29490,7 @@
         <v>44914</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -29547,7 +29547,7 @@
         <v>45457.92854166667</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -29604,7 +29604,7 @@
         <v>45387</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -29661,7 +29661,7 @@
         <v>45061.61002314815</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -29723,7 +29723,7 @@
         <v>45785.33164351852</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -29780,7 +29780,7 @@
         <v>44977.44643518519</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -29842,7 +29842,7 @@
         <v>44316</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -29899,7 +29899,7 @@
         <v>45785.34165509259</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -29956,7 +29956,7 @@
         <v>45784.59012731481</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -30018,7 +30018,7 @@
         <v>45260.35777777778</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -30075,7 +30075,7 @@
         <v>45670.34313657408</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -30132,7 +30132,7 @@
         <v>45740.57487268518</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -30194,7 +30194,7 @@
         <v>45632.64078703704</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -30251,7 +30251,7 @@
         <v>45642</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -30308,7 +30308,7 @@
         <v>44312</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -30365,7 +30365,7 @@
         <v>45453.6619212963</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -30422,7 +30422,7 @@
         <v>45280</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -30479,7 +30479,7 @@
         <v>44732</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -30536,7 +30536,7 @@
         <v>45569.6909837963</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -30593,7 +30593,7 @@
         <v>45617</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -30655,7 +30655,7 @@
         <v>44242</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -30712,7 +30712,7 @@
         <v>44643.81518518519</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -30769,7 +30769,7 @@
         <v>45471.66556712963</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -30831,7 +30831,7 @@
         <v>45252</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -30888,7 +30888,7 @@
         <v>44928</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -30950,7 +30950,7 @@
         <v>44928</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -31012,7 +31012,7 @@
         <v>45621</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -31069,7 +31069,7 @@
         <v>45621</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -31126,7 +31126,7 @@
         <v>44953</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -31183,7 +31183,7 @@
         <v>44827</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -31240,7 +31240,7 @@
         <v>44827</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -31297,7 +31297,7 @@
         <v>45635.4916087963</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -31354,7 +31354,7 @@
         <v>45111</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -31411,7 +31411,7 @@
         <v>45257</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -31473,7 +31473,7 @@
         <v>45362.67293981482</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -31530,7 +31530,7 @@
         <v>45579.57390046296</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -31592,7 +31592,7 @@
         <v>45786.66425925926</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -31654,7 +31654,7 @@
         <v>45411.44549768518</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -31716,7 +31716,7 @@
         <v>45768.29469907407</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -31778,7 +31778,7 @@
         <v>45768.30260416667</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -31840,7 +31840,7 @@
         <v>45768.30388888889</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -31902,7 +31902,7 @@
         <v>45786.66853009259</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -31964,7 +31964,7 @@
         <v>45020</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -32021,7 +32021,7 @@
         <v>45614.62445601852</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -32083,7 +32083,7 @@
         <v>45751.63266203704</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -32145,7 +32145,7 @@
         <v>45786.66209490741</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -32207,7 +32207,7 @@
         <v>45786.66032407407</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -32269,7 +32269,7 @@
         <v>44872</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -32326,7 +32326,7 @@
         <v>44924.59140046296</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -32388,7 +32388,7 @@
         <v>44167</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -32445,7 +32445,7 @@
         <v>45119.38675925926</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -32507,7 +32507,7 @@
         <v>44424</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -32564,7 +32564,7 @@
         <v>44853.41693287037</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -32621,7 +32621,7 @@
         <v>45790.43</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -32683,7 +32683,7 @@
         <v>45705.32643518518</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -32740,7 +32740,7 @@
         <v>45517.38320601852</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -32797,7 +32797,7 @@
         <v>45533.67138888889</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -32854,7 +32854,7 @@
         <v>45645.47609953704</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -32916,7 +32916,7 @@
         <v>45196</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -32978,7 +32978,7 @@
         <v>45279.57732638889</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -33035,7 +33035,7 @@
         <v>45243.63798611111</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -33092,7 +33092,7 @@
         <v>45517.39274305556</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -33154,7 +33154,7 @@
         <v>45790.87653935186</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -33211,7 +33211,7 @@
         <v>45159.46996527778</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -33273,7 +33273,7 @@
         <v>45630.5731712963</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -33335,7 +33335,7 @@
         <v>45568</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -33397,7 +33397,7 @@
         <v>45792.64795138889</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -33454,7 +33454,7 @@
         <v>45792.50942129629</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -33516,7 +33516,7 @@
         <v>45688.46570601852</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -33578,7 +33578,7 @@
         <v>44153</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -33635,7 +33635,7 @@
         <v>45604.66936342593</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -33692,7 +33692,7 @@
         <v>45793.41994212963</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -33754,7 +33754,7 @@
         <v>44708.48859953704</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -33816,7 +33816,7 @@
         <v>45510</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -33878,7 +33878,7 @@
         <v>44985.6125</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -33940,7 +33940,7 @@
         <v>45485</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -34002,7 +34002,7 @@
         <v>45485</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -34064,7 +34064,7 @@
         <v>45611.38759259259</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -34121,7 +34121,7 @@
         <v>44957</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -34183,7 +34183,7 @@
         <v>45737.37006944444</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -34240,7 +34240,7 @@
         <v>45792.65047453704</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -34297,7 +34297,7 @@
         <v>45559</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -34354,7 +34354,7 @@
         <v>45484.66521990741</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -34416,7 +34416,7 @@
         <v>45506.36702546296</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -34473,7 +34473,7 @@
         <v>44348</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -34530,7 +34530,7 @@
         <v>45791</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -34587,7 +34587,7 @@
         <v>45631</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -34649,7 +34649,7 @@
         <v>45707</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -34706,7 +34706,7 @@
         <v>45707</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -34763,7 +34763,7 @@
         <v>45569</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -34825,7 +34825,7 @@
         <v>45743.61899305556</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -34882,7 +34882,7 @@
         <v>45743.62116898148</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -34939,7 +34939,7 @@
         <v>44823.84673611111</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -34996,7 +34996,7 @@
         <v>45618.35097222222</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -35053,7 +35053,7 @@
         <v>44209</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -35115,7 +35115,7 @@
         <v>45796.39770833333</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -35172,7 +35172,7 @@
         <v>45118.47491898148</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -35234,7 +35234,7 @@
         <v>44999.60127314815</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -35291,7 +35291,7 @@
         <v>45665.59925925926</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -35348,7 +35348,7 @@
         <v>45631</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -35410,7 +35410,7 @@
         <v>45791</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -35467,7 +35467,7 @@
         <v>45147</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -35524,7 +35524,7 @@
         <v>44631.37701388889</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -35586,7 +35586,7 @@
         <v>45796.57802083333</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -35643,7 +35643,7 @@
         <v>45677.43028935185</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -35700,7 +35700,7 @@
         <v>45205</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -35757,7 +35757,7 @@
         <v>45345.65929398148</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -35819,7 +35819,7 @@
         <v>45797.37096064815</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -35876,7 +35876,7 @@
         <v>44925.60457175926</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -35938,7 +35938,7 @@
         <v>44925.64309027778</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -36000,7 +36000,7 @@
         <v>44928.36418981481</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -36062,7 +36062,7 @@
         <v>45673.65925925926</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -36124,7 +36124,7 @@
         <v>45173</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -36186,7 +36186,7 @@
         <v>45408</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -36243,7 +36243,7 @@
         <v>45621</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -36305,7 +36305,7 @@
         <v>45733.59667824074</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -36367,7 +36367,7 @@
         <v>45484.57285879629</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -36429,7 +36429,7 @@
         <v>45209.45420138889</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -36486,7 +36486,7 @@
         <v>45063</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -36543,7 +36543,7 @@
         <v>45644.56674768519</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -36605,7 +36605,7 @@
         <v>45685.52405092592</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -36667,7 +36667,7 @@
         <v>45607</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -36729,7 +36729,7 @@
         <v>45830</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -36786,7 +36786,7 @@
         <v>45830</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -36843,7 +36843,7 @@
         <v>45830</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -36900,7 +36900,7 @@
         <v>44435</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -36962,7 +36962,7 @@
         <v>45754.67329861111</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -37019,7 +37019,7 @@
         <v>45453.6672800926</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -37076,7 +37076,7 @@
         <v>45799.64804398148</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -37138,7 +37138,7 @@
         <v>45742.42793981481</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -37200,7 +37200,7 @@
         <v>44231</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -37262,7 +37262,7 @@
         <v>45674.57393518519</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -37319,7 +37319,7 @@
         <v>45432</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -37381,7 +37381,7 @@
         <v>45799.4658912037</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -37443,7 +37443,7 @@
         <v>45799.46642361111</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -37500,7 +37500,7 @@
         <v>45830</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -37557,7 +37557,7 @@
         <v>44225</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -37614,7 +37614,7 @@
         <v>45772.46951388889</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -37676,7 +37676,7 @@
         <v>45799.43550925926</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -37738,7 +37738,7 @@
         <v>45799.47225694444</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -37800,7 +37800,7 @@
         <v>45531.78386574074</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -37857,7 +37857,7 @@
         <v>44638.44958333333</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -37914,7 +37914,7 @@
         <v>45799.45770833334</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -37976,7 +37976,7 @@
         <v>44939.45376157408</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -38033,7 +38033,7 @@
         <v>45216</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -38090,7 +38090,7 @@
         <v>45484.65768518519</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -38152,7 +38152,7 @@
         <v>45799.57883101852</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -38209,7 +38209,7 @@
         <v>45799.43086805556</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -38271,7 +38271,7 @@
         <v>45264.92637731481</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -38328,7 +38328,7 @@
         <v>45800.64065972222</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -38390,7 +38390,7 @@
         <v>45546.54530092593</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -38447,7 +38447,7 @@
         <v>45803.37480324074</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -38504,7 +38504,7 @@
         <v>45237.5815162037</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -38561,7 +38561,7 @@
         <v>44474.59423611111</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -38618,7 +38618,7 @@
         <v>45837</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -38675,7 +38675,7 @@
         <v>45406</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -38737,7 +38737,7 @@
         <v>45834</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -38794,7 +38794,7 @@
         <v>45118.91633101852</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -38851,7 +38851,7 @@
         <v>45800.63738425926</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -38913,7 +38913,7 @@
         <v>45800.37524305555</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -38975,7 +38975,7 @@
         <v>45533.75398148148</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -39032,7 +39032,7 @@
         <v>45800.58859953703</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -39089,7 +39089,7 @@
         <v>45800.59567129629</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -39151,7 +39151,7 @@
         <v>45800.64719907408</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -39213,7 +39213,7 @@
         <v>45800.65341435185</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -39275,7 +39275,7 @@
         <v>45800.42797453704</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -39332,7 +39332,7 @@
         <v>45800.44090277778</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -39389,7 +39389,7 @@
         <v>45800.66043981481</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -39451,7 +39451,7 @@
         <v>45800.33436342593</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -39513,7 +39513,7 @@
         <v>45800.3425</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -39575,7 +39575,7 @@
         <v>45800.44868055556</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -39637,7 +39637,7 @@
         <v>45800.4687962963</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -39699,7 +39699,7 @@
         <v>44928</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -39761,7 +39761,7 @@
         <v>45800.56222222222</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -39823,7 +39823,7 @@
         <v>44928.48072916667</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -39885,7 +39885,7 @@
         <v>44985</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -39947,7 +39947,7 @@
         <v>45212</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -40004,7 +40004,7 @@
         <v>45800.46069444445</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -40066,7 +40066,7 @@
         <v>45730</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -40123,7 +40123,7 @@
         <v>45397.64855324074</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -40180,7 +40180,7 @@
         <v>45800.56995370371</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -40242,7 +40242,7 @@
         <v>45800.35670138889</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -40304,7 +40304,7 @@
         <v>45768.29289351852</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -40366,7 +40366,7 @@
         <v>45768.30086805556</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -40428,7 +40428,7 @@
         <v>45803.37258101852</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -40485,7 +40485,7 @@
         <v>45800.48060185185</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -40547,7 +40547,7 @@
         <v>45474.54432870371</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -40604,7 +40604,7 @@
         <v>45800.3503587963</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -40666,7 +40666,7 @@
         <v>45800.50431712963</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -40728,7 +40728,7 @@
         <v>45800.60508101852</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -40790,7 +40790,7 @@
         <v>45800.56313657408</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -40847,7 +40847,7 @@
         <v>45800.57837962963</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -40909,7 +40909,7 @@
         <v>45800.3787037037</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -40971,7 +40971,7 @@
         <v>45800.41883101852</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -41033,7 +41033,7 @@
         <v>45800.48515046296</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -41095,7 +41095,7 @@
         <v>45159</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -41157,7 +41157,7 @@
         <v>45159</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -41219,7 +41219,7 @@
         <v>44423</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -41276,7 +41276,7 @@
         <v>45804.589375</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -41333,7 +41333,7 @@
         <v>45642</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -41390,7 +41390,7 @@
         <v>44958</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -41452,7 +41452,7 @@
         <v>45632.65197916667</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -41509,7 +41509,7 @@
         <v>45063</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -41566,7 +41566,7 @@
         <v>45644.50141203704</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -41628,7 +41628,7 @@
         <v>45804.5813425926</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -41690,7 +41690,7 @@
         <v>45805.53280092592</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -41752,7 +41752,7 @@
         <v>45638.416875</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -41814,7 +41814,7 @@
         <v>44886</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -41876,7 +41876,7 @@
         <v>45303.5187037037</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -41933,7 +41933,7 @@
         <v>45509.5980787037</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -41995,7 +41995,7 @@
         <v>45807.58393518518</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -42057,7 +42057,7 @@
         <v>45807.47479166667</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -42119,7 +42119,7 @@
         <v>45807.3409837963</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -42181,7 +42181,7 @@
         <v>45807.35476851852</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -42243,7 +42243,7 @@
         <v>45807.41287037037</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -42305,7 +42305,7 @@
         <v>45807.42212962963</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -42367,7 +42367,7 @@
         <v>45807.49436342593</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -42429,7 +42429,7 @@
         <v>45807.56403935186</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -42491,7 +42491,7 @@
         <v>45807.65438657408</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -42553,7 +42553,7 @@
         <v>45807.60333333333</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -42615,7 +42615,7 @@
         <v>45807.55893518519</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -42677,7 +42677,7 @@
         <v>45807.36304398148</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -42739,7 +42739,7 @@
         <v>45807.49045138889</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -42801,7 +42801,7 @@
         <v>45807.5684375</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -42863,7 +42863,7 @@
         <v>45807.63334490741</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -42925,7 +42925,7 @@
         <v>45807.45288194445</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -42987,7 +42987,7 @@
         <v>45617</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -43049,7 +43049,7 @@
         <v>45617</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -43111,7 +43111,7 @@
         <v>45588.56039351852</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -43168,7 +43168,7 @@
         <v>45630.62513888889</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -43225,7 +43225,7 @@
         <v>45624.36858796296</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -43282,7 +43282,7 @@
         <v>44757.37524305555</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -43339,7 +43339,7 @@
         <v>45625.56934027778</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -43401,7 +43401,7 @@
         <v>45807.41717592593</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -43463,7 +43463,7 @@
         <v>45807.43461805556</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -43525,7 +43525,7 @@
         <v>45807.44070601852</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -43587,7 +43587,7 @@
         <v>45807.44608796296</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -43649,7 +43649,7 @@
         <v>45807.49832175926</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -43711,7 +43711,7 @@
         <v>45807.58868055556</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -43773,7 +43773,7 @@
         <v>45807.59407407408</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -43835,7 +43835,7 @@
         <v>44924.61315972222</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -43897,7 +43897,7 @@
         <v>45719.45277777778</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -43954,7 +43954,7 @@
         <v>45728.61006944445</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -44011,7 +44011,7 @@
         <v>45811.34540509259</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -44073,7 +44073,7 @@
         <v>45433</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -44130,7 +44130,7 @@
         <v>44091</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -44187,7 +44187,7 @@
         <v>45593.6821412037</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -44244,7 +44244,7 @@
         <v>45593.68434027778</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -44301,7 +44301,7 @@
         <v>45811.34578703704</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -44363,7 +44363,7 @@
         <v>45562.65759259259</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -44425,7 +44425,7 @@
         <v>45345</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -44487,7 +44487,7 @@
         <v>45097</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -44549,7 +44549,7 @@
         <v>45485</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -44606,7 +44606,7 @@
         <v>45517.69590277778</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -44668,7 +44668,7 @@
         <v>45063.92605324074</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -44725,7 +44725,7 @@
         <v>44827</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -44782,7 +44782,7 @@
         <v>45170.46923611111</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -44844,7 +44844,7 @@
         <v>45576.48657407407</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -44906,7 +44906,7 @@
         <v>45616.49530092593</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -44963,7 +44963,7 @@
         <v>45496.67178240741</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -45025,7 +45025,7 @@
         <v>45642.35256944445</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -45082,7 +45082,7 @@
         <v>45685.50063657408</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -45144,7 +45144,7 @@
         <v>45111</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -45206,7 +45206,7 @@
         <v>45813.48734953703</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -45263,7 +45263,7 @@
         <v>45622</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -45325,7 +45325,7 @@
         <v>45813.47074074074</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -45382,7 +45382,7 @@
         <v>45280</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -45439,7 +45439,7 @@
         <v>44858</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -45496,7 +45496,7 @@
         <v>45406.64024305555</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -45558,7 +45558,7 @@
         <v>45813.64590277777</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -45615,7 +45615,7 @@
         <v>45154</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -45672,7 +45672,7 @@
         <v>45334</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -45734,7 +45734,7 @@
         <v>45685</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -45791,7 +45791,7 @@
         <v>45733</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -45848,7 +45848,7 @@
         <v>45506.3637962963</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -45905,7 +45905,7 @@
         <v>45817.33819444444</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -45967,7 +45967,7 @@
         <v>45817.62439814815</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -46024,7 +46024,7 @@
         <v>45195.61476851852</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -46081,7 +46081,7 @@
         <v>45531.66196759259</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -46143,7 +46143,7 @@
         <v>45429.39</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -46200,7 +46200,7 @@
         <v>44460.44315972222</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -46262,7 +46262,7 @@
         <v>45477.62255787037</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -46324,7 +46324,7 @@
         <v>45484.48854166667</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -46386,7 +46386,7 @@
         <v>45303</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -46443,7 +46443,7 @@
         <v>45154</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -46500,7 +46500,7 @@
         <v>45345</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -46562,7 +46562,7 @@
         <v>45407.36894675926</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -46624,7 +46624,7 @@
         <v>44883</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -46681,7 +46681,7 @@
         <v>44153</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -46743,7 +46743,7 @@
         <v>45821.57201388889</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -46805,7 +46805,7 @@
         <v>45820.64821759259</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -46862,7 +46862,7 @@
         <v>45631.39950231482</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -46924,7 +46924,7 @@
         <v>45751.65657407408</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -46986,7 +46986,7 @@
         <v>44082</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -47048,7 +47048,7 @@
         <v>45688.6749537037</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -47110,7 +47110,7 @@
         <v>44883</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -47167,7 +47167,7 @@
         <v>44854</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -47229,7 +47229,7 @@
         <v>45275</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -47286,7 +47286,7 @@
         <v>45678.37956018518</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -47343,7 +47343,7 @@
         <v>45496.66903935185</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -47405,7 +47405,7 @@
         <v>45509</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -47467,7 +47467,7 @@
         <v>45509</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -47529,7 +47529,7 @@
         <v>45821.77903935185</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -47586,7 +47586,7 @@
         <v>45867.55305555555</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -47643,7 +47643,7 @@
         <v>45867.55642361111</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -47705,7 +47705,7 @@
         <v>45866.40701388889</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -47762,7 +47762,7 @@
         <v>45866.62908564815</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -47819,7 +47819,7 @@
         <v>45827.41753472222</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -47881,7 +47881,7 @@
         <v>45826.43267361111</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -47943,7 +47943,7 @@
         <v>45539.43545138889</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -48000,7 +48000,7 @@
         <v>44169</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -48057,7 +48057,7 @@
         <v>45827</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -48114,7 +48114,7 @@
         <v>45868.639375</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -48171,7 +48171,7 @@
         <v>45791</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -48228,7 +48228,7 @@
         <v>45827.42467592593</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -48290,7 +48290,7 @@
         <v>45061.36835648148</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -48347,7 +48347,7 @@
         <v>44180</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -48404,7 +48404,7 @@
         <v>44728</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -48466,7 +48466,7 @@
         <v>45873.59511574074</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -48528,7 +48528,7 @@
         <v>45831</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -48590,7 +48590,7 @@
         <v>45875.5196875</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -48647,7 +48647,7 @@
         <v>45874.64199074074</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -48704,7 +48704,7 @@
         <v>45345.34219907408</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -48766,7 +48766,7 @@
         <v>45345.47642361111</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -48828,7 +48828,7 @@
         <v>45874.64513888889</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -48885,7 +48885,7 @@
         <v>45832</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -48947,7 +48947,7 @@
         <v>45833</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -49009,7 +49009,7 @@
         <v>45833</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -49071,7 +49071,7 @@
         <v>45875.47854166666</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -49133,7 +49133,7 @@
         <v>45832</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -49195,7 +49195,7 @@
         <v>45833.36467592593</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -49257,7 +49257,7 @@
         <v>45832.64047453704</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -49314,7 +49314,7 @@
         <v>45832.3859837963</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -49376,7 +49376,7 @@
         <v>45833</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -49438,7 +49438,7 @@
         <v>45833.6081712963</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -49500,7 +49500,7 @@
         <v>45832</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -49562,7 +49562,7 @@
         <v>45834.80229166667</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -49619,7 +49619,7 @@
         <v>45835.55998842593</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -49681,7 +49681,7 @@
         <v>45835.57069444445</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -49738,7 +49738,7 @@
         <v>45834</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -49800,7 +49800,7 @@
         <v>45834.7087962963</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -49857,7 +49857,7 @@
         <v>45834</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -49919,7 +49919,7 @@
         <v>45834.38173611111</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -49976,7 +49976,7 @@
         <v>45559.43645833333</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -50038,7 +50038,7 @@
         <v>45041</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -50095,7 +50095,7 @@
         <v>45618</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -50152,7 +50152,7 @@
         <v>45834.69577546296</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -50209,7 +50209,7 @@
         <v>45532</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -50266,7 +50266,7 @@
         <v>45835.5583912037</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -50328,7 +50328,7 @@
         <v>45362.64613425926</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -50385,7 +50385,7 @@
         <v>45362.65407407407</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -50442,7 +50442,7 @@
         <v>45834.6568287037</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -50499,7 +50499,7 @@
         <v>45834</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -50556,7 +50556,7 @@
         <v>45876.49113425926</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -50613,7 +50613,7 @@
         <v>45876.39362268519</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -50675,7 +50675,7 @@
         <v>45834.51079861111</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -50737,7 +50737,7 @@
         <v>45834.71440972222</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -50794,7 +50794,7 @@
         <v>45881.36469907407</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -50851,7 +50851,7 @@
         <v>45881.6609375</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -50908,7 +50908,7 @@
         <v>44987.35637731481</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -50970,7 +50970,7 @@
         <v>44987</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -51032,7 +51032,7 @@
         <v>45483.47207175926</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -51089,7 +51089,7 @@
         <v>45839.5658912037</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -51146,7 +51146,7 @@
         <v>45881.46869212963</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -51203,7 +51203,7 @@
         <v>45881.43114583333</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -51260,7 +51260,7 @@
         <v>45881.64365740741</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -51317,7 +51317,7 @@
         <v>45880.37472222222</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -51374,7 +51374,7 @@
         <v>45840.64394675926</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -51436,7 +51436,7 @@
         <v>45883.4108912037</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -51493,7 +51493,7 @@
         <v>45646</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -51550,7 +51550,7 @@
         <v>45477.66773148148</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -51612,7 +51612,7 @@
         <v>44631.42353009259</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -51674,7 +51674,7 @@
         <v>45882.64755787037</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -51736,7 +51736,7 @@
         <v>45883.51854166666</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -51793,7 +51793,7 @@
         <v>45478.44497685185</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -51855,7 +51855,7 @@
         <v>45882.63179398148</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -51917,7 +51917,7 @@
         <v>45841.69273148148</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -51974,7 +51974,7 @@
         <v>45883.40538194445</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -52031,7 +52031,7 @@
         <v>45841.4312037037</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -52088,7 +52088,7 @@
         <v>45841.46512731481</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -52150,7 +52150,7 @@
         <v>45883.58944444444</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -52212,7 +52212,7 @@
         <v>45841.45137731481</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -52269,7 +52269,7 @@
         <v>45481.3330787037</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -52331,7 +52331,7 @@
         <v>45197.46966435185</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -52388,7 +52388,7 @@
         <v>45218.58609953704</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -52445,7 +52445,7 @@
         <v>45601.58355324074</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -52502,7 +52502,7 @@
         <v>45845.6920949074</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -52564,7 +52564,7 @@
         <v>45569</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -52626,7 +52626,7 @@
         <v>45876</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -52688,7 +52688,7 @@
         <v>45667</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -52750,7 +52750,7 @@
         <v>45887.59913194444</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -52812,7 +52812,7 @@
         <v>45569</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -52874,7 +52874,7 @@
         <v>45845.55270833334</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -52931,7 +52931,7 @@
         <v>45568</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -52993,7 +52993,7 @@
         <v>45568</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -53055,7 +53055,7 @@
         <v>45842.48990740741</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -53112,7 +53112,7 @@
         <v>45869</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -53169,7 +53169,7 @@
         <v>45884.55263888889</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -53231,7 +53231,7 @@
         <v>45569</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -53293,7 +53293,7 @@
         <v>45845.60496527778</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -53350,7 +53350,7 @@
         <v>45876</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -53412,7 +53412,7 @@
         <v>45869</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -53469,7 +53469,7 @@
         <v>45845.55259259259</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -53526,7 +53526,7 @@
         <v>45845.55266203704</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -53583,7 +53583,7 @@
         <v>45485.42287037037</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -53640,7 +53640,7 @@
         <v>45485</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -53697,7 +53697,7 @@
         <v>45485.44258101852</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -53759,7 +53759,7 @@
         <v>45509.6427662037</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -53821,7 +53821,7 @@
         <v>45888.59509259259</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -53878,7 +53878,7 @@
         <v>45610.55846064815</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -53940,7 +53940,7 @@
         <v>45847.58865740741</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -54002,7 +54002,7 @@
         <v>45888.78833333333</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -54059,7 +54059,7 @@
         <v>45888.78960648148</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -54116,7 +54116,7 @@
         <v>45098.48666666666</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -54178,7 +54178,7 @@
         <v>45888.78539351852</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -54235,7 +54235,7 @@
         <v>45119</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -54292,7 +54292,7 @@
         <v>45889.40916666666</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -54349,7 +54349,7 @@
         <v>45889.41715277778</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -54406,7 +54406,7 @@
         <v>45496.67342592592</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -54468,7 +54468,7 @@
         <v>45848.45113425926</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -54530,7 +54530,7 @@
         <v>45848.65003472222</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -54587,7 +54587,7 @@
         <v>45849</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -54644,7 +54644,7 @@
         <v>45848</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -54706,7 +54706,7 @@
         <v>45848.57644675926</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -54768,7 +54768,7 @@
         <v>45848.6568287037</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -54825,7 +54825,7 @@
         <v>45848.68640046296</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -54887,7 +54887,7 @@
         <v>45848.62873842593</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -54944,7 +54944,7 @@
         <v>45848.639375</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -55001,7 +55001,7 @@
         <v>45848.35400462963</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -55058,7 +55058,7 @@
         <v>45853.28325231482</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -55115,7 +55115,7 @@
         <v>45894.64358796296</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -55177,7 +55177,7 @@
         <v>45892.53184027778</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -55234,7 +55234,7 @@
         <v>45852</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -55291,7 +55291,7 @@
         <v>45894.65869212963</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -55348,7 +55348,7 @@
         <v>45895.29387731481</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -55410,7 +55410,7 @@
         <v>45764.44825231482</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -55472,7 +55472,7 @@
         <v>45764.44861111111</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -55534,7 +55534,7 @@
         <v>45852.48290509259</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -55591,7 +55591,7 @@
         <v>45853.61865740741</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -55648,7 +55648,7 @@
         <v>45853.62415509259</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -55710,7 +55710,7 @@
         <v>45897.44645833333</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -55772,7 +55772,7 @@
         <v>45854.44850694444</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -55834,7 +55834,7 @@
         <v>45854.44864583333</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -55896,7 +55896,7 @@
         <v>45896.49959490741</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -55953,7 +55953,7 @@
         <v>45854.40662037037</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -56015,7 +56015,7 @@
         <v>45896.49821759259</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -56072,7 +56072,7 @@
         <v>45885</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -56129,7 +56129,7 @@
         <v>44853</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -56186,7 +56186,7 @@
         <v>44550.39550925926</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -56243,7 +56243,7 @@
         <v>45265</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -56300,7 +56300,7 @@
         <v>45898.40267361111</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -56362,7 +56362,7 @@
         <v>45898.40481481481</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -56419,7 +56419,7 @@
         <v>44925.59333333333</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -56481,7 +56481,7 @@
         <v>44818</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -56538,7 +56538,7 @@
         <v>44957</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -56600,7 +56600,7 @@
         <v>45177.9224537037</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -56657,7 +56657,7 @@
         <v>45901.4881712963</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -56719,7 +56719,7 @@
         <v>45901.58591435185</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -56781,7 +56781,7 @@
         <v>45869</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -56838,7 +56838,7 @@
         <v>45898.55296296296</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -56900,7 +56900,7 @@
         <v>45898.41540509259</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -56957,7 +56957,7 @@
         <v>45590.31899305555</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -57014,7 +57014,7 @@
         <v>44305</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -57071,7 +57071,7 @@
         <v>45107</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -57128,7 +57128,7 @@
         <v>45903.6066087963</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -57190,7 +57190,7 @@
         <v>45861</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -57252,7 +57252,7 @@
         <v>45859</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -57309,7 +57309,7 @@
         <v>45903.60319444445</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -57371,7 +57371,7 @@
         <v>45902.59438657408</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -57433,7 +57433,7 @@
         <v>45485</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -57495,7 +57495,7 @@
         <v>45902.55119212963</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -57552,7 +57552,7 @@
         <v>45902.66265046296</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -57614,7 +57614,7 @@
         <v>45817.594375</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -57676,7 +57676,7 @@
         <v>45902.35612268518</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -57738,7 +57738,7 @@
         <v>45274</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -57795,7 +57795,7 @@
         <v>45154</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -57852,7 +57852,7 @@
         <v>45385</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -57909,7 +57909,7 @@
         <v>45723.58140046296</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -57966,7 +57966,7 @@
         <v>45904.60483796296</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -58028,7 +58028,7 @@
         <v>45730</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -58085,7 +58085,7 @@
         <v>45853</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -58142,7 +58142,7 @@
         <v>45755</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -58199,7 +58199,7 @@
         <v>45075.59148148148</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -58261,7 +58261,7 @@
         <v>44091</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -58318,7 +58318,7 @@
         <v>45670.66085648148</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -58375,7 +58375,7 @@
         <v>45687.53689814815</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -58432,7 +58432,7 @@
         <v>45904.41844907407</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -58494,7 +58494,7 @@
         <v>45730</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -58551,7 +58551,7 @@
         <v>45905.66966435185</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -58613,7 +58613,7 @@
         <v>45887</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -58675,7 +58675,7 @@
         <v>45622</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -58732,7 +58732,7 @@
         <v>45905.67454861111</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -58794,7 +58794,7 @@
         <v>45904</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -58856,7 +58856,7 @@
         <v>45691</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -58918,7 +58918,7 @@
         <v>45691</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -58980,7 +58980,7 @@
         <v>45728</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -59037,7 +59037,7 @@
         <v>45635.35274305556</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -59099,7 +59099,7 @@
         <v>45509</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -59161,7 +59161,7 @@
         <v>45904.40663194445</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -59223,7 +59223,7 @@
         <v>45904.47059027778</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -59285,7 +59285,7 @@
         <v>45244</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -59342,7 +59342,7 @@
         <v>45685</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -59404,7 +59404,7 @@
         <v>44475</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -59461,7 +59461,7 @@
         <v>45593.67809027778</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -59518,7 +59518,7 @@
         <v>45170.46134259259</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -59580,7 +59580,7 @@
         <v>45670</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -59642,7 +59642,7 @@
         <v>45166.34795138889</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -59699,7 +59699,7 @@
         <v>44985</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -59761,7 +59761,7 @@
         <v>45485</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -59818,7 +59818,7 @@
         <v>45898</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -59875,7 +59875,7 @@
         <v>45665.563125</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -59937,7 +59937,7 @@
         <v>45735.60342592592</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -59994,7 +59994,7 @@
         <v>45203</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -60051,7 +60051,7 @@
         <v>45460.47969907407</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -60108,7 +60108,7 @@
         <v>45656.51157407407</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -60170,7 +60170,7 @@
         <v>45460.48582175926</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -60227,7 +60227,7 @@
         <v>45478.48700231482</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -60289,7 +60289,7 @@
         <v>45231</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -60346,7 +60346,7 @@
         <v>45345.4940625</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -60408,7 +60408,7 @@
         <v>45680.42497685185</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -60465,7 +60465,7 @@
         <v>44722</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -60522,7 +60522,7 @@
         <v>45345.48181712963</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -60584,7 +60584,7 @@
         <v>44914</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -60666,7 +60666,7 @@
         <v>45439.62893518519</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -60723,7 +60723,7 @@
         <v>45054</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -60785,7 +60785,7 @@
         <v>45208</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -60842,7 +60842,7 @@
         <v>44312</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -60899,7 +60899,7 @@
         <v>44082</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -60961,7 +60961,7 @@
         <v>45260.59042824074</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -61018,7 +61018,7 @@
         <v>44385</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -61075,7 +61075,7 @@
         <v>44862</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -61137,7 +61137,7 @@
         <v>45705.32456018519</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -61194,7 +61194,7 @@
         <v>45741.39084490741</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -61251,7 +61251,7 @@
         <v>45624.57098379629</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -61308,7 +61308,7 @@
         <v>45622.64627314815</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -61365,7 +61365,7 @@
         <v>45288.58685185185</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -61422,7 +61422,7 @@
         <v>45071.92488425926</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -61479,7 +61479,7 @@
         <v>45371.66217592593</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -61541,7 +61541,7 @@
         <v>44886</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -61603,7 +61603,7 @@
         <v>45488</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -61660,7 +61660,7 @@
         <v>45204</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -61717,7 +61717,7 @@
         <v>45238.64153935185</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -61774,7 +61774,7 @@
         <v>45041</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -61831,7 +61831,7 @@
         <v>45245</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -61888,7 +61888,7 @@
         <v>45688.6769212963</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -61950,7 +61950,7 @@
         <v>45153.42725694444</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -62012,7 +62012,7 @@
         <v>45485</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -62074,7 +62074,7 @@
         <v>45485</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -62136,7 +62136,7 @@
         <v>45159.60288194445</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -62193,7 +62193,7 @@
         <v>45215</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -62250,7 +62250,7 @@
         <v>45763.4266087963</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -62307,7 +62307,7 @@
         <v>44987.34981481481</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -62369,7 +62369,7 @@
         <v>45582.59753472222</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -62431,7 +62431,7 @@
         <v>45735.57390046296</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -62488,7 +62488,7 @@
         <v>44642</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -62550,7 +62550,7 @@
         <v>45429</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -62607,7 +62607,7 @@
         <v>45342</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -62664,7 +62664,7 @@
         <v>45390</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -62721,7 +62721,7 @@
         <v>45406</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -62783,7 +62783,7 @@
         <v>44819.56722222222</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -62840,7 +62840,7 @@
         <v>45638</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -62902,7 +62902,7 @@
         <v>44216</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -62964,7 +62964,7 @@
         <v>44216</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -63026,7 +63026,7 @@
         <v>45467</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -63083,7 +63083,7 @@
         <v>45775.36589120371</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -63140,7 +63140,7 @@
         <v>45173</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -63197,7 +63197,7 @@
         <v>45642.41907407407</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -63254,7 +63254,7 @@
         <v>45252.45481481482</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -63311,7 +63311,7 @@
         <v>45252.48409722222</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -63368,7 +63368,7 @@
         <v>44998</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -63425,7 +63425,7 @@
         <v>44151</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -63482,7 +63482,7 @@
         <v>45575.6125925926</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -63544,7 +63544,7 @@
         <v>45705.72106481482</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -63601,7 +63601,7 @@
         <v>45610.56706018518</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -63663,7 +63663,7 @@
         <v>44708.45504629629</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -63725,7 +63725,7 @@
         <v>45085</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -63782,7 +63782,7 @@
         <v>45568</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -63844,7 +63844,7 @@
         <v>45484</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -63906,7 +63906,7 @@
         <v>45239.43173611111</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -63968,7 +63968,7 @@
         <v>45719.48778935185</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -64025,7 +64025,7 @@
         <v>44214</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -64087,7 +64087,7 @@
         <v>45202</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -64149,7 +64149,7 @@
         <v>45772.36106481482</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -64211,7 +64211,7 @@
         <v>45644</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -64268,7 +64268,7 @@
         <v>45225.58005787037</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -64325,7 +64325,7 @@
         <v>44925.33584490741</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -64387,7 +64387,7 @@
         <v>44925</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -64444,7 +64444,7 @@
         <v>45049.59826388889</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -64501,7 +64501,7 @@
         <v>45632</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -64558,7 +64558,7 @@
         <v>45632</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -64615,7 +64615,7 @@
         <v>45621</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -64677,7 +64677,7 @@
         <v>45170.4643287037</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -64739,7 +64739,7 @@
         <v>45611.4021875</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -64796,7 +64796,7 @@
         <v>45118.3959375</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -64858,7 +64858,7 @@
         <v>45362.65903935185</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -64915,7 +64915,7 @@
         <v>45637.39587962963</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -64977,7 +64977,7 @@
         <v>45560.33311342593</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -65039,7 +65039,7 @@
         <v>45632</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -65096,7 +65096,7 @@
         <v>44698</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -65158,7 +65158,7 @@
         <v>45604.32543981481</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -65220,7 +65220,7 @@
         <v>45685.38901620371</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -65282,7 +65282,7 @@
         <v>44571</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -65339,7 +65339,7 @@
         <v>45447.35144675926</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -65396,7 +65396,7 @@
         <v>44484.55535879629</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -65453,7 +65453,7 @@
         <v>44182</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -65510,7 +65510,7 @@
         <v>45238.46430555556</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -65567,7 +65567,7 @@
         <v>45631.63091435185</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -65624,7 +65624,7 @@
         <v>44229</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -65686,7 +65686,7 @@
         <v>44225</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -65743,7 +65743,7 @@
         <v>45737.3787962963</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -65800,7 +65800,7 @@
         <v>45505</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -65862,7 +65862,7 @@
         <v>45253.55737268519</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -65919,7 +65919,7 @@
         <v>45257</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -65976,7 +65976,7 @@
         <v>45758.66108796297</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -66033,7 +66033,7 @@
         <v>45758.69123842593</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -66090,7 +66090,7 @@
         <v>44314</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -66147,7 +66147,7 @@
         <v>45688.67145833333</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -66209,7 +66209,7 @@
         <v>44665</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -66266,7 +66266,7 @@
         <v>45684.51006944444</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -66323,7 +66323,7 @@
         <v>44987.35282407407</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -66385,7 +66385,7 @@
         <v>45768.29630787037</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -66447,7 +66447,7 @@
         <v>45768.30954861111</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -66509,7 +66509,7 @@
         <v>45727.35621527778</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -66571,7 +66571,7 @@
         <v>45012</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -66633,7 +66633,7 @@
         <v>45254</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -66690,7 +66690,7 @@
         <v>44565.31975694445</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -66752,7 +66752,7 @@
         <v>44565</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -66814,7 +66814,7 @@
         <v>45362.67789351852</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -66871,7 +66871,7 @@
         <v>44972.57449074074</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -66928,7 +66928,7 @@
         <v>45751.34636574074</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -66990,7 +66990,7 @@
         <v>45670.4570949074</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -67052,7 +67052,7 @@
         <v>45282.64012731481</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -67114,7 +67114,7 @@
         <v>45731.69629629629</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -67171,7 +67171,7 @@
         <v>44440</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -67228,7 +67228,7 @@
         <v>45763.4178587963</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -67285,7 +67285,7 @@
         <v>45509</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -67347,7 +67347,7 @@
         <v>44628.36402777778</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -67404,7 +67404,7 @@
         <v>45174</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -67461,7 +67461,7 @@
         <v>45195.3878125</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -67518,7 +67518,7 @@
         <v>44994</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -67575,7 +67575,7 @@
         <v>45351</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -67632,7 +67632,7 @@
         <v>45491.5859375</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -67689,7 +67689,7 @@
         <v>45632</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -67746,7 +67746,7 @@
         <v>44414.58354166667</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -67803,7 +67803,7 @@
         <v>45229.92739583334</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -67860,7 +67860,7 @@
         <v>44258</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -67917,7 +67917,7 @@
         <v>44155</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -67974,7 +67974,7 @@
         <v>44925</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -68031,7 +68031,7 @@
         <v>45624.36090277778</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -68088,7 +68088,7 @@
         <v>45733.43663194445</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -68150,7 +68150,7 @@
         <v>44088</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -68207,7 +68207,7 @@
         <v>45624.63614583333</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -68269,7 +68269,7 @@
         <v>45041</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -68326,7 +68326,7 @@
         <v>44925</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -68388,7 +68388,7 @@
         <v>45595.5666550926</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -68445,7 +68445,7 @@
         <v>45509</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -68507,7 +68507,7 @@
         <v>45687.65449074074</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -68569,7 +68569,7 @@
         <v>44708</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -68631,7 +68631,7 @@
         <v>44964</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -68688,7 +68688,7 @@
         <v>45761.61501157407</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -68750,7 +68750,7 @@
         <v>45484.58422453704</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -68812,7 +68812,7 @@
         <v>45775.36587962963</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -68869,7 +68869,7 @@
         <v>44889.56582175926</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -68926,7 +68926,7 @@
         <v>45240</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -68983,7 +68983,7 @@
         <v>45635.33439814814</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -69045,7 +69045,7 @@
         <v>44531.43927083333</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -69107,7 +69107,7 @@
         <v>45772.69290509259</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -69169,7 +69169,7 @@
         <v>45574.66106481481</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -69226,7 +69226,7 @@
         <v>45763.41402777778</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -69283,7 +69283,7 @@
         <v>45579.59980324074</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -69340,7 +69340,7 @@
         <v>45575</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -69397,7 +69397,7 @@
         <v>44784.60677083334</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -69459,7 +69459,7 @@
         <v>45506.36534722222</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -69516,7 +69516,7 @@
         <v>45614.47960648148</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -69573,7 +69573,7 @@
         <v>45758.49096064815</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -69635,7 +69635,7 @@
         <v>45096.62344907408</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -69697,7 +69697,7 @@
         <v>45607</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -69754,7 +69754,7 @@
         <v>45075.59358796296</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -69816,7 +69816,7 @@
         <v>45420.44414351852</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -69878,7 +69878,7 @@
         <v>45741.45597222223</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -69935,7 +69935,7 @@
         <v>45667</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -69992,7 +69992,7 @@
         <v>45195.35877314815</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -70049,7 +70049,7 @@
         <v>45672.61748842592</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -70106,7 +70106,7 @@
         <v>45510</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -70163,7 +70163,7 @@
         <v>45622.64012731481</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -70225,7 +70225,7 @@
         <v>45756</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -70282,7 +70282,7 @@
         <v>45659.57361111111</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -70344,7 +70344,7 @@
         <v>45439.43106481482</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -70406,7 +70406,7 @@
         <v>45762.55899305556</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -70463,7 +70463,7 @@
         <v>45345.35003472222</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -70525,7 +70525,7 @@
         <v>45688.67935185185</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -70587,7 +70587,7 @@
         <v>45754.35055555555</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -70644,7 +70644,7 @@
         <v>45772.46965277778</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -70706,7 +70706,7 @@
         <v>45772.46988425926</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -70768,7 +70768,7 @@
         <v>45106</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -70830,7 +70830,7 @@
         <v>45677.44273148148</v>
       </c>
       <c r="C1075" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
@@ -70887,7 +70887,7 @@
         <v>45603</v>
       </c>
       <c r="C1076" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
@@ -70949,7 +70949,7 @@
         <v>45603</v>
       </c>
       <c r="C1077" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
@@ -71011,7 +71011,7 @@
         <v>44916</v>
       </c>
       <c r="C1078" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1078" t="inlineStr">
         <is>
@@ -71068,7 +71068,7 @@
         <v>45719.45215277778</v>
       </c>
       <c r="C1079" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1079" t="inlineStr">
         <is>
@@ -71125,7 +71125,7 @@
         <v>44475</v>
       </c>
       <c r="C1080" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
@@ -71182,7 +71182,7 @@
         <v>45459</v>
       </c>
       <c r="C1081" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1081" t="inlineStr">
         <is>
@@ -71239,7 +71239,7 @@
         <v>45622</v>
       </c>
       <c r="C1082" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1082" t="inlineStr">
         <is>
@@ -71301,7 +71301,7 @@
         <v>44126</v>
       </c>
       <c r="C1083" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1083" t="inlineStr">
         <is>
@@ -71358,7 +71358,7 @@
         <v>45537.60471064815</v>
       </c>
       <c r="C1084" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1084" t="inlineStr">
         <is>
@@ -71420,7 +71420,7 @@
         <v>44925.64049768518</v>
       </c>
       <c r="C1085" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1085" t="inlineStr">
         <is>
@@ -71482,7 +71482,7 @@
         <v>45642.33616898148</v>
       </c>
       <c r="C1086" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1086" t="inlineStr">
         <is>
@@ -71539,7 +71539,7 @@
         <v>45741.38347222222</v>
       </c>
       <c r="C1087" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1087" t="inlineStr">
         <is>
@@ -71596,7 +71596,7 @@
         <v>45303.5047337963</v>
       </c>
       <c r="C1088" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1088" t="inlineStr">
         <is>
@@ -71653,7 +71653,7 @@
         <v>45728.44329861111</v>
       </c>
       <c r="C1089" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1089" t="inlineStr">
         <is>
@@ -71715,7 +71715,7 @@
         <v>44726</v>
       </c>
       <c r="C1090" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1090" t="inlineStr">
         <is>
@@ -71772,7 +71772,7 @@
         <v>45743.38449074074</v>
       </c>
       <c r="C1091" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1091" t="inlineStr">
         <is>
@@ -71829,7 +71829,7 @@
         <v>45442</v>
       </c>
       <c r="C1092" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1092" t="inlineStr">
         <is>
@@ -71891,7 +71891,7 @@
         <v>45728.49267361111</v>
       </c>
       <c r="C1093" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1093" t="inlineStr">
         <is>
@@ -71953,7 +71953,7 @@
         <v>45540.4264699074</v>
       </c>
       <c r="C1094" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1094" t="inlineStr">
         <is>
@@ -72015,7 +72015,7 @@
         <v>45685.5349074074</v>
       </c>
       <c r="C1095" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1095" t="inlineStr">
         <is>
@@ -72077,7 +72077,7 @@
         <v>44795</v>
       </c>
       <c r="C1096" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1096" t="inlineStr">
         <is>
@@ -72134,7 +72134,7 @@
         <v>45572.60001157408</v>
       </c>
       <c r="C1097" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1097" t="inlineStr">
         <is>
@@ -72191,7 +72191,7 @@
         <v>45568</v>
       </c>
       <c r="C1098" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1098" t="inlineStr">
         <is>
@@ -72253,7 +72253,7 @@
         <v>45691</v>
       </c>
       <c r="C1099" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1099" t="inlineStr">
         <is>
@@ -72315,7 +72315,7 @@
         <v>45691</v>
       </c>
       <c r="C1100" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1100" t="inlineStr">
         <is>
@@ -72377,7 +72377,7 @@
         <v>45764</v>
       </c>
       <c r="C1101" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1101" t="inlineStr">
         <is>
@@ -72434,7 +72434,7 @@
         <v>44472</v>
       </c>
       <c r="C1102" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1102" t="inlineStr">
         <is>
@@ -72491,7 +72491,7 @@
         <v>44280</v>
       </c>
       <c r="C1103" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1103" t="inlineStr">
         <is>
@@ -72548,7 +72548,7 @@
         <v>45338</v>
       </c>
       <c r="C1104" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1104" t="inlineStr">
         <is>
@@ -72610,7 +72610,7 @@
         <v>45432</v>
       </c>
       <c r="C1105" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1105" t="inlineStr">
         <is>
@@ -72672,7 +72672,7 @@
         <v>44381</v>
       </c>
       <c r="C1106" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1106" t="inlineStr">
         <is>
@@ -72729,7 +72729,7 @@
         <v>45604.31657407407</v>
       </c>
       <c r="C1107" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1107" t="inlineStr">
         <is>
@@ -72791,7 +72791,7 @@
         <v>45758.69638888889</v>
       </c>
       <c r="C1108" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1108" t="inlineStr">
         <is>
@@ -72848,7 +72848,7 @@
         <v>45496.59202546296</v>
       </c>
       <c r="C1109" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1109" t="inlineStr">
         <is>

--- a/Översikt HÄRJEDALEN.xlsx
+++ b/Översikt HÄRJEDALEN.xlsx
@@ -601,7 +601,7 @@
         <v>45982</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
         <v>44785</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
         <v>44790</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>45763</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>45953</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>44837</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>46199</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>44749</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1719,7 +1719,7 @@
         <v>44844</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>46232</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>44501</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>44553</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
         <v>45691</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>44831</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>45837</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
         <v>45761</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>44496</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>45834</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>46196</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3212,7 +3212,7 @@
         <v>45351</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         <v>46196</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>45471</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         <v>45667</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3742,7 +3742,7 @@
         <v>45659</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>44865</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         <v>45323</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>45761</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>44690</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
         <v>45554</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4539,7 +4539,7 @@
         <v>44650</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
         <v>44487</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
         <v>45631</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>46163</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5060,7 +5060,7 @@
         <v>45631</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>46125</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5315,7 +5315,7 @@
         <v>45250</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>45477</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5571,7 +5571,7 @@
         <v>45180</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5695,7 +5695,7 @@
         <v>45061</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5818,7 +5818,7 @@
         <v>45929</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5950,7 +5950,7 @@
         <v>45544</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>45837</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         <v>45995</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         <v>44774</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6442,7 +6442,7 @@
         <v>44440</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6559,7 +6559,7 @@
         <v>46196</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6684,7 +6684,7 @@
         <v>45175</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
         <v>45106</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6935,7 +6935,7 @@
         <v>45198</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>45625</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7190,7 +7190,7 @@
         <v>45426</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         <v>45544</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7432,7 +7432,7 @@
         <v>45761</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7558,7 +7558,7 @@
         <v>45457</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7683,7 +7683,7 @@
         <v>45217</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7807,7 +7807,7 @@
         <v>46199</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         <v>45007</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         <v>45571</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
         <v>44631</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         <v>44517</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8419,7 +8419,7 @@
         <v>45975</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8542,7 +8542,7 @@
         <v>45411</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8660,7 +8660,7 @@
         <v>45833</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8783,7 +8783,7 @@
         <v>44553</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8901,7 +8901,7 @@
         <v>45625</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         <v>45614</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -9153,7 +9153,7 @@
         <v>46027</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         <v>45911</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
         <v>46105</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
         <v>45825</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9644,7 +9644,7 @@
         <v>44553</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9761,7 +9761,7 @@
         <v>46056</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9886,7 +9886,7 @@
         <v>44987</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -10007,7 +10007,7 @@
         <v>45574</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -10123,7 +10123,7 @@
         <v>44979</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -10239,7 +10239,7 @@
         <v>45349</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10364,7 +10364,7 @@
         <v>44909</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10481,7 +10481,7 @@
         <v>46073</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10602,7 +10602,7 @@
         <v>44430</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10718,7 +10718,7 @@
         <v>44553</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10834,7 +10834,7 @@
         <v>44476</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10949,7 +10949,7 @@
         <v>45909</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -11065,7 +11065,7 @@
         <v>45085</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -11180,7 +11180,7 @@
         <v>45741</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -11291,7 +11291,7 @@
         <v>46027</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -11411,7 +11411,7 @@
         <v>45531</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11526,7 +11526,7 @@
         <v>45559</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11646,7 +11646,7 @@
         <v>44713</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11769,7 +11769,7 @@
         <v>45243</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11883,7 +11883,7 @@
         <v>45936</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11998,7 +11998,7 @@
         <v>45568</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -12113,7 +12113,7 @@
         <v>45552</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -12223,7 +12223,7 @@
         <v>45719</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -12337,7 +12337,7 @@
         <v>46014</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12447,7 +12447,7 @@
         <v>46160</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12566,7 +12566,7 @@
         <v>45869</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12680,7 +12680,7 @@
         <v>45617</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12798,7 +12798,7 @@
         <v>45909</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12912,7 +12912,7 @@
         <v>45954</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -13026,7 +13026,7 @@
         <v>45975</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -13140,7 +13140,7 @@
         <v>46136</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -13254,7 +13254,7 @@
         <v>45443</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -13368,7 +13368,7 @@
         <v>45757</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -13482,7 +13482,7 @@
         <v>44677</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13595,7 +13595,7 @@
         <v>44475</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13703,7 +13703,7 @@
         <v>44803</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13815,7 +13815,7 @@
         <v>45467</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13928,7 +13928,7 @@
         <v>45007</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -14041,7 +14041,7 @@
         <v>44698</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -14158,7 +14158,7 @@
         <v>44882</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -14270,7 +14270,7 @@
         <v>44517</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -14378,7 +14378,7 @@
         <v>45531</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -14486,7 +14486,7 @@
         <v>45913</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14598,7 +14598,7 @@
         <v>45666</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14715,7 +14715,7 @@
         <v>44955</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14827,7 +14827,7 @@
         <v>45772</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14940,7 +14940,7 @@
         <v>45838</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -15053,7 +15053,7 @@
         <v>44430</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -15173,7 +15173,7 @@
         <v>44475</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -15280,7 +15280,7 @@
         <v>44475</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -15387,7 +15387,7 @@
         <v>44475</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -15494,7 +15494,7 @@
         <v>44475</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15605,7 +15605,7 @@
         <v>44914</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15721,7 +15721,7 @@
         <v>45035</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15837,7 +15837,7 @@
         <v>45485</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15953,7 +15953,7 @@
         <v>46147</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -16065,7 +16065,7 @@
         <v>46154</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -16177,7 +16177,7 @@
         <v>45975</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -16289,7 +16289,7 @@
         <v>45617</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -16405,7 +16405,7 @@
         <v>45761</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -16517,7 +16517,7 @@
         <v>46014</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16628,7 +16628,7 @@
         <v>46027</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16740,7 +16740,7 @@
         <v>45993</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16852,7 +16852,7 @@
         <v>46200</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16959,7 +16959,7 @@
         <v>44957</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -17070,7 +17070,7 @@
         <v>45694</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -17177,7 +17177,7 @@
         <v>45791</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -17284,7 +17284,7 @@
         <v>45821</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -17396,7 +17396,7 @@
         <v>46217</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -17512,7 +17512,7 @@
         <v>44475</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -17618,7 +17618,7 @@
         <v>44441</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17724,7 +17724,7 @@
         <v>44475</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17830,7 +17830,7 @@
         <v>44987</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17941,7 +17941,7 @@
         <v>45406</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -18056,7 +18056,7 @@
         <v>45406</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -18171,7 +18171,7 @@
         <v>45485</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -18282,7 +18282,7 @@
         <v>44475</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -18388,7 +18388,7 @@
         <v>45538</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -18499,7 +18499,7 @@
         <v>45485</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -18610,7 +18610,7 @@
         <v>45621</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18725,7 +18725,7 @@
         <v>45933</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18836,7 +18836,7 @@
         <v>45638</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18947,7 +18947,7 @@
         <v>45938</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -19057,7 +19057,7 @@
         <v>45485</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -19172,7 +19172,7 @@
         <v>44866</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -19287,7 +19287,7 @@
         <v>46009</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -19398,7 +19398,7 @@
         <v>44449</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -19504,7 +19504,7 @@
         <v>45945</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -19610,7 +19610,7 @@
         <v>46200</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19720,7 +19720,7 @@
         <v>45644</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -19835,7 +19835,7 @@
         <v>46084</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19946,7 +19946,7 @@
         <v>46136</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -20057,7 +20057,7 @@
         <v>45786</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -20168,7 +20168,7 @@
         <v>45786</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -20279,7 +20279,7 @@
         <v>45442</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -20390,7 +20390,7 @@
         <v>45694</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -20496,7 +20496,7 @@
         <v>45786</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -20607,7 +20607,7 @@
         <v>45153</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -20717,7 +20717,7 @@
         <v>45786</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -20828,7 +20828,7 @@
         <v>44853</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20938,7 +20938,7 @@
         <v>45805</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -21049,7 +21049,7 @@
         <v>45805</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -21160,7 +21160,7 @@
         <v>45835</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -21271,7 +21271,7 @@
         <v>45349</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -21382,7 +21382,7 @@
         <v>44582</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -21497,7 +21497,7 @@
         <v>46163</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -21608,7 +21608,7 @@
         <v>44475</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -21713,7 +21713,7 @@
         <v>44475</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -21818,7 +21818,7 @@
         <v>44475</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -21923,7 +21923,7 @@
         <v>44475</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -22028,7 +22028,7 @@
         <v>45320</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -22133,7 +22133,7 @@
         <v>45772</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -22247,7 +22247,7 @@
         <v>44769</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -22357,7 +22357,7 @@
         <v>45538</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -22466,7 +22466,7 @@
         <v>44914</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -22571,7 +22571,7 @@
         <v>45754</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -22676,7 +22676,7 @@
         <v>45889</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -22786,7 +22786,7 @@
         <v>45894</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -22900,7 +22900,7 @@
         <v>45898</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -23014,7 +23014,7 @@
         <v>44475</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -23119,7 +23119,7 @@
         <v>45908</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -23233,7 +23233,7 @@
         <v>45910</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -23343,7 +23343,7 @@
         <v>45345</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -23453,7 +23453,7 @@
         <v>45607</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -23567,7 +23567,7 @@
         <v>45622</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -23672,7 +23672,7 @@
         <v>46142</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -23782,7 +23782,7 @@
         <v>45869</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -23887,7 +23887,7 @@
         <v>46066</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -23992,7 +23992,7 @@
         <v>46146</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -24102,7 +24102,7 @@
         <v>45390</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -24207,7 +24207,7 @@
         <v>46154</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -24321,7 +24321,7 @@
         <v>45952</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -24435,7 +24435,7 @@
         <v>45953</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -24544,7 +24544,7 @@
         <v>45345</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -24654,7 +24654,7 @@
         <v>45764</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -24764,7 +24764,7 @@
         <v>45603</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -24874,7 +24874,7 @@
         <v>45972</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -24984,7 +24984,7 @@
         <v>45617</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -25098,7 +25098,7 @@
         <v>46168</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -25208,7 +25208,7 @@
         <v>45308</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -25317,7 +25317,7 @@
         <v>45833</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -25422,7 +25422,7 @@
         <v>46014</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -25527,7 +25527,7 @@
         <v>45345</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -25637,7 +25637,7 @@
         <v>46055</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -25746,7 +25746,7 @@
         <v>46185</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -25856,7 +25856,7 @@
         <v>45791</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -25961,7 +25961,7 @@
         <v>45351</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -26066,7 +26066,7 @@
         <v>46084</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -26176,7 +26176,7 @@
         <v>46084</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -26286,7 +26286,7 @@
         <v>46084</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -26396,7 +26396,7 @@
         <v>45111</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -26506,7 +26506,7 @@
         <v>45729</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -26616,7 +26616,7 @@
         <v>45687</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -26726,7 +26726,7 @@
         <v>46127</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -26836,7 +26836,7 @@
         <v>45800</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -26946,7 +26946,7 @@
         <v>45800</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -27060,7 +27060,7 @@
         <v>45805</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -27174,7 +27174,7 @@
         <v>45454</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -27279,7 +27279,7 @@
         <v>45812</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -27389,7 +27389,7 @@
         <v>45832</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -27498,7 +27498,7 @@
         <v>45889</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -27608,7 +27608,7 @@
         <v>45933</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -27713,7 +27713,7 @@
         <v>46185</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -27823,7 +27823,7 @@
         <v>44727</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -27901,7 +27901,7 @@
         <v>44543</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -27974,7 +27974,7 @@
         <v>44614</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -28052,7 +28052,7 @@
         <v>44430</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -28130,7 +28130,7 @@
         <v>44417</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -28203,7 +28203,7 @@
         <v>44417</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -28276,7 +28276,7 @@
         <v>44497</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -28349,7 +28349,7 @@
         <v>44475</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -28422,7 +28422,7 @@
         <v>44531</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -28495,7 +28495,7 @@
         <v>44600</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -28568,7 +28568,7 @@
         <v>44540</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -28646,7 +28646,7 @@
         <v>44475</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -28719,7 +28719,7 @@
         <v>44854</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -28792,7 +28792,7 @@
         <v>44823</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -28870,7 +28870,7 @@
         <v>44538</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -28948,7 +28948,7 @@
         <v>44424</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -29021,7 +29021,7 @@
         <v>44483</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -29094,7 +29094,7 @@
         <v>44421</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -29167,7 +29167,7 @@
         <v>44418</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -29245,7 +29245,7 @@
         <v>44488</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -29323,7 +29323,7 @@
         <v>44418</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -29401,7 +29401,7 @@
         <v>44564</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -29479,7 +29479,7 @@
         <v>44615</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -29557,7 +29557,7 @@
         <v>44466</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -29630,7 +29630,7 @@
         <v>44475</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -29703,7 +29703,7 @@
         <v>44410</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -29776,7 +29776,7 @@
         <v>44728</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -29849,7 +29849,7 @@
         <v>44417</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -29922,7 +29922,7 @@
         <v>44475</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -29995,7 +29995,7 @@
         <v>44424</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -30068,7 +30068,7 @@
         <v>44424</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -30141,7 +30141,7 @@
         <v>44818</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -30214,7 +30214,7 @@
         <v>44690</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -30287,7 +30287,7 @@
         <v>44770</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -30360,7 +30360,7 @@
         <v>44792</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -30433,7 +30433,7 @@
         <v>44475</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -30506,7 +30506,7 @@
         <v>44475</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -30579,7 +30579,7 @@
         <v>44475</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -30652,7 +30652,7 @@
         <v>44475</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -30725,7 +30725,7 @@
         <v>44475</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -30798,7 +30798,7 @@
         <v>44544</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -30876,7 +30876,7 @@
         <v>44420</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -30949,7 +30949,7 @@
         <v>44483</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -31022,7 +31022,7 @@
         <v>44417</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -31095,7 +31095,7 @@
         <v>44426</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -31168,7 +31168,7 @@
         <v>44859</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -31246,7 +31246,7 @@
         <v>44473</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -31319,7 +31319,7 @@
         <v>44543</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -31397,7 +31397,7 @@
         <v>44725</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -31475,7 +31475,7 @@
         <v>44417</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -31548,7 +31548,7 @@
         <v>44540</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -31621,7 +31621,7 @@
         <v>44872</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -31699,7 +31699,7 @@
         <v>44742</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -31777,7 +31777,7 @@
         <v>44530</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -31850,7 +31850,7 @@
         <v>44475</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -31923,7 +31923,7 @@
         <v>44855</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -31996,7 +31996,7 @@
         <v>44768</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -32069,7 +32069,7 @@
         <v>44886</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -32142,7 +32142,7 @@
         <v>44886</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -32215,7 +32215,7 @@
         <v>44838</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -32293,7 +32293,7 @@
         <v>45385</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -32366,7 +32366,7 @@
         <v>45257</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -32444,7 +32444,7 @@
         <v>44788</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -32522,7 +32522,7 @@
         <v>45279</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -32595,7 +32595,7 @@
         <v>44727</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -32673,7 +32673,7 @@
         <v>44883</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -32746,7 +32746,7 @@
         <v>45509</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -32824,7 +32824,7 @@
         <v>44853</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -32897,7 +32897,7 @@
         <v>44957</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -32975,7 +32975,7 @@
         <v>44475</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -33048,7 +33048,7 @@
         <v>44475</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -33121,7 +33121,7 @@
         <v>44481</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -33194,7 +33194,7 @@
         <v>44475</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -33267,7 +33267,7 @@
         <v>44631</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -33345,7 +33345,7 @@
         <v>44538</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -33423,7 +33423,7 @@
         <v>44985</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -33501,7 +33501,7 @@
         <v>44475</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -33574,7 +33574,7 @@
         <v>44475</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -33647,7 +33647,7 @@
         <v>44475</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -33720,7 +33720,7 @@
         <v>44708</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -33798,7 +33798,7 @@
         <v>44684</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -33876,7 +33876,7 @@
         <v>45484</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -33954,7 +33954,7 @@
         <v>45506</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -34027,7 +34027,7 @@
         <v>44531</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -34100,7 +34100,7 @@
         <v>44531</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -34173,7 +34173,7 @@
         <v>44531</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -34246,7 +34246,7 @@
         <v>45604</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -34324,7 +34324,7 @@
         <v>45433</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -34397,7 +34397,7 @@
         <v>45174</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -34470,7 +34470,7 @@
         <v>44825</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -34543,7 +34543,7 @@
         <v>45635</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -34621,7 +34621,7 @@
         <v>45280</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -34694,7 +34694,7 @@
         <v>45253</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -34767,7 +34767,7 @@
         <v>44565</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -34845,7 +34845,7 @@
         <v>44565</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -34923,7 +34923,7 @@
         <v>45166</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -34996,7 +34996,7 @@
         <v>45642</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -35069,7 +35069,7 @@
         <v>45883</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -35142,7 +35142,7 @@
         <v>45362</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -35215,7 +35215,7 @@
         <v>45362</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -35288,7 +35288,7 @@
         <v>45362</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -35361,7 +35361,7 @@
         <v>44987</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -35439,7 +35439,7 @@
         <v>44823</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -35512,7 +35512,7 @@
         <v>45342</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -35585,7 +35585,7 @@
         <v>45119</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -35663,7 +35663,7 @@
         <v>45085</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -35736,7 +35736,7 @@
         <v>45883</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -35814,7 +35814,7 @@
         <v>45531</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -35887,7 +35887,7 @@
         <v>45202</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -35965,7 +35965,7 @@
         <v>45362</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -36038,7 +36038,7 @@
         <v>45884</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -36116,7 +36116,7 @@
         <v>44924</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -36194,7 +36194,7 @@
         <v>44862</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -36272,7 +36272,7 @@
         <v>45243</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -36345,7 +36345,7 @@
         <v>45429</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -36418,7 +36418,7 @@
         <v>45477</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -36496,7 +36496,7 @@
         <v>45460</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -36569,7 +36569,7 @@
         <v>45407</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -36647,7 +36647,7 @@
         <v>44631</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -36725,7 +36725,7 @@
         <v>45607</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -36803,7 +36803,7 @@
         <v>44414</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -36876,7 +36876,7 @@
         <v>45212</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -36949,7 +36949,7 @@
         <v>45691</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -37027,7 +37027,7 @@
         <v>45691</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -37105,7 +37105,7 @@
         <v>45763</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -37178,7 +37178,7 @@
         <v>45546</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -37251,7 +37251,7 @@
         <v>45510</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -37324,7 +37324,7 @@
         <v>45624</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -37397,7 +37397,7 @@
         <v>45568</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -37475,7 +37475,7 @@
         <v>45888</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -37548,7 +37548,7 @@
         <v>45889</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -37621,7 +37621,7 @@
         <v>45889</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -37694,7 +37694,7 @@
         <v>45622</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -37767,7 +37767,7 @@
         <v>45888</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -37840,7 +37840,7 @@
         <v>45260</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -37913,7 +37913,7 @@
         <v>45432</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -37991,7 +37991,7 @@
         <v>44939</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -38064,7 +38064,7 @@
         <v>44925</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -38142,7 +38142,7 @@
         <v>45894</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -38215,7 +38215,7 @@
         <v>45624</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -38293,7 +38293,7 @@
         <v>45896</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -38366,7 +38366,7 @@
         <v>45896</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -38439,7 +38439,7 @@
         <v>45895</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -38517,7 +38517,7 @@
         <v>45898</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -38590,7 +38590,7 @@
         <v>45898</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -38668,7 +38668,7 @@
         <v>45041</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -38741,7 +38741,7 @@
         <v>45041</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -38814,7 +38814,7 @@
         <v>45898</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -38887,7 +38887,7 @@
         <v>45560</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -38960,7 +38960,7 @@
         <v>44916</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -39033,7 +39033,7 @@
         <v>44440</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -39106,7 +39106,7 @@
         <v>45902</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -39184,7 +39184,7 @@
         <v>44977</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -39262,7 +39262,7 @@
         <v>45225</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -39335,7 +39335,7 @@
         <v>45902</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -39413,7 +39413,7 @@
         <v>44957</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -39491,7 +39491,7 @@
         <v>45775</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -39564,7 +39564,7 @@
         <v>45881</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -39637,7 +39637,7 @@
         <v>45496</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -39715,7 +39715,7 @@
         <v>45974</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -39788,7 +39788,7 @@
         <v>45562</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -39866,7 +39866,7 @@
         <v>45904</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -39944,7 +39944,7 @@
         <v>44550</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -40017,7 +40017,7 @@
         <v>45904</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -40095,7 +40095,7 @@
         <v>45903</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -40173,7 +40173,7 @@
         <v>45903</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -40251,7 +40251,7 @@
         <v>45485</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -40329,7 +40329,7 @@
         <v>44985</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -40407,7 +40407,7 @@
         <v>44475</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -40480,7 +40480,7 @@
         <v>45575</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -40558,7 +40558,7 @@
         <v>45908</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -40631,7 +40631,7 @@
         <v>45595</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -40704,7 +40704,7 @@
         <v>45908</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -40777,7 +40777,7 @@
         <v>44953</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -40850,7 +40850,7 @@
         <v>45908</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -40923,7 +40923,7 @@
         <v>45909</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -40996,7 +40996,7 @@
         <v>45910</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -41074,7 +41074,7 @@
         <v>45909</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -41152,7 +41152,7 @@
         <v>45547</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -41225,7 +41225,7 @@
         <v>45208</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -41298,7 +41298,7 @@
         <v>45909</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -41376,7 +41376,7 @@
         <v>45772</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -41454,7 +41454,7 @@
         <v>45911</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -41532,7 +41532,7 @@
         <v>45912</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -41610,7 +41610,7 @@
         <v>45853</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -41683,7 +41683,7 @@
         <v>44722</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -41756,7 +41756,7 @@
         <v>45756</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -41829,7 +41829,7 @@
         <v>45880</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -41902,7 +41902,7 @@
         <v>44827</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -41975,7 +41975,7 @@
         <v>45604</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -42053,7 +42053,7 @@
         <v>45926</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -42126,7 +42126,7 @@
         <v>45603</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -42204,7 +42204,7 @@
         <v>44784</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -42282,7 +42282,7 @@
         <v>45925</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -42360,7 +42360,7 @@
         <v>45926</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -42433,7 +42433,7 @@
         <v>45975</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -42506,7 +42506,7 @@
         <v>45930</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -42579,7 +42579,7 @@
         <v>45580</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -42652,7 +42652,7 @@
         <v>45929</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -42725,7 +42725,7 @@
         <v>45986</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -42798,7 +42798,7 @@
         <v>45929</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -42876,7 +42876,7 @@
         <v>45931</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -42949,7 +42949,7 @@
         <v>45917</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -43022,7 +43022,7 @@
         <v>45154</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -43095,7 +43095,7 @@
         <v>45506</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -43168,7 +43168,7 @@
         <v>45931</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -43246,7 +43246,7 @@
         <v>45622</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -43324,7 +43324,7 @@
         <v>45926</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -43397,7 +43397,7 @@
         <v>45478</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -43475,7 +43475,7 @@
         <v>45496</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -43553,7 +43553,7 @@
         <v>45931</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -43626,7 +43626,7 @@
         <v>45533</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -43699,7 +43699,7 @@
         <v>45618</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -43772,7 +43772,7 @@
         <v>45282</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -43850,7 +43850,7 @@
         <v>45673</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -43928,7 +43928,7 @@
         <v>45420</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -44006,7 +44006,7 @@
         <v>45933</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -44079,7 +44079,7 @@
         <v>46071</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -44152,7 +44152,7 @@
         <v>45869</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -44225,7 +44225,7 @@
         <v>45869</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -44298,7 +44298,7 @@
         <v>45938</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -44371,7 +44371,7 @@
         <v>46146</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -44449,7 +44449,7 @@
         <v>45936</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -44522,7 +44522,7 @@
         <v>45568</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -44600,7 +44600,7 @@
         <v>45569</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -44673,7 +44673,7 @@
         <v>45938</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -44746,7 +44746,7 @@
         <v>46048</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -44819,7 +44819,7 @@
         <v>45568</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -44897,7 +44897,7 @@
         <v>45938</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -44975,7 +44975,7 @@
         <v>46071</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -45048,7 +45048,7 @@
         <v>46071</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -45121,7 +45121,7 @@
         <v>45685</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -45199,7 +45199,7 @@
         <v>46146</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -45277,7 +45277,7 @@
         <v>46146</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -45355,7 +45355,7 @@
         <v>45677</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -45428,7 +45428,7 @@
         <v>46146</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -45506,7 +45506,7 @@
         <v>46133</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -45579,7 +45579,7 @@
         <v>44460</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -45657,7 +45657,7 @@
         <v>45632</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -45730,7 +45730,7 @@
         <v>45239</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -45808,7 +45808,7 @@
         <v>45939</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -45881,7 +45881,7 @@
         <v>45939</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -45954,7 +45954,7 @@
         <v>45624</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -46027,7 +46027,7 @@
         <v>45939</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -46100,7 +46100,7 @@
         <v>45020</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -46173,7 +46173,7 @@
         <v>45939</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -46246,7 +46246,7 @@
         <v>44872</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -46319,7 +46319,7 @@
         <v>45075</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -46397,7 +46397,7 @@
         <v>45685</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -46475,7 +46475,7 @@
         <v>45610</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -46553,7 +46553,7 @@
         <v>45946</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -46626,7 +46626,7 @@
         <v>44925</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -46704,7 +46704,7 @@
         <v>45672</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -46777,7 +46777,7 @@
         <v>45845</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -46850,7 +46850,7 @@
         <v>45945</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -46928,7 +46928,7 @@
         <v>45930</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -47001,7 +47001,7 @@
         <v>45947</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -47079,7 +47079,7 @@
         <v>45949</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -47152,7 +47152,7 @@
         <v>45919</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -47225,7 +47225,7 @@
         <v>45533</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -47298,7 +47298,7 @@
         <v>45159</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -47376,7 +47376,7 @@
         <v>45159</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -47454,7 +47454,7 @@
         <v>45947</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -47532,7 +47532,7 @@
         <v>46154</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -47610,7 +47610,7 @@
         <v>45951</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -47688,7 +47688,7 @@
         <v>44998</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -47761,7 +47761,7 @@
         <v>45687</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -47834,7 +47834,7 @@
         <v>45954</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -47907,7 +47907,7 @@
         <v>45953</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -47980,7 +47980,7 @@
         <v>45958</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -48053,7 +48053,7 @@
         <v>46153</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -48126,7 +48126,7 @@
         <v>45719</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -48199,7 +48199,7 @@
         <v>45958</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -48272,7 +48272,7 @@
         <v>45170</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -48350,7 +48350,7 @@
         <v>46154</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -48428,7 +48428,7 @@
         <v>46154</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -48506,7 +48506,7 @@
         <v>45958</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -48579,7 +48579,7 @@
         <v>45958</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -48652,7 +48652,7 @@
         <v>45958</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -48725,7 +48725,7 @@
         <v>46154</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -48803,7 +48803,7 @@
         <v>46154</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -48881,7 +48881,7 @@
         <v>45719</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -48954,7 +48954,7 @@
         <v>45958</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -49027,7 +49027,7 @@
         <v>46154</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -49105,7 +49105,7 @@
         <v>45617</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -49178,7 +49178,7 @@
         <v>45621</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -49256,7 +49256,7 @@
         <v>46195</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -49334,7 +49334,7 @@
         <v>45203</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -49407,7 +49407,7 @@
         <v>45154</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -49480,7 +49480,7 @@
         <v>45960</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -49558,7 +49558,7 @@
         <v>45604</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -49631,7 +49631,7 @@
         <v>44423</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -49704,7 +49704,7 @@
         <v>44423</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -49777,7 +49777,7 @@
         <v>44883</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -49850,7 +49850,7 @@
         <v>45118</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -49923,7 +49923,7 @@
         <v>45119</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -49996,7 +49996,7 @@
         <v>44708</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -50074,7 +50074,7 @@
         <v>45632</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -50147,7 +50147,7 @@
         <v>45952</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -50220,7 +50220,7 @@
         <v>45603</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -50298,7 +50298,7 @@
         <v>45147</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -50371,7 +50371,7 @@
         <v>45763</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -50444,7 +50444,7 @@
         <v>45351</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -50517,7 +50517,7 @@
         <v>45063</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -50590,7 +50590,7 @@
         <v>45575</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -50663,7 +50663,7 @@
         <v>45961</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -50736,7 +50736,7 @@
         <v>45630</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -50809,7 +50809,7 @@
         <v>45961</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -50882,7 +50882,7 @@
         <v>45965</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -50960,7 +50960,7 @@
         <v>45707</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -51033,7 +51033,7 @@
         <v>45965</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -51106,7 +51106,7 @@
         <v>45965</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -51184,7 +51184,7 @@
         <v>45603</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -51262,7 +51262,7 @@
         <v>45510</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -51340,7 +51340,7 @@
         <v>45965</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -51418,7 +51418,7 @@
         <v>45852</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -51491,7 +51491,7 @@
         <v>45966</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -51569,7 +51569,7 @@
         <v>45691</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -51647,7 +51647,7 @@
         <v>45621</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -51720,7 +51720,7 @@
         <v>45621</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -51793,7 +51793,7 @@
         <v>45485</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -51866,7 +51866,7 @@
         <v>45972</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -51944,7 +51944,7 @@
         <v>45971</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -52017,7 +52017,7 @@
         <v>46160</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -52090,7 +52090,7 @@
         <v>44928</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -52168,7 +52168,7 @@
         <v>45972</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -52246,7 +52246,7 @@
         <v>45974</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -52324,7 +52324,7 @@
         <v>45707</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -52397,7 +52397,7 @@
         <v>44795</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -52470,7 +52470,7 @@
         <v>45974</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -52548,7 +52548,7 @@
         <v>45973</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -52626,7 +52626,7 @@
         <v>45705</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -52699,7 +52699,7 @@
         <v>45974</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -52777,7 +52777,7 @@
         <v>44757</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -52850,7 +52850,7 @@
         <v>45973</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -52928,7 +52928,7 @@
         <v>45972</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -53001,7 +53001,7 @@
         <v>45764</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -53079,7 +53079,7 @@
         <v>45973</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -53157,7 +53157,7 @@
         <v>45973</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -53235,7 +53235,7 @@
         <v>44435</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -53313,7 +53313,7 @@
         <v>45975</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -53391,7 +53391,7 @@
         <v>45572</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -53464,7 +53464,7 @@
         <v>45616</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -53537,7 +53537,7 @@
         <v>46204</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -53610,7 +53610,7 @@
         <v>45978</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -53683,7 +53683,7 @@
         <v>45975</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -53761,7 +53761,7 @@
         <v>46178</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -53834,7 +53834,7 @@
         <v>45975</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -53912,7 +53912,7 @@
         <v>45979</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -53985,7 +53985,7 @@
         <v>46204</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -54058,7 +54058,7 @@
         <v>45768</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -54136,7 +54136,7 @@
         <v>45768</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -54214,7 +54214,7 @@
         <v>45768</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -54292,7 +54292,7 @@
         <v>45154</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -54365,7 +54365,7 @@
         <v>45978</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -54443,7 +54443,7 @@
         <v>45979</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -54516,7 +54516,7 @@
         <v>45569</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -54594,7 +54594,7 @@
         <v>45063</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -54667,7 +54667,7 @@
         <v>45979</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -54740,7 +54740,7 @@
         <v>44474</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -54813,7 +54813,7 @@
         <v>45569</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -54891,7 +54891,7 @@
         <v>45569</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -54969,7 +54969,7 @@
         <v>45743</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -55042,7 +55042,7 @@
         <v>45978</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -55120,7 +55120,7 @@
         <v>45979</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -55193,7 +55193,7 @@
         <v>46178</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -55266,7 +55266,7 @@
         <v>46178</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -55339,7 +55339,7 @@
         <v>45981</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -55412,7 +55412,7 @@
         <v>45539</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -55485,7 +55485,7 @@
         <v>45982</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -55558,7 +55558,7 @@
         <v>45876</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -55636,7 +55636,7 @@
         <v>45204</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -55709,7 +55709,7 @@
         <v>45876</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -55787,7 +55787,7 @@
         <v>45982</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -55865,7 +55865,7 @@
         <v>45887</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -55943,7 +55943,7 @@
         <v>44827</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -56016,7 +56016,7 @@
         <v>44827</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -56089,7 +56089,7 @@
         <v>46204</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -56162,7 +56162,7 @@
         <v>45238</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -56235,7 +56235,7 @@
         <v>45985</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -56308,7 +56308,7 @@
         <v>45916</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -56386,7 +56386,7 @@
         <v>45986</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -56459,7 +56459,7 @@
         <v>45986</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -56532,7 +56532,7 @@
         <v>45985</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -56610,7 +56610,7 @@
         <v>45730</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -56683,7 +56683,7 @@
         <v>45988</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -56756,7 +56756,7 @@
         <v>45617</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -56834,7 +56834,7 @@
         <v>46206</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -56912,7 +56912,7 @@
         <v>46206</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -56985,7 +56985,7 @@
         <v>45987</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -57058,7 +57058,7 @@
         <v>45621</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -57136,7 +57136,7 @@
         <v>45688</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -57214,7 +57214,7 @@
         <v>44886</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -57292,7 +57292,7 @@
         <v>45617</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -57370,7 +57370,7 @@
         <v>45989</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -57443,7 +57443,7 @@
         <v>45758</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -57516,7 +57516,7 @@
         <v>45485</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -57589,7 +57589,7 @@
         <v>45642</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -57662,7 +57662,7 @@
         <v>45989</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -57735,7 +57735,7 @@
         <v>45989</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -57808,7 +57808,7 @@
         <v>45989</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -57881,7 +57881,7 @@
         <v>45989</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -57954,7 +57954,7 @@
         <v>45989</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -58027,7 +58027,7 @@
         <v>44853</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -58100,7 +58100,7 @@
         <v>45484</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -58178,7 +58178,7 @@
         <v>45371</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -58256,7 +58256,7 @@
         <v>44925</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -58334,7 +58334,7 @@
         <v>45989</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -58407,7 +58407,7 @@
         <v>45706</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -58480,7 +58480,7 @@
         <v>45989</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -58553,7 +58553,7 @@
         <v>44886</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -58631,7 +58631,7 @@
         <v>44985</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -58709,7 +58709,7 @@
         <v>45763</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -58782,7 +58782,7 @@
         <v>45491</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -58855,7 +58855,7 @@
         <v>46206</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -58933,7 +58933,7 @@
         <v>45345</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -59011,7 +59011,7 @@
         <v>45439</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -59089,7 +59089,7 @@
         <v>46206</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -59167,7 +59167,7 @@
         <v>44972</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -59240,7 +59240,7 @@
         <v>45993</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -59313,7 +59313,7 @@
         <v>44484</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -59386,7 +59386,7 @@
         <v>45996</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -59459,7 +59459,7 @@
         <v>45885</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -59532,7 +59532,7 @@
         <v>45996</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -59605,7 +59605,7 @@
         <v>45995</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -59678,7 +59678,7 @@
         <v>45995</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -59751,7 +59751,7 @@
         <v>45996</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -59824,7 +59824,7 @@
         <v>46163</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -59902,7 +59902,7 @@
         <v>45996</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -59975,7 +59975,7 @@
         <v>45996</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -60048,7 +60048,7 @@
         <v>45961</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -60121,7 +60121,7 @@
         <v>44889</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -60194,7 +60194,7 @@
         <v>46168</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -60272,7 +60272,7 @@
         <v>46168</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -60350,7 +60350,7 @@
         <v>44928</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -60428,7 +60428,7 @@
         <v>46000</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -60506,7 +60506,7 @@
         <v>46168</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -60584,7 +60584,7 @@
         <v>46168</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -60662,7 +60662,7 @@
         <v>46167</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -60740,7 +60740,7 @@
         <v>46167</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -60818,7 +60818,7 @@
         <v>46167</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -60896,7 +60896,7 @@
         <v>45999</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -60974,7 +60974,7 @@
         <v>46167</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -61052,7 +61052,7 @@
         <v>46167</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -61130,7 +61130,7 @@
         <v>45731</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -61203,7 +61203,7 @@
         <v>45999</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -61276,7 +61276,7 @@
         <v>44819</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -61349,7 +61349,7 @@
         <v>46168</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -61427,7 +61427,7 @@
         <v>45999</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -61500,7 +61500,7 @@
         <v>46167</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -61578,7 +61578,7 @@
         <v>46167</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -61656,7 +61656,7 @@
         <v>46168</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -61734,7 +61734,7 @@
         <v>44854</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -61812,7 +61812,7 @@
         <v>46002</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -61885,7 +61885,7 @@
         <v>46006</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -61958,7 +61958,7 @@
         <v>46209</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -62036,7 +62036,7 @@
         <v>46168</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -62114,7 +62114,7 @@
         <v>46168</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -62192,7 +62192,7 @@
         <v>46168</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -62270,7 +62270,7 @@
         <v>46168</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -62348,7 +62348,7 @@
         <v>46168</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -62426,7 +62426,7 @@
         <v>45496</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -62504,7 +62504,7 @@
         <v>46006</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -62577,7 +62577,7 @@
         <v>46168</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -62655,7 +62655,7 @@
         <v>46168</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -62733,7 +62733,7 @@
         <v>46168</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -62811,7 +62811,7 @@
         <v>45303</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -62884,7 +62884,7 @@
         <v>46167</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -62962,7 +62962,7 @@
         <v>46006</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -63035,7 +63035,7 @@
         <v>46006</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -63108,7 +63108,7 @@
         <v>45665</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -63181,7 +63181,7 @@
         <v>46007</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -63254,7 +63254,7 @@
         <v>46007</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -63327,7 +63327,7 @@
         <v>45447</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -63400,7 +63400,7 @@
         <v>45054</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -63478,7 +63478,7 @@
         <v>45637</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -63556,7 +63556,7 @@
         <v>45593</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -63629,7 +63629,7 @@
         <v>45593</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -63702,7 +63702,7 @@
         <v>45559</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -63780,7 +63780,7 @@
         <v>45517</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -63858,7 +63858,7 @@
         <v>46169</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -63931,7 +63931,7 @@
         <v>45590</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -64004,7 +64004,7 @@
         <v>46212</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -64082,7 +64082,7 @@
         <v>45642</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -64155,7 +64155,7 @@
         <v>46212</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -64233,7 +64233,7 @@
         <v>45049</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -64306,7 +64306,7 @@
         <v>46009</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -64379,7 +64379,7 @@
         <v>45684</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -64452,7 +64452,7 @@
         <v>45625</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -64530,7 +64530,7 @@
         <v>45274</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -64603,7 +64603,7 @@
         <v>45411</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -64681,7 +64681,7 @@
         <v>45303</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -64754,7 +64754,7 @@
         <v>46014</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -64827,7 +64827,7 @@
         <v>45635</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -64905,7 +64905,7 @@
         <v>45728</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -64978,7 +64978,7 @@
         <v>45579</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -65056,7 +65056,7 @@
         <v>44643</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -65129,7 +65129,7 @@
         <v>46206</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -65207,7 +65207,7 @@
         <v>44999</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -65280,7 +65280,7 @@
         <v>45631</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -65358,7 +65358,7 @@
         <v>45945</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -65436,7 +65436,7 @@
         <v>44642</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -65514,7 +65514,7 @@
         <v>45244</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -65587,7 +65587,7 @@
         <v>46014</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -65660,7 +65660,7 @@
         <v>45252</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -65733,7 +65733,7 @@
         <v>45252</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -65806,7 +65806,7 @@
         <v>46170</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -65884,7 +65884,7 @@
         <v>46024</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -65957,7 +65957,7 @@
         <v>46027</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -66035,7 +66035,7 @@
         <v>46027</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -66113,7 +66113,7 @@
         <v>46027</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -66191,7 +66191,7 @@
         <v>45834</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -66264,7 +66264,7 @@
         <v>46129</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -66337,7 +66337,7 @@
         <v>46027</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -66415,7 +66415,7 @@
         <v>46029</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -66488,7 +66488,7 @@
         <v>45575</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -66561,7 +66561,7 @@
         <v>45834</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -66634,7 +66634,7 @@
         <v>46217</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -66707,7 +66707,7 @@
         <v>45303</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -66780,7 +66780,7 @@
         <v>44472</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -66853,7 +66853,7 @@
         <v>45254</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -66926,7 +66926,7 @@
         <v>45345</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -67004,7 +67004,7 @@
         <v>46035</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -67082,7 +67082,7 @@
         <v>46031</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -67155,7 +67155,7 @@
         <v>46031</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -67228,7 +67228,7 @@
         <v>45537</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -67306,7 +67306,7 @@
         <v>46177</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -67384,7 +67384,7 @@
         <v>46036</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -67457,7 +67457,7 @@
         <v>45768</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -67535,7 +67535,7 @@
         <v>45768</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -67613,7 +67613,7 @@
         <v>46038</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -67686,7 +67686,7 @@
         <v>45275</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -67759,7 +67759,7 @@
         <v>45988</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -67832,7 +67832,7 @@
         <v>45568</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -67910,7 +67910,7 @@
         <v>45719</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -67983,7 +67983,7 @@
         <v>44925</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -68056,7 +68056,7 @@
         <v>45670</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -68134,7 +68134,7 @@
         <v>45667</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -68212,7 +68212,7 @@
         <v>45574</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -68285,7 +68285,7 @@
         <v>44732</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -68358,7 +68358,7 @@
         <v>45264</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -68431,7 +68431,7 @@
         <v>46041</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -68509,7 +68509,7 @@
         <v>46176</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -68582,7 +68582,7 @@
         <v>46041</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -68660,7 +68660,7 @@
         <v>45540</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -68738,7 +68738,7 @@
         <v>46043</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -68811,7 +68811,7 @@
         <v>46043</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -68884,7 +68884,7 @@
         <v>45610</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -68962,7 +68962,7 @@
         <v>46015</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -69035,7 +69035,7 @@
         <v>46047</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -69113,7 +69113,7 @@
         <v>46006</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -69186,7 +69186,7 @@
         <v>46049</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -69259,7 +69259,7 @@
         <v>46049</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -69332,7 +69332,7 @@
         <v>45252</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -69405,7 +69405,7 @@
         <v>46049</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -69478,7 +69478,7 @@
         <v>45582</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -69556,7 +69556,7 @@
         <v>46224</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -69629,7 +69629,7 @@
         <v>45632</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -69702,7 +69702,7 @@
         <v>46052</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -69780,7 +69780,7 @@
         <v>45624</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -69853,7 +69853,7 @@
         <v>45260</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -69926,7 +69926,7 @@
         <v>46055</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -69999,7 +69999,7 @@
         <v>46226</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -70072,7 +70072,7 @@
         <v>45075</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -70150,7 +70150,7 @@
         <v>46055</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -70223,7 +70223,7 @@
         <v>44987</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -70301,7 +70301,7 @@
         <v>46183</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -70374,7 +70374,7 @@
         <v>46058</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -70452,7 +70452,7 @@
         <v>45485</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -70525,7 +70525,7 @@
         <v>45041</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -70598,7 +70598,7 @@
         <v>45575</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -70676,7 +70676,7 @@
         <v>46051</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -70749,7 +70749,7 @@
         <v>45569</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -70827,7 +70827,7 @@
         <v>45173</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -70900,7 +70900,7 @@
         <v>45170</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -70978,7 +70978,7 @@
         <v>46185</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -71051,7 +71051,7 @@
         <v>45637</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -71124,7 +71124,7 @@
         <v>46185</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -71202,7 +71202,7 @@
         <v>45481</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -71280,7 +71280,7 @@
         <v>46185</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -71358,7 +71358,7 @@
         <v>45460</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -71431,7 +71431,7 @@
         <v>45509</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -71509,7 +71509,7 @@
         <v>45509</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -71587,7 +71587,7 @@
         <v>45483</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -71660,7 +71660,7 @@
         <v>45593</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -71733,7 +71733,7 @@
         <v>46069</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -71806,7 +71806,7 @@
         <v>44628</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -71879,7 +71879,7 @@
         <v>46069</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -71952,7 +71952,7 @@
         <v>46069</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -72025,7 +72025,7 @@
         <v>46232</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -72103,7 +72103,7 @@
         <v>46232</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -72181,7 +72181,7 @@
         <v>45755</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -72254,7 +72254,7 @@
         <v>45730</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -72327,7 +72327,7 @@
         <v>45644</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -72405,7 +72405,7 @@
         <v>46071</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -72478,7 +72478,7 @@
         <v>45345</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -72556,7 +72556,7 @@
         <v>45345</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -72634,7 +72634,7 @@
         <v>45345</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -72712,7 +72712,7 @@
         <v>46210</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -72790,7 +72790,7 @@
         <v>45362</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -72863,7 +72863,7 @@
         <v>45614</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -72936,7 +72936,7 @@
         <v>45153</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -73014,7 +73014,7 @@
         <v>45517</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -73087,7 +73087,7 @@
         <v>45830</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -73160,7 +73160,7 @@
         <v>45830</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -73233,7 +73233,7 @@
         <v>46191</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -73311,7 +73311,7 @@
         <v>45830</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -73384,7 +73384,7 @@
         <v>45644</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -73462,7 +73462,7 @@
         <v>45485</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -73535,7 +73535,7 @@
         <v>45485</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -73613,7 +73613,7 @@
         <v>45830</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -73686,7 +73686,7 @@
         <v>45159</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -73759,7 +73759,7 @@
         <v>45622</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -73837,7 +73837,7 @@
         <v>45568</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -73915,7 +73915,7 @@
         <v>45728</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -73993,7 +73993,7 @@
         <v>45791</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -74066,7 +74066,7 @@
         <v>45727</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -74144,7 +74144,7 @@
         <v>45408</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -74217,7 +74217,7 @@
         <v>45728</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -74295,7 +74295,7 @@
         <v>45350</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -74368,7 +74368,7 @@
         <v>45257</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -74441,7 +74441,7 @@
         <v>45345</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -74519,7 +74519,7 @@
         <v>46087</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -74592,7 +74592,7 @@
         <v>45111</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -74665,7 +74665,7 @@
         <v>45768</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -74743,7 +74743,7 @@
         <v>45768</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -74821,7 +74821,7 @@
         <v>44638</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -74894,7 +74894,7 @@
         <v>45642</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -74967,7 +74967,7 @@
         <v>45061</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -75045,7 +75045,7 @@
         <v>46093</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -75118,7 +75118,7 @@
         <v>46092</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -75196,7 +75196,7 @@
         <v>45429</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -75269,7 +75269,7 @@
         <v>46093</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -75347,7 +75347,7 @@
         <v>45635</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -75420,7 +75420,7 @@
         <v>45012</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -75498,7 +75498,7 @@
         <v>45231</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -75571,7 +75571,7 @@
         <v>45607</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -75644,7 +75644,7 @@
         <v>45677</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -75717,7 +75717,7 @@
         <v>44571</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -75790,7 +75790,7 @@
         <v>45579</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -75863,7 +75863,7 @@
         <v>45439</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -75936,7 +75936,7 @@
         <v>45195</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -76009,7 +76009,7 @@
         <v>45898</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -76082,7 +76082,7 @@
         <v>45632</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -76155,7 +76155,7 @@
         <v>45632</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -76228,7 +76228,7 @@
         <v>46098</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -76301,7 +76301,7 @@
         <v>45240</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -76374,7 +76374,7 @@
         <v>46048</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -76447,7 +76447,7 @@
         <v>46048</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -76520,7 +76520,7 @@
         <v>46021</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -76593,7 +76593,7 @@
         <v>45215</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -76666,7 +76666,7 @@
         <v>45196</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -76744,7 +76744,7 @@
         <v>45869</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -76817,7 +76817,7 @@
         <v>44708</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -76895,7 +76895,7 @@
         <v>44708</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -76973,7 +76973,7 @@
         <v>45118</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -77051,7 +77051,7 @@
         <v>45216</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -77124,7 +77124,7 @@
         <v>45604</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -77202,7 +77202,7 @@
         <v>46105</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -77275,7 +77275,7 @@
         <v>46104</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -77353,7 +77353,7 @@
         <v>45205</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -77426,7 +77426,7 @@
         <v>46104</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -77499,7 +77499,7 @@
         <v>46104</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -77577,7 +77577,7 @@
         <v>46105</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -77655,7 +77655,7 @@
         <v>45614</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -77733,7 +77733,7 @@
         <v>46105</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -77811,7 +77811,7 @@
         <v>44728</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -77889,7 +77889,7 @@
         <v>45670</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -77962,7 +77962,7 @@
         <v>45509</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -78040,7 +78040,7 @@
         <v>45204</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -78113,7 +78113,7 @@
         <v>45632</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -78186,7 +78186,7 @@
         <v>45632</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -78259,7 +78259,7 @@
         <v>45614</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -78332,7 +78332,7 @@
         <v>46106</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -78410,7 +78410,7 @@
         <v>45204</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -78483,7 +78483,7 @@
         <v>45174</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -78556,7 +78556,7 @@
         <v>45484</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -78634,7 +78634,7 @@
         <v>45776</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -78707,7 +78707,7 @@
         <v>45238</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -78780,7 +78780,7 @@
         <v>46119</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -78853,7 +78853,7 @@
         <v>46119</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -78926,7 +78926,7 @@
         <v>46119</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -78999,7 +78999,7 @@
         <v>45265</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -79072,7 +79072,7 @@
         <v>46119</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -79145,7 +79145,7 @@
         <v>46119</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -79218,7 +79218,7 @@
         <v>45195</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -79291,7 +79291,7 @@
         <v>45195</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -79364,7 +79364,7 @@
         <v>45459</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -79437,7 +79437,7 @@
         <v>46120</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -79510,7 +79510,7 @@
         <v>46123</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -79588,7 +79588,7 @@
         <v>45218</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>
@@ -79661,7 +79661,7 @@
         <v>46125</v>
       </c>
       <c r="E926" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F926" t="inlineStr">
         <is>
@@ -79739,7 +79739,7 @@
         <v>45737</v>
       </c>
       <c r="E927" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F927" t="inlineStr">
         <is>
@@ -79812,7 +79812,7 @@
         <v>45779</v>
       </c>
       <c r="E928" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F928" t="inlineStr">
         <is>
@@ -79890,7 +79890,7 @@
         <v>45733</v>
       </c>
       <c r="E929" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F929" t="inlineStr">
         <is>
@@ -79963,7 +79963,7 @@
         <v>45779</v>
       </c>
       <c r="E930" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F930" t="inlineStr">
         <is>
@@ -80041,7 +80041,7 @@
         <v>45737</v>
       </c>
       <c r="E931" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F931" t="inlineStr">
         <is>
@@ -80114,7 +80114,7 @@
         <v>45782</v>
       </c>
       <c r="E932" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F932" t="inlineStr">
         <is>
@@ -80187,7 +80187,7 @@
         <v>45779</v>
       </c>
       <c r="E933" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F933" t="inlineStr">
         <is>
@@ -80265,7 +80265,7 @@
         <v>45779</v>
       </c>
       <c r="E934" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F934" t="inlineStr">
         <is>
@@ -80343,7 +80343,7 @@
         <v>45779</v>
       </c>
       <c r="E935" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F935" t="inlineStr">
         <is>
@@ -80421,7 +80421,7 @@
         <v>46125</v>
       </c>
       <c r="E936" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F936" t="inlineStr">
         <is>
@@ -80494,7 +80494,7 @@
         <v>46127</v>
       </c>
       <c r="E937" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F937" t="inlineStr">
         <is>
@@ -80572,7 +80572,7 @@
         <v>46127</v>
       </c>
       <c r="E938" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F938" t="inlineStr">
         <is>
@@ -80650,7 +80650,7 @@
         <v>45618</v>
       </c>
       <c r="E939" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F939" t="inlineStr">
         <is>
@@ -80723,7 +80723,7 @@
         <v>44726</v>
       </c>
       <c r="E940" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F940" t="inlineStr">
         <is>
@@ -80796,7 +80796,7 @@
         <v>45632</v>
       </c>
       <c r="E941" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F941" t="inlineStr">
         <is>
@@ -80869,7 +80869,7 @@
         <v>46132</v>
       </c>
       <c r="E942" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F942" t="inlineStr">
         <is>
@@ -80942,7 +80942,7 @@
         <v>45483</v>
       </c>
       <c r="E943" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F943" t="inlineStr">
         <is>
@@ -81015,7 +81015,7 @@
         <v>44665</v>
       </c>
       <c r="E944" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F944" t="inlineStr">
         <is>
@@ -81088,7 +81088,7 @@
         <v>45173</v>
       </c>
       <c r="E945" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F945" t="inlineStr">
         <is>
@@ -81166,7 +81166,7 @@
         <v>46129</v>
       </c>
       <c r="E946" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F946" t="inlineStr">
         <is>
@@ -81239,7 +81239,7 @@
         <v>46129</v>
       </c>
       <c r="E947" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F947" t="inlineStr">
         <is>
@@ -81312,7 +81312,7 @@
         <v>46129</v>
       </c>
       <c r="E948" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F948" t="inlineStr">
         <is>
@@ -81385,7 +81385,7 @@
         <v>46129</v>
       </c>
       <c r="E949" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F949" t="inlineStr">
         <is>
@@ -81458,7 +81458,7 @@
         <v>45723</v>
       </c>
       <c r="E950" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F950" t="inlineStr">
         <is>
@@ -81531,7 +81531,7 @@
         <v>45642</v>
       </c>
       <c r="E951" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F951" t="inlineStr">
         <is>
@@ -81604,7 +81604,7 @@
         <v>46129</v>
       </c>
       <c r="E952" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F952" t="inlineStr">
         <is>
@@ -81677,7 +81677,7 @@
         <v>46129</v>
       </c>
       <c r="E953" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F953" t="inlineStr">
         <is>
@@ -81750,7 +81750,7 @@
         <v>45245</v>
       </c>
       <c r="E954" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F954" t="inlineStr">
         <is>
@@ -81823,7 +81823,7 @@
         <v>45569</v>
       </c>
       <c r="E955" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F955" t="inlineStr">
         <is>
@@ -81896,7 +81896,7 @@
         <v>45453</v>
       </c>
       <c r="E956" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F956" t="inlineStr">
         <is>
@@ -81969,7 +81969,7 @@
         <v>45071</v>
       </c>
       <c r="E957" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F957" t="inlineStr">
         <is>
@@ -82042,7 +82042,7 @@
         <v>44818</v>
       </c>
       <c r="E958" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F958" t="inlineStr">
         <is>
@@ -82115,7 +82115,7 @@
         <v>46135</v>
       </c>
       <c r="E959" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F959" t="inlineStr">
         <is>
@@ -82193,7 +82193,7 @@
         <v>46135</v>
       </c>
       <c r="E960" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F960" t="inlineStr">
         <is>
@@ -82271,7 +82271,7 @@
         <v>45670</v>
       </c>
       <c r="E961" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F961" t="inlineStr">
         <is>
@@ -82344,7 +82344,7 @@
         <v>45387</v>
       </c>
       <c r="E962" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
@@ -82417,7 +82417,7 @@
         <v>45063</v>
       </c>
       <c r="E963" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
@@ -82490,7 +82490,7 @@
         <v>46135</v>
       </c>
       <c r="E964" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
@@ -82568,7 +82568,7 @@
         <v>46135</v>
       </c>
       <c r="E965" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
@@ -82646,7 +82646,7 @@
         <v>45229</v>
       </c>
       <c r="E966" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
@@ -82719,7 +82719,7 @@
         <v>46135</v>
       </c>
       <c r="E967" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
@@ -82797,7 +82797,7 @@
         <v>46136</v>
       </c>
       <c r="E968" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
@@ -82875,7 +82875,7 @@
         <v>46136</v>
       </c>
       <c r="E969" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
@@ -82953,7 +82953,7 @@
         <v>46135</v>
       </c>
       <c r="E970" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
@@ -83031,7 +83031,7 @@
         <v>46135</v>
       </c>
       <c r="E971" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
@@ -83109,7 +83109,7 @@
         <v>45177</v>
       </c>
       <c r="E972" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F972" t="inlineStr">
         <is>
@@ -83182,7 +83182,7 @@
         <v>46135</v>
       </c>
       <c r="E973" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
@@ -83260,7 +83260,7 @@
         <v>46135</v>
       </c>
       <c r="E974" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
@@ -83338,7 +83338,7 @@
         <v>46136</v>
       </c>
       <c r="E975" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
@@ -83416,7 +83416,7 @@
         <v>44413</v>
       </c>
       <c r="E976" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
@@ -83489,7 +83489,7 @@
         <v>45790</v>
       </c>
       <c r="E977" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
@@ -83567,7 +83567,7 @@
         <v>46135</v>
       </c>
       <c r="E978" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
@@ -83645,7 +83645,7 @@
         <v>46135</v>
       </c>
       <c r="E979" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
@@ -83723,7 +83723,7 @@
         <v>45457</v>
       </c>
       <c r="E980" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
@@ -83796,7 +83796,7 @@
         <v>46136</v>
       </c>
       <c r="E981" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
@@ -83874,7 +83874,7 @@
         <v>44825</v>
       </c>
       <c r="E982" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F982" t="inlineStr">
         <is>
@@ -83947,7 +83947,7 @@
         <v>46136</v>
       </c>
       <c r="E983" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F983" t="inlineStr">
         <is>
@@ -84025,7 +84025,7 @@
         <v>46136</v>
       </c>
       <c r="E984" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F984" t="inlineStr">
         <is>
@@ -84103,7 +84103,7 @@
         <v>44994</v>
       </c>
       <c r="E985" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F985" t="inlineStr">
         <is>
@@ -84176,7 +84176,7 @@
         <v>45904</v>
       </c>
       <c r="E986" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F986" t="inlineStr">
         <is>
@@ -84254,7 +84254,7 @@
         <v>45118</v>
       </c>
       <c r="E987" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F987" t="inlineStr">
         <is>
@@ -84332,7 +84332,7 @@
         <v>45685</v>
       </c>
       <c r="E988" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F988" t="inlineStr">
         <is>
@@ -84410,7 +84410,7 @@
         <v>45098</v>
       </c>
       <c r="E989" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F989" t="inlineStr">
         <is>
@@ -84488,7 +84488,7 @@
         <v>44925</v>
       </c>
       <c r="E990" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F990" t="inlineStr">
         <is>
@@ -84561,7 +84561,7 @@
         <v>45911</v>
       </c>
       <c r="E991" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F991" t="inlineStr">
         <is>
@@ -84634,7 +84634,7 @@
         <v>45705</v>
       </c>
       <c r="E992" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F992" t="inlineStr">
         <is>
@@ -84707,7 +84707,7 @@
         <v>45496</v>
       </c>
       <c r="E993" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F993" t="inlineStr">
         <is>
@@ -84785,7 +84785,7 @@
         <v>45509</v>
       </c>
       <c r="E994" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F994" t="inlineStr">
         <is>
@@ -84863,7 +84863,7 @@
         <v>44958</v>
       </c>
       <c r="E995" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F995" t="inlineStr">
         <is>
@@ -84941,7 +84941,7 @@
         <v>45743</v>
       </c>
       <c r="E996" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F996" t="inlineStr">
         <is>
@@ -85014,7 +85014,7 @@
         <v>45517</v>
       </c>
       <c r="E997" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F997" t="inlineStr">
         <is>
@@ -85092,7 +85092,7 @@
         <v>44483</v>
       </c>
       <c r="E998" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F998" t="inlineStr">
         <is>
@@ -85165,7 +85165,7 @@
         <v>45792</v>
       </c>
       <c r="E999" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F999" t="inlineStr">
         <is>
@@ -85243,7 +85243,7 @@
         <v>44424</v>
       </c>
       <c r="E1000" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1000" t="inlineStr">
         <is>
@@ -85316,7 +85316,7 @@
         <v>45618</v>
       </c>
       <c r="E1001" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1001" t="inlineStr">
         <is>
@@ -85389,7 +85389,7 @@
         <v>45488</v>
       </c>
       <c r="E1002" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
@@ -85462,7 +85462,7 @@
         <v>44858</v>
       </c>
       <c r="E1003" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1003" t="inlineStr">
         <is>
@@ -85535,7 +85535,7 @@
         <v>45288</v>
       </c>
       <c r="E1004" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1004" t="inlineStr">
         <is>
@@ -85608,7 +85608,7 @@
         <v>45509</v>
       </c>
       <c r="E1005" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1005" t="inlineStr">
         <is>
@@ -85686,7 +85686,7 @@
         <v>45793</v>
       </c>
       <c r="E1006" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1006" t="inlineStr">
         <is>
@@ -85764,7 +85764,7 @@
         <v>45768</v>
       </c>
       <c r="E1007" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1007" t="inlineStr">
         <is>
@@ -85842,7 +85842,7 @@
         <v>44964</v>
       </c>
       <c r="E1008" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1008" t="inlineStr">
         <is>
@@ -85915,7 +85915,7 @@
         <v>45674</v>
       </c>
       <c r="E1009" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1009" t="inlineStr">
         <is>
@@ -85988,7 +85988,7 @@
         <v>45791</v>
       </c>
       <c r="E1010" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1010" t="inlineStr">
         <is>
@@ -86061,7 +86061,7 @@
         <v>45797</v>
       </c>
       <c r="E1011" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1011" t="inlineStr">
         <is>
@@ -86134,7 +86134,7 @@
         <v>45800</v>
       </c>
       <c r="E1012" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1012" t="inlineStr">
         <is>
@@ -86207,7 +86207,7 @@
         <v>45800</v>
       </c>
       <c r="E1013" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1013" t="inlineStr">
         <is>
@@ -86285,7 +86285,7 @@
         <v>45800</v>
       </c>
       <c r="E1014" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1014" t="inlineStr">
         <is>
@@ -86363,7 +86363,7 @@
         <v>45800</v>
       </c>
       <c r="E1015" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1015" t="inlineStr">
         <is>
@@ -86436,7 +86436,7 @@
         <v>45800</v>
       </c>
       <c r="E1016" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
@@ -86514,7 +86514,7 @@
         <v>45800</v>
       </c>
       <c r="E1017" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
@@ -86592,7 +86592,7 @@
         <v>45799</v>
       </c>
       <c r="E1018" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1018" t="inlineStr">
         <is>
@@ -86670,7 +86670,7 @@
         <v>45799</v>
       </c>
       <c r="E1019" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1019" t="inlineStr">
         <is>
@@ -86748,7 +86748,7 @@
         <v>45800</v>
       </c>
       <c r="E1020" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1020" t="inlineStr">
         <is>
@@ -86826,7 +86826,7 @@
         <v>45800</v>
       </c>
       <c r="E1021" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1021" t="inlineStr">
         <is>
@@ -86904,7 +86904,7 @@
         <v>45800</v>
       </c>
       <c r="E1022" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1022" t="inlineStr">
         <is>
@@ -86982,7 +86982,7 @@
         <v>45800</v>
       </c>
       <c r="E1023" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1023" t="inlineStr">
         <is>
@@ -87060,7 +87060,7 @@
         <v>45237</v>
       </c>
       <c r="E1024" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1024" t="inlineStr">
         <is>
@@ -87133,7 +87133,7 @@
         <v>45800</v>
       </c>
       <c r="E1025" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1025" t="inlineStr">
         <is>
@@ -87211,7 +87211,7 @@
         <v>45800</v>
       </c>
       <c r="E1026" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1026" t="inlineStr">
         <is>
@@ -87289,7 +87289,7 @@
         <v>45800</v>
       </c>
       <c r="E1027" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1027" t="inlineStr">
         <is>
@@ -87367,7 +87367,7 @@
         <v>45799</v>
       </c>
       <c r="E1028" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1028" t="inlineStr">
         <is>
@@ -87440,7 +87440,7 @@
         <v>45800</v>
       </c>
       <c r="E1029" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1029" t="inlineStr">
         <is>
@@ -87518,7 +87518,7 @@
         <v>45800</v>
       </c>
       <c r="E1030" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1030" t="inlineStr">
         <is>
@@ -87596,7 +87596,7 @@
         <v>45799</v>
       </c>
       <c r="E1031" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1031" t="inlineStr">
         <is>
@@ -87674,7 +87674,7 @@
         <v>45803</v>
       </c>
       <c r="E1032" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1032" t="inlineStr">
         <is>
@@ -87747,7 +87747,7 @@
         <v>45804</v>
       </c>
       <c r="E1033" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1033" t="inlineStr">
         <is>
@@ -87820,7 +87820,7 @@
         <v>45803</v>
       </c>
       <c r="E1034" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1034" t="inlineStr">
         <is>
@@ -87893,7 +87893,7 @@
         <v>45807</v>
       </c>
       <c r="E1035" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1035" t="inlineStr">
         <is>
@@ -87971,7 +87971,7 @@
         <v>45807</v>
       </c>
       <c r="E1036" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1036" t="inlineStr">
         <is>
@@ -88049,7 +88049,7 @@
         <v>45807</v>
       </c>
       <c r="E1037" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1037" t="inlineStr">
         <is>
@@ -88127,7 +88127,7 @@
         <v>45807</v>
       </c>
       <c r="E1038" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1038" t="inlineStr">
         <is>
@@ -88205,7 +88205,7 @@
         <v>45807</v>
       </c>
       <c r="E1039" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1039" t="inlineStr">
         <is>
@@ -88283,7 +88283,7 @@
         <v>45807</v>
       </c>
       <c r="E1040" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1040" t="inlineStr">
         <is>
@@ -88361,7 +88361,7 @@
         <v>45807</v>
       </c>
       <c r="E1041" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1041" t="inlineStr">
         <is>
@@ -88439,7 +88439,7 @@
         <v>45807</v>
       </c>
       <c r="E1042" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1042" t="inlineStr">
         <is>
@@ -88517,7 +88517,7 @@
         <v>45807</v>
       </c>
       <c r="E1043" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1043" t="inlineStr">
         <is>
@@ -88595,7 +88595,7 @@
         <v>45807</v>
       </c>
       <c r="E1044" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1044" t="inlineStr">
         <is>
@@ -88673,7 +88673,7 @@
         <v>45807</v>
       </c>
       <c r="E1045" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1045" t="inlineStr">
         <is>
@@ -88751,7 +88751,7 @@
         <v>45807</v>
       </c>
       <c r="E1046" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1046" t="inlineStr">
         <is>
@@ -88829,7 +88829,7 @@
         <v>45807</v>
       </c>
       <c r="E1047" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1047" t="inlineStr">
         <is>
@@ -88907,7 +88907,7 @@
         <v>45807</v>
       </c>
       <c r="E1048" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1048" t="inlineStr">
         <is>
@@ -88985,7 +88985,7 @@
         <v>45807</v>
       </c>
       <c r="E1049" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1049" t="inlineStr">
         <is>
@@ -89063,7 +89063,7 @@
         <v>45334</v>
       </c>
       <c r="E1050" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1050" t="inlineStr">
         <is>
@@ -89141,7 +89141,7 @@
         <v>45685</v>
       </c>
       <c r="E1051" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1051" t="inlineStr">
         <is>
@@ -89214,7 +89214,7 @@
         <v>45280</v>
       </c>
       <c r="E1052" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1052" t="inlineStr">
         <is>
@@ -89287,7 +89287,7 @@
         <v>45811</v>
       </c>
       <c r="E1053" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1053" t="inlineStr">
         <is>
@@ -89365,7 +89365,7 @@
         <v>45813</v>
       </c>
       <c r="E1054" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1054" t="inlineStr">
         <is>
@@ -89438,7 +89438,7 @@
         <v>45813</v>
       </c>
       <c r="E1055" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1055" t="inlineStr">
         <is>
@@ -89511,7 +89511,7 @@
         <v>45813</v>
       </c>
       <c r="E1056" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1056" t="inlineStr">
         <is>
@@ -89584,7 +89584,7 @@
         <v>45406</v>
       </c>
       <c r="E1057" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1057" t="inlineStr">
         <is>
@@ -89662,7 +89662,7 @@
         <v>45303</v>
       </c>
       <c r="E1058" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1058" t="inlineStr">
         <is>
@@ -89735,7 +89735,7 @@
         <v>45506</v>
       </c>
       <c r="E1059" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1059" t="inlineStr">
         <is>
@@ -89808,7 +89808,7 @@
         <v>45817</v>
       </c>
       <c r="E1060" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1060" t="inlineStr">
         <is>
@@ -89886,7 +89886,7 @@
         <v>45678</v>
       </c>
       <c r="E1061" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1061" t="inlineStr">
         <is>
@@ -89959,7 +89959,7 @@
         <v>45821</v>
       </c>
       <c r="E1062" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1062" t="inlineStr">
         <is>
@@ -90032,7 +90032,7 @@
         <v>45821</v>
       </c>
       <c r="E1063" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1063" t="inlineStr">
         <is>
@@ -90110,7 +90110,7 @@
         <v>45826</v>
       </c>
       <c r="E1064" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1064" t="inlineStr">
         <is>
@@ -90188,7 +90188,7 @@
         <v>45827</v>
       </c>
       <c r="E1065" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1065" t="inlineStr">
         <is>
@@ -90266,7 +90266,7 @@
         <v>45827</v>
       </c>
       <c r="E1066" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1066" t="inlineStr">
         <is>
@@ -90339,7 +90339,7 @@
         <v>45827</v>
       </c>
       <c r="E1067" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1067" t="inlineStr">
         <is>
@@ -90417,7 +90417,7 @@
         <v>45831</v>
       </c>
       <c r="E1068" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1068" t="inlineStr">
         <is>
@@ -90495,7 +90495,7 @@
         <v>45832</v>
       </c>
       <c r="E1069" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1069" t="inlineStr">
         <is>
@@ -90573,7 +90573,7 @@
         <v>45832</v>
       </c>
       <c r="E1070" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1070" t="inlineStr">
         <is>
@@ -90651,7 +90651,7 @@
         <v>45834</v>
       </c>
       <c r="E1071" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1071" t="inlineStr">
         <is>
@@ -90729,7 +90729,7 @@
         <v>45834</v>
       </c>
       <c r="E1072" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1072" t="inlineStr">
         <is>
@@ -90802,7 +90802,7 @@
         <v>45833</v>
       </c>
       <c r="E1073" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1073" t="inlineStr">
         <is>
@@ -90880,7 +90880,7 @@
         <v>45833</v>
       </c>
       <c r="E1074" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1074" t="inlineStr">
         <is>
@@ -90958,7 +90958,7 @@
         <v>45833</v>
       </c>
       <c r="E1075" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1075" t="inlineStr">
         <is>
@@ -91036,7 +91036,7 @@
         <v>45833</v>
       </c>
       <c r="E1076" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1076" t="inlineStr">
         <is>
@@ -91114,7 +91114,7 @@
         <v>45834</v>
       </c>
       <c r="E1077" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1077" t="inlineStr">
         <is>
@@ -91187,7 +91187,7 @@
         <v>45835</v>
       </c>
       <c r="E1078" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1078" t="inlineStr">
         <is>
@@ -91265,7 +91265,7 @@
         <v>45835</v>
       </c>
       <c r="E1079" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1079" t="inlineStr">
         <is>
@@ -91343,7 +91343,7 @@
         <v>45835</v>
       </c>
       <c r="E1080" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1080" t="inlineStr">
         <is>
@@ -91416,7 +91416,7 @@
         <v>45839</v>
       </c>
       <c r="E1081" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1081" t="inlineStr">
         <is>
@@ -91489,7 +91489,7 @@
         <v>45840</v>
       </c>
       <c r="E1082" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1082" t="inlineStr">
         <is>
@@ -91567,7 +91567,7 @@
         <v>45841</v>
       </c>
       <c r="E1083" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1083" t="inlineStr">
         <is>
@@ -91640,7 +91640,7 @@
         <v>45841</v>
       </c>
       <c r="E1084" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1084" t="inlineStr">
         <is>
@@ -91713,7 +91713,7 @@
         <v>45841</v>
       </c>
       <c r="E1085" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1085" t="inlineStr">
         <is>
@@ -91786,7 +91786,7 @@
         <v>45842</v>
       </c>
       <c r="E1086" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1086" t="inlineStr">
         <is>
@@ -91859,7 +91859,7 @@
         <v>45848</v>
       </c>
       <c r="E1087" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1087" t="inlineStr">
         <is>
@@ -91932,7 +91932,7 @@
         <v>45848</v>
       </c>
       <c r="E1088" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1088" t="inlineStr">
         <is>
@@ -92005,7 +92005,7 @@
         <v>45848</v>
       </c>
       <c r="E1089" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1089" t="inlineStr">
         <is>
@@ -92078,7 +92078,7 @@
         <v>45848</v>
       </c>
       <c r="E1090" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1090" t="inlineStr">
         <is>
@@ -92151,7 +92151,7 @@
         <v>45852</v>
       </c>
       <c r="E1091" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1091" t="inlineStr">
         <is>
@@ -92224,7 +92224,7 @@
         <v>45853</v>
       </c>
       <c r="E1092" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1092" t="inlineStr">
         <is>
@@ -92297,7 +92297,7 @@
         <v>45853</v>
       </c>
       <c r="E1093" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1093" t="inlineStr">
         <is>
@@ -92375,7 +92375,7 @@
         <v>45107</v>
       </c>
       <c r="E1094" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1094" t="inlineStr">
         <is>
@@ -92448,7 +92448,7 @@
         <v>45859</v>
       </c>
       <c r="E1095" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1095" t="inlineStr">
         <is>
@@ -92521,7 +92521,7 @@
         <v>45866</v>
       </c>
       <c r="E1096" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1096" t="inlineStr">
         <is>
@@ -92594,7 +92594,7 @@
         <v>45868</v>
       </c>
       <c r="E1097" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1097" t="inlineStr">
         <is>
@@ -92667,7 +92667,7 @@
         <v>45867</v>
       </c>
       <c r="E1098" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1098" t="inlineStr">
         <is>
@@ -92740,7 +92740,7 @@
         <v>45874</v>
       </c>
       <c r="E1099" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1099" t="inlineStr">
         <is>
@@ -92813,7 +92813,7 @@
         <v>45875</v>
       </c>
       <c r="E1100" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1100" t="inlineStr">
         <is>
@@ -92891,7 +92891,7 @@
         <v>45882</v>
       </c>
       <c r="E1101" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1101" t="inlineStr">
         <is>
@@ -92969,7 +92969,7 @@
         <v>45881</v>
       </c>
       <c r="E1102" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1102" t="inlineStr">
         <is>
@@ -93042,7 +93042,7 @@
         <v>45881</v>
       </c>
       <c r="E1103" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1103" t="inlineStr">
         <is>
@@ -93115,7 +93115,7 @@
         <v>45881</v>
       </c>
       <c r="E1104" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1104" t="inlineStr">
         <is>
@@ -93188,7 +93188,7 @@
         <v>45883</v>
       </c>
       <c r="E1105" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1105" t="inlineStr">
         <is>
@@ -93266,7 +93266,7 @@
         <v>45960</v>
       </c>
       <c r="E1106" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1106" t="inlineStr">
         <is>
@@ -93339,7 +93339,7 @@
         <v>46185</v>
       </c>
       <c r="E1107" s="1" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="F1107" t="inlineStr">
         <is>
